--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676AF7E1-BB07-416E-B55F-CE934DA012B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60269A66-F8A2-476A-97C7-A95174A5895C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="419">
   <si>
     <t>CF =42</t>
   </si>
@@ -1298,12 +1298,21 @@
   </si>
   <si>
     <t>'sheet!'!R[1]C[1]</t>
+  </si>
+  <si>
+    <t>CustomStyle</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ hh:mm:ss"/>
@@ -2209,7 +2218,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="46">
     <dxf>
       <fill>
         <patternFill>
@@ -2220,165 +2229,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2764,8 +2615,185 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MyCustomTableStyle" pivot="0" count="2" xr9:uid="{DDE0F8F2-27C1-476B-B1FE-0502518857F6}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <mruColors>
       <color rgb="FF000000"/>
@@ -6247,7 +6275,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="45" dataDxfId="44">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6259,26 +6287,37 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="11">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="9">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="7">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="3">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="1" showLastColumn="1" showRowStripes="0" showColumnStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B96C8832-8BF1-48C8-B9E9-9E059A81B5EF}" name="Table2" displayName="Table2" ref="C34:D35" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="C34:D35" xr:uid="{B96C8832-8BF1-48C8-B9E9-9E059A81B5EF}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{0CD8A320-6EED-46F6-8606-8C017A8A7672}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{4EDBDF5C-3A86-4C30-807B-5FBD3E92A53B}" name="Column2"/>
+  </tableColumns>
+  <tableStyleInfo name="MyCustomTableStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -7071,7 +7110,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9014,7 +9053,7 @@
       </c>
       <c r="B100" s="20">
         <f ca="1">NOW()</f>
-        <v>45359.413205787037</v>
+        <v>45359.41589340278</v>
       </c>
       <c r="D100" s="2">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -10018,10 +10057,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11267,67 +11306,67 @@
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="43" priority="73" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="24" priority="73" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="42" priority="71">
+    <cfRule type="containsBlanks" dxfId="23" priority="71">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="41" priority="70">
+    <cfRule type="containsErrors" dxfId="22" priority="70">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="40" priority="69" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="21" priority="69" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="39" priority="67" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="20" priority="67" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="38" priority="66">
+    <cfRule type="notContainsBlanks" dxfId="19" priority="66">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="37" priority="65">
+    <cfRule type="notContainsErrors" dxfId="18" priority="65">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="36" priority="64" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="17" priority="64" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="35" priority="63" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="16" priority="63" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="34" priority="58">
+    <cfRule type="expression" dxfId="15" priority="58">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="33" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="14" priority="56" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="32" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="31" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="45" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11493,10 +11532,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="30" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="29" priority="96"/>
+    <cfRule type="uniqueValues" dxfId="10" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:C24">
     <cfRule type="dataBar" priority="100">
@@ -11513,10 +11552,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="28" priority="114"/>
+    <cfRule type="aboveAverage" dxfId="9" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="27" priority="115" rank="1"/>
+    <cfRule type="top10" dxfId="8" priority="115" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:K21">
     <cfRule type="iconSet" priority="18">
@@ -11613,33 +11652,33 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="26" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="25" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -11823,7 +11862,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA2AD09-EFB1-4B74-862F-432090DD90CB}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
@@ -12131,9 +12170,20 @@
         <v>408</v>
       </c>
     </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>416</v>
+      </c>
+      <c r="C34" t="s">
+        <v>417</v>
+      </c>
+      <c r="D34" t="s">
+        <v>418</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="9">
+  <tableParts count="10">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -12143,6 +12193,7 @@
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\odoo\spreadsheet\tests\__xlsx__\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0F1A66-FDA3-41D2-8301-AC5DB36FDC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5418097B-5455-451A-9833-8DDA204394AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,17 +34,6 @@
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId15"/>
   </pivotCaches>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -2208,25 +2197,11 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2781,11 +2756,25 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="2" xr9:uid="{33B8EB55-D8D8-4B00-B5CF-C84A8AC9E775}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="firstRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="45"/>
+      <tableStyleElement type="firstRowStripe" dxfId="44"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2812,7 +2801,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3413,7 +3402,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3841,7 +3830,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4459,7 +4448,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4825,7 +4814,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5124,7 +5113,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5560,7 +5549,409 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>radar chart</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="1F77B4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A060-40CF-8F7B-7D927B019D4E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF7F0E"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$27:$C$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A060-40CF-8F7B-7D927B019D4E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="17781237"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="88853993"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="88853993"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="17781237"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -6671,6 +7062,44 @@
     </xdr:graphicFrame>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 2" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2768A00C-0BD9-43E8-B0A0-2D9210A64EA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7080,7 +7509,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7092,22 +7521,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7217,9 +7646,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7257,7 +7686,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7363,7 +7792,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7505,7 +7934,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7514,7 +7943,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D5EBC-45F5-4C42-AA75-560DF70B9F2E}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -7914,7 +8343,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7959,7 +8388,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7968,7 +8397,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7977,7 +8406,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -7994,7 +8423,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8004,7 +8433,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0630FA18-71FC-4ACD-8379-39A3603D1DD6}">
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
@@ -9857,7 +10286,7 @@
       </c>
       <c r="B100" s="20">
         <f ca="1">NOW()</f>
-        <v>45398.580923148147</v>
+        <v>45450.649344444442</v>
       </c>
       <c r="D100" s="2">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -10547,7 +10976,7 @@
       </c>
       <c r="B144" s="19">
         <f ca="1">TODAY()</f>
-        <v>45398</v>
+        <v>45450</v>
       </c>
       <c r="D144" s="2">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -10861,10 +11290,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10878,7 +11307,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -10961,7 +11390,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
@@ -11347,7 +11776,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
@@ -11576,7 +12005,7 @@
       </c>
       <c r="B12" s="40">
         <f ca="1">TODAY()</f>
-        <v>45398</v>
+        <v>45450</v>
       </c>
       <c r="C12" s="40">
         <f>DATE(2010,10,2)</f>
@@ -12110,104 +12539,104 @@
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="24" priority="58">
+    <cfRule type="expression" dxfId="22" priority="58">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="23" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="22" priority="114"/>
+    <cfRule type="aboveAverage" dxfId="20" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="21" priority="73" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="19" priority="73" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="20" priority="71">
+    <cfRule type="containsBlanks" dxfId="18" priority="71">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="19" priority="70">
+    <cfRule type="containsErrors" dxfId="17" priority="70">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="18" priority="69" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="16" priority="69" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="17" priority="67" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="15" priority="67" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="16" priority="66">
+    <cfRule type="notContainsBlanks" dxfId="14" priority="66">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="15" priority="65">
+    <cfRule type="notContainsErrors" dxfId="13" priority="65">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="14" priority="64" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="12" priority="64" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="13" priority="63" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="11" priority="63" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="12" priority="115" rank="1"/>
+    <cfRule type="top10" dxfId="10" priority="115" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="11" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="45" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="10" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="8" priority="56" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -12241,10 +12670,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="3" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="2" priority="96"/>
+    <cfRule type="uniqueValues" dxfId="0" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="44">
@@ -12667,7 +13096,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -12999,7 +13428,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -13311,7 +13740,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -13347,7 +13776,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A1" s="100" t="s">

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\odoo\spreadsheet\tests\__xlsx__\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05E556DF-B6A9-4914-8E28-82201545992C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EAB923-A1B3-42FF-B544-1E3FCDFFEEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,9 @@
   <externalReferences>
     <externalReference r:id="rId14"/>
   </externalReferences>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="153" r:id="rId15"/>
+    <pivotCache cacheId="0" r:id="rId15"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,8 +45,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1321,7 +1319,7 @@
     <numFmt numFmtId="169" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="170" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2198,6 +2196,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2210,165 +2209,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2775,6 +2622,157 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -2818,7 +2816,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2874,7 +2872,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3196,7 +3194,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="fr-FR"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3229,7 +3227,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3300,7 +3298,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="fr-FR"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3333,7 +3331,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3377,7 +3375,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3405,7 +3403,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="fr-FR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3419,7 +3417,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3732,7 +3730,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3794,7 +3792,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3822,7 +3820,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3851,7 +3849,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4440,7 +4438,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4469,7 +4467,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4806,7 +4804,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4835,7 +4833,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5018,7 +5016,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5077,7 +5075,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5105,7 +5103,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5134,7 +5132,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5451,7 +5449,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5513,7 +5511,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5541,7 +5539,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5570,7 +5568,412 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>radar chart</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F77B4"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="1F77B4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E3B9-4952-B105-568BDB7EC1F4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF7F0E"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$27:$C$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E3B9-4952-B105-568BDB7EC1F4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="17781237"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="88853993"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="88853993"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="17781237"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5868,7 +6271,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="344680958"/>
@@ -5944,7 +6347,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="998664793"/>
@@ -5967,7 +6370,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -6684,6 +7087,44 @@
     </xdr:graphicFrame>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>70485</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 6" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2B20B98-FA84-44C9-8DBB-5852658E9967}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6943,7 +7384,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="153" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -7093,7 +7534,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7105,22 +7546,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7230,7 +7671,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7530,16 +7971,16 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="26" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -7548,7 +7989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75">
+    <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
       <c r="B2" s="23" t="s">
         <v>2</v>
       </c>
@@ -7561,25 +8002,25 @@
       <c r="H2" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="110"/>
+      <c r="I2" s="106"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="2">
         <v>8</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
       <c r="J3" s="6"/>
-      <c r="K3" s="106">
+      <c r="K3" s="107">
         <v>5</v>
       </c>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
@@ -7592,50 +8033,50 @@
       <c r="G4" s="2">
         <v>9</v>
       </c>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="2">
         <v>42</v>
       </c>
       <c r="G5" s="2">
         <v>15</v>
       </c>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="107"/>
+      <c r="K5" s="108"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G6" s="2">
         <v>22</v>
       </c>
       <c r="J6" s="6"/>
-      <c r="K6" s="107"/>
+      <c r="K6" s="108"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="2">
         <v>3</v>
       </c>
       <c r="J7" s="6"/>
-      <c r="K7" s="107"/>
+      <c r="K7" s="108"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G8" s="2">
         <v>30</v>
       </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="108"/>
+      <c r="K8" s="109"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -7645,7 +8086,7 @@
       </c>
       <c r="K9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="2">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -7654,13 +8095,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="2">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="2">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -7669,13 +8110,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G13" s="2">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12" t="s">
         <v>11</v>
       </c>
@@ -7684,32 +8125,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="2" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -7723,7 +8164,7 @@
       </c>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>18</v>
       </c>
@@ -7733,7 +8174,7 @@
       </c>
       <c r="G21" s="11"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>19</v>
       </c>
@@ -7747,7 +8188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="17">
         <v>10</v>
       </c>
@@ -7758,7 +8199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="17">
         <v>10.122999999999999</v>
       </c>
@@ -7769,7 +8210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
@@ -7783,7 +8224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
@@ -7800,7 +8241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
@@ -7817,7 +8258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
@@ -7834,7 +8275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>25</v>
       </c>
@@ -7851,7 +8292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
@@ -7868,7 +8309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -7885,7 +8326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
@@ -7902,7 +8343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
@@ -7913,7 +8354,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
@@ -7930,7 +8371,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7975,7 +8416,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7984,7 +8425,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7993,10 +8434,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="65.140625" customWidth="1"/>
-    <col min="2" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="65.109375" customWidth="1"/>
+    <col min="2" max="26" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8010,7 +8451,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8023,12 +8464,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="26" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
@@ -8063,7 +8504,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -8109,7 +8550,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -8155,7 +8596,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>45</v>
       </c>
@@ -8201,7 +8642,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
@@ -8247,7 +8688,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
@@ -8293,7 +8734,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>52</v>
       </c>
@@ -8327,7 +8768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -8361,7 +8802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
@@ -8392,7 +8833,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>58</v>
       </c>
@@ -8408,7 +8849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>59</v>
       </c>
@@ -8427,7 +8868,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>61</v>
       </c>
@@ -8458,7 +8899,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>62</v>
       </c>
@@ -8489,7 +8930,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
@@ -8505,7 +8946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
@@ -8521,7 +8962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>69</v>
       </c>
@@ -8537,7 +8978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>70</v>
       </c>
@@ -8553,7 +8994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>71</v>
       </c>
@@ -8569,7 +9010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>72</v>
       </c>
@@ -8585,7 +9026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>73</v>
       </c>
@@ -8601,7 +9042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>74</v>
       </c>
@@ -8617,7 +9058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>76</v>
       </c>
@@ -8633,7 +9074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>77</v>
       </c>
@@ -8649,7 +9090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>78</v>
       </c>
@@ -8666,7 +9107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -8682,7 +9123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>81</v>
       </c>
@@ -8698,7 +9139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -8714,7 +9155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>83</v>
       </c>
@@ -8731,7 +9172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>84</v>
       </c>
@@ -8747,7 +9188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -8763,7 +9204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>86</v>
       </c>
@@ -8779,7 +9220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>87</v>
       </c>
@@ -8795,7 +9236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>88</v>
       </c>
@@ -8811,7 +9252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>89</v>
       </c>
@@ -8827,7 +9268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>90</v>
       </c>
@@ -8843,7 +9284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>91</v>
       </c>
@@ -8859,7 +9300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>92</v>
       </c>
@@ -8875,7 +9316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>93</v>
       </c>
@@ -8892,7 +9333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>94</v>
       </c>
@@ -8908,7 +9349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>95</v>
       </c>
@@ -8924,7 +9365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>96</v>
       </c>
@@ -8940,7 +9381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>97</v>
       </c>
@@ -8956,7 +9397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>98</v>
       </c>
@@ -8972,7 +9413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>99</v>
       </c>
@@ -8988,7 +9429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>100</v>
       </c>
@@ -9004,7 +9445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>101</v>
       </c>
@@ -9020,7 +9461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>102</v>
       </c>
@@ -9036,7 +9477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>103</v>
       </c>
@@ -9052,7 +9493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>104</v>
       </c>
@@ -9068,7 +9509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>105</v>
       </c>
@@ -9085,7 +9526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>106</v>
       </c>
@@ -9102,7 +9543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>107</v>
       </c>
@@ -9118,7 +9559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>108</v>
       </c>
@@ -9134,7 +9575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>109</v>
       </c>
@@ -9150,7 +9591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -9166,7 +9607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>111</v>
       </c>
@@ -9182,7 +9623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>112</v>
       </c>
@@ -9198,7 +9639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>113</v>
       </c>
@@ -9214,7 +9655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>114</v>
       </c>
@@ -9230,7 +9671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>115</v>
       </c>
@@ -9246,7 +9687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>116</v>
       </c>
@@ -9262,7 +9703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>117</v>
       </c>
@@ -9278,7 +9719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>118</v>
       </c>
@@ -9294,7 +9735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>119</v>
       </c>
@@ -9310,7 +9751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>120</v>
       </c>
@@ -9326,7 +9767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>121</v>
       </c>
@@ -9342,7 +9783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>122</v>
       </c>
@@ -9358,7 +9799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>123</v>
       </c>
@@ -9374,7 +9815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>125</v>
       </c>
@@ -9390,7 +9831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>127</v>
       </c>
@@ -9406,7 +9847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>129</v>
       </c>
@@ -9422,7 +9863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>130</v>
       </c>
@@ -9438,7 +9879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>131</v>
       </c>
@@ -9454,7 +9895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>132</v>
       </c>
@@ -9470,7 +9911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>133</v>
       </c>
@@ -9486,7 +9927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>134</v>
       </c>
@@ -9502,7 +9943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>135</v>
       </c>
@@ -9518,7 +9959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>136</v>
       </c>
@@ -9534,7 +9975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>137</v>
       </c>
@@ -9550,7 +9991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>138</v>
       </c>
@@ -9566,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>139</v>
       </c>
@@ -9582,7 +10023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>141</v>
       </c>
@@ -9598,7 +10039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>142</v>
       </c>
@@ -9614,7 +10055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>143</v>
       </c>
@@ -9630,7 +10071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>144</v>
       </c>
@@ -9646,7 +10087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>146</v>
       </c>
@@ -9662,7 +10103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>147</v>
       </c>
@@ -9678,7 +10119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>148</v>
       </c>
@@ -9694,7 +10135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>149</v>
       </c>
@@ -9710,7 +10151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>150</v>
       </c>
@@ -9726,7 +10167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>151</v>
       </c>
@@ -9742,7 +10183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>152</v>
       </c>
@@ -9758,7 +10199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>153</v>
       </c>
@@ -9774,7 +10215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>154</v>
       </c>
@@ -9790,7 +10231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>155</v>
       </c>
@@ -9806,7 +10247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>156</v>
       </c>
@@ -9822,7 +10263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>157</v>
       </c>
@@ -9838,7 +10279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>158</v>
       </c>
@@ -9854,7 +10295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>159</v>
       </c>
@@ -9870,20 +10311,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="20">
         <f ca="1">NOW()</f>
-        <v>45526.511599421297</v>
+        <v>45538.429115162035</v>
       </c>
       <c r="D100" s="2">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>161</v>
       </c>
@@ -9899,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>162</v>
       </c>
@@ -9915,7 +10356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>163</v>
       </c>
@@ -9931,7 +10372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>164</v>
       </c>
@@ -9947,7 +10388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>165</v>
       </c>
@@ -9963,7 +10404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>166</v>
       </c>
@@ -9979,7 +10420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>167</v>
       </c>
@@ -9995,7 +10436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>168</v>
       </c>
@@ -10011,7 +10452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>169</v>
       </c>
@@ -10027,7 +10468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>170</v>
       </c>
@@ -10043,7 +10484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>171</v>
       </c>
@@ -10059,12 +10500,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="D112" s="2"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>172</v>
       </c>
@@ -10080,7 +10521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>173</v>
       </c>
@@ -10096,7 +10537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>175</v>
       </c>
@@ -10112,7 +10553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>177</v>
       </c>
@@ -10128,7 +10569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>178</v>
       </c>
@@ -10144,7 +10585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>179</v>
       </c>
@@ -10160,7 +10601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>180</v>
       </c>
@@ -10176,7 +10617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>181</v>
       </c>
@@ -10192,7 +10633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>182</v>
       </c>
@@ -10208,7 +10649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>183</v>
       </c>
@@ -10224,7 +10665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>184</v>
       </c>
@@ -10240,7 +10681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>185</v>
       </c>
@@ -10256,7 +10697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>186</v>
       </c>
@@ -10272,7 +10713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>187</v>
       </c>
@@ -10288,7 +10729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>188</v>
       </c>
@@ -10304,7 +10745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>189</v>
       </c>
@@ -10320,7 +10761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>190</v>
       </c>
@@ -10336,7 +10777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>191</v>
       </c>
@@ -10352,7 +10793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>192</v>
       </c>
@@ -10368,7 +10809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>193</v>
       </c>
@@ -10384,7 +10825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>194</v>
       </c>
@@ -10400,7 +10841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>195</v>
       </c>
@@ -10416,7 +10857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>196</v>
       </c>
@@ -10432,7 +10873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>198</v>
       </c>
@@ -10448,7 +10889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>199</v>
       </c>
@@ -10464,7 +10905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>200</v>
       </c>
@@ -10480,7 +10921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>201</v>
       </c>
@@ -10496,7 +10937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>202</v>
       </c>
@@ -10512,7 +10953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>203</v>
       </c>
@@ -10528,7 +10969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>205</v>
       </c>
@@ -10544,7 +10985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>206</v>
       </c>
@@ -10560,20 +11001,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="19">
         <f ca="1">TODAY()</f>
-        <v>45526</v>
+        <v>45538</v>
       </c>
       <c r="D144" s="2">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>208</v>
       </c>
@@ -10589,7 +11030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
@@ -10605,7 +11046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>211</v>
       </c>
@@ -10621,7 +11062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>213</v>
       </c>
@@ -10637,7 +11078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>214</v>
       </c>
@@ -10653,7 +11094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>215</v>
       </c>
@@ -10669,7 +11110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>216</v>
       </c>
@@ -10685,7 +11126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>217</v>
       </c>
@@ -10701,7 +11142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>218</v>
       </c>
@@ -10717,7 +11158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>219</v>
       </c>
@@ -10734,7 +11175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>220</v>
       </c>
@@ -10750,7 +11191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>221</v>
       </c>
@@ -10766,7 +11207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>222</v>
       </c>
@@ -10782,7 +11223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>223</v>
       </c>
@@ -10798,7 +11239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>224</v>
       </c>
@@ -10814,7 +11255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>225</v>
       </c>
@@ -10830,7 +11271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>226</v>
       </c>
@@ -10846,7 +11287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>227</v>
       </c>
@@ -10862,7 +11303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>229</v>
       </c>
@@ -10880,10 +11321,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10898,27 +11339,27 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" outlineLevel="1"/>
-    <col min="11" max="11" width="9.140625" outlineLevel="1" collapsed="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" outlineLevel="1"/>
+    <col min="11" max="11" width="9.109375" outlineLevel="1" collapsed="1"/>
     <col min="12" max="14" width="0" hidden="1" outlineLevel="2"/>
-    <col min="15" max="18" width="9.140625" outlineLevel="1"/>
+    <col min="15" max="18" width="9.109375" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="109"/>
+      <c r="E1" s="110"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -10926,19 +11367,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D3" s="86" t="s">
         <v>235</v>
       </c>
@@ -10946,25 +11387,25 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1">
+    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1"/>
-    <row r="11" spans="1:8" outlineLevel="1"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
-    <row r="16" spans="1:8" outlineLevel="1"/>
-    <row r="17" outlineLevel="1"/>
-    <row r="18" outlineLevel="1"/>
+    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="17" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="18" outlineLevel="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:E2"/>
@@ -10981,14 +11422,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1">
+    <row r="1" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="69" t="s">
         <v>239</v>
       </c>
@@ -11010,7 +11451,7 @@
       </c>
       <c r="M1" s="37"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="41" t="s">
         <v>245</v>
       </c>
@@ -11036,7 +11477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
         <v>252</v>
       </c>
@@ -11059,7 +11500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15">
+    <row r="4" spans="1:13" ht="16.2" x14ac:dyDescent="0.4">
       <c r="A4" s="43" t="s">
         <v>256</v>
       </c>
@@ -11085,7 +11526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>262</v>
       </c>
@@ -11105,7 +11546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="45" t="s">
         <v>266</v>
       </c>
@@ -11128,7 +11569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75">
+    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="46" t="s">
         <v>271</v>
       </c>
@@ -11148,7 +11589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.4">
       <c r="A8" s="47" t="s">
         <v>275</v>
       </c>
@@ -11171,7 +11612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="48" t="s">
         <v>280</v>
       </c>
@@ -11188,7 +11629,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="49" t="s">
         <v>283</v>
       </c>
@@ -11196,7 +11637,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1">
+    <row r="11" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="50" t="s">
         <v>285</v>
       </c>
@@ -11205,7 +11646,7 @@
       </c>
       <c r="F11" s="37"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51" t="s">
         <v>287</v>
       </c>
@@ -11219,7 +11660,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="52" t="s">
         <v>290</v>
       </c>
@@ -11230,7 +11671,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="53" t="s">
         <v>291</v>
       </c>
@@ -11244,7 +11685,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="54" t="s">
         <v>293</v>
       </c>
@@ -11255,7 +11696,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="55" t="s">
         <v>294</v>
       </c>
@@ -11269,12 +11710,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1">
+    <row r="17" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="56" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1">
+    <row r="18" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="75" t="s">
         <v>297</v>
       </c>
@@ -11286,7 +11727,7 @@
       </c>
       <c r="F18" s="37"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1">
+    <row r="19" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="76" t="s">
         <v>300</v>
       </c>
@@ -11297,7 +11738,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1">
+    <row r="20" spans="1:6" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="77" t="s">
         <v>303</v>
       </c>
@@ -11311,12 +11752,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1">
+    <row r="21" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="78" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1">
+    <row r="22" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="79" t="s">
         <v>307</v>
       </c>
@@ -11325,13 +11766,13 @@
       </c>
       <c r="E22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1">
+    <row r="23" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="80" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="24" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="81" t="s">
         <v>310</v>
       </c>
@@ -11340,20 +11781,20 @@
       </c>
       <c r="E24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="25" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="68" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="27" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C28" s="89" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
-    <row r="30" spans="1:6">
+    <row r="29" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C30" s="88" t="s">
         <v>314</v>
       </c>
@@ -11367,13 +11808,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1">
+    <row r="1" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="38" t="s">
         <v>315</v>
       </c>
@@ -11390,7 +11831,7 @@
       <c r="I1" s="37"/>
       <c r="J1" s="37"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
         <v>319</v>
       </c>
@@ -11413,7 +11854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>321</v>
       </c>
@@ -11436,7 +11877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="39" t="s">
         <v>325</v>
       </c>
@@ -11456,7 +11897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
         <v>328</v>
       </c>
@@ -11480,7 +11921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
         <v>330</v>
       </c>
@@ -11503,7 +11944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="39" t="s">
         <v>333</v>
       </c>
@@ -11529,7 +11970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
         <v>337</v>
       </c>
@@ -11540,7 +11981,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="39" t="s">
         <v>339</v>
       </c>
@@ -11549,7 +11990,7 @@
       </c>
       <c r="C9" s="22"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1">
+    <row r="10" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="39" t="s">
         <v>340</v>
       </c>
@@ -11567,7 +12008,7 @@
       <c r="I10" s="37"/>
       <c r="J10" s="37"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
         <v>342</v>
       </c>
@@ -11590,13 +12031,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="40">
         <f ca="1">TODAY()</f>
-        <v>45526</v>
+        <v>45538</v>
       </c>
       <c r="C12" s="40">
         <f>DATE(2010,10,2)</f>
@@ -11615,7 +12056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
         <v>346</v>
       </c>
@@ -11638,7 +12079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
         <v>348</v>
       </c>
@@ -11664,7 +12105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
         <v>350</v>
       </c>
@@ -11684,7 +12125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="39" t="s">
         <v>352</v>
       </c>
@@ -11707,7 +12148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="39" t="s">
         <v>354</v>
       </c>
@@ -11730,7 +12171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
         <v>356</v>
       </c>
@@ -11753,7 +12194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="39" t="s">
         <v>358</v>
       </c>
@@ -11776,7 +12217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
         <v>360</v>
       </c>
@@ -11799,7 +12240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
         <v>362</v>
       </c>
@@ -11825,7 +12266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="39" t="s">
         <v>364</v>
       </c>
@@ -11851,7 +12292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="39" t="s">
         <v>366</v>
       </c>
@@ -11877,7 +12318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G24" s="35" t="s">
         <v>368</v>
       </c>
@@ -11894,7 +12335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
         <v>369</v>
       </c>
@@ -11920,7 +12361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G26" s="35" t="s">
         <v>371</v>
       </c>
@@ -11940,7 +12381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>372</v>
       </c>
@@ -11966,7 +12407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G28" s="35" t="s">
         <v>374</v>
       </c>
@@ -11986,7 +12427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G29" s="35" t="s">
         <v>375</v>
       </c>
@@ -12006,7 +12447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G30" s="35" t="s">
         <v>376</v>
       </c>
@@ -12026,7 +12467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1">
+    <row r="31" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="36" t="s">
         <v>377</v>
       </c>
@@ -12040,7 +12481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G32" s="35" t="s">
         <v>378</v>
       </c>
@@ -12054,7 +12495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10">
+    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G33" s="35" t="s">
         <v>379</v>
       </c>
@@ -12068,7 +12509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10">
+    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G34" s="35" t="s">
         <v>380</v>
       </c>
@@ -12082,7 +12523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10">
+    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G35" s="35" t="s">
         <v>381</v>
       </c>
@@ -12096,7 +12537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10">
+    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G36" s="35" t="s">
         <v>382</v>
       </c>
@@ -12110,7 +12551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10">
+    <row r="37" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G37" s="35" t="s">
         <v>383</v>
       </c>
@@ -12124,110 +12565,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G39" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="40" priority="58">
+    <cfRule type="expression" dxfId="22" priority="58">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="39" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="38" priority="114"/>
+    <cfRule type="aboveAverage" dxfId="20" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="37" priority="73" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="19" priority="73" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="36" priority="71">
+    <cfRule type="containsBlanks" dxfId="18" priority="71">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="35" priority="70">
+    <cfRule type="containsErrors" dxfId="17" priority="70">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="34" priority="69" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="16" priority="69" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="33" priority="67" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="15" priority="67" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="32" priority="66">
+    <cfRule type="notContainsBlanks" dxfId="14" priority="66">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="31" priority="65">
+    <cfRule type="notContainsErrors" dxfId="13" priority="65">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="30" priority="64" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="12" priority="64" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="29" priority="63" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="11" priority="63" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="28" priority="115" rank="1"/>
+    <cfRule type="top10" dxfId="10" priority="115" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="27" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="45" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="26" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="8" priority="56" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -12261,10 +12702,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="19" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="18" priority="96"/>
+    <cfRule type="uniqueValues" dxfId="0" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="44">
@@ -12687,24 +13128,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" customWidth="1"/>
+    <col min="6" max="6" width="27.5546875" customWidth="1"/>
+    <col min="7" max="7" width="23.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C3" s="18" t="s">
         <v>35</v>
       </c>
@@ -12730,7 +13171,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
         <v>42</v>
       </c>
@@ -12761,7 +13202,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="2" t="s">
         <v>44</v>
       </c>
@@ -12792,7 +13233,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C6" s="2" t="s">
         <v>391</v>
       </c>
@@ -12825,7 +13266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>392</v>
       </c>
@@ -12836,7 +13277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>3</v>
       </c>
@@ -12844,7 +13285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>393</v>
       </c>
@@ -12855,7 +13296,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>3</v>
       </c>
@@ -12863,7 +13304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>396</v>
       </c>
@@ -12874,7 +13315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>3</v>
       </c>
@@ -12882,7 +13323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>397</v>
       </c>
@@ -12893,7 +13334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>3</v>
       </c>
@@ -12901,7 +13342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>398</v>
       </c>
@@ -12912,7 +13353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>3</v>
       </c>
@@ -12920,7 +13361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>399</v>
       </c>
@@ -12931,7 +13372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C24">
         <v>3</v>
       </c>
@@ -12939,7 +13380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>400</v>
       </c>
@@ -12950,7 +13391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C27">
         <v>3</v>
       </c>
@@ -12958,7 +13399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>391</v>
       </c>
@@ -12967,7 +13408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>401</v>
       </c>
@@ -12978,7 +13419,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="31" spans="2:4" hidden="1">
+    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>404</v>
       </c>
@@ -12986,7 +13427,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>405</v>
       </c>
@@ -12994,7 +13435,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>406</v>
       </c>
@@ -13019,28 +13460,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="93" t="s">
         <v>407</v>
       </c>
@@ -13050,7 +13491,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13058,7 +13499,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="90" t="s">
@@ -13068,7 +13509,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="90" t="s">
@@ -13102,7 +13543,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="91" t="s">
@@ -13115,7 +13556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="92">
@@ -13128,7 +13569,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="91" t="s">
@@ -13141,7 +13582,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="92">
@@ -13154,7 +13595,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="91" t="s">
@@ -13167,7 +13608,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="92">
@@ -13180,7 +13621,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" s="91" t="s">
         <v>44</v>
       </c>
@@ -13191,7 +13632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C12" s="92">
         <v>23000</v>
       </c>
@@ -13202,7 +13643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C13" s="91" t="s">
         <v>50</v>
       </c>
@@ -13213,7 +13654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C14" s="92">
         <v>2</v>
       </c>
@@ -13224,7 +13665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C15" s="91" t="s">
         <v>48</v>
       </c>
@@ -13235,7 +13676,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C16" s="92">
         <v>50024</v>
       </c>
@@ -13246,7 +13687,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C17" s="91" t="s">
         <v>53</v>
       </c>
@@ -13257,7 +13698,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C18" s="92">
         <v>189576</v>
       </c>
@@ -13268,7 +13709,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C19" s="91" t="s">
         <v>57</v>
       </c>
@@ -13279,7 +13720,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C20" s="92">
         <v>5000</v>
       </c>
@@ -13290,7 +13731,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C21" s="91" t="s">
         <v>411</v>
       </c>
@@ -13331,29 +13772,29 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="65.140625" customWidth="1"/>
-    <col min="2" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="65.109375" customWidth="1"/>
+    <col min="2" max="26" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>413</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>415</v>
       </c>
@@ -13367,9 +13808,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="38.25">
+    <row r="1" spans="1:1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A1" s="100" t="s">
         <v>416</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\odoo\spreadsheet\tests\__xlsx__\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82EC8D04-FB30-4625-805F-DD659B4B146F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0219CD72-FC93-4738-B246-ADCEF801BFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,9 @@
   <externalReferences>
     <externalReference r:id="rId14"/>
   </externalReferences>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="828" r:id="rId15"/>
+    <pivotCache cacheId="0" r:id="rId15"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="418">
   <si>
     <t>CF =42</t>
   </si>
@@ -1306,6 +1306,9 @@
   <si>
     <t>This text have
  a newLine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      with whitespace before</t>
   </si>
 </sst>
 </file>
@@ -1321,7 +1324,7 @@
     <numFmt numFmtId="169" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="170" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2198,6 +2201,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2210,7 +2214,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2218,157 +2221,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2775,6 +2627,157 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -2873,7 +2876,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3195,7 +3198,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="fr-FR"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3228,7 +3231,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3299,7 +3302,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="fr-FR"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3332,7 +3335,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3376,7 +3379,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3404,7 +3407,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="fr-FR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3731,7 +3734,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3793,7 +3796,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3821,7 +3824,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4439,7 +4442,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4805,7 +4808,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5017,7 +5020,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5076,7 +5079,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5104,7 +5107,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5450,7 +5453,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5512,7 +5515,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5540,7 +5543,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5867,7 +5870,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="344680958"/>
@@ -5943,7 +5946,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="998664793"/>
@@ -5966,7 +5969,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -6942,7 +6945,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="828" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -7092,7 +7095,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7104,22 +7107,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7229,9 +7232,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7269,7 +7272,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7375,7 +7378,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7517,7 +7520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7526,7 +7529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D5EBC-45F5-4C42-AA75-560DF70B9F2E}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -7535,7 +7538,7 @@
     <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -7544,7 +7547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75">
+    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B2" s="23" t="s">
         <v>2</v>
       </c>
@@ -7557,25 +7560,25 @@
       <c r="H2" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="110"/>
+      <c r="I2" s="106"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="2">
         <v>8</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
       <c r="J3" s="6"/>
-      <c r="K3" s="106">
+      <c r="K3" s="107">
         <v>5</v>
       </c>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
@@ -7588,50 +7591,50 @@
       <c r="G4" s="2">
         <v>9</v>
       </c>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="2">
         <v>42</v>
       </c>
       <c r="G5" s="2">
         <v>15</v>
       </c>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="107"/>
+      <c r="K5" s="108"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G6" s="2">
         <v>22</v>
       </c>
       <c r="J6" s="6"/>
-      <c r="K6" s="107"/>
+      <c r="K6" s="108"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="2">
         <v>3</v>
       </c>
       <c r="J7" s="6"/>
-      <c r="K7" s="107"/>
+      <c r="K7" s="108"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G8" s="2">
         <v>30</v>
       </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="108"/>
+      <c r="K8" s="109"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -7641,7 +7644,7 @@
       </c>
       <c r="K9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="2">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -7650,13 +7653,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="2">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="2">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -7665,13 +7668,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G13" s="2">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>11</v>
       </c>
@@ -7680,32 +7683,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="2" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -7719,7 +7722,7 @@
       </c>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
         <v>18</v>
       </c>
@@ -7729,7 +7732,7 @@
       </c>
       <c r="G21" s="11"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
         <v>19</v>
       </c>
@@ -7743,7 +7746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="17">
         <v>10</v>
       </c>
@@ -7754,7 +7757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="17">
         <v>10.122999999999999</v>
       </c>
@@ -7765,7 +7768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
@@ -7779,7 +7782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
@@ -7796,7 +7799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
@@ -7813,7 +7816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
@@ -7830,7 +7833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>25</v>
       </c>
@@ -7847,7 +7850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
@@ -7864,7 +7867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -7881,7 +7884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
@@ -7898,7 +7901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
@@ -7909,7 +7912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
@@ -7926,7 +7929,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7971,7 +7974,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7980,7 +7983,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7989,7 +7992,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -8006,7 +8009,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8016,12 +8019,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0630FA18-71FC-4ACD-8379-39A3603D1DD6}">
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
@@ -8056,7 +8059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -8102,7 +8105,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -8148,7 +8151,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>45</v>
       </c>
@@ -8194,7 +8197,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
@@ -8240,7 +8243,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
@@ -8286,7 +8289,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>52</v>
       </c>
@@ -8320,7 +8323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -8354,7 +8357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
@@ -8385,7 +8388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>58</v>
       </c>
@@ -8401,7 +8404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>59</v>
       </c>
@@ -8420,7 +8423,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>61</v>
       </c>
@@ -8451,7 +8454,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>62</v>
       </c>
@@ -8482,7 +8485,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
@@ -8498,7 +8501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
@@ -8514,7 +8517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>69</v>
       </c>
@@ -8530,7 +8533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>70</v>
       </c>
@@ -8546,7 +8549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>71</v>
       </c>
@@ -8562,7 +8565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>72</v>
       </c>
@@ -8578,7 +8581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>73</v>
       </c>
@@ -8594,7 +8597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>74</v>
       </c>
@@ -8610,7 +8613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>76</v>
       </c>
@@ -8626,7 +8629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>77</v>
       </c>
@@ -8642,7 +8645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>78</v>
       </c>
@@ -8659,7 +8662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -8675,7 +8678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>81</v>
       </c>
@@ -8691,7 +8694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -8707,7 +8710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>83</v>
       </c>
@@ -8724,7 +8727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>84</v>
       </c>
@@ -8740,7 +8743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -8756,7 +8759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>86</v>
       </c>
@@ -8772,7 +8775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>87</v>
       </c>
@@ -8788,7 +8791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>88</v>
       </c>
@@ -8804,7 +8807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>89</v>
       </c>
@@ -8820,7 +8823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>90</v>
       </c>
@@ -8836,7 +8839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>91</v>
       </c>
@@ -8852,7 +8855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>92</v>
       </c>
@@ -8868,7 +8871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>93</v>
       </c>
@@ -8885,7 +8888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>94</v>
       </c>
@@ -8901,7 +8904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>95</v>
       </c>
@@ -8917,7 +8920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>96</v>
       </c>
@@ -8933,7 +8936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>97</v>
       </c>
@@ -8949,7 +8952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>98</v>
       </c>
@@ -8965,7 +8968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>99</v>
       </c>
@@ -8981,7 +8984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>100</v>
       </c>
@@ -8997,7 +9000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>101</v>
       </c>
@@ -9013,7 +9016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>102</v>
       </c>
@@ -9029,7 +9032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>103</v>
       </c>
@@ -9045,7 +9048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>104</v>
       </c>
@@ -9061,7 +9064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>105</v>
       </c>
@@ -9078,7 +9081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>106</v>
       </c>
@@ -9095,7 +9098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>107</v>
       </c>
@@ -9111,7 +9114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>108</v>
       </c>
@@ -9127,7 +9130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>109</v>
       </c>
@@ -9143,7 +9146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -9159,7 +9162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>111</v>
       </c>
@@ -9175,7 +9178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>112</v>
       </c>
@@ -9191,7 +9194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>113</v>
       </c>
@@ -9207,7 +9210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>114</v>
       </c>
@@ -9223,7 +9226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>115</v>
       </c>
@@ -9239,7 +9242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>116</v>
       </c>
@@ -9255,7 +9258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>117</v>
       </c>
@@ -9271,7 +9274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>118</v>
       </c>
@@ -9287,7 +9290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>119</v>
       </c>
@@ -9303,7 +9306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>120</v>
       </c>
@@ -9319,7 +9322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>121</v>
       </c>
@@ -9335,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>122</v>
       </c>
@@ -9351,7 +9354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>123</v>
       </c>
@@ -9367,7 +9370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>125</v>
       </c>
@@ -9383,7 +9386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>127</v>
       </c>
@@ -9399,7 +9402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>129</v>
       </c>
@@ -9415,7 +9418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>130</v>
       </c>
@@ -9431,7 +9434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>131</v>
       </c>
@@ -9447,7 +9450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>132</v>
       </c>
@@ -9463,7 +9466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>133</v>
       </c>
@@ -9479,7 +9482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>134</v>
       </c>
@@ -9495,7 +9498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>135</v>
       </c>
@@ -9511,7 +9514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>136</v>
       </c>
@@ -9527,7 +9530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>137</v>
       </c>
@@ -9543,7 +9546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>138</v>
       </c>
@@ -9559,7 +9562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>139</v>
       </c>
@@ -9575,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>141</v>
       </c>
@@ -9591,7 +9594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>142</v>
       </c>
@@ -9607,7 +9610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>143</v>
       </c>
@@ -9623,7 +9626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>144</v>
       </c>
@@ -9639,7 +9642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>146</v>
       </c>
@@ -9655,7 +9658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>147</v>
       </c>
@@ -9671,7 +9674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>148</v>
       </c>
@@ -9687,7 +9690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>149</v>
       </c>
@@ -9703,7 +9706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>150</v>
       </c>
@@ -9719,7 +9722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>151</v>
       </c>
@@ -9735,7 +9738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>152</v>
       </c>
@@ -9751,7 +9754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>153</v>
       </c>
@@ -9767,7 +9770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>154</v>
       </c>
@@ -9783,7 +9786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>155</v>
       </c>
@@ -9799,7 +9802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>156</v>
       </c>
@@ -9815,7 +9818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>157</v>
       </c>
@@ -9831,7 +9834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>158</v>
       </c>
@@ -9847,7 +9850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>159</v>
       </c>
@@ -9863,20 +9866,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="20">
         <f ca="1">NOW()</f>
-        <v>45512.434189004627</v>
+        <v>45643.379599189815</v>
       </c>
       <c r="D100" s="2">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>161</v>
       </c>
@@ -9892,7 +9895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>162</v>
       </c>
@@ -9908,7 +9911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>163</v>
       </c>
@@ -9924,7 +9927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>164</v>
       </c>
@@ -9940,7 +9943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>165</v>
       </c>
@@ -9956,7 +9959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>166</v>
       </c>
@@ -9972,7 +9975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>167</v>
       </c>
@@ -9988,7 +9991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>168</v>
       </c>
@@ -10004,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>169</v>
       </c>
@@ -10020,7 +10023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>170</v>
       </c>
@@ -10036,7 +10039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>171</v>
       </c>
@@ -10052,12 +10055,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="D112" s="2"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>172</v>
       </c>
@@ -10073,7 +10076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>173</v>
       </c>
@@ -10089,7 +10092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>175</v>
       </c>
@@ -10105,7 +10108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>177</v>
       </c>
@@ -10121,7 +10124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>178</v>
       </c>
@@ -10137,7 +10140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>179</v>
       </c>
@@ -10153,7 +10156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>180</v>
       </c>
@@ -10169,7 +10172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>181</v>
       </c>
@@ -10185,7 +10188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>182</v>
       </c>
@@ -10201,7 +10204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>183</v>
       </c>
@@ -10217,7 +10220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>184</v>
       </c>
@@ -10233,7 +10236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>185</v>
       </c>
@@ -10249,7 +10252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>186</v>
       </c>
@@ -10265,7 +10268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>187</v>
       </c>
@@ -10281,7 +10284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>188</v>
       </c>
@@ -10297,7 +10300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>189</v>
       </c>
@@ -10313,7 +10316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>190</v>
       </c>
@@ -10329,7 +10332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>191</v>
       </c>
@@ -10345,7 +10348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>192</v>
       </c>
@@ -10361,7 +10364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>193</v>
       </c>
@@ -10377,7 +10380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>194</v>
       </c>
@@ -10393,7 +10396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>195</v>
       </c>
@@ -10409,7 +10412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>196</v>
       </c>
@@ -10425,7 +10428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>198</v>
       </c>
@@ -10441,7 +10444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>199</v>
       </c>
@@ -10457,7 +10460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>200</v>
       </c>
@@ -10473,7 +10476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>201</v>
       </c>
@@ -10489,7 +10492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>202</v>
       </c>
@@ -10505,7 +10508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>203</v>
       </c>
@@ -10521,7 +10524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>205</v>
       </c>
@@ -10537,7 +10540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>206</v>
       </c>
@@ -10553,20 +10556,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="19">
         <f ca="1">TODAY()</f>
-        <v>45512</v>
+        <v>45643</v>
       </c>
       <c r="D144" s="2">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>208</v>
       </c>
@@ -10582,7 +10585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
@@ -10598,7 +10601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>211</v>
       </c>
@@ -10614,7 +10617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>213</v>
       </c>
@@ -10630,7 +10633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>214</v>
       </c>
@@ -10646,7 +10649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>215</v>
       </c>
@@ -10662,7 +10665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>216</v>
       </c>
@@ -10678,7 +10681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>217</v>
       </c>
@@ -10694,7 +10697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>218</v>
       </c>
@@ -10710,7 +10713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>219</v>
       </c>
@@ -10727,7 +10730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>220</v>
       </c>
@@ -10743,7 +10746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>221</v>
       </c>
@@ -10759,7 +10762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>222</v>
       </c>
@@ -10775,7 +10778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>223</v>
       </c>
@@ -10791,7 +10794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>224</v>
       </c>
@@ -10807,7 +10810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>225</v>
       </c>
@@ -10823,7 +10826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>226</v>
       </c>
@@ -10839,7 +10842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>227</v>
       </c>
@@ -10855,7 +10858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>229</v>
       </c>
@@ -10873,10 +10876,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10890,7 +10893,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -10900,17 +10903,17 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="109"/>
+      <c r="E1" s="110"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -10918,19 +10921,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D3" s="86" t="s">
         <v>235</v>
       </c>
@@ -10938,25 +10941,25 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1">
+    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1"/>
-    <row r="11" spans="1:8" outlineLevel="1"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
-    <row r="16" spans="1:8" outlineLevel="1"/>
-    <row r="17" outlineLevel="1"/>
-    <row r="18" outlineLevel="1"/>
+    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="17" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="18" outlineLevel="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:E2"/>
@@ -10973,14 +10976,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="69" t="s">
         <v>239</v>
       </c>
@@ -11002,7 +11005,7 @@
       </c>
       <c r="M1" s="37"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
         <v>245</v>
       </c>
@@ -11028,7 +11031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="42" t="s">
         <v>252</v>
       </c>
@@ -11051,7 +11054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15">
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
         <v>256</v>
       </c>
@@ -11077,7 +11080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
         <v>262</v>
       </c>
@@ -11097,7 +11100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="45" t="s">
         <v>266</v>
       </c>
@@ -11120,7 +11123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="46" t="s">
         <v>271</v>
       </c>
@@ -11140,7 +11143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="47" t="s">
         <v>275</v>
       </c>
@@ -11163,7 +11166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="48" t="s">
         <v>280</v>
       </c>
@@ -11180,7 +11183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="49" t="s">
         <v>283</v>
       </c>
@@ -11188,7 +11191,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
         <v>285</v>
       </c>
@@ -11197,7 +11200,7 @@
       </c>
       <c r="F11" s="37"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
         <v>287</v>
       </c>
@@ -11211,7 +11214,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="52" t="s">
         <v>290</v>
       </c>
@@ -11222,7 +11225,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
         <v>291</v>
       </c>
@@ -11236,7 +11239,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54" t="s">
         <v>293</v>
       </c>
@@ -11247,7 +11250,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
         <v>294</v>
       </c>
@@ -11261,12 +11264,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="75" t="s">
         <v>297</v>
       </c>
@@ -11278,7 +11281,7 @@
       </c>
       <c r="F18" s="37"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="76" t="s">
         <v>300</v>
       </c>
@@ -11289,7 +11292,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="77" t="s">
         <v>303</v>
       </c>
@@ -11303,12 +11306,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="78" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="79" t="s">
         <v>307</v>
       </c>
@@ -11317,13 +11320,13 @@
       </c>
       <c r="E22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="80" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="81" t="s">
         <v>310</v>
       </c>
@@ -11332,20 +11335,20 @@
       </c>
       <c r="E24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="68" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C28" s="89" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
-    <row r="30" spans="1:6">
+    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="88" t="s">
         <v>314</v>
       </c>
@@ -11359,13 +11362,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>315</v>
       </c>
@@ -11382,7 +11385,7 @@
       <c r="I1" s="37"/>
       <c r="J1" s="37"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
         <v>319</v>
       </c>
@@ -11405,7 +11408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
         <v>321</v>
       </c>
@@ -11428,7 +11431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
         <v>325</v>
       </c>
@@ -11448,7 +11451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
         <v>328</v>
       </c>
@@ -11472,7 +11475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="39" t="s">
         <v>330</v>
       </c>
@@ -11495,7 +11498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="39" t="s">
         <v>333</v>
       </c>
@@ -11521,7 +11524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
         <v>337</v>
       </c>
@@ -11532,7 +11535,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="39" t="s">
         <v>339</v>
       </c>
@@ -11541,7 +11544,7 @@
       </c>
       <c r="C9" s="22"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
         <v>340</v>
       </c>
@@ -11559,7 +11562,7 @@
       <c r="I10" s="37"/>
       <c r="J10" s="37"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="39" t="s">
         <v>342</v>
       </c>
@@ -11582,13 +11585,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="39" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="40">
         <f ca="1">TODAY()</f>
-        <v>45512</v>
+        <v>45643</v>
       </c>
       <c r="C12" s="40">
         <f>DATE(2010,10,2)</f>
@@ -11607,7 +11610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="39" t="s">
         <v>346</v>
       </c>
@@ -11630,7 +11633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="39" t="s">
         <v>348</v>
       </c>
@@ -11656,7 +11659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="39" t="s">
         <v>350</v>
       </c>
@@ -11676,7 +11679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="39" t="s">
         <v>352</v>
       </c>
@@ -11699,7 +11702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="39" t="s">
         <v>354</v>
       </c>
@@ -11722,7 +11725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="39" t="s">
         <v>356</v>
       </c>
@@ -11745,7 +11748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="39" t="s">
         <v>358</v>
       </c>
@@ -11768,7 +11771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="39" t="s">
         <v>360</v>
       </c>
@@ -11791,7 +11794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="39" t="s">
         <v>362</v>
       </c>
@@ -11817,7 +11820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="39" t="s">
         <v>364</v>
       </c>
@@ -11843,7 +11846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="39" t="s">
         <v>366</v>
       </c>
@@ -11869,7 +11872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G24" s="35" t="s">
         <v>368</v>
       </c>
@@ -11886,7 +11889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="39" t="s">
         <v>369</v>
       </c>
@@ -11912,7 +11915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G26" s="35" t="s">
         <v>371</v>
       </c>
@@ -11932,7 +11935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="22" t="s">
         <v>372</v>
       </c>
@@ -11958,7 +11961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G28" s="35" t="s">
         <v>374</v>
       </c>
@@ -11978,7 +11981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G29" s="35" t="s">
         <v>375</v>
       </c>
@@ -11998,7 +12001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G30" s="35" t="s">
         <v>376</v>
       </c>
@@ -12018,7 +12021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G31" s="36" t="s">
         <v>377</v>
       </c>
@@ -12032,7 +12035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G32" s="35" t="s">
         <v>378</v>
       </c>
@@ -12046,7 +12049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10">
+    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G33" s="35" t="s">
         <v>379</v>
       </c>
@@ -12060,7 +12063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10">
+    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G34" s="35" t="s">
         <v>380</v>
       </c>
@@ -12074,7 +12077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10">
+    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G35" s="35" t="s">
         <v>381</v>
       </c>
@@ -12088,7 +12091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10">
+    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G36" s="35" t="s">
         <v>382</v>
       </c>
@@ -12102,7 +12105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10">
+    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G37" s="35" t="s">
         <v>383</v>
       </c>
@@ -12116,110 +12119,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G39" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="40" priority="58">
+    <cfRule type="expression" dxfId="22" priority="58">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="39" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="38" priority="114"/>
+    <cfRule type="aboveAverage" dxfId="20" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="37" priority="73" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="19" priority="73" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="36" priority="71">
+    <cfRule type="containsBlanks" dxfId="18" priority="71">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="35" priority="70">
+    <cfRule type="containsErrors" dxfId="17" priority="70">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="34" priority="69" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="16" priority="69" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="33" priority="67" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="15" priority="67" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="32" priority="66">
+    <cfRule type="notContainsBlanks" dxfId="14" priority="66">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="31" priority="65">
+    <cfRule type="notContainsErrors" dxfId="13" priority="65">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="30" priority="64" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="12" priority="64" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="29" priority="63" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="11" priority="63" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="28" priority="115" rank="1"/>
+    <cfRule type="top10" dxfId="10" priority="115" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="27" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="45" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="26" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="8" priority="56" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -12253,10 +12256,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="19" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="18" priority="96"/>
+    <cfRule type="uniqueValues" dxfId="0" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="44">
@@ -12679,7 +12682,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -12691,12 +12694,12 @@
     <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15">
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="C3" s="18" t="s">
         <v>35</v>
       </c>
@@ -12722,7 +12725,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C4" s="2" t="s">
         <v>42</v>
       </c>
@@ -12753,7 +12756,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C5" s="2" t="s">
         <v>44</v>
       </c>
@@ -12784,7 +12787,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C6" s="2" t="s">
         <v>391</v>
       </c>
@@ -12817,7 +12820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>392</v>
       </c>
@@ -12828,7 +12831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C9">
         <v>3</v>
       </c>
@@ -12836,7 +12839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>393</v>
       </c>
@@ -12847,7 +12850,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C12">
         <v>3</v>
       </c>
@@ -12855,7 +12858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>396</v>
       </c>
@@ -12866,7 +12869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C15">
         <v>3</v>
       </c>
@@ -12874,7 +12877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>397</v>
       </c>
@@ -12885,7 +12888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C18">
         <v>3</v>
       </c>
@@ -12893,7 +12896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>398</v>
       </c>
@@ -12904,7 +12907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C21">
         <v>3</v>
       </c>
@@ -12912,7 +12915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>399</v>
       </c>
@@ -12923,7 +12926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C24">
         <v>3</v>
       </c>
@@ -12931,7 +12934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>400</v>
       </c>
@@ -12942,7 +12945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C27">
         <v>3</v>
       </c>
@@ -12950,7 +12953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
         <v>391</v>
       </c>
@@ -12959,7 +12962,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>401</v>
       </c>
@@ -12970,7 +12973,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="31" spans="2:4" hidden="1">
+    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
         <v>404</v>
       </c>
@@ -12978,7 +12981,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
         <v>405</v>
       </c>
@@ -12986,7 +12989,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>406</v>
       </c>
@@ -13011,7 +13014,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -13032,7 +13035,7 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="93" t="s">
         <v>407</v>
       </c>
@@ -13042,7 +13045,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13050,7 +13053,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="90" t="s">
@@ -13060,7 +13063,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="90" t="s">
@@ -13094,7 +13097,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="91" t="s">
@@ -13107,7 +13110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="92">
@@ -13120,7 +13123,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="91" t="s">
@@ -13133,7 +13136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="92">
@@ -13146,7 +13149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="91" t="s">
@@ -13159,7 +13162,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="92">
@@ -13172,7 +13175,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="91" t="s">
         <v>44</v>
       </c>
@@ -13183,7 +13186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="92">
         <v>23000</v>
       </c>
@@ -13194,7 +13197,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="91" t="s">
         <v>50</v>
       </c>
@@ -13205,7 +13208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="92">
         <v>2</v>
       </c>
@@ -13216,7 +13219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="91" t="s">
         <v>48</v>
       </c>
@@ -13227,7 +13230,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C16" s="92">
         <v>50024</v>
       </c>
@@ -13238,7 +13241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="91" t="s">
         <v>53</v>
       </c>
@@ -13249,7 +13252,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="92">
         <v>189576</v>
       </c>
@@ -13260,7 +13263,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="91" t="s">
         <v>57</v>
       </c>
@@ -13271,7 +13274,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="92">
         <v>5000</v>
       </c>
@@ -13282,7 +13285,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="91" t="s">
         <v>411</v>
       </c>
@@ -13323,29 +13326,29 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>413</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>415</v>
       </c>
@@ -13358,12 +13361,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="38.25">
+    <row r="1" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A1" s="100" t="s">
         <v>416</v>
+      </c>
+      <c r="B1" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05E556DF-B6A9-4914-8E28-82201545992C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41C3570E-9DC4-41A4-9181-236A5B499B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,13 +26,14 @@
     <sheet name="jestFreezePane" sheetId="14" r:id="rId11"/>
     <sheet name="jestImages" sheetId="15" r:id="rId12"/>
     <sheet name="jestOneCellAnchor" sheetId="16" r:id="rId13"/>
+    <sheet name="jestDataValidations" sheetId="17" r:id="rId14"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId14"/>
+    <externalReference r:id="rId15"/>
   </externalReferences>
   <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="153" r:id="rId15"/>
+    <pivotCache cacheId="698" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="422">
   <si>
     <t>CF =42</t>
   </si>
@@ -1306,20 +1307,34 @@
   <si>
     <t>This text have
  a newLine</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>test123</t>
+  </si>
+  <si>
+    <t>hola</t>
+  </si>
+  <si>
+    <t>A1234556</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="167" formatCode="[$$-409]#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="[$₪-40D]\ #,##0"/>
-    <numFmt numFmtId="169" formatCode="#,##0&quot; EUR €&quot;"/>
-    <numFmt numFmtId="170" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="[$₪-40D]\ #,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
+    <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1480,7 +1495,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1655,8 +1670,14 @@
         </stop>
       </gradientFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -2005,18 +2026,95 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2067,10 +2165,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="19" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2184,20 +2282,39 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="28" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="28" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2210,7 +2327,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2240,7 +2356,7 @@
         <u/>
         <color theme="7"/>
       </font>
-      <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
       <fill>
         <patternFill patternType="lightTrellis">
           <fgColor theme="4"/>
@@ -6554,6 +6670,9 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
@@ -6589,6 +6708,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E90E321-E964-46C8-9CE7-DEE1186146D9}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6628,6 +6750,9 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CC27214-40A9-4FF9-BB37-40F876B2768B}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1E90E321-E964-46C8-9CE7-DEE1186146D9}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
@@ -6665,6 +6790,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5685A00-859E-4641-A529-E7042819F3BF}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6CC27214-40A9-4FF9-BB37-40F876B2768B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6943,7 +7071,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="153" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="698" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -7540,387 +7668,387 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A1" s="22"/>
+      <c r="A1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="119" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="27.75">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="119">
         <v>5</v>
       </c>
-      <c r="H2" s="105" t="s">
+      <c r="H2" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="110"/>
-      <c r="K2" s="4"/>
+      <c r="I2" s="121"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1">
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="119">
         <v>8</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="106">
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="122">
         <v>5</v>
       </c>
-      <c r="L3" s="7"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="17.25" customHeight="1">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="119">
         <v>12.4</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="119">
         <v>9</v>
       </c>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="7"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1">
-      <c r="C5" s="2">
+      <c r="C5" s="119">
         <v>42</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="119">
         <v>15</v>
       </c>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="7"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1">
-      <c r="G6" s="2">
+      <c r="G6" s="119">
         <v>22</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="107"/>
-      <c r="L6" s="7"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1">
-      <c r="C7" s="2">
+      <c r="C7" s="119">
         <v>3</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="7"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1">
-      <c r="G8" s="2">
+      <c r="G8" s="119">
         <v>30</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="108"/>
-      <c r="L8" s="7"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="119">
         <f>SUM(C4:C5)</f>
         <v>54.4</v>
       </c>
-      <c r="K9" s="11"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:12" ht="17.25" customHeight="1">
-      <c r="C10" s="2">
+      <c r="C10" s="119">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="119" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1">
-      <c r="C11" s="2">
+      <c r="C11" s="119">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="17.25" customHeight="1">
-      <c r="C12" s="2">
+      <c r="C12" s="119">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="119" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1">
-      <c r="G13" s="2">
+      <c r="G13" s="119">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="17.25" customHeight="1">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="str">
+      <c r="C14" s="119" t="str">
         <f ca="1">C14</f>
         <v>#CYCLE</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" customHeight="1">
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="119" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="17.25" customHeight="1">
-      <c r="C16" s="2" t="str">
+      <c r="C16" s="119" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.25" customHeight="1">
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="119" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25" customHeight="1">
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="119" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.25" customHeight="1">
-      <c r="E19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:9" ht="17.25" customHeight="1">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="13" t="s">
+      <c r="F20" s="5"/>
+      <c r="G20" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <f>jestCharts!B2</f>
         <v>0</v>
       </c>
-      <c r="G21" s="11"/>
+      <c r="G21" s="10"/>
     </row>
     <row r="23" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="15">
         <v>0.43</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="119">
         <v>0</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="119">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25" customHeight="1">
-      <c r="C24" s="17">
+      <c r="C24" s="16">
         <v>10</v>
       </c>
-      <c r="H24" s="2">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2">
+      <c r="H24" s="119">
+        <v>1</v>
+      </c>
+      <c r="I24" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.25" customHeight="1">
-      <c r="C25" s="17">
+      <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="119">
         <v>2</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="119">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.25" customHeight="1">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="119">
         <v>3</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="119">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="119">
         <v>12</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="119">
         <v>24</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="119">
         <v>4</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="119">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="119">
         <v>48</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="119">
         <v>12</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="119">
         <v>5</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="119">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="119">
         <v>45</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="119">
         <v>27</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="119">
         <v>6</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="119">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="2">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="119">
+        <v>1</v>
+      </c>
+      <c r="C30" s="119">
         <v>9</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="119">
         <v>7</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="119">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="119">
         <v>25</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="119">
         <v>45</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="119">
         <v>8</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="119">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="119">
         <v>31</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="119">
         <v>17</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="119">
         <v>9</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="119">
         <v>20</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="119">
         <v>43</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="119">
         <v>10</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="119">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="119">
         <v>19</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="119">
         <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="119">
         <v>16</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="119">
         <v>16</v>
       </c>
     </row>
@@ -8017,6 +8145,179 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A8BD8D-B6B2-4BF7-95D3-E773B857DC1C}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="104">
+        <v>4</v>
+      </c>
+      <c r="B1" s="105">
+        <v>99.5</v>
+      </c>
+      <c r="C1" s="105">
+        <v>1</v>
+      </c>
+      <c r="D1" s="116">
+        <v>45575</v>
+      </c>
+      <c r="E1" s="113">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F1" s="113" t="s">
+        <v>417</v>
+      </c>
+      <c r="G1" s="116">
+        <v>45292</v>
+      </c>
+      <c r="H1" s="106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="107">
+        <v>3</v>
+      </c>
+      <c r="B2" s="108">
+        <v>40</v>
+      </c>
+      <c r="C2" s="108">
+        <v>2</v>
+      </c>
+      <c r="D2" s="117">
+        <v>45576</v>
+      </c>
+      <c r="E2" s="114">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="F2" s="114" t="s">
+        <v>418</v>
+      </c>
+      <c r="G2" s="117">
+        <v>45231</v>
+      </c>
+      <c r="H2" s="109" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="107">
+        <v>9</v>
+      </c>
+      <c r="B3" s="108">
+        <v>0</v>
+      </c>
+      <c r="C3" s="108">
+        <v>3</v>
+      </c>
+      <c r="D3" s="117">
+        <v>45574</v>
+      </c>
+      <c r="E3" s="114">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F3" s="114" t="s">
+        <v>419</v>
+      </c>
+      <c r="G3" s="117">
+        <v>45325</v>
+      </c>
+      <c r="H3" s="109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="107">
+        <v>5</v>
+      </c>
+      <c r="B4" s="108">
+        <v>120</v>
+      </c>
+      <c r="C4" s="108">
+        <v>4</v>
+      </c>
+      <c r="D4" s="117">
+        <v>45573</v>
+      </c>
+      <c r="E4" s="114">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="108" t="s">
+        <v>420</v>
+      </c>
+      <c r="G4" s="117">
+        <v>45084</v>
+      </c>
+      <c r="H4" s="109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="110">
+        <v>7</v>
+      </c>
+      <c r="B5" s="111">
+        <v>12</v>
+      </c>
+      <c r="C5" s="111">
+        <v>5</v>
+      </c>
+      <c r="D5" s="118">
+        <v>45566</v>
+      </c>
+      <c r="E5" s="115">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="F5" s="111" t="s">
+        <v>421</v>
+      </c>
+      <c r="G5" s="118">
+        <v>45420</v>
+      </c>
+      <c r="H5" s="112" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A5" xr:uid="{3DE5A080-5608-43E8-BF23-7D74DE4075FA}">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B5" xr:uid="{7F0958B9-591D-46E4-B3C0-E66AFED4FBC7}">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C5" xr:uid="{2A5A7B69-FF02-4203-BAAB-F5C563E139D1}">
+      <formula1>$C$1:$C$5</formula1>
+    </dataValidation>
+    <dataValidation type="date" errorStyle="warning" operator="notEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D5" xr:uid="{E151B6B0-55E6-472F-A761-13DF2E533EA0}">
+      <formula1>45575</formula1>
+    </dataValidation>
+    <dataValidation type="time" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E5" xr:uid="{DFD45D62-DA0F-4256-B5E3-B09834D69F8E}">
+      <formula1>0.625</formula1>
+      <formula2>0.75</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F5" xr:uid="{0D657D85-A411-4ABD-BC29-6BE59A75B220}">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H5" xr:uid="{01673B3B-8DF8-479F-80A2-9555170A976E}">
+      <formula1>ISNUMBER(H1)</formula1>
+    </dataValidation>
+    <dataValidation type="date" errorStyle="warning" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G5" xr:uid="{E54F91C6-3EC1-42A0-8B1C-05C6CBEBADF5}">
+      <formula1>45261</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0630FA18-71FC-4ACD-8379-39A3603D1DD6}">
   <sheetPr>
@@ -8029,71 +8330,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="119" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="2">
+      <c r="N1" s="119">
         <v>0.1</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="119">
         <f>ABS(-5.5)</f>
         <v>5.5</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="119">
         <v>5.5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="119">
         <f t="shared" ref="D2:D33" si="0">IF(B2=C2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="119">
         <v>26</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="119">
         <v>1204.7</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="119">
         <v>25618</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="119">
         <v>5</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="119">
         <v>0.2</v>
       </c>
       <c r="P2">
@@ -8110,36 +8411,36 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="119">
         <f>ACOS(1)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="119">
         <v>0</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="119">
         <v>13</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="119">
         <v>500.9</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="119">
         <v>23000</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="119">
         <v>7</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="119">
         <v>0.4</v>
       </c>
       <c r="P3">
@@ -8156,36 +8457,36 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="119">
         <f>ROUND(ACOSH(2),5)</f>
         <v>1.3169599999999999</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="119">
         <v>1.3169599999999999</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="119">
         <v>26</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="119">
         <v>252.4</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="119">
         <v>110120.5</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="119">
         <v>3</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="119">
         <v>0.5</v>
       </c>
       <c r="P4">
@@ -8202,36 +8503,36 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="119">
         <f>ROUND(_xlfn.ACOT(1),5)</f>
         <v>0.78539999999999999</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="119">
         <v>0.78539999999999999</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="119">
         <v>42</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="119">
         <v>4701.3</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="119">
         <v>50024</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="119">
         <v>4</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="119">
         <v>0.6</v>
       </c>
       <c r="P5">
@@ -8248,36 +8549,36 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="119">
         <f>ROUND(_xlfn.ACOTH(2),5)</f>
         <v>0.54930999999999996</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="119">
         <v>0.54930999999999996</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="119">
         <f>IF(B6=C6,1,0)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="119">
         <v>9</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="119">
         <v>12.1</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="119">
         <v>2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="119">
         <v>1000</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="119" t="s">
         <v>51</v>
       </c>
       <c r="P6">
@@ -8294,2586 +8595,2586 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="2" t="b">
+      <c r="B7" s="119" t="b">
         <f>AND(TRUE,TRUE)</f>
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="119">
         <v>27</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="119">
         <v>4000</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="119">
         <v>189576</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="119">
         <v>2</v>
       </c>
-      <c r="N7" s="2" t="b">
+      <c r="N7" s="119" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="119">
         <f>ROUND(ASIN(0.5),5)</f>
         <v>0.52359999999999995</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="119">
         <v>0.52359999999999995</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="119">
         <v>30</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="119">
         <v>12052</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="119">
         <v>256018</v>
       </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="b">
+      <c r="K8" s="119">
+        <v>1</v>
+      </c>
+      <c r="N8" s="119" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="119" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="119">
         <f>ROUND(ASINH(2),5)</f>
         <v>1.44364</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="119">
         <v>1.44364</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="119">
         <v>37</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="119">
         <v>4890.1000000000004</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="119">
         <v>5000</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="119">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="119">
         <f>ROUND(ATAN(1),5)</f>
         <v>0.78539999999999999</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="119">
         <v>0.78539999999999999</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="119">
         <f>ROUND(ATAN2(-1,0),5)</f>
         <v>3.1415899999999999</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="119">
         <v>3.1415899999999999</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="119" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="119" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="119">
         <f>ROUND(ATANH(0.7),5)</f>
         <v>0.86729999999999996</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="119">
         <v>0.86729999999999996</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="119">
         <f>ROUND(AVEDEV(I2:I9),5)</f>
         <v>2959.1624999999999</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="119">
         <v>2959.1624999999999</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="119" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="119" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="119">
         <f>ROUND(AVERAGE(H2:H9),5)</f>
         <v>26.25</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="119">
         <v>26.25</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="119">
         <f>AVERAGEA(G2:H9)</f>
         <v>13.125</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="119">
         <v>13.125</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="119">
         <f>ROUND(AVERAGEIF(J2:J9,"&gt;150000"),5)</f>
         <v>222797</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="119">
         <v>222797</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="119">
         <f>ROUND(AVERAGEIFS(I2:I9,H2:H9,"&gt;=30",K2:K9,"&lt;10"),5)</f>
         <v>8376.65</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="119">
         <v>8376.65</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="119" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="119">
         <f>CEILING(20.4,1)</f>
         <v>21</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="119">
         <v>21</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="119">
         <f>_xlfn.CEILING.MATH(-5.5,1,0)</f>
         <v>-5</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="119">
         <v>-5</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="119">
         <f>_xlfn.CEILING.PRECISE(230,100)</f>
         <v>300</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="119">
         <v>300</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="2" t="str">
+      <c r="B21" s="119" t="str">
         <f>CHAR(74)</f>
         <v>J</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="119" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="119" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="119">
         <f>COLUMN(C4)</f>
         <v>3</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="119">
         <v>3</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="119" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="119">
         <f>COLUMNS(A5:D12)</f>
         <v>4</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="119">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="2" t="str">
+      <c r="B24" s="119" t="str">
         <f>_xlfn.CONCAT(1,23)</f>
         <v>123</v>
       </c>
-      <c r="C24" s="2" t="str">
+      <c r="C24" s="119" t="str">
         <f>"123"</f>
         <v>123</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="2" t="str">
+      <c r="B25" s="119" t="str">
         <f>CONCATENATE("BUT, ","MICHEL")</f>
         <v>BUT, MICHEL</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="119">
         <f>ROUND(COS(PI()/3),2)</f>
         <v>0.5</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="119">
         <v>0.5</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="119">
         <f>ROUND(COSH(2),5)</f>
         <v>3.7622</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="119">
         <v>3.7622</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="119">
         <f>ROUND(_xlfn.COT(PI()/6),5)</f>
         <v>1.7320500000000001</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="119">
         <f>ROUND(SQRT(3),5)</f>
         <v>1.7320500000000001</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="119">
         <f>ROUND(_xlfn.COTH(0.5),5)</f>
         <v>2.1639499999999998</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="119">
         <v>2.1639499999999998</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="119">
         <f>COUNT(1,"a","5","2021-03-14")</f>
         <v>3</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="119">
         <v>2</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="119">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="119">
         <f>COUNTA(1,"a","5","2021-03-14")</f>
         <v>4</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="119">
         <v>4</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="119" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="119">
         <f>COUNTBLANK(F1:G1)</f>
         <v>1</v>
       </c>
-      <c r="C32" s="2">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="C32" s="119">
+        <v>1</v>
+      </c>
+      <c r="D32" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="119" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="119">
         <f>COUNTIF(H2:H9,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="119">
         <v>2</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="119">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="119" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="119">
         <f>COUNTIFS(H2:H9,"&gt;25",K2:K9,"&lt;4")</f>
         <v>3</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="119">
         <v>3</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="119">
         <f t="shared" ref="D34:D65" si="4">IF(B34=C34,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="119">
         <f>ROUND(COVAR(H2:H9,K2:K9),5)</f>
         <v>-2119.25</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="119">
         <v>-2119.25</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="119" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="119">
         <f>ROUND(_xlfn.COVARIANCE.P(K2:K9,H2:H9),5)</f>
         <v>-2119.25</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="119">
         <v>-2119.25</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="119" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="119">
         <f>ROUND(_xlfn.COVARIANCE.P(I2:I9,J2:J9),5)</f>
         <v>237217364.71641001</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="119">
         <v>237217364.71641001</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="119" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="119">
         <f>ROUND(_xlfn.CSC(PI()/4),5)</f>
         <v>1.41421</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="119">
         <f>ROUND(SQRT(2),5)</f>
         <v>1.41421</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="119" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="119">
         <f>ROUND(_xlfn.CSCH(PI()/3),5)</f>
         <v>0.80040999999999995</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="119">
         <v>0.80040999999999995</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="119" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="18">
         <f>DATE(2020,5,25)</f>
         <v>43976</v>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="18">
         <v>43976</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="119">
         <f>DATEVALUE("1969-08-15")</f>
         <v>25430</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="119">
         <v>25430</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="119" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="119">
         <f>ROUND(DAVERAGE(G1:K9,"Tot. Score",J12:J13),5)</f>
         <v>151434.625</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="119">
         <v>151434.625</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="119" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="119">
         <f>DAY("2020-03-17")</f>
         <v>17</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="119">
         <v>17</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="119" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="119">
         <f>_xlfn.DAYS("2022-03-17","2021-03-17")</f>
         <v>365</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="119">
         <v>365</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="119">
         <f>DCOUNT(G1:K9,"Name",H12:H13)</f>
         <v>0</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="119">
         <v>0</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="119" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="119">
         <f>DCOUNTA(G1:K9,"Name",H12:H13)</f>
         <v>3</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="119">
         <v>3</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="119" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="119">
         <f>_xlfn.DECIMAL(20,16)</f>
         <v>32</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="119">
         <v>32</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="119">
         <f>DEGREES(PI()/4)</f>
         <v>45</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="119">
         <v>45</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="119" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="119">
         <f>DGET(G1:K9,"Hours Played",G12:G13)</f>
         <v>252.4</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="119">
         <v>252.4</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="119" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="119">
         <f>DMAX(G1:K9,"Tot. Score",I12:I13)</f>
         <v>189576</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="119">
         <f>J7</f>
         <v>189576</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="119">
         <f>DMIN(G1:K9,"Tot. Score",H12:H13)</f>
         <v>5000</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="119">
         <f>J9</f>
         <v>5000</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="119">
         <f>DPRODUCT(G1:K9,"Age",K12:K13)</f>
         <v>333</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="119">
         <v>333</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="119" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="119">
         <f>ROUND(DSTDEV(G1:K9,"Age",H12:H13),5)</f>
         <v>6.0277099999999999</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="119">
         <v>6.0277099999999999</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="119" t="s">
         <v>109</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="119">
         <f>ROUND(DSTDEVP(G1:K9,"Age",H12:H13),5)</f>
         <v>4.9216100000000003</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="119">
         <v>4.9216100000000003</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="119" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="119">
         <f>DSUM(G1:K9,"Age",I12:I13)</f>
         <v>101</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="119">
         <v>101</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="119" t="s">
         <v>111</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="119">
         <f>ROUND(DVAR(G1:K9,"Hours Played",H12:H13),5)</f>
         <v>17560207.923330002</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="119">
         <v>17560207.923330002</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="119" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="119">
         <f>ROUND(DVARP(G1:K9,"Hours Played",H12:H13),5)</f>
         <v>11706805.28222</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="119">
         <v>11706805.28222</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="18">
         <f>EDATE("1969-07-22",-2)</f>
         <v>25345</v>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="18">
         <v>25345</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="119" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="18">
         <f>EOMONTH("2020-07-21",1)</f>
         <v>44074</v>
       </c>
-      <c r="C59" s="19">
+      <c r="C59" s="18">
         <v>44074</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="119" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="2" t="b">
+      <c r="B60" s="119" t="b">
         <f>EXACT("AbsSdf%","AbsSdf%")</f>
         <v>1</v>
       </c>
-      <c r="C60" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="C60" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="119" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="119">
         <f>ROUND(EXP(4),5)</f>
         <v>54.598149999999997</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="119">
         <v>54.598149999999997</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="119" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="119">
         <f>FIND("A","qbdahbaazo A")</f>
         <v>12</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="119">
         <v>12</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="119" t="s">
         <v>118</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="119">
         <f>FLOOR(5.5,2)</f>
         <v>4</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="119">
         <v>4</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="119" t="s">
         <v>119</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="119">
         <f>_xlfn.FLOOR.MATH(-5.55,2,1)</f>
         <v>-4</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="119">
         <v>-4</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="119" t="s">
         <v>120</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="119">
         <f>_xlfn.FLOOR.PRECISE(199,100)</f>
         <v>100</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="119">
         <v>100</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="119">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="119" t="s">
         <v>121</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="119">
         <f>HLOOKUP("Tot. Score",H1:K9,4,FALSE)</f>
         <v>110120.5</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="119">
         <v>110120.5</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="119">
         <f t="shared" ref="D66:D97" si="5">IF(B66=C66,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="119">
         <f>HOUR("02:14:56")</f>
         <v>2</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="119">
         <v>2</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="119" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="2" t="str">
+      <c r="B68" s="119" t="str">
         <f>IF(TRUE,"TABOURET","JAMBON")</f>
         <v>TABOURET</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="B69" s="2" t="str">
+      <c r="B69" s="119" t="str">
         <f>IFERROR(0/0,"no diving by zero.")</f>
         <v>no diving by zero.</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="119" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="119" t="s">
         <v>127</v>
       </c>
-      <c r="B70" s="2" t="str">
+      <c r="B70" s="119" t="str">
         <f>_xlfn.IFS($H2&gt;$H3,"first player is older",$H3&gt;$H2,"second player is older")</f>
         <v>first player is older</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="119" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="2" t="b">
+      <c r="B71" s="119" t="b">
         <f>ISERROR(0/0)</f>
         <v>1</v>
       </c>
-      <c r="C71" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="C71" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="119" t="s">
         <v>130</v>
       </c>
-      <c r="B72" s="2" t="b">
+      <c r="B72" s="119" t="b">
         <f>ISEVEN(3)</f>
         <v>0</v>
       </c>
-      <c r="C72" s="2" t="b">
+      <c r="C72" s="119" t="b">
         <v>0</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="2" t="b">
+      <c r="B73" s="119" t="b">
         <f>ISLOGICAL("TRUE")</f>
         <v>0</v>
       </c>
-      <c r="C73" s="2" t="b">
+      <c r="C73" s="119" t="b">
         <v>0</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="119" t="s">
         <v>132</v>
       </c>
-      <c r="B74" s="2" t="b">
+      <c r="B74" s="119" t="b">
         <f>ISNONTEXT(TRUE)</f>
         <v>1</v>
       </c>
-      <c r="C74" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D74" s="2">
+      <c r="C74" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="119" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="2" t="b">
+      <c r="B75" s="119" t="b">
         <f>ISNUMBER(1231.5)</f>
         <v>1</v>
       </c>
-      <c r="C75" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2">
+      <c r="C75" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="119" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="119">
         <f>ISO.CEILING(-7.89)</f>
         <v>-7</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="119">
         <v>-7</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="119" t="s">
         <v>135</v>
       </c>
-      <c r="B77" s="2" t="b">
+      <c r="B77" s="119" t="b">
         <f>ISODD(4)</f>
         <v>0</v>
       </c>
-      <c r="C77" s="2" t="b">
+      <c r="C77" s="119" t="b">
         <v>0</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="119" t="s">
         <v>136</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="119">
         <f>_xlfn.ISOWEEKNUM("2016-01-03")</f>
         <v>53</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="119">
         <v>53</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="119" t="s">
         <v>137</v>
       </c>
-      <c r="B79" s="2" t="b">
+      <c r="B79" s="119" t="b">
         <f>ISTEXT("123")</f>
         <v>1</v>
       </c>
-      <c r="C79" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
+      <c r="C79" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="119">
         <f>LARGE(H2:H9,3)</f>
         <v>30</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="119">
         <v>30</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="119" t="s">
         <v>139</v>
       </c>
-      <c r="B81" s="2" t="str">
+      <c r="B81" s="119" t="str">
         <f>LEFT("Mich",4)</f>
         <v>Mich</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="119" t="s">
         <v>140</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="119" t="s">
         <v>141</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="119">
         <f>LEN("anticonstitutionnellement")</f>
         <v>25</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="119">
         <v>25</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="119">
         <f>ROUND(LN(2),5)</f>
         <v>0.69315000000000004</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="119">
         <v>0.69315000000000004</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="119" t="s">
         <v>143</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="119">
         <f>LOOKUP(23000,H3:J3,H5:J5)</f>
         <v>50024</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="119">
         <v>50024</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="2" t="str">
+      <c r="B85" s="119" t="str">
         <f>LOWER("オAドB")</f>
         <v>オaドb</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="119" t="s">
         <v>145</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="119" t="s">
         <v>146</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="119">
         <f>MATCH(42,H2:H9,0)</f>
         <v>4</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="119">
         <v>4</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="119" t="s">
         <v>147</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="119">
         <f>MAX(N1:N8)</f>
         <v>0.6</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="119">
         <v>0.6</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="119" t="s">
         <v>148</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="119">
         <f>MAXA(N1:N8)</f>
         <v>1</v>
       </c>
-      <c r="C88" s="2">
-        <v>1</v>
-      </c>
-      <c r="D88" s="2">
+      <c r="C88" s="119">
+        <v>1</v>
+      </c>
+      <c r="D88" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="119">
         <f>_xlfn.MAXIFS(H2:H9,K2:K9,"&lt;20",K2:K9,"&lt;&gt;4")</f>
         <v>30</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="119">
         <v>30</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="119">
         <f>MEDIAN(-1,6,7,234,163845)</f>
         <v>7</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="119">
         <v>7</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="119" t="s">
         <v>151</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="119">
         <f>MIN(N1:N8)</f>
         <v>0.1</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="119">
         <v>0.1</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="119" t="s">
         <v>152</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="119">
         <f>MINA(N1:N8)</f>
         <v>0</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="119">
         <v>0</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="119" t="s">
         <v>153</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="119">
         <f>_xlfn.MINIFS(J2:J9,H2:H9,"&gt;20")</f>
         <v>5000</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="119">
         <v>5000</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="119" t="s">
         <v>154</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="119">
         <f>MINUTE(0.126)</f>
         <v>1</v>
       </c>
-      <c r="C94" s="2">
-        <v>1</v>
-      </c>
-      <c r="D94" s="2">
+      <c r="C94" s="119">
+        <v>1</v>
+      </c>
+      <c r="D94" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="119" t="s">
         <v>155</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="119">
         <f>MOD(42,12)</f>
         <v>6</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="119">
         <v>6</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="119" t="s">
         <v>156</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="119">
         <f>MONTH("1954-05-02")</f>
         <v>5</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="119">
         <v>5</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="119" t="s">
         <v>157</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="119">
         <f>NETWORKDAYS("2013-01-01","2013-02-01")</f>
         <v>24</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="119">
         <v>24</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="119">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="119" t="s">
         <v>158</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="119">
         <f>NETWORKDAYS.INTL("2013-01-01","2013-02-01","0000111")</f>
         <v>19</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="119">
         <v>19</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="119">
         <f t="shared" ref="D98:D99" si="6">IF(B98=C98,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="119" t="s">
         <v>159</v>
       </c>
-      <c r="B99" s="2" t="b">
+      <c r="B99" s="119" t="b">
         <f>NOT(FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C99" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D99" s="2">
+      <c r="C99" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" s="119">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="119" t="s">
         <v>160</v>
       </c>
-      <c r="B100" s="20">
+      <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45526.511599421297</v>
-      </c>
-      <c r="D100" s="2">
+        <v>45579.670868402776</v>
+      </c>
+      <c r="D100" s="119">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="119" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="119">
         <f>ODD(4)</f>
         <v>5</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="119">
         <v>5</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="119">
         <f t="shared" ref="D101:D111" si="7">IF(B101=C101,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="119" t="s">
         <v>162</v>
       </c>
-      <c r="B102" s="2" t="b">
+      <c r="B102" s="119" t="b">
         <f>OR("true",FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C102" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D102" s="2">
+      <c r="C102" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="119" t="s">
         <v>163</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="119">
         <f>PERCENTILE(N1:N5,1)</f>
         <v>0.6</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="119">
         <v>0.6</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="119" t="s">
         <v>164</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="119">
         <f>_xlfn.PERCENTILE.EXC(N1:N5,0.5)</f>
         <v>0.4</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="119">
         <v>0.4</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="119" t="s">
         <v>165</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="119">
         <f>_xlfn.PERCENTILE.INC(N1:N5,0)</f>
         <v>0.1</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="119">
         <v>0.1</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="119" t="s">
         <v>166</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="119">
         <f>ROUND(PI(),5)</f>
         <v>3.1415899999999999</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106" s="119">
         <v>3.1415899999999999</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="119" t="s">
         <v>167</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="119">
         <f>POWER(42,2)</f>
         <v>1764</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="119">
         <v>1764</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="119">
         <f>PRODUCT(1,2,3)</f>
         <v>6</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="119">
         <v>6</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="119" t="s">
         <v>169</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="119">
         <f>QUARTILE(N1:N5,0)</f>
         <v>0.1</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="119">
         <v>0.1</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="119" t="s">
         <v>170</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="119">
         <f>ROUND(_xlfn.QUARTILE.EXC(N1:N5,1),5)</f>
         <v>0.15</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110" s="119">
         <v>0.15</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="119" t="s">
         <v>171</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="119">
         <f>_xlfn.QUARTILE.INC(N1:N5,4)</f>
         <v>0.6</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="119">
         <v>0.6</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="119">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="D112" s="2"/>
+      <c r="A112" s="119"/>
+      <c r="B112" s="119"/>
+      <c r="D112" s="119"/>
     </row>
     <row r="113" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="119" t="s">
         <v>172</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="119">
         <f ca="1">RANDBETWEEN(1.1,2)</f>
         <v>2</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="119">
         <v>2</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="119">
         <f t="shared" ref="D113:D143" ca="1" si="8">IF(B113=C113,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="119" t="s">
         <v>173</v>
       </c>
-      <c r="B114" s="2" t="str">
+      <c r="B114" s="119" t="str">
         <f>REPLACE("ABZ",2,1,"Y")</f>
         <v>AYZ</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="119" t="s">
         <v>174</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="119" t="s">
         <v>175</v>
       </c>
-      <c r="B115" s="2" t="str">
+      <c r="B115" s="119" t="str">
         <f>RIGHT("kikou",2)</f>
         <v>ou</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="119" t="s">
         <v>176</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="119" t="s">
         <v>177</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="119">
         <f>ROUND(49.9,0)</f>
         <v>50</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="119">
         <v>50</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="119">
         <f>ROUNDDOWN(42,-1)</f>
         <v>40</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="119">
         <v>40</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="119">
         <f>ROUNDUP(-1.6,0)</f>
         <v>-2</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118" s="119">
         <v>-2</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="119" t="s">
         <v>180</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="119">
         <f>ROW(A234)</f>
         <v>234</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="119">
         <v>234</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="119" t="s">
         <v>181</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="119">
         <f>ROWS(B3:C40)</f>
         <v>38</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="119">
         <v>38</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="119" t="s">
         <v>182</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="119">
         <f>SEARCH("C","ABCD")</f>
         <v>3</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="119">
         <v>3</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="119">
         <f>ROUND(_xlfn.SEC(PI()/3),5)</f>
         <v>2</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122" s="119">
         <v>2</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="119">
         <f>ROUND(_xlfn.SECH(1),5)</f>
         <v>0.64805000000000001</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="119">
         <v>0.64805000000000001</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="119" t="s">
         <v>185</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="119">
         <f>SECOND("00:21:42")</f>
         <v>42</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124" s="119">
         <v>42</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="119" t="s">
         <v>186</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="119">
         <f>ROUND(SIN(PI()/6),5)</f>
         <v>0.5</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="119">
         <v>0.5</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="119">
         <f>ROUND(SINH(1),5)</f>
         <v>1.1752</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126" s="119">
         <v>1.1752</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="119" t="s">
         <v>188</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="119">
         <f>SMALL(H2:H9,3)</f>
         <v>26</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="119">
         <v>26</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="119">
         <f>SQRT(4)</f>
         <v>2</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="119">
         <v>2</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="119" t="s">
         <v>190</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="119">
         <f>STDEV(-2,0,2)</f>
         <v>2</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="119">
         <v>2</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="119" t="s">
         <v>191</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="119">
         <f>_xlfn.STDEV.P(2,4)</f>
         <v>1</v>
       </c>
-      <c r="C130" s="2">
-        <v>1</v>
-      </c>
-      <c r="D130" s="2">
+      <c r="C130" s="119">
+        <v>1</v>
+      </c>
+      <c r="D130" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="119" t="s">
         <v>192</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="119">
         <f>_xlfn.STDEV.S(2,4,6)</f>
         <v>2</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="119">
         <v>2</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="119">
         <f>STDEVA(TRUE,3,5)</f>
         <v>2</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132" s="119">
         <v>2</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="119" t="s">
         <v>194</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="119">
         <f>ROUND(STDEVP(2,5,8),2)</f>
         <v>2.4500000000000002</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="119">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="119" t="s">
         <v>195</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="119">
         <f>ROUND(STDEVPA(TRUE,4,7),2)</f>
         <v>2.4500000000000002</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="119">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="119" t="s">
         <v>196</v>
       </c>
-      <c r="B135" s="2" t="str">
+      <c r="B135" s="119" t="str">
         <f>SUBSTITUTE("SAP is best","SAP","Odoo")</f>
         <v>Odoo is best</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="119" t="s">
         <v>197</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="119">
         <f>SUM(1,2,3,4,5)</f>
         <v>15</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="119">
         <v>15</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="119" t="s">
         <v>199</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="119">
         <f>SUMIF(K2:K9,"&lt;100")</f>
         <v>52</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="119">
         <v>52</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="119" t="s">
         <v>200</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="119">
         <f>SUMIFS(H2:H9,K2:K9,"&lt;100")</f>
         <v>201</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138" s="119">
         <v>201</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="119" t="s">
         <v>201</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="119">
         <f>ROUND(TAN(PI()/4),5)</f>
         <v>1</v>
       </c>
-      <c r="C139" s="2">
-        <v>1</v>
-      </c>
-      <c r="D139" s="2">
+      <c r="C139" s="119">
+        <v>1</v>
+      </c>
+      <c r="D139" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="119" t="s">
         <v>202</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="119">
         <f>ROUND(TANH(1),5)</f>
         <v>0.76158999999999999</v>
       </c>
-      <c r="C140" s="2">
+      <c r="C140" s="119">
         <v>0.76158999999999999</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="119" t="s">
         <v>203</v>
       </c>
-      <c r="B141" s="2" t="str">
+      <c r="B141" s="119" t="str">
         <f>_xlfn.TEXTJOIN("-",TRUE,"","1","A","%")</f>
         <v>1-A-%</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="119" t="s">
         <v>204</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="119" t="s">
         <v>205</v>
       </c>
-      <c r="B142" s="21">
+      <c r="B142" s="20">
         <f>TIME(9,11,31)</f>
         <v>0.38299768518518523</v>
       </c>
-      <c r="C142" s="21">
+      <c r="C142" s="20">
         <v>0.38299768519999999</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="119">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="119" t="s">
         <v>206</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="119">
         <f>TIMEVALUE("18:00:00")</f>
         <v>0.75</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="119">
         <v>0.75</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="119">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="119" t="s">
         <v>207</v>
       </c>
-      <c r="B144" s="19">
+      <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45526</v>
-      </c>
-      <c r="D144" s="2">
+        <v>45579</v>
+      </c>
+      <c r="D144" s="119">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="119" t="s">
         <v>208</v>
       </c>
-      <c r="B145" s="2" t="str">
+      <c r="B145" s="119" t="str">
         <f>TRIM(" Jean Ticonstitutionnalise ")</f>
         <v>Jean Ticonstitutionnalise</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="119" t="s">
         <v>209</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="119">
         <f t="shared" ref="D145:D163" si="9">IF(B145=C145,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="119" t="s">
         <v>210</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="119">
         <f>TRUNC(42.42,1)</f>
         <v>42.4</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146" s="119">
         <v>42.4</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="119" t="s">
         <v>211</v>
       </c>
-      <c r="B147" s="2" t="str">
+      <c r="B147" s="119" t="str">
         <f>UPPER("grrrr !")</f>
         <v>GRRRR !</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="119" t="s">
         <v>213</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="119">
         <f>ROUND(VAR(K1:K5),5)</f>
         <v>2.9166699999999999</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148" s="119">
         <v>2.9166699999999999</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="119" t="s">
         <v>214</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="119">
         <f>ROUND(_xlfn.VAR.P(K1:K5),5)</f>
         <v>2.1875</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149" s="119">
         <v>2.1875</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A150" s="2" t="s">
+      <c r="A150" s="119" t="s">
         <v>215</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="119">
         <f>_xlfn.VAR.S(2,5,8)</f>
         <v>9</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150" s="119">
         <v>9</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A151" s="2" t="s">
+      <c r="A151" s="119" t="s">
         <v>216</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="119">
         <f>ROUND(VARA(K1:K5),5)</f>
         <v>6.7</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151" s="119">
         <v>6.7</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A152" s="2" t="s">
+      <c r="A152" s="119" t="s">
         <v>217</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="119">
         <f>ROUND(VARP(K1:K5),5)</f>
         <v>2.1875</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152" s="119">
         <v>2.1875</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A153" s="2" t="s">
+      <c r="A153" s="119" t="s">
         <v>218</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="119">
         <f>ROUND(VARPA(K1:K5),5)</f>
         <v>5.36</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C153" s="119">
         <v>5.36</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A154" s="2" t="s">
+      <c r="A154" s="119" t="s">
         <v>219</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154" s="119">
         <f>VLOOKUP("NotACheater",G1:K9,3,FALSE)</f>
         <v>252.4</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C154" s="119">
         <f>252.4</f>
         <v>252.4</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A155" s="2" t="s">
+      <c r="A155" s="119" t="s">
         <v>220</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="119">
         <f>WEEKDAY("2021-06-12")</f>
         <v>7</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155" s="119">
         <v>7</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A156" s="2" t="s">
+      <c r="A156" s="119" t="s">
         <v>221</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156" s="119">
         <f>WEEKNUM("2021-06-29")</f>
         <v>27</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C156" s="119">
         <v>27</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A157" s="2" t="s">
+      <c r="A157" s="119" t="s">
         <v>222</v>
       </c>
-      <c r="B157" s="19">
+      <c r="B157" s="18">
         <f>WORKDAY("2021-03-15",6)</f>
         <v>44278</v>
       </c>
-      <c r="C157" s="19">
+      <c r="C157" s="18">
         <v>44278</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A158" s="2" t="s">
+      <c r="A158" s="119" t="s">
         <v>223</v>
       </c>
-      <c r="B158" s="19">
+      <c r="B158" s="18">
         <f>WORKDAY.INTL("2021-03-15",6,"0111111")</f>
         <v>44312</v>
       </c>
-      <c r="C158" s="19">
+      <c r="C158" s="18">
         <v>44312</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A159" s="2" t="s">
+      <c r="A159" s="119" t="s">
         <v>224</v>
       </c>
-      <c r="B159" s="2" t="b">
+      <c r="B159" s="119" t="b">
         <f>_xlfn.XOR(FALSE,TRUE,FALSE,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C159" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D159" s="2">
+      <c r="C159" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D159" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A160" s="2" t="s">
+      <c r="A160" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160" s="119">
         <f>YEAR("2012-03-12")</f>
         <v>2012</v>
       </c>
-      <c r="C160" s="2">
+      <c r="C160" s="119">
         <v>2012</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A161" s="2" t="s">
+      <c r="A161" s="119" t="s">
         <v>226</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="119">
         <f>DELTA(1,1)</f>
         <v>1</v>
       </c>
-      <c r="C161" s="2">
-        <v>1</v>
-      </c>
-      <c r="D161" s="2">
+      <c r="C161" s="119">
+        <v>1</v>
+      </c>
+      <c r="D161" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A162" s="2" t="s">
+      <c r="A162" s="119" t="s">
         <v>227</v>
       </c>
-      <c r="B162" s="2" t="str">
+      <c r="B162" s="119" t="str">
         <f>ADDRESS(1,1,4,FALSE,"sheet!")</f>
         <v>'sheet!'!R[1]C[1]</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="119" t="s">
         <v>228</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A163" s="2" t="s">
+      <c r="A163" s="119" t="s">
         <v>229</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163" s="119">
         <f>DATEDIF("2002/01/01","2002/01/02","D")</f>
         <v>1</v>
       </c>
-      <c r="C163" s="2">
-        <v>1</v>
-      </c>
-      <c r="D163" s="2">
+      <c r="C163" s="119">
+        <v>1</v>
+      </c>
+      <c r="D163" s="119">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -10915,14 +11216,14 @@
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="109"/>
+      <c r="E1" s="125"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>234</v>
       </c>
     </row>
@@ -10931,18 +11232,18 @@
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
-      <c r="F3" s="86" t="s">
+      <c r="F3" s="85" t="s">
         <v>236</v>
       </c>
     </row>
@@ -10989,308 +11290,308 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="13.5" thickBot="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="F1" s="37"/>
-      <c r="H1" s="35" t="s">
+      <c r="F1" s="36"/>
+      <c r="H1" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="L1" s="94" t="s">
+      <c r="L1" s="93" t="s">
         <v>244</v>
       </c>
-      <c r="M1" s="37"/>
+      <c r="M1" s="36"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="86" t="s">
         <v>246</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="72" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="84" t="s">
+      <c r="J2" s="83" t="s">
         <v>250</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="M2" s="95">
+      <c r="M2" s="94">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="71" t="s">
         <v>253</v>
       </c>
-      <c r="J3" s="74" t="s">
+      <c r="J3" s="73" t="s">
         <v>254</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="M3" s="96">
+      <c r="M3" s="95">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="J4" s="85" t="s">
+      <c r="J4" s="84" t="s">
         <v>260</v>
       </c>
-      <c r="L4" s="22" t="s">
+      <c r="L4" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="M4" s="97">
+      <c r="M4" s="96">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="H5" s="71" t="s">
+      <c r="H5" s="70" t="s">
         <v>264</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="98">
+      <c r="M5" s="97">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>267</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="H6" s="70" t="s">
+      <c r="H6" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="L6" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="M6" s="99">
+      <c r="M6" s="98">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="H7" s="83" t="s">
+      <c r="H7" s="82" t="s">
         <v>273</v>
       </c>
-      <c r="L7" s="39" t="s">
+      <c r="L7" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="M7" s="101">
+      <c r="M7" s="100">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="H8" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="L8" s="39" t="s">
+      <c r="L8" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="M8" s="102">
+      <c r="M8" s="101">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="102">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="59" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="F11" s="37"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="21" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="30" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="61" t="s">
         <v>292</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="31" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="32" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="33" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="63" t="s">
         <v>298</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="F18" s="37"/>
+      <c r="F18" s="36"/>
     </row>
     <row r="19" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="38" t="s">
         <v>301</v>
       </c>
       <c r="F19" t="s">
@@ -11298,63 +11599,63 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="51.75" thickBot="1">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="64" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="104" t="s">
+      <c r="F20" s="103" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A21" s="78" t="s">
+      <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A22" s="79" t="s">
+      <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="65" t="s">
         <v>308</v>
       </c>
-      <c r="E22" s="22"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
-      <c r="E23" s="22"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
-      <c r="A24" s="81" t="s">
+      <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="66" t="s">
         <v>311</v>
       </c>
-      <c r="E24" s="22"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
     <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
     <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
     <row r="30" spans="1:6">
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
     </row>
@@ -11374,24 +11675,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
       <c r="B2">
@@ -11400,30 +11701,30 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="21">
         <v>5</v>
       </c>
       <c r="I2">
         <v>3</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="34" t="s">
         <v>324</v>
       </c>
       <c r="H3">
@@ -11437,13 +11738,13 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="34" t="s">
         <v>327</v>
       </c>
       <c r="H4">
@@ -11457,7 +11758,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
       <c r="B5" t="e">
@@ -11467,7 +11768,7 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="34" t="s">
         <v>329</v>
       </c>
       <c r="H5">
@@ -11481,16 +11782,16 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="34" t="s">
         <v>332</v>
       </c>
       <c r="H6">
@@ -11504,19 +11805,19 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="34" t="s">
         <v>336</v>
       </c>
       <c r="H7">
@@ -11530,27 +11831,27 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="21"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" thickBot="1">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
       <c r="B10">
@@ -11560,24 +11861,24 @@
         <f>0/0</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="34" t="s">
         <v>343</v>
       </c>
       <c r="H11">
@@ -11591,18 +11892,18 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45526</v>
-      </c>
-      <c r="C12" s="40">
+        <v>45579</v>
+      </c>
+      <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
         <v>40453</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="34" t="s">
         <v>345</v>
       </c>
       <c r="H12">
@@ -11616,7 +11917,7 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
       <c r="B13">
@@ -11625,7 +11926,7 @@
       <c r="C13">
         <v>5</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="34" t="s">
         <v>347</v>
       </c>
       <c r="H13">
@@ -11639,19 +11940,19 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="34" t="s">
         <v>349</v>
       </c>
       <c r="H14">
@@ -11665,13 +11966,13 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="34" t="s">
         <v>351</v>
       </c>
       <c r="H15">
@@ -11685,7 +11986,7 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
       <c r="B16">
@@ -11694,7 +11995,7 @@
       <c r="C16">
         <v>1</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="34" t="s">
         <v>353</v>
       </c>
       <c r="H16">
@@ -11708,7 +12009,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
       <c r="B17">
@@ -11717,7 +12018,7 @@
       <c r="C17">
         <v>2</v>
       </c>
-      <c r="G17" s="35" t="s">
+      <c r="G17" s="34" t="s">
         <v>355</v>
       </c>
       <c r="H17">
@@ -11731,7 +12032,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
       <c r="B18">
@@ -11740,7 +12041,7 @@
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="34" t="s">
         <v>357</v>
       </c>
       <c r="H18">
@@ -11754,7 +12055,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
       <c r="B19">
@@ -11763,7 +12064,7 @@
       <c r="C19">
         <v>0</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="34" t="s">
         <v>359</v>
       </c>
       <c r="H19">
@@ -11777,7 +12078,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
       <c r="B20">
@@ -11786,7 +12087,7 @@
       <c r="C20">
         <v>2</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="34" t="s">
         <v>361</v>
       </c>
       <c r="H20">
@@ -11800,7 +12101,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
       <c r="B21">
@@ -11809,7 +12110,7 @@
       <c r="C21">
         <v>3</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="34" t="s">
         <v>363</v>
       </c>
       <c r="H21">
@@ -11826,7 +12127,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
       <c r="B22">
@@ -11835,7 +12136,7 @@
       <c r="C22">
         <v>0</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="34" t="s">
         <v>365</v>
       </c>
       <c r="H22">
@@ -11852,7 +12153,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
       <c r="B23">
@@ -11861,7 +12162,7 @@
       <c r="C23">
         <v>2</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="34" t="s">
         <v>367</v>
       </c>
       <c r="H23">
@@ -11878,7 +12179,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
       <c r="H24">
@@ -11895,7 +12196,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
       <c r="B25">
@@ -11904,7 +12205,7 @@
       <c r="C25">
         <v>2</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="34" t="s">
         <v>370</v>
       </c>
       <c r="H25">
@@ -11921,7 +12222,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
       <c r="H26">
@@ -11941,13 +12242,13 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="34" t="s">
         <v>373</v>
       </c>
       <c r="H27">
@@ -11967,7 +12268,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
       <c r="H28">
@@ -11987,7 +12288,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="34" t="s">
         <v>375</v>
       </c>
       <c r="H29">
@@ -12007,7 +12308,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="G30" s="35" t="s">
+      <c r="G30" s="34" t="s">
         <v>376</v>
       </c>
       <c r="H30">
@@ -12027,21 +12328,21 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="13.5" thickBot="1">
-      <c r="G31" s="36" t="s">
+      <c r="G31" s="35" t="s">
         <v>377</v>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="36">
         <v>5</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="36">
         <v>3</v>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="G32" s="35" t="s">
+      <c r="G32" s="34" t="s">
         <v>378</v>
       </c>
       <c r="H32">
@@ -12055,7 +12356,7 @@
       </c>
     </row>
     <row r="33" spans="7:10">
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="34" t="s">
         <v>379</v>
       </c>
       <c r="H33">
@@ -12069,7 +12370,7 @@
       </c>
     </row>
     <row r="34" spans="7:10">
-      <c r="G34" s="35" t="s">
+      <c r="G34" s="34" t="s">
         <v>380</v>
       </c>
       <c r="H34">
@@ -12083,7 +12384,7 @@
       </c>
     </row>
     <row r="35" spans="7:10">
-      <c r="G35" s="35" t="s">
+      <c r="G35" s="34" t="s">
         <v>381</v>
       </c>
       <c r="H35">
@@ -12097,7 +12398,7 @@
       </c>
     </row>
     <row r="36" spans="7:10">
-      <c r="G36" s="35" t="s">
+      <c r="G36" s="34" t="s">
         <v>382</v>
       </c>
       <c r="H36">
@@ -12111,7 +12412,7 @@
       </c>
     </row>
     <row r="37" spans="7:10">
-      <c r="G37" s="35" t="s">
+      <c r="G37" s="34" t="s">
         <v>383</v>
       </c>
       <c r="H37">
@@ -12125,7 +12426,7 @@
       </c>
     </row>
     <row r="39" spans="7:10">
-      <c r="G39" s="35"/>
+      <c r="G39" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
@@ -12705,122 +13006,122 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="17" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="119">
         <v>26</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="119">
         <v>5</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="119">
         <f>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</f>
         <v>31</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="119">
         <f>SUM(Table3[Rank])</f>
         <v>12</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="119">
         <f>SUM(Table3[[#All],[Rank]])</f>
         <v>24</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="119">
         <f>Table3[[#Totals],[Rank]]</f>
         <v>12</v>
       </c>
-      <c r="J4" s="2" t="str">
+      <c r="J4" s="119" t="str">
         <f>Table3[[#Headers],[Rank]]</f>
         <v>Rank</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="119">
         <v>13</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="119">
         <v>7</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="119">
         <f>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</f>
         <v>20</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="119">
         <f>SUM(Table3[Rank])</f>
         <v>12</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="119">
         <f>SUM(Table3[[#All],[Rank]])</f>
         <v>24</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="119">
         <f>Table3[[#Totals],[Rank]]</f>
         <v>12</v>
       </c>
-      <c r="J5" s="2" t="str">
+      <c r="J5" s="119" t="str">
         <f>Table3[[#Headers],[Rank]]</f>
         <v>Rank</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="119" t="s">
         <v>391</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="119">
         <f>SUBTOTAL(109,Table3[Age])</f>
         <v>39</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="119">
         <f>SUBTOTAL(109,Table3[Rank])</f>
         <v>12</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="119">
         <f>SUBTOTAL(109,Table3[Rank+Age =E4+D4])</f>
         <v>51</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="119">
         <f>SUBTOTAL(109,Table3[Data =SUM(E4:E5)])</f>
         <v>24</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="119">
         <f>SUBTOTAL(109,Table3[All =SUM(E3:E6)])</f>
         <v>48</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="119">
         <f>SUBTOTAL(109,Table3[Totals =E6])</f>
         <v>24</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="119">
         <f>SUBTOTAL(109,Table3[Headers =E3])</f>
         <v>0</v>
       </c>
@@ -13041,37 +13342,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="92" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="119"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="90" t="s">
+      <c r="A3" s="119"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="89" t="s">
         <v>408</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="89" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="90" t="s">
+      <c r="A4" s="119"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="89" t="s">
         <v>410</v>
       </c>
       <c r="D4">
@@ -13103,9 +13404,9 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="91" t="s">
+      <c r="A5" s="119"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="90" t="s">
         <v>55</v>
       </c>
       <c r="K5">
@@ -13116,9 +13417,9 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="92">
+      <c r="A6" s="119"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="91">
         <v>256018</v>
       </c>
       <c r="K6">
@@ -13129,9 +13430,9 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="91" t="s">
+      <c r="A7" s="119"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="90" t="s">
         <v>46</v>
       </c>
       <c r="E7">
@@ -13142,9 +13443,9 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="92">
+      <c r="A8" s="119"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="91">
         <v>110120.5</v>
       </c>
       <c r="E8">
@@ -13155,9 +13456,9 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="91" t="s">
+      <c r="A9" s="119"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="90" t="s">
         <v>42</v>
       </c>
       <c r="G9">
@@ -13168,9 +13469,9 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="92">
+      <c r="A10" s="119"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="91">
         <v>25618</v>
       </c>
       <c r="G10">
@@ -13181,7 +13482,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="C11" s="91" t="s">
+      <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
       <c r="F11">
@@ -13192,7 +13493,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="C12" s="92">
+      <c r="C12" s="91">
         <v>23000</v>
       </c>
       <c r="F12">
@@ -13203,7 +13504,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
       <c r="D13">
@@ -13214,7 +13515,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="C14" s="92">
+      <c r="C14" s="91">
         <v>2</v>
       </c>
       <c r="D14">
@@ -13225,7 +13526,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="C15" s="91" t="s">
+      <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I15">
@@ -13236,7 +13537,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="C16" s="92">
+      <c r="C16" s="91">
         <v>50024</v>
       </c>
       <c r="I16">
@@ -13247,7 +13548,7 @@
       </c>
     </row>
     <row r="17" spans="3:12">
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
       <c r="H17">
@@ -13258,7 +13559,7 @@
       </c>
     </row>
     <row r="18" spans="3:12">
-      <c r="C18" s="92">
+      <c r="C18" s="91">
         <v>189576</v>
       </c>
       <c r="H18">
@@ -13269,7 +13570,7 @@
       </c>
     </row>
     <row r="19" spans="3:12">
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
       <c r="J19">
@@ -13280,7 +13581,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="92">
+      <c r="C20" s="91">
         <v>5000</v>
       </c>
       <c r="J20">
@@ -13291,7 +13592,7 @@
       </c>
     </row>
     <row r="21" spans="3:12">
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="90" t="s">
         <v>411</v>
       </c>
       <c r="D21">
@@ -13346,7 +13647,7 @@
       <c r="A2" t="s">
         <v>413</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="119"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
@@ -13370,7 +13671,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:1" ht="38.25">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="99" t="s">
         <v>416</v>
       </c>
     </row>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EAB923-A1B3-42FF-B544-1E3FCDFFEEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2A2F833-F20C-4974-839C-93827D860F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,13 +26,14 @@
     <sheet name="jestFreezePane" sheetId="14" r:id="rId11"/>
     <sheet name="jestImages" sheetId="15" r:id="rId12"/>
     <sheet name="jestOneCellAnchor" sheetId="16" r:id="rId13"/>
+    <sheet name="jestDataValidations" sheetId="17" r:id="rId14"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId14"/>
+    <externalReference r:id="rId15"/>
   </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId15"/>
+    <pivotCache cacheId="5374" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,6 +46,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -52,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="422">
   <si>
     <t>CF =42</t>
   </si>
@@ -1304,22 +1307,36 @@
   <si>
     <t>This text have
  a newLine</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>test123</t>
+  </si>
+  <si>
+    <t>hola</t>
+  </si>
+  <si>
+    <t>A1234556</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="167" formatCode="[$$-409]#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="[$₪-40D]\ #,##0"/>
-    <numFmt numFmtId="169" formatCode="#,##0&quot; EUR €&quot;"/>
-    <numFmt numFmtId="170" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="[$₪-40D]\ #,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
+    <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1478,7 +1495,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1653,8 +1670,14 @@
         </stop>
       </gradientFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -2003,18 +2026,95 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2065,10 +2165,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="19" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2182,14 +2282,14 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2197,6 +2297,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2209,13 +2312,180 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="28" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="28" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2622,157 +2892,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -2816,7 +2935,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2872,7 +2991,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3194,7 +3313,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3227,7 +3346,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3298,7 +3417,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3331,7 +3450,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3375,7 +3494,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3403,7 +3522,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3417,7 +3536,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3730,7 +3849,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3792,7 +3911,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3820,7 +3939,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3849,7 +3968,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4438,7 +4557,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4467,7 +4586,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4804,7 +4923,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4833,7 +4952,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5016,7 +5135,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5075,7 +5194,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5103,7 +5222,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5132,7 +5251,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5449,7 +5568,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5511,7 +5630,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5539,7 +5658,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5568,7 +5687,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5612,9 +5731,6 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1F77B4"/>
-            </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
                 <a:srgbClr val="1F77B4"/>
@@ -5854,7 +5970,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5916,7 +6032,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5944,7 +6060,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5973,7 +6089,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -6271,7 +6387,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="344680958"/>
@@ -6347,7 +6463,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="998664793"/>
@@ -6370,7 +6486,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -6957,6 +7073,9 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
@@ -6992,6 +7111,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E90E321-E964-46C8-9CE7-DEE1186146D9}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7031,6 +7153,9 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CC27214-40A9-4FF9-BB37-40F876B2768B}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1E90E321-E964-46C8-9CE7-DEE1186146D9}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
@@ -7069,6 +7194,9 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5685A00-859E-4641-A529-E7042819F3BF}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6CC27214-40A9-4FF9-BB37-40F876B2768B}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
@@ -7106,6 +7234,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2B20B98-FA84-44C9-8DBB-5852658E9967}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A5685A00-859E-4641-A529-E7042819F3BF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7384,7 +7515,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="5374" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -7534,7 +7665,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7546,22 +7677,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7671,7 +7802,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7971,399 +8102,628 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="26" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22"/>
+    <row r="1" spans="1:12" ht="38.25" customHeight="1">
+      <c r="A1" s="21"/>
+      <c r="B1" s="105"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="B2" s="23" t="s">
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="104" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.15">
+      <c r="A2" s="105"/>
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="104">
         <v>5</v>
       </c>
-      <c r="H2" s="105" t="s">
+      <c r="H2" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="106"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F3" s="5" t="s">
+      <c r="I2" s="126"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="105"/>
+    </row>
+    <row r="3" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A3" s="105"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="104">
         <v>8</v>
       </c>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="6"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="5"/>
       <c r="K3" s="107">
         <v>5</v>
       </c>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A4" s="105"/>
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="104">
         <v>12.4</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="104">
         <v>9</v>
       </c>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="6"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="5"/>
       <c r="K4" s="108"/>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="2">
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A5" s="105"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="104">
         <v>42</v>
       </c>
-      <c r="G5" s="2">
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="104">
         <v>15</v>
       </c>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="6"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="108"/>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G6" s="2">
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A6" s="105"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="104">
         <v>22</v>
       </c>
-      <c r="J6" s="6"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="5"/>
       <c r="K6" s="108"/>
-      <c r="L6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="2">
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A7" s="105"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="104">
         <v>3</v>
       </c>
-      <c r="J7" s="6"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="5"/>
       <c r="K7" s="108"/>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="2">
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A8" s="105"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="104">
         <v>30</v>
       </c>
-      <c r="J8" s="6"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="5"/>
       <c r="K8" s="109"/>
-      <c r="L8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="10" t="s">
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A9" s="105"/>
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="104">
         <f>SUM(C4:C5)</f>
         <v>54.4</v>
       </c>
-      <c r="K9" s="11"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="2">
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="105"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A10" s="105"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="104">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="104" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="2">
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A11" s="105"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="104">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="2">
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A12" s="105"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="104">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="104" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G13" s="2">
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A13" s="105"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="104">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A14" s="105"/>
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="str">
+      <c r="C14" s="104" t="str">
         <f ca="1">C14</f>
         <v>#CYCLE</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="2" t="s">
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A15" s="105"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="104" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="2" t="str">
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A16" s="105"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="104" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="2" t="s">
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="105"/>
+    </row>
+    <row r="17" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A17" s="105"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="104" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="2" t="s">
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="105"/>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A18" s="105"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="104" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7" t="s">
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A19" s="105"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+    </row>
+    <row r="20" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A20" s="105"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="D20" s="105"/>
+      <c r="E20" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="13" t="s">
+      <c r="F20" s="5"/>
+      <c r="G20" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="H20" s="6"/>
+      <c r="I20" s="105"/>
+    </row>
+    <row r="21" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <f>jestCharts!B2</f>
         <v>0</v>
       </c>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+    </row>
+    <row r="23" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="16">
+      <c r="B23" s="105"/>
+      <c r="C23" s="15">
         <v>0.43</v>
       </c>
-      <c r="H23" s="2">
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="104">
         <v>0</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="104">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="17">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A24" s="105"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="16">
         <v>10</v>
       </c>
-      <c r="H24" s="2">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="17">
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="104">
+        <v>1</v>
+      </c>
+      <c r="I24" s="104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A25" s="105"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
-      <c r="H25" s="2">
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="104">
         <v>2</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="104">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A26" s="105"/>
+      <c r="B26" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="2">
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="104">
         <v>3</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="104">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A27" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="104">
         <v>12</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="104">
         <v>24</v>
       </c>
-      <c r="H27" s="2">
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="104">
         <v>4</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="104">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A28" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="104">
         <v>48</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="104">
         <v>12</v>
       </c>
-      <c r="H28" s="2">
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="104">
         <v>5</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="104">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A29" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="104">
         <v>45</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="104">
         <v>27</v>
       </c>
-      <c r="H29" s="2">
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="104">
         <v>6</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="104">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A30" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="2">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="104">
+        <v>1</v>
+      </c>
+      <c r="C30" s="104">
         <v>9</v>
       </c>
-      <c r="H30" s="2">
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="104">
         <v>7</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="104">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A31" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="104">
         <v>25</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="104">
         <v>45</v>
       </c>
-      <c r="H31" s="2">
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="104">
         <v>8</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="104">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A32" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="104">
         <v>31</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="104">
         <v>17</v>
       </c>
-      <c r="H32" s="2">
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="104">
         <v>9</v>
       </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="I32" s="104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A33" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="104">
         <v>20</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="104">
         <v>43</v>
       </c>
-      <c r="H33" s="2">
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="104">
         <v>10</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="104">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A34" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="104">
         <v>19</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="104">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A35" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="104">
         <v>16</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="104">
         <v>16</v>
       </c>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8371,7 +8731,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8416,7 +8776,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.9"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8425,7 +8785,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="13.9"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8434,10 +8794,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="65.109375" customWidth="1"/>
-    <col min="2" max="26" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="65.140625" customWidth="1"/>
+    <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8451,10 +8811,180 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="111">
+        <v>4</v>
+      </c>
+      <c r="B1" s="112">
+        <v>99.5</v>
+      </c>
+      <c r="C1" s="112">
+        <v>1</v>
+      </c>
+      <c r="D1" s="113">
+        <v>45575</v>
+      </c>
+      <c r="E1" s="114">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F1" s="114" t="s">
+        <v>417</v>
+      </c>
+      <c r="G1" s="113">
+        <v>45292</v>
+      </c>
+      <c r="H1" s="115">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="116">
+        <v>3</v>
+      </c>
+      <c r="B2" s="117">
+        <v>40</v>
+      </c>
+      <c r="C2" s="117">
+        <v>2</v>
+      </c>
+      <c r="D2" s="118">
+        <v>45576</v>
+      </c>
+      <c r="E2" s="119">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="F2" s="119" t="s">
+        <v>418</v>
+      </c>
+      <c r="G2" s="118">
+        <v>45231</v>
+      </c>
+      <c r="H2" s="120" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="116">
+        <v>9</v>
+      </c>
+      <c r="B3" s="117">
+        <v>0</v>
+      </c>
+      <c r="C3" s="117">
+        <v>3</v>
+      </c>
+      <c r="D3" s="118">
+        <v>45574</v>
+      </c>
+      <c r="E3" s="119">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F3" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="G3" s="118">
+        <v>45325</v>
+      </c>
+      <c r="H3" s="120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="116">
+        <v>5</v>
+      </c>
+      <c r="B4" s="117">
+        <v>120</v>
+      </c>
+      <c r="C4" s="117">
+        <v>4</v>
+      </c>
+      <c r="D4" s="118">
+        <v>45573</v>
+      </c>
+      <c r="E4" s="119">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="117" t="s">
+        <v>420</v>
+      </c>
+      <c r="G4" s="118">
+        <v>45084</v>
+      </c>
+      <c r="H4" s="120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="121">
+        <v>7</v>
+      </c>
+      <c r="B5" s="122">
+        <v>12</v>
+      </c>
+      <c r="C5" s="122">
+        <v>5</v>
+      </c>
+      <c r="D5" s="123">
+        <v>45566</v>
+      </c>
+      <c r="E5" s="124">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="F5" s="122" t="s">
+        <v>421</v>
+      </c>
+      <c r="G5" s="123">
+        <v>45420</v>
+      </c>
+      <c r="H5" s="125" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A5" xr:uid="{B9309757-E2F4-49A1-880B-2F47F04364D6}">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B5" xr:uid="{7B68D26A-1B1D-4327-906D-753CF39E281C}">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C5" xr:uid="{1150F523-8C6C-482F-8738-910EECBB2A28}">
+      <formula1>$C$1:$C$5</formula1>
+    </dataValidation>
+    <dataValidation type="date" errorStyle="warning" operator="notEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D5" xr:uid="{54DB89C3-BBA6-4A2D-B5BB-AC6E00AEE4DA}">
+      <formula1>45575</formula1>
+    </dataValidation>
+    <dataValidation type="time" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E5" xr:uid="{EF20CA15-C64F-4A4E-82C5-8291CBEAEB85}">
+      <formula1>0.625</formula1>
+      <formula2>0.75</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F5" xr:uid="{C9CA9AA5-9067-42E1-AC95-BEC22F4C4C16}">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H5" xr:uid="{B1282AE0-81A7-4F83-934D-520FB78380E5}">
+      <formula1>ISNUMBER(H1)</formula1>
+    </dataValidation>
+    <dataValidation type="date" errorStyle="warning" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G5" xr:uid="{A800671A-DD3E-492C-AC04-70928416B8CA}">
+      <formula1>45261</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8464,2867 +8994,3014 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="26" width="13.6640625" customWidth="1"/>
+    <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A1" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="2">
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="104">
         <v>0.1</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="O1" s="105"/>
+      <c r="P1" s="17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A2" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="104">
         <f>ABS(-5.5)</f>
         <v>5.5</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="104">
         <v>5.5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="104">
         <f t="shared" ref="D2:D33" si="0">IF(B2=C2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="104">
         <v>26</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="104">
         <v>1204.7</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="104">
         <v>25618</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="104">
         <v>5</v>
       </c>
-      <c r="N2" s="2">
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="104">
         <v>0.2</v>
       </c>
-      <c r="P2">
+      <c r="O2" s="105"/>
+      <c r="P2" s="105">
         <f>SUM(H2, I$2)</f>
         <v>1230.7</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="105">
         <f>SUM(H2, $I2)</f>
         <v>1230.7</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="105">
         <f>SUM(H2, $I$2)</f>
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A3" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="104">
         <f>ACOS(1)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="104">
         <v>0</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="104">
         <v>13</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="104">
         <v>500.9</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="104">
         <v>23000</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="104">
         <v>7</v>
       </c>
-      <c r="N3" s="2">
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="104">
         <v>0.4</v>
       </c>
-      <c r="P3">
+      <c r="O3" s="105"/>
+      <c r="P3" s="105">
         <f t="shared" ref="P3:P6" si="1">SUM(H3, I$2)</f>
         <v>1217.7</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="105">
         <f t="shared" ref="Q3:Q6" si="2">SUM(H3, $I3)</f>
         <v>513.9</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="105">
         <f t="shared" ref="R3:R6" si="3">SUM(H3, $I$2)</f>
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A4" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="104">
         <f>ROUND(ACOSH(2),5)</f>
         <v>1.3169599999999999</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="104">
         <v>1.3169599999999999</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="104">
         <v>26</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="104">
         <v>252.4</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="104">
         <v>110120.5</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="104">
         <v>3</v>
       </c>
-      <c r="N4" s="2">
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="104">
         <v>0.5</v>
       </c>
-      <c r="P4">
+      <c r="O4" s="105"/>
+      <c r="P4" s="105">
         <f t="shared" si="1"/>
         <v>1230.7</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="105">
         <f t="shared" si="2"/>
         <v>278.39999999999998</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="105">
         <f t="shared" si="3"/>
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A5" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="104">
         <f>ROUND(_xlfn.ACOT(1),5)</f>
         <v>0.78539999999999999</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="104">
         <v>0.78539999999999999</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="104">
         <v>42</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="104">
         <v>4701.3</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="104">
         <v>50024</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="104">
         <v>4</v>
       </c>
-      <c r="N5" s="2">
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="104">
         <v>0.6</v>
       </c>
-      <c r="P5">
+      <c r="O5" s="105"/>
+      <c r="P5" s="105">
         <f t="shared" si="1"/>
         <v>1246.7</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="105">
         <f t="shared" si="2"/>
         <v>4743.3</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="105">
         <f t="shared" si="3"/>
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A6" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="104">
         <f>ROUND(_xlfn.ACOTH(2),5)</f>
         <v>0.54930999999999996</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="104">
         <v>0.54930999999999996</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="104">
         <f>IF(B6=C6,1,0)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="104">
         <v>9</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="104">
         <v>12.1</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="104">
         <v>2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="104">
         <v>1000</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="P6">
+      <c r="O6" s="105"/>
+      <c r="P6" s="105">
         <f t="shared" si="1"/>
         <v>1213.7</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="105">
         <f t="shared" si="2"/>
         <v>21.1</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="105">
         <f t="shared" si="3"/>
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A7" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="2" t="b">
+      <c r="B7" s="104" t="b">
         <f>AND(TRUE,TRUE)</f>
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="104">
         <v>27</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="104">
         <v>4000</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="104">
         <v>189576</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="104">
         <v>2</v>
       </c>
-      <c r="N7" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="L7" s="105"/>
+      <c r="M7" s="105"/>
+      <c r="N7" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="105"/>
+      <c r="P7" s="105"/>
+      <c r="Q7" s="105"/>
+      <c r="R7" s="105"/>
+    </row>
+    <row r="8" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="104">
         <f>ROUND(ASIN(0.5),5)</f>
         <v>0.52359999999999995</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="104">
         <v>0.52359999999999995</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="104">
         <v>30</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="104">
         <v>12052</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="104">
         <v>256018</v>
       </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="b">
+      <c r="K8" s="104">
+        <v>1</v>
+      </c>
+      <c r="L8" s="105"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="104" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="O8" s="105"/>
+      <c r="P8" s="105"/>
+      <c r="Q8" s="105"/>
+      <c r="R8" s="105"/>
+    </row>
+    <row r="9" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A9" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="104">
         <f>ROUND(ASINH(2),5)</f>
         <v>1.44364</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="104">
         <v>1.44364</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="104">
         <v>37</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="104">
         <v>4890.1000000000004</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="104">
         <v>5000</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="104">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="105"/>
+    </row>
+    <row r="10" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A10" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="104">
         <f>ROUND(ATAN(1),5)</f>
         <v>0.78539999999999999</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="104">
         <v>0.78539999999999999</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="105"/>
+      <c r="P10" s="105"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="105"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A11" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="104">
         <f>ROUND(ATAN2(-1,0),5)</f>
         <v>3.1415899999999999</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="104">
         <v>3.1415899999999999</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="104" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="105"/>
+      <c r="O11" s="105"/>
+      <c r="P11" s="105"/>
+      <c r="Q11" s="105"/>
+      <c r="R11" s="105"/>
+    </row>
+    <row r="12" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A12" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="104">
         <f>ROUND(ATANH(0.7),5)</f>
         <v>0.86729999999999996</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="104">
         <v>0.86729999999999996</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="L12" s="105"/>
+      <c r="M12" s="105"/>
+      <c r="N12" s="105"/>
+      <c r="O12" s="105"/>
+      <c r="P12" s="105"/>
+      <c r="Q12" s="105"/>
+      <c r="R12" s="105"/>
+    </row>
+    <row r="13" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A13" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="104">
         <f>ROUND(AVEDEV(I2:I9),5)</f>
         <v>2959.1624999999999</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="104">
         <v>2959.1624999999999</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="104" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
+      <c r="N13" s="105"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="105"/>
+      <c r="Q13" s="105"/>
+      <c r="R13" s="105"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A14" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="104">
         <f>ROUND(AVERAGE(H2:H9),5)</f>
         <v>26.25</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="104">
         <v>26.25</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="105"/>
+      <c r="O14" s="105"/>
+      <c r="P14" s="105"/>
+      <c r="Q14" s="105"/>
+      <c r="R14" s="105"/>
+    </row>
+    <row r="15" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A15" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="104">
         <f>AVERAGEA(G2:H9)</f>
         <v>13.125</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="104">
         <v>13.125</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="105"/>
+      <c r="N15" s="105"/>
+      <c r="O15" s="105"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="105"/>
+      <c r="R15" s="105"/>
+    </row>
+    <row r="16" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A16" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="104">
         <f>ROUND(AVERAGEIF(J2:J9,"&gt;150000"),5)</f>
         <v>222797</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="104">
         <v>222797</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="105"/>
+      <c r="M16" s="105"/>
+      <c r="N16" s="105"/>
+      <c r="O16" s="105"/>
+      <c r="P16" s="105"/>
+      <c r="Q16" s="105"/>
+      <c r="R16" s="105"/>
+    </row>
+    <row r="17" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A17" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="104">
         <f>ROUND(AVERAGEIFS(I2:I9,H2:H9,"&gt;=30",K2:K9,"&lt;10"),5)</f>
         <v>8376.65</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="104">
         <v>8376.65</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A18" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="104">
         <f>CEILING(20.4,1)</f>
         <v>21</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="104">
         <v>21</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A19" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="104">
         <f>_xlfn.CEILING.MATH(-5.5,1,0)</f>
         <v>-5</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="104">
         <v>-5</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A20" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="104">
         <f>_xlfn.CEILING.PRECISE(230,100)</f>
         <v>300</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="104">
         <v>300</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A21" s="104" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="2" t="str">
+      <c r="B21" s="104" t="str">
         <f>CHAR(74)</f>
         <v>J</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A22" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="104">
         <f>COLUMN(C4)</f>
         <v>3</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="104">
         <v>3</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A23" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="104">
         <f>COLUMNS(A5:D12)</f>
         <v>4</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="104">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A24" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="2" t="str">
+      <c r="B24" s="104" t="str">
         <f>_xlfn.CONCAT(1,23)</f>
         <v>123</v>
       </c>
-      <c r="C24" s="2" t="str">
+      <c r="C24" s="104" t="str">
         <f>"123"</f>
         <v>123</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A25" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="2" t="str">
+      <c r="B25" s="104" t="str">
         <f>CONCATENATE("BUT, ","MICHEL")</f>
         <v>BUT, MICHEL</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A26" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="104">
         <f>ROUND(COS(PI()/3),2)</f>
         <v>0.5</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="104">
         <v>0.5</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A27" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="104">
         <f>ROUND(COSH(2),5)</f>
         <v>3.7622</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="104">
         <v>3.7622</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A28" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="104">
         <f>ROUND(_xlfn.COT(PI()/6),5)</f>
         <v>1.7320500000000001</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="104">
         <f>ROUND(SQRT(3),5)</f>
         <v>1.7320500000000001</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A29" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="104">
         <f>ROUND(_xlfn.COTH(0.5),5)</f>
         <v>2.1639499999999998</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="104">
         <v>2.1639499999999998</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A30" s="104" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="104">
         <f>COUNT(1,"a","5","2021-03-14")</f>
         <v>3</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="104">
         <v>2</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="104">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A31" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="104">
         <f>COUNTA(1,"a","5","2021-03-14")</f>
         <v>4</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="104">
         <v>4</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A32" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="104">
         <f>COUNTBLANK(F1:G1)</f>
         <v>1</v>
       </c>
-      <c r="C32" s="2">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="C32" s="104">
+        <v>1</v>
+      </c>
+      <c r="D32" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A33" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="104">
         <f>COUNTIF(H2:H9,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="104">
         <v>2</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="104">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A34" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="104">
         <f>COUNTIFS(H2:H9,"&gt;25",K2:K9,"&lt;4")</f>
         <v>3</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="104">
         <v>3</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="104">
         <f t="shared" ref="D34:D65" si="4">IF(B34=C34,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A35" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="104">
         <f>ROUND(COVAR(H2:H9,K2:K9),5)</f>
         <v>-2119.25</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="104">
         <v>-2119.25</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A36" s="104" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="104">
         <f>ROUND(_xlfn.COVARIANCE.P(K2:K9,H2:H9),5)</f>
         <v>-2119.25</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="104">
         <v>-2119.25</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A37" s="104" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="104">
         <f>ROUND(_xlfn.COVARIANCE.P(I2:I9,J2:J9),5)</f>
         <v>237217364.71641001</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="104">
         <v>237217364.71641001</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A38" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="104">
         <f>ROUND(_xlfn.CSC(PI()/4),5)</f>
         <v>1.41421</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="104">
         <f>ROUND(SQRT(2),5)</f>
         <v>1.41421</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A39" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="104">
         <f>ROUND(_xlfn.CSCH(PI()/3),5)</f>
         <v>0.80040999999999995</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="104">
         <v>0.80040999999999995</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A40" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="18">
         <f>DATE(2020,5,25)</f>
         <v>43976</v>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="18">
         <v>43976</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A41" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="104">
         <f>DATEVALUE("1969-08-15")</f>
         <v>25430</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="104">
         <v>25430</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A42" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="104">
         <f>ROUND(DAVERAGE(G1:K9,"Tot. Score",J12:J13),5)</f>
         <v>151434.625</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="104">
         <v>151434.625</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A43" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="104">
         <f>DAY("2020-03-17")</f>
         <v>17</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="104">
         <v>17</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A44" s="104" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="104">
         <f>_xlfn.DAYS("2022-03-17","2021-03-17")</f>
         <v>365</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="104">
         <v>365</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A45" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="104">
         <f>DCOUNT(G1:K9,"Name",H12:H13)</f>
         <v>0</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="104">
         <v>0</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A46" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="104">
         <f>DCOUNTA(G1:K9,"Name",H12:H13)</f>
         <v>3</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="104">
         <v>3</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A47" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="104">
         <f>_xlfn.DECIMAL(20,16)</f>
         <v>32</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="104">
         <v>32</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A48" s="104" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="104">
         <f>DEGREES(PI()/4)</f>
         <v>45</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="104">
         <v>45</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A49" s="104" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="104">
         <f>DGET(G1:K9,"Hours Played",G12:G13)</f>
         <v>252.4</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="104">
         <v>252.4</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A50" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="104">
         <f>DMAX(G1:K9,"Tot. Score",I12:I13)</f>
         <v>189576</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="104">
         <f>J7</f>
         <v>189576</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A51" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="104">
         <f>DMIN(G1:K9,"Tot. Score",H12:H13)</f>
         <v>5000</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="104">
         <f>J9</f>
         <v>5000</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A52" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="104">
         <f>DPRODUCT(G1:K9,"Age",K12:K13)</f>
         <v>333</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="104">
         <v>333</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A53" s="104" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="104">
         <f>ROUND(DSTDEV(G1:K9,"Age",H12:H13),5)</f>
         <v>6.0277099999999999</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="104">
         <v>6.0277099999999999</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A54" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="104">
         <f>ROUND(DSTDEVP(G1:K9,"Age",H12:H13),5)</f>
         <v>4.9216100000000003</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="104">
         <v>4.9216100000000003</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A55" s="104" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="104">
         <f>DSUM(G1:K9,"Age",I12:I13)</f>
         <v>101</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="104">
         <v>101</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A56" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="104">
         <f>ROUND(DVAR(G1:K9,"Hours Played",H12:H13),5)</f>
         <v>17560207.923330002</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="104">
         <v>17560207.923330002</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A57" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="104">
         <f>ROUND(DVARP(G1:K9,"Hours Played",H12:H13),5)</f>
         <v>11706805.28222</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="104">
         <v>11706805.28222</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A58" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="18">
         <f>EDATE("1969-07-22",-2)</f>
         <v>25345</v>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="18">
         <v>25345</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A59" s="104" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="18">
         <f>EOMONTH("2020-07-21",1)</f>
         <v>44074</v>
       </c>
-      <c r="C59" s="19">
+      <c r="C59" s="18">
         <v>44074</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A60" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="2" t="b">
+      <c r="B60" s="104" t="b">
         <f>EXACT("AbsSdf%","AbsSdf%")</f>
         <v>1</v>
       </c>
-      <c r="C60" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="C60" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A61" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="104">
         <f>ROUND(EXP(4),5)</f>
         <v>54.598149999999997</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="104">
         <v>54.598149999999997</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A62" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="104">
         <f>FIND("A","qbdahbaazo A")</f>
         <v>12</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="104">
         <v>12</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A63" s="104" t="s">
         <v>118</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="104">
         <f>FLOOR(5.5,2)</f>
         <v>4</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="104">
         <v>4</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A64" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="104">
         <f>_xlfn.FLOOR.MATH(-5.55,2,1)</f>
         <v>-4</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="104">
         <v>-4</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A65" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="104">
         <f>_xlfn.FLOOR.PRECISE(199,100)</f>
         <v>100</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="104">
         <v>100</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="104">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A66" s="104" t="s">
         <v>121</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="104">
         <f>HLOOKUP("Tot. Score",H1:K9,4,FALSE)</f>
         <v>110120.5</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="104">
         <v>110120.5</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="104">
         <f t="shared" ref="D66:D97" si="5">IF(B66=C66,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A67" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="104">
         <f>HOUR("02:14:56")</f>
         <v>2</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="104">
         <v>2</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A68" s="104" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="2" t="str">
+      <c r="B68" s="104" t="str">
         <f>IF(TRUE,"TABOURET","JAMBON")</f>
         <v>TABOURET</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="104" t="s">
         <v>124</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A69" s="104" t="s">
         <v>125</v>
       </c>
-      <c r="B69" s="2" t="str">
+      <c r="B69" s="104" t="str">
         <f>IFERROR(0/0,"no diving by zero.")</f>
         <v>no diving by zero.</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="104" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A70" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="B70" s="2" t="str">
+      <c r="B70" s="104" t="str">
         <f>_xlfn.IFS($H2&gt;$H3,"first player is older",$H3&gt;$H2,"second player is older")</f>
         <v>first player is older</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="104" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A71" s="104" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="2" t="b">
+      <c r="B71" s="104" t="b">
         <f>ISERROR(0/0)</f>
         <v>1</v>
       </c>
-      <c r="C71" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="C71" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A72" s="104" t="s">
         <v>130</v>
       </c>
-      <c r="B72" s="2" t="b">
+      <c r="B72" s="104" t="b">
         <f>ISEVEN(3)</f>
         <v>0</v>
       </c>
-      <c r="C72" s="2" t="b">
+      <c r="C72" s="104" t="b">
         <v>0</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A73" s="104" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="2" t="b">
+      <c r="B73" s="104" t="b">
         <f>ISLOGICAL("TRUE")</f>
         <v>0</v>
       </c>
-      <c r="C73" s="2" t="b">
+      <c r="C73" s="104" t="b">
         <v>0</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A74" s="104" t="s">
         <v>132</v>
       </c>
-      <c r="B74" s="2" t="b">
+      <c r="B74" s="104" t="b">
         <f>ISNONTEXT(TRUE)</f>
         <v>1</v>
       </c>
-      <c r="C74" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D74" s="2">
+      <c r="C74" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A75" s="104" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="2" t="b">
+      <c r="B75" s="104" t="b">
         <f>ISNUMBER(1231.5)</f>
         <v>1</v>
       </c>
-      <c r="C75" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2">
+      <c r="C75" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A76" s="104" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="104">
         <f>ISO.CEILING(-7.89)</f>
         <v>-7</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="104">
         <v>-7</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A77" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="B77" s="2" t="b">
+      <c r="B77" s="104" t="b">
         <f>ISODD(4)</f>
         <v>0</v>
       </c>
-      <c r="C77" s="2" t="b">
+      <c r="C77" s="104" t="b">
         <v>0</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A78" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="104">
         <f>_xlfn.ISOWEEKNUM("2016-01-03")</f>
         <v>53</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="104">
         <v>53</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A79" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="B79" s="2" t="b">
+      <c r="B79" s="104" t="b">
         <f>ISTEXT("123")</f>
         <v>1</v>
       </c>
-      <c r="C79" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
+      <c r="C79" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A80" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="104">
         <f>LARGE(H2:H9,3)</f>
         <v>30</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="104">
         <v>30</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A81" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="B81" s="2" t="str">
+      <c r="B81" s="104" t="str">
         <f>LEFT("Mich",4)</f>
         <v>Mich</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A82" s="104" t="s">
         <v>141</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="104">
         <f>LEN("anticonstitutionnellement")</f>
         <v>25</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="104">
         <v>25</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A83" s="104" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="104">
         <f>ROUND(LN(2),5)</f>
         <v>0.69315000000000004</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="104">
         <v>0.69315000000000004</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A84" s="104" t="s">
         <v>143</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="104">
         <f>LOOKUP(23000,H3:J3,H5:J5)</f>
         <v>50024</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="104">
         <v>50024</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A85" s="104" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="2" t="str">
+      <c r="B85" s="104" t="str">
         <f>LOWER("オAドB")</f>
         <v>オaドb</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="104" t="s">
         <v>145</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A86" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="104">
         <f>MATCH(42,H2:H9,0)</f>
         <v>4</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="104">
         <v>4</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A87" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="104">
         <f>MAX(N1:N8)</f>
         <v>0.6</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="104">
         <v>0.6</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A88" s="104" t="s">
         <v>148</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="104">
         <f>MAXA(N1:N8)</f>
         <v>1</v>
       </c>
-      <c r="C88" s="2">
-        <v>1</v>
-      </c>
-      <c r="D88" s="2">
+      <c r="C88" s="104">
+        <v>1</v>
+      </c>
+      <c r="D88" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A89" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="104">
         <f>_xlfn.MAXIFS(H2:H9,K2:K9,"&lt;20",K2:K9,"&lt;&gt;4")</f>
         <v>30</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="104">
         <v>30</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A90" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="104">
         <f>MEDIAN(-1,6,7,234,163845)</f>
         <v>7</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="104">
         <v>7</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A91" s="104" t="s">
         <v>151</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="104">
         <f>MIN(N1:N8)</f>
         <v>0.1</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="104">
         <v>0.1</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A92" s="104" t="s">
         <v>152</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="104">
         <f>MINA(N1:N8)</f>
         <v>0</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="104">
         <v>0</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A93" s="104" t="s">
         <v>153</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="104">
         <f>_xlfn.MINIFS(J2:J9,H2:H9,"&gt;20")</f>
         <v>5000</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="104">
         <v>5000</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A94" s="104" t="s">
         <v>154</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="104">
         <f>MINUTE(0.126)</f>
         <v>1</v>
       </c>
-      <c r="C94" s="2">
-        <v>1</v>
-      </c>
-      <c r="D94" s="2">
+      <c r="C94" s="104">
+        <v>1</v>
+      </c>
+      <c r="D94" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A95" s="104" t="s">
         <v>155</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="104">
         <f>MOD(42,12)</f>
         <v>6</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="104">
         <v>6</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A96" s="104" t="s">
         <v>156</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="104">
         <f>MONTH("1954-05-02")</f>
         <v>5</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="104">
         <v>5</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A97" s="104" t="s">
         <v>157</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="104">
         <f>NETWORKDAYS("2013-01-01","2013-02-01")</f>
         <v>24</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="104">
         <v>24</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="104">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A98" s="104" t="s">
         <v>158</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="104">
         <f>NETWORKDAYS.INTL("2013-01-01","2013-02-01","0000111")</f>
         <v>19</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="104">
         <v>19</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="104">
         <f t="shared" ref="D98:D99" si="6">IF(B98=C98,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A99" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="B99" s="2" t="b">
+      <c r="B99" s="104" t="b">
         <f>NOT(FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C99" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D99" s="2">
+      <c r="C99" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" s="104">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A100" s="104" t="s">
         <v>160</v>
       </c>
-      <c r="B100" s="20">
+      <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45538.429115162035</v>
-      </c>
-      <c r="D100" s="2">
+        <v>45587.698421412038</v>
+      </c>
+      <c r="C100" s="105"/>
+      <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A101" s="104" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="104">
         <f>ODD(4)</f>
         <v>5</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="104">
         <v>5</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="104">
         <f t="shared" ref="D101:D111" si="7">IF(B101=C101,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A102" s="104" t="s">
         <v>162</v>
       </c>
-      <c r="B102" s="2" t="b">
+      <c r="B102" s="104" t="b">
         <f>OR("true",FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C102" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D102" s="2">
+      <c r="C102" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A103" s="104" t="s">
         <v>163</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="104">
         <f>PERCENTILE(N1:N5,1)</f>
         <v>0.6</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="104">
         <v>0.6</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A104" s="104" t="s">
         <v>164</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="104">
         <f>_xlfn.PERCENTILE.EXC(N1:N5,0.5)</f>
         <v>0.4</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="104">
         <v>0.4</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A105" s="104" t="s">
         <v>165</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="104">
         <f>_xlfn.PERCENTILE.INC(N1:N5,0)</f>
         <v>0.1</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="104">
         <v>0.1</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A106" s="104" t="s">
         <v>166</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="104">
         <f>ROUND(PI(),5)</f>
         <v>3.1415899999999999</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106" s="104">
         <v>3.1415899999999999</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A107" s="104" t="s">
         <v>167</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="104">
         <f>POWER(42,2)</f>
         <v>1764</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="104">
         <v>1764</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A108" s="104" t="s">
         <v>168</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="104">
         <f>PRODUCT(1,2,3)</f>
         <v>6</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="104">
         <v>6</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A109" s="104" t="s">
         <v>169</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="104">
         <f>QUARTILE(N1:N5,0)</f>
         <v>0.1</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="104">
         <v>0.1</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A110" s="104" t="s">
         <v>170</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="104">
         <f>ROUND(_xlfn.QUARTILE.EXC(N1:N5,1),5)</f>
         <v>0.15</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110" s="104">
         <v>0.15</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A111" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="104">
         <f>_xlfn.QUARTILE.INC(N1:N5,4)</f>
         <v>0.6</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="104">
         <v>0.6</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="104">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="D112" s="2"/>
-    </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A112" s="104"/>
+      <c r="B112" s="104"/>
+      <c r="C112" s="105"/>
+      <c r="D112" s="104"/>
+    </row>
+    <row r="113" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A113" s="104" t="s">
         <v>172</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="104">
         <f ca="1">RANDBETWEEN(1.1,2)</f>
         <v>2</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="104">
         <v>2</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="104">
         <f t="shared" ref="D113:D143" ca="1" si="8">IF(B113=C113,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A114" s="104" t="s">
         <v>173</v>
       </c>
-      <c r="B114" s="2" t="str">
+      <c r="B114" s="104" t="str">
         <f>REPLACE("ABZ",2,1,"Y")</f>
         <v>AYZ</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A115" s="104" t="s">
         <v>175</v>
       </c>
-      <c r="B115" s="2" t="str">
+      <c r="B115" s="104" t="str">
         <f>RIGHT("kikou",2)</f>
         <v>ou</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="104" t="s">
         <v>176</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A116" s="104" t="s">
         <v>177</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="104">
         <f>ROUND(49.9,0)</f>
         <v>50</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="104">
         <v>50</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A117" s="104" t="s">
         <v>178</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="104">
         <f>ROUNDDOWN(42,-1)</f>
         <v>40</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="104">
         <v>40</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A118" s="104" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="104">
         <f>ROUNDUP(-1.6,0)</f>
         <v>-2</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118" s="104">
         <v>-2</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A119" s="104" t="s">
         <v>180</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="104">
         <f>ROW(A234)</f>
         <v>234</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="104">
         <v>234</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A120" s="104" t="s">
         <v>181</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="104">
         <f>ROWS(B3:C40)</f>
         <v>38</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="104">
         <v>38</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A121" s="104" t="s">
         <v>182</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="104">
         <f>SEARCH("C","ABCD")</f>
         <v>3</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="104">
         <v>3</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A122" s="104" t="s">
         <v>183</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="104">
         <f>ROUND(_xlfn.SEC(PI()/3),5)</f>
         <v>2</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122" s="104">
         <v>2</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A123" s="104" t="s">
         <v>184</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="104">
         <f>ROUND(_xlfn.SECH(1),5)</f>
         <v>0.64805000000000001</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="104">
         <v>0.64805000000000001</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A124" s="104" t="s">
         <v>185</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="104">
         <f>SECOND("00:21:42")</f>
         <v>42</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124" s="104">
         <v>42</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A125" s="104" t="s">
         <v>186</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="104">
         <f>ROUND(SIN(PI()/6),5)</f>
         <v>0.5</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="104">
         <v>0.5</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A126" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="104">
         <f>ROUND(SINH(1),5)</f>
         <v>1.1752</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126" s="104">
         <v>1.1752</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A127" s="104" t="s">
         <v>188</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="104">
         <f>SMALL(H2:H9,3)</f>
         <v>26</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="104">
         <v>26</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A128" s="104" t="s">
         <v>189</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="104">
         <f>SQRT(4)</f>
         <v>2</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="104">
         <v>2</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A129" s="104" t="s">
         <v>190</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="104">
         <f>STDEV(-2,0,2)</f>
         <v>2</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="104">
         <v>2</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A130" s="104" t="s">
         <v>191</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="104">
         <f>_xlfn.STDEV.P(2,4)</f>
         <v>1</v>
       </c>
-      <c r="C130" s="2">
-        <v>1</v>
-      </c>
-      <c r="D130" s="2">
+      <c r="C130" s="104">
+        <v>1</v>
+      </c>
+      <c r="D130" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A131" s="104" t="s">
         <v>192</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="104">
         <f>_xlfn.STDEV.S(2,4,6)</f>
         <v>2</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="104">
         <v>2</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A132" s="104" t="s">
         <v>193</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="104">
         <f>STDEVA(TRUE,3,5)</f>
         <v>2</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132" s="104">
         <v>2</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A133" s="104" t="s">
         <v>194</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="104">
         <f>ROUND(STDEVP(2,5,8),2)</f>
         <v>2.4500000000000002</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="104">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A134" s="104" t="s">
         <v>195</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="104">
         <f>ROUND(STDEVPA(TRUE,4,7),2)</f>
         <v>2.4500000000000002</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="104">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A135" s="104" t="s">
         <v>196</v>
       </c>
-      <c r="B135" s="2" t="str">
+      <c r="B135" s="104" t="str">
         <f>SUBSTITUTE("SAP is best","SAP","Odoo")</f>
         <v>Odoo is best</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="104" t="s">
         <v>197</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A136" s="104" t="s">
         <v>198</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="104">
         <f>SUM(1,2,3,4,5)</f>
         <v>15</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="104">
         <v>15</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A137" s="104" t="s">
         <v>199</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="104">
         <f>SUMIF(K2:K9,"&lt;100")</f>
         <v>52</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="104">
         <v>52</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A138" s="104" t="s">
         <v>200</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="104">
         <f>SUMIFS(H2:H9,K2:K9,"&lt;100")</f>
         <v>201</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138" s="104">
         <v>201</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A139" s="104" t="s">
         <v>201</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="104">
         <f>ROUND(TAN(PI()/4),5)</f>
         <v>1</v>
       </c>
-      <c r="C139" s="2">
-        <v>1</v>
-      </c>
-      <c r="D139" s="2">
+      <c r="C139" s="104">
+        <v>1</v>
+      </c>
+      <c r="D139" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A140" s="104" t="s">
         <v>202</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="104">
         <f>ROUND(TANH(1),5)</f>
         <v>0.76158999999999999</v>
       </c>
-      <c r="C140" s="2">
+      <c r="C140" s="104">
         <v>0.76158999999999999</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="2" t="s">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A141" s="104" t="s">
         <v>203</v>
       </c>
-      <c r="B141" s="2" t="str">
+      <c r="B141" s="104" t="str">
         <f>_xlfn.TEXTJOIN("-",TRUE,"","1","A","%")</f>
         <v>1-A-%</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="104" t="s">
         <v>204</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A142" s="104" t="s">
         <v>205</v>
       </c>
-      <c r="B142" s="21">
+      <c r="B142" s="20">
         <f>TIME(9,11,31)</f>
         <v>0.38299768518518523</v>
       </c>
-      <c r="C142" s="21">
+      <c r="C142" s="20">
         <v>0.38299768519999999</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="104">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A143" s="104" t="s">
         <v>206</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="104">
         <f>TIMEVALUE("18:00:00")</f>
         <v>0.75</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="104">
         <v>0.75</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="104">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A144" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="B144" s="19">
+      <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45538</v>
-      </c>
-      <c r="D144" s="2">
+        <v>45587</v>
+      </c>
+      <c r="C144" s="105"/>
+      <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="2" t="s">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A145" s="104" t="s">
         <v>208</v>
       </c>
-      <c r="B145" s="2" t="str">
+      <c r="B145" s="104" t="str">
         <f>TRIM(" Jean Ticonstitutionnalise ")</f>
         <v>Jean Ticonstitutionnalise</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="104" t="s">
         <v>209</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="104">
         <f t="shared" ref="D145:D163" si="9">IF(B145=C145,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A146" s="104" t="s">
         <v>210</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="104">
         <f>TRUNC(42.42,1)</f>
         <v>42.4</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146" s="104">
         <v>42.4</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A147" s="104" t="s">
         <v>211</v>
       </c>
-      <c r="B147" s="2" t="str">
+      <c r="B147" s="104" t="str">
         <f>UPPER("grrrr !")</f>
         <v>GRRRR !</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="104" t="s">
         <v>212</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A148" s="104" t="s">
         <v>213</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="104">
         <f>ROUND(VAR(K1:K5),5)</f>
         <v>2.9166699999999999</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148" s="104">
         <v>2.9166699999999999</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A149" s="104" t="s">
         <v>214</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="104">
         <f>ROUND(_xlfn.VAR.P(K1:K5),5)</f>
         <v>2.1875</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149" s="104">
         <v>2.1875</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A150" s="104" t="s">
         <v>215</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="104">
         <f>_xlfn.VAR.S(2,5,8)</f>
         <v>9</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150" s="104">
         <v>9</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A151" s="104" t="s">
         <v>216</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="104">
         <f>ROUND(VARA(K1:K5),5)</f>
         <v>6.7</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151" s="104">
         <v>6.7</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A152" s="104" t="s">
         <v>217</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="104">
         <f>ROUND(VARP(K1:K5),5)</f>
         <v>2.1875</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152" s="104">
         <v>2.1875</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A153" s="104" t="s">
         <v>218</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="104">
         <f>ROUND(VARPA(K1:K5),5)</f>
         <v>5.36</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C153" s="104">
         <v>5.36</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A154" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154" s="104">
         <f>VLOOKUP("NotACheater",G1:K9,3,FALSE)</f>
         <v>252.4</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C154" s="104">
         <f>252.4</f>
         <v>252.4</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A155" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="104">
         <f>WEEKDAY("2021-06-12")</f>
         <v>7</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155" s="104">
         <v>7</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A156" s="104" t="s">
         <v>221</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156" s="104">
         <f>WEEKNUM("2021-06-29")</f>
         <v>27</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C156" s="104">
         <v>27</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A157" s="104" t="s">
         <v>222</v>
       </c>
-      <c r="B157" s="19">
+      <c r="B157" s="18">
         <f>WORKDAY("2021-03-15",6)</f>
         <v>44278</v>
       </c>
-      <c r="C157" s="19">
+      <c r="C157" s="18">
         <v>44278</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A158" s="104" t="s">
         <v>223</v>
       </c>
-      <c r="B158" s="19">
+      <c r="B158" s="18">
         <f>WORKDAY.INTL("2021-03-15",6,"0111111")</f>
         <v>44312</v>
       </c>
-      <c r="C158" s="19">
+      <c r="C158" s="18">
         <v>44312</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A159" s="104" t="s">
         <v>224</v>
       </c>
-      <c r="B159" s="2" t="b">
+      <c r="B159" s="104" t="b">
         <f>_xlfn.XOR(FALSE,TRUE,FALSE,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C159" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D159" s="2">
+      <c r="C159" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D159" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="2" t="s">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A160" s="104" t="s">
         <v>225</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160" s="104">
         <f>YEAR("2012-03-12")</f>
         <v>2012</v>
       </c>
-      <c r="C160" s="2">
+      <c r="C160" s="104">
         <v>2012</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="2" t="s">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A161" s="104" t="s">
         <v>226</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="104">
         <f>DELTA(1,1)</f>
         <v>1</v>
       </c>
-      <c r="C161" s="2">
-        <v>1</v>
-      </c>
-      <c r="D161" s="2">
+      <c r="C161" s="104">
+        <v>1</v>
+      </c>
+      <c r="D161" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="2" t="s">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A162" s="104" t="s">
         <v>227</v>
       </c>
-      <c r="B162" s="2" t="str">
+      <c r="B162" s="104" t="str">
         <f>ADDRESS(1,1,4,FALSE,"sheet!")</f>
         <v>'sheet!'!R[1]C[1]</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="104" t="s">
         <v>228</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A163" s="104" t="s">
         <v>229</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163" s="104">
         <f>DATEDIF("2002/01/01","2002/01/02","D")</f>
         <v>1</v>
       </c>
-      <c r="C163" s="2">
-        <v>1</v>
-      </c>
-      <c r="D163" s="2">
+      <c r="C163" s="104">
+        <v>1</v>
+      </c>
+      <c r="D163" s="104">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11339,73 +12016,162 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" outlineLevel="1"/>
-    <col min="11" max="11" width="9.109375" outlineLevel="1" collapsed="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" outlineLevel="1"/>
+    <col min="11" max="11" width="9.140625" outlineLevel="1" collapsed="1"/>
     <col min="12" max="14" width="0" hidden="1" outlineLevel="2"/>
-    <col min="15" max="18" width="9.109375" outlineLevel="1"/>
+    <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="105" t="s">
         <v>230</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="105" t="s">
         <v>231</v>
       </c>
       <c r="D1" s="110" t="s">
         <v>232</v>
       </c>
       <c r="E1" s="110"/>
-      <c r="F1" t="s">
+      <c r="F1" s="105" t="s">
         <v>233</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="105"/>
+      <c r="H1" s="34" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:8">
+      <c r="A2" s="105">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
       <c r="D2" s="110"/>
       <c r="E2" s="110"/>
-      <c r="H2" t="str">
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D3" s="86" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="105"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
-      <c r="F3" s="86" t="s">
+      <c r="E3" s="105"/>
+      <c r="F3" s="85" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+    </row>
+    <row r="4" spans="1:8" hidden="1">
+      <c r="A4" s="105" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" s="105"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+    </row>
+    <row r="5" spans="1:8" ht="75" customHeight="1">
+      <c r="A5" s="105" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="17" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="18" outlineLevel="1" x14ac:dyDescent="0.3"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+    </row>
+    <row r="10" spans="1:8" outlineLevel="1">
+      <c r="A10" s="105"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+    </row>
+    <row r="11" spans="1:8" outlineLevel="1">
+      <c r="A11" s="105"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+    </row>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2">
+      <c r="A12" s="105"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+    </row>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2">
+      <c r="A13" s="105"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+    </row>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2">
+      <c r="A14" s="105"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+    </row>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1">
+      <c r="A15" s="105"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+    </row>
+    <row r="16" spans="1:8" outlineLevel="1">
+      <c r="A16" s="105"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+    </row>
+    <row r="17" outlineLevel="1"/>
+    <row r="18" outlineLevel="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:E2"/>
@@ -11422,382 +12188,568 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:13" ht="14.45" thickBot="1">
+      <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="D1" s="105"/>
+      <c r="E1" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="F1" s="37"/>
-      <c r="H1" s="35" t="s">
+      <c r="F1" s="36"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="I1" s="105"/>
+      <c r="J1" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="L1" s="94" t="s">
+      <c r="K1" s="105"/>
+      <c r="L1" s="93" t="s">
         <v>244</v>
       </c>
-      <c r="M1" s="37"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="M1" s="36"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="B2" s="105"/>
+      <c r="C2" s="86" t="s">
         <v>246</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="D2" s="105"/>
+      <c r="E2" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="72" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="84" t="s">
+      <c r="I2" s="105"/>
+      <c r="J2" s="83" t="s">
         <v>250</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="K2" s="105"/>
+      <c r="L2" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="M2" s="95">
+      <c r="M2" s="94">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="G3" s="105"/>
+      <c r="H3" s="71" t="s">
         <v>253</v>
       </c>
-      <c r="J3" s="74" t="s">
+      <c r="I3" s="105"/>
+      <c r="J3" s="73" t="s">
         <v>254</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="K3" s="105"/>
+      <c r="L3" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="M3" s="96">
+      <c r="M3" s="95">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A4" s="43" t="s">
+    <row r="4" spans="1:13" ht="16.149999999999999">
+      <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="B4" s="105"/>
+      <c r="C4" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="D4" s="105"/>
+      <c r="E4" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="G4" s="105"/>
+      <c r="H4" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="J4" s="85" t="s">
+      <c r="I4" s="105"/>
+      <c r="J4" s="84" t="s">
         <v>260</v>
       </c>
-      <c r="L4" s="22" t="s">
+      <c r="K4" s="105"/>
+      <c r="L4" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="M4" s="97">
+      <c r="M4" s="96">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="H5" s="71" t="s">
+      <c r="G5" s="105"/>
+      <c r="H5" s="70" t="s">
         <v>264</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="98">
+      <c r="M5" s="97">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+    <row r="6" spans="1:13">
+      <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="B6" s="105"/>
+      <c r="C6" s="57" t="s">
         <v>267</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="D6" s="105"/>
+      <c r="E6" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="H6" s="70" t="s">
+      <c r="G6" s="105"/>
+      <c r="H6" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="M6" s="99">
+      <c r="M6" s="98">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="46" t="s">
+    <row r="7" spans="1:13" ht="15.6">
+      <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="H7" s="83" t="s">
+      <c r="G7" s="105"/>
+      <c r="H7" s="82" t="s">
         <v>273</v>
       </c>
-      <c r="L7" s="39" t="s">
+      <c r="I7" s="105"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="M7" s="101">
+      <c r="M7" s="100">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="47" t="s">
+    <row r="8" spans="1:13" ht="21">
+      <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="B8" s="105"/>
+      <c r="C8" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="D8" s="105"/>
+      <c r="E8" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="G8" s="105"/>
+      <c r="H8" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="L8" s="39" t="s">
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="M8" s="102">
+      <c r="M8" s="101">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="48" t="s">
+    <row r="9" spans="1:13">
+      <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="102">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="49" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="B10" s="105"/>
+      <c r="C10" s="59" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="50" t="s">
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+    </row>
+    <row r="11" spans="1:13" ht="14.45" thickBot="1">
+      <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="F11" s="37"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="51" t="s">
+      <c r="F11" s="36"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+    </row>
+    <row r="12" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="B12" s="105"/>
+      <c r="C12" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="D12" s="105"/>
+      <c r="E12" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="21" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="52" t="s">
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="105"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="30" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="53" t="s">
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="B14" s="105"/>
+      <c r="C14" s="61" t="s">
         <v>292</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="D14" s="105"/>
+      <c r="E14" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="31" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="54" t="s">
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="105"/>
+    </row>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="32" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="55" t="s">
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="105"/>
+    </row>
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="B16" s="105"/>
+      <c r="C16" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="D16" s="105"/>
+      <c r="E16" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="33" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56" t="s">
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="105"/>
+      <c r="M16" s="105"/>
+    </row>
+    <row r="17" spans="1:6" ht="14.45" thickBot="1">
+      <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="75" t="s">
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+    </row>
+    <row r="18" spans="1:6" ht="14.45" thickBot="1">
+      <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="B18" s="105"/>
+      <c r="C18" s="63" t="s">
         <v>298</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="D18" s="105"/>
+      <c r="E18" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="F18" s="37"/>
-    </row>
-    <row r="19" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="76" t="s">
+      <c r="F18" s="36"/>
+    </row>
+    <row r="19" spans="1:6" ht="14.45" thickBot="1">
+      <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="105" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="77" t="s">
+    <row r="20" spans="1:6" ht="55.9" thickBot="1">
+      <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="B20" s="105"/>
+      <c r="C20" s="64" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="D20" s="105"/>
+      <c r="E20" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="104" t="s">
+      <c r="F20" s="103" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="78" t="s">
+    <row r="21" spans="1:6" ht="14.45" thickBot="1">
+      <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="79" t="s">
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+    </row>
+    <row r="22" spans="1:6" ht="14.45" thickBot="1">
+      <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="B22" s="105"/>
+      <c r="C22" s="65" t="s">
         <v>308</v>
       </c>
-      <c r="E22" s="22"/>
-    </row>
-    <row r="23" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="80" t="s">
+      <c r="D22" s="105"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="105"/>
+    </row>
+    <row r="23" spans="1:6" ht="14.45" thickBot="1">
+      <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
-      <c r="E23" s="22"/>
-    </row>
-    <row r="24" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="81" t="s">
+      <c r="B23" s="105"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="105"/>
+    </row>
+    <row r="24" spans="1:6" ht="15" thickTop="1" thickBot="1">
+      <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="B24" s="105"/>
+      <c r="C24" s="66" t="s">
         <v>311</v>
       </c>
-      <c r="E24" s="22"/>
-    </row>
-    <row r="25" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C26" s="68" t="s">
+      <c r="D24" s="105"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="105"/>
+    </row>
+    <row r="25" spans="1:6" ht="15" thickTop="1" thickBot="1">
+      <c r="A25" s="105"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+    </row>
+    <row r="26" spans="1:6" ht="15" thickTop="1" thickBot="1">
+      <c r="A26" s="105"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C28" s="89" t="s">
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickTop="1" thickBot="1">
+      <c r="A27" s="105"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickTop="1" thickBot="1">
+      <c r="A28" s="105"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C30" s="88" t="s">
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+    </row>
+    <row r="29" spans="1:6" ht="14.45" thickTop="1">
+      <c r="A29" s="105"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="105"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11808,867 +12760,1013 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:10" ht="14.45" thickBot="1">
+      <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="105">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="35" t="s">
+      <c r="C2" s="105">
+        <v>1</v>
+      </c>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="21">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="105">
         <v>3</v>
       </c>
-      <c r="J2" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="J2" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="105">
         <v>5</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="105">
         <v>3</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="J3" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="B4" s="105"/>
+      <c r="C4" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="105">
         <v>5</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="105">
         <v>3</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="J4" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="B5" t="e">
+      <c r="B5" s="105" t="e">
         <f>0/0</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="105">
         <v>0</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="105">
         <v>5</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="105">
         <v>3</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="J5" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="105">
         <v>5</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="105">
         <v>3</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
+      <c r="J6" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="105">
         <v>5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="105">
         <v>3</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
+      <c r="J7" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="C9" s="22"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="39" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+    </row>
+    <row r="10" spans="1:10" ht="14.45" thickBot="1">
+      <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="105">
         <v>0</v>
       </c>
-      <c r="C10" t="e">
+      <c r="C10" s="105" t="e">
         <f>0/0</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="105">
         <v>5</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="105">
         <v>3</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="39" t="s">
+      <c r="J11" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45538</v>
-      </c>
-      <c r="C12" s="40">
+        <v>45587</v>
+      </c>
+      <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
         <v>40453</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="105">
         <v>5</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="105">
         <v>3</v>
       </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
+      <c r="J12" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="105">
         <v>7</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="105">
         <v>5</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="34" t="s">
         <v>347</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="105">
         <v>5</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="105">
         <v>3</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="39" t="s">
+      <c r="J13" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="105">
         <v>5</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="105">
         <v>3</v>
       </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="39" t="s">
+      <c r="J14" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="35" t="s">
+      <c r="B15" s="105">
+        <v>1</v>
+      </c>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="105">
         <v>5</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="105">
         <v>3</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="39" t="s">
+      <c r="J15" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="105">
         <v>2</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="35" t="s">
+      <c r="C16" s="105">
+        <v>1</v>
+      </c>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="105">
         <v>5</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="105">
         <v>3</v>
       </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="39" t="s">
+      <c r="J16" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="105">
         <v>0</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="105">
         <v>2</v>
       </c>
-      <c r="G17" s="35" t="s">
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="105">
         <v>5</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="105">
         <v>3</v>
       </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
+      <c r="J17" s="105">
+        <v>1</v>
+      </c>
+      <c r="K17" s="105"/>
+      <c r="L17" s="105"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="105">
         <v>3</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="105">
         <v>0</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="105">
         <v>5</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="105">
         <v>3</v>
       </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="39" t="s">
+      <c r="J18" s="105">
+        <v>1</v>
+      </c>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="105">
         <v>2</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="105">
         <v>0</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="34" t="s">
         <v>359</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="105">
         <v>5</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="105">
         <v>3</v>
       </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="39" t="s">
+      <c r="J19" s="105">
+        <v>1</v>
+      </c>
+      <c r="K19" s="105"/>
+      <c r="L19" s="105"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="105">
         <v>0</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="105">
         <v>2</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="34" t="s">
         <v>361</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="105">
         <v>5</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="105">
         <v>3</v>
       </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="39" t="s">
+      <c r="J20" s="105">
+        <v>1</v>
+      </c>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="105">
         <v>2</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="105">
         <v>3</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="105">
         <v>5</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="105">
         <v>4</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="105">
         <v>3</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="105">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="39" t="s">
+      <c r="L21" s="105"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="105">
         <v>2</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="105">
         <v>0</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="34" t="s">
         <v>365</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="105">
         <v>5</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="105">
         <v>4</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="105">
         <v>3</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="105">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="39" t="s">
+      <c r="L22" s="105"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="105">
+        <v>1</v>
+      </c>
+      <c r="C23" s="105">
         <v>2</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="105">
         <v>5</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="105">
         <v>4</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="105">
         <v>3</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="105">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G24" s="35" t="s">
+      <c r="L23" s="105"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="105"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="105">
         <v>5</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="105">
         <v>4</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="105">
         <v>3</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="105">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
+      <c r="L24" s="105"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="105">
         <v>5</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="105">
         <v>2</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="105">
         <v>5</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="105">
         <v>4</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="105">
         <v>3</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="105">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G26" s="35" t="s">
+      <c r="L25" s="105"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="105"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="105">
         <v>5</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="105">
         <v>4</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="105">
         <v>3</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="105">
         <v>2</v>
       </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
+      <c r="L26" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="105">
         <v>2</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="105">
         <v>5</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="105">
         <v>4</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="105">
         <v>3</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="105">
         <v>2</v>
       </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G28" s="35" t="s">
+      <c r="L27" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="105"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="105">
         <v>5</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="105">
         <v>4</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="105">
         <v>3</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="105">
         <v>2</v>
       </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G29" s="35" t="s">
+      <c r="L28" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="105"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="34" t="s">
         <v>375</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="105">
         <v>5</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="105">
         <v>4</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="105">
         <v>3</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="105">
         <v>2</v>
       </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G30" s="35" t="s">
+      <c r="L29" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="105"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="34" t="s">
         <v>376</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="105">
         <v>5</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="105">
         <v>4</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="105">
         <v>3</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="105">
         <v>2</v>
       </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G31" s="36" t="s">
+      <c r="L30" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="14.45" thickBot="1">
+      <c r="A31" s="105"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="35" t="s">
         <v>377</v>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="36">
         <v>5</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="36">
         <v>3</v>
       </c>
-      <c r="J31" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G32" s="35" t="s">
+      <c r="J31" s="36">
+        <v>1</v>
+      </c>
+      <c r="K31" s="105"/>
+      <c r="L31" s="105"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="34" t="s">
         <v>378</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="105">
         <v>5</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="105">
         <v>3</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G33" s="35" t="s">
+      <c r="J32" s="105">
+        <v>1</v>
+      </c>
+      <c r="K32" s="105"/>
+      <c r="L32" s="105"/>
+    </row>
+    <row r="33" spans="7:10">
+      <c r="G33" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="105">
         <v>5</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="105">
         <v>3</v>
       </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G34" s="35" t="s">
+      <c r="J33" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="7:10">
+      <c r="G34" s="34" t="s">
         <v>380</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="105">
         <v>5</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="105">
         <v>3</v>
       </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G35" s="35" t="s">
+      <c r="J34" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="7:10">
+      <c r="G35" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="105">
         <v>5</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="105">
         <v>3</v>
       </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G36" s="35" t="s">
+      <c r="J35" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="7:10">
+      <c r="G36" s="34" t="s">
         <v>382</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="105">
         <v>5</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="105">
         <v>3</v>
       </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G37" s="35" t="s">
+      <c r="J36" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="7:10">
+      <c r="G37" s="34" t="s">
         <v>383</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="105">
         <v>5</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="105">
         <v>3</v>
       </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G39" s="35"/>
+      <c r="J37" s="105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="7:10">
+      <c r="G39" s="34"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="105"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="22" priority="58">
+    <cfRule type="expression" dxfId="40" priority="58">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="21" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="20" priority="114"/>
+    <cfRule type="aboveAverage" dxfId="38" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="19" priority="73" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="37" priority="73" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="18" priority="71">
+    <cfRule type="containsBlanks" dxfId="36" priority="71">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="17" priority="70">
+    <cfRule type="containsErrors" dxfId="35" priority="70">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="16" priority="69" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="34" priority="69" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="15" priority="67" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="33" priority="67" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="14" priority="66">
+    <cfRule type="notContainsBlanks" dxfId="32" priority="66">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="13" priority="65">
+    <cfRule type="notContainsErrors" dxfId="31" priority="65">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="12" priority="64" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="30" priority="64" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="11" priority="63" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="29" priority="63" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="10" priority="115" rank="1"/>
+    <cfRule type="top10" dxfId="28" priority="115" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="9" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="45" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="8" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="26" priority="56" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -12702,10 +13800,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="0" priority="96"/>
+    <cfRule type="uniqueValues" dxfId="18" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="44">
@@ -13128,315 +14226,384 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" customWidth="1"/>
-    <col min="5" max="5" width="26.44140625" customWidth="1"/>
-    <col min="6" max="6" width="27.5546875" customWidth="1"/>
-    <col min="7" max="7" width="23.5546875" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="105" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C3" s="18" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="105"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="17" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="2" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="105"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="104">
         <v>26</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="104">
         <v>5</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="104">
         <f>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</f>
         <v>31</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="104">
         <f>SUM(Table3[Rank])</f>
         <v>12</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="104">
         <f>SUM(Table3[[#All],[Rank]])</f>
         <v>24</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="104">
         <f>Table3[[#Totals],[Rank]]</f>
         <v>12</v>
       </c>
-      <c r="J4" s="2" t="str">
+      <c r="J4" s="104" t="str">
         <f>Table3[[#Headers],[Rank]]</f>
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="2" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="105"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="104">
         <v>13</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="104">
         <v>7</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="104">
         <f>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</f>
         <v>20</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="104">
         <f>SUM(Table3[Rank])</f>
         <v>12</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="104">
         <f>SUM(Table3[[#All],[Rank]])</f>
         <v>24</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="104">
         <f>Table3[[#Totals],[Rank]]</f>
         <v>12</v>
       </c>
-      <c r="J5" s="2" t="str">
+      <c r="J5" s="104" t="str">
         <f>Table3[[#Headers],[Rank]]</f>
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="2" t="s">
+    <row r="6" spans="1:10">
+      <c r="A6" s="105"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="104" t="s">
         <v>391</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="104">
         <f>SUBTOTAL(109,Table3[Age])</f>
         <v>39</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="104">
         <f>SUBTOTAL(109,Table3[Rank])</f>
         <v>12</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="104">
         <f>SUBTOTAL(109,Table3[Rank+Age =E4+D4])</f>
         <v>51</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="104">
         <f>SUBTOTAL(109,Table3[Data =SUM(E4:E5)])</f>
         <v>24</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="104">
         <f>SUBTOTAL(109,Table3[All =SUM(E3:E6)])</f>
         <v>48</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="104">
         <f>SUBTOTAL(109,Table3[Totals =E6])</f>
         <v>24</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="104">
         <f>SUBTOTAL(109,Table3[Headers =E3])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+    <row r="8" spans="1:10">
+      <c r="A8" s="105"/>
+      <c r="B8" s="105" t="s">
         <v>392</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="105">
+        <v>1</v>
+      </c>
+      <c r="D8" s="105">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C9">
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="105"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105">
         <v>3</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="105">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="105"/>
+      <c r="B11" s="105" t="s">
         <v>393</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="105" t="s">
         <v>394</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="105" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C12">
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="105"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105">
         <v>3</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="105">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="105"/>
+      <c r="B14" s="105" t="s">
         <v>396</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="105">
+        <v>1</v>
+      </c>
+      <c r="D14" s="105">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C15">
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="105"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105">
         <v>3</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="105">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="105" t="s">
         <v>397</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="105">
+        <v>1</v>
+      </c>
+      <c r="D17" s="105">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C18">
+    <row r="18" spans="2:4">
+      <c r="B18" s="105"/>
+      <c r="C18" s="105">
         <v>3</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="105">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
+    <row r="20" spans="2:4">
+      <c r="B20" s="105" t="s">
         <v>398</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="105">
+        <v>1</v>
+      </c>
+      <c r="D20" s="105">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C21">
+    <row r="21" spans="2:4">
+      <c r="B21" s="105"/>
+      <c r="C21" s="105">
         <v>3</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="105">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+    <row r="23" spans="2:4">
+      <c r="B23" s="105" t="s">
         <v>399</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
+      <c r="C23" s="105">
+        <v>1</v>
+      </c>
+      <c r="D23" s="105">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C24">
+    <row r="24" spans="2:4">
+      <c r="B24" s="105"/>
+      <c r="C24" s="105">
         <v>3</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="105">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="26" spans="2:4">
+      <c r="B26" s="105" t="s">
         <v>400</v>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
+      <c r="C26" s="105">
+        <v>1</v>
+      </c>
+      <c r="D26" s="105">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C27">
+    <row r="27" spans="2:4">
+      <c r="B27" s="105"/>
+      <c r="C27" s="105">
         <v>3</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="105">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
+    <row r="28" spans="2:4">
+      <c r="B28" s="105"/>
+      <c r="C28" s="105" t="s">
         <v>391</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="105">
         <f>SUBTOTAL(109,Table4910[Column2])</f>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+    <row r="30" spans="2:4">
+      <c r="B30" s="105" t="s">
         <v>401</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="105" t="s">
         <v>402</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="105" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C31" t="s">
+    <row r="31" spans="2:4" hidden="1">
+      <c r="B31" s="105"/>
+      <c r="C31" s="105" t="s">
         <v>404</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="105" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
+    <row r="32" spans="2:4">
+      <c r="B32" s="105"/>
+      <c r="C32" s="105" t="s">
         <v>405</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="105" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
+    <row r="34" spans="2:2">
+      <c r="B34" s="105" t="s">
         <v>406</v>
       </c>
     </row>
@@ -13460,306 +14627,450 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="92" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="90" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="104"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="104"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="89" t="s">
         <v>408</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="89" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="90" t="s">
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="104"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="89" t="s">
         <v>410</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="105">
         <v>12.1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="105">
         <v>252.4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="105">
         <v>500.9</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="105">
         <v>1204.7</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="105">
         <v>4000</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="105">
         <v>4701.3</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="105">
         <v>4890.1000000000004</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="105">
         <v>12052</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="105" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="91" t="s">
+    <row r="5" spans="1:12">
+      <c r="A5" s="104"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="K5">
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105">
         <v>30</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="105">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="92">
+    <row r="6" spans="1:12">
+      <c r="A6" s="104"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="91">
         <v>256018</v>
       </c>
-      <c r="K6">
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105">
         <v>30</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="105">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="91" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="E7">
+      <c r="D7" s="105"/>
+      <c r="E7" s="105">
         <v>26</v>
       </c>
-      <c r="L7">
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="105">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="92">
+    <row r="8" spans="1:12">
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="91">
         <v>110120.5</v>
       </c>
-      <c r="E8">
+      <c r="D8" s="105"/>
+      <c r="E8" s="105">
         <v>26</v>
       </c>
-      <c r="L8">
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="91" t="s">
+    <row r="9" spans="1:12">
+      <c r="A9" s="104"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="G9">
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105">
         <v>26</v>
       </c>
-      <c r="L9">
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="92">
+    <row r="10" spans="1:12">
+      <c r="A10" s="104"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="91">
         <v>25618</v>
       </c>
-      <c r="G10">
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105">
         <v>26</v>
       </c>
-      <c r="L10">
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C11" s="91" t="s">
+    <row r="11" spans="1:12">
+      <c r="A11" s="105"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="F11">
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105">
         <v>13</v>
       </c>
-      <c r="L11">
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="92">
+    <row r="12" spans="1:12">
+      <c r="A12" s="105"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="91">
         <v>23000</v>
       </c>
-      <c r="F12">
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105">
         <v>13</v>
       </c>
-      <c r="L12">
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="91" t="s">
+    <row r="13" spans="1:12">
+      <c r="A13" s="105"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="105">
         <v>9</v>
       </c>
-      <c r="L13">
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="92">
+    <row r="14" spans="1:12">
+      <c r="A14" s="105"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="91">
         <v>2</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="105">
         <v>9</v>
       </c>
-      <c r="L14">
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C15" s="91" t="s">
+    <row r="15" spans="1:12">
+      <c r="A15" s="105"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="I15">
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105">
         <v>42</v>
       </c>
-      <c r="L15">
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="92">
+    <row r="16" spans="1:12">
+      <c r="A16" s="105"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="91">
         <v>50024</v>
       </c>
-      <c r="I16">
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105">
         <v>42</v>
       </c>
-      <c r="L16">
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="105">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C17" s="91" t="s">
+    <row r="17" spans="3:12">
+      <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="H17">
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="105">
         <v>27</v>
       </c>
-      <c r="L17">
+      <c r="I17" s="105"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
+      <c r="L17" s="105">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C18" s="92">
+    <row r="18" spans="3:12">
+      <c r="C18" s="91">
         <v>189576</v>
       </c>
-      <c r="H18">
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105">
         <v>27</v>
       </c>
-      <c r="L18">
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C19" s="91" t="s">
+    <row r="19" spans="3:12">
+      <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="J19">
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105">
         <v>37</v>
       </c>
-      <c r="L19">
+      <c r="K19" s="105"/>
+      <c r="L19" s="105">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C20" s="92">
+    <row r="20" spans="3:12">
+      <c r="C20" s="91">
         <v>5000</v>
       </c>
-      <c r="J20">
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105">
         <v>37</v>
       </c>
-      <c r="L20">
+      <c r="K20" s="105"/>
+      <c r="L20" s="105">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C21" s="91" t="s">
+    <row r="21" spans="3:12">
+      <c r="C21" s="90" t="s">
         <v>411</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="105">
         <v>9</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="105">
         <v>26</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="105">
         <v>13</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="105">
         <v>26</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="105">
         <v>27</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="105">
         <v>42</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="105">
         <v>37</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="105">
         <v>30</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="105">
         <v>210</v>
       </c>
     </row>
@@ -13772,32 +15083,35 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="65.109375" customWidth="1"/>
-    <col min="2" max="26" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="65.140625" customWidth="1"/>
+    <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="105" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B1" s="105"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="105" t="s">
         <v>413</v>
       </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" s="104"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="105" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" s="105"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="105" t="s">
         <v>415</v>
       </c>
+      <c r="B4" s="105"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13808,10 +15122,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.9"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
+    <row r="1" spans="1:1" ht="55.15">
+      <c r="A1" s="99" t="s">
         <v>416</v>
       </c>
     </row>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{157AC437-DB84-431C-BDD0-6A0421B0B149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3C4A8EF-BCA2-4707-8E96-AC9A2E2BCE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23295" yWindow="195" windowWidth="21600" windowHeight="11385" firstSheet="13" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23295" yWindow="195" windowWidth="21600" windowHeight="11385" firstSheet="8" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
   </externalReferences>
   <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="3563" r:id="rId16"/>
+    <pivotCache cacheId="7905" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2375,6 +2375,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2387,7 +2388,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -3102,6 +3102,22 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="6350" cap="rnd" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -3645,6 +3661,11 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -5053,6 +5074,11 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:trendline>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$27:$B$35</c:f>
@@ -5366,6 +5392,12 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -7575,7 +7607,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="3563" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="7905" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8193,7 +8225,7 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="123"/>
+      <c r="I2" s="119"/>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1">
@@ -8203,10 +8235,10 @@
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="119">
+      <c r="K3" s="120">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
@@ -8224,10 +8256,10 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1">
@@ -8237,10 +8269,10 @@
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1">
@@ -8248,7 +8280,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="120"/>
+      <c r="K6" s="121"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1">
@@ -8256,7 +8288,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="120"/>
+      <c r="K7" s="121"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1">
@@ -8264,7 +8296,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="121"/>
+      <c r="K8" s="122"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1">
@@ -10732,7 +10764,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45663.51402037037</v>
+        <v>45713.533170138886</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -11422,7 +11454,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45663</v>
+        <v>45713</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -11771,10 +11803,10 @@
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="122" t="s">
+      <c r="D1" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="122"/>
+      <c r="E1" s="123"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -11787,8 +11819,8 @@
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
@@ -12452,7 +12484,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45663</v>
+        <v>45713</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28706"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28712"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C3FAEF4-9495-4537-B722-A5A16F9D6A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5D1CDA2-3EA0-4080-9949-42D9CDC649F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
   </externalReferences>
   <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5972" r:id="rId16"/>
+    <pivotCache cacheId="3029" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1390,7 +1390,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1552,6 +1552,11 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF5733"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -2184,7 +2189,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2390,6 +2395,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2402,7 +2408,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2987,6 +2993,7 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFF5733"/>
       <color rgb="FF00FF00"/>
       <color rgb="FF000000"/>
       <color rgb="FFCECECE"/>
@@ -3117,6 +3124,22 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="6350" cap="rnd" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -3547,6 +3570,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.18463710322342519"/>
+          <c:y val="0.25410895455002247"/>
+          <c:w val="0.63340157480314963"/>
+          <c:h val="0.10860608640136199"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3660,6 +3693,19 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -5068,6 +5114,26 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="A9D08E"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C65911"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$27:$B$35</c:f>
@@ -5381,6 +5447,20 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C65911"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -7936,7 +8016,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="5972" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="3029" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8565,7 +8645,7 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="123"/>
+      <c r="I2" s="119"/>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1">
@@ -8575,10 +8655,10 @@
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="119">
+      <c r="K3" s="120">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
@@ -8596,10 +8676,10 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1">
@@ -8609,10 +8689,10 @@
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1">
@@ -8620,7 +8700,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="120"/>
+      <c r="K6" s="121"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1">
@@ -8628,7 +8708,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="120"/>
+      <c r="K7" s="121"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1">
@@ -8636,7 +8716,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="121"/>
+      <c r="K8" s="122"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1">
@@ -11104,7 +11184,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45728.469061574076</v>
+        <v>45733.554276041665</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -11794,7 +11874,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45728</v>
+        <v>45733</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -12143,10 +12223,10 @@
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="122" t="s">
+      <c r="D1" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="122"/>
+      <c r="E1" s="123"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -12159,8 +12239,8 @@
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
@@ -12824,7 +12904,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45728</v>
+        <v>45733</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -14593,7 +14673,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
@@ -14620,6 +14700,9 @@
       <c r="A4" t="s">
         <v>420</v>
       </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="124"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28627"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F15F33D-0A5F-4E8A-8973-B5E6D3A30B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB568EAE-D5FE-4913-BF89-9ACAE939443F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,9 @@
   <externalReferences>
     <externalReference r:id="rId15"/>
   </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId16"/>
+    <pivotCache cacheId="3142" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1236,6 +1236,21 @@
     <t>BasicTable</t>
   </si>
   <si>
+    <t>Total table</t>
+  </si>
+  <si>
+    <t>Column of table of other sheet</t>
+  </si>
+  <si>
+    <t>Multiple columns total</t>
+  </si>
+  <si>
+    <t>Multiple Columns</t>
+  </si>
+  <si>
+    <t>Multiple keywords</t>
+  </si>
+  <si>
     <t>Header</t>
   </si>
   <si>
@@ -1361,21 +1376,6 @@
   </si>
   <si>
     <t>A1234556</t>
-  </si>
-  <si>
-    <t>Total table</t>
-  </si>
-  <si>
-    <t>Column of table of other sheet</t>
-  </si>
-  <si>
-    <t>Multiple columns total</t>
-  </si>
-  <si>
-    <t>Multiple Columns</t>
-  </si>
-  <si>
-    <t>Multiple keywords</t>
   </si>
 </sst>
 </file>
@@ -1390,7 +1390,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2390,7 +2390,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2403,6 +2402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2410,6 +2410,157 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2816,157 +2967,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -3117,6 +3117,22 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="6350" cap="rnd" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -3660,6 +3676,11 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -5068,6 +5089,11 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:trendline>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$27:$B$35</c:f>
@@ -5381,6 +5407,12 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -7590,7 +7622,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="3142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -7740,7 +7772,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7752,22 +7784,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7888,9 +7920,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7928,7 +7960,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -8034,7 +8066,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8176,7 +8208,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -8188,7 +8220,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -8197,7 +8229,7 @@
     <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1">
       <c r="A1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -8206,7 +8238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.75">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -8219,25 +8251,25 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="119"/>
+      <c r="I2" s="123"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1">
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="120">
+      <c r="K3" s="119">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1">
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
@@ -8250,50 +8282,50 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="121"/>
+      <c r="K4" s="120"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1">
       <c r="C5" s="117">
         <v>42</v>
       </c>
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="121"/>
+      <c r="K5" s="120"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1">
       <c r="G6" s="117">
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="121"/>
+      <c r="K6" s="120"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1">
       <c r="C7" s="117">
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="121"/>
+      <c r="K7" s="120"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1">
       <c r="G8" s="117">
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="122"/>
+      <c r="K8" s="121"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1">
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -8303,7 +8335,7 @@
       </c>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1">
       <c r="C10" s="117">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -8312,13 +8344,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1">
       <c r="C11" s="117">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1">
       <c r="C12" s="117">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -8327,13 +8359,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1">
       <c r="G13" s="117">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -8342,32 +8374,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1">
       <c r="C15" s="117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1">
       <c r="C16" s="117" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1">
       <c r="C17" s="117" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1">
       <c r="C18" s="117" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1">
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1">
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
@@ -8381,7 +8413,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -8391,7 +8423,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
@@ -8405,7 +8437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
       <c r="C24" s="16">
         <v>10</v>
       </c>
@@ -8416,7 +8448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
@@ -8427,7 +8459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="B26" s="117" t="s">
         <v>20</v>
       </c>
@@ -8441,7 +8473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>22</v>
       </c>
@@ -8458,7 +8490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>23</v>
       </c>
@@ -8475,7 +8507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>24</v>
       </c>
@@ -8492,7 +8524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>25</v>
       </c>
@@ -8509,7 +8541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>26</v>
       </c>
@@ -8526,7 +8558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>27</v>
       </c>
@@ -8543,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>28</v>
       </c>
@@ -8560,7 +8592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>29</v>
       </c>
@@ -8571,7 +8603,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>30</v>
       </c>
@@ -8588,7 +8620,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8633,7 +8665,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8642,7 +8674,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8651,7 +8683,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -8668,7 +8700,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8678,7 +8710,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
@@ -8687,36 +8719,36 @@
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="114" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B1" s="115" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C1" s="115" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D1" s="115" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="E1" s="115" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F1" s="115" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="G1" s="115" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H1" s="115" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="I1" s="116" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="104">
         <v>4</v>
       </c>
@@ -8727,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="105" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E2" s="106">
         <v>45575</v>
@@ -8736,7 +8768,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="G2" s="107" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="H2" s="106">
         <v>45292</v>
@@ -8745,7 +8777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" s="104">
         <v>3</v>
       </c>
@@ -8756,7 +8788,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="105" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E3" s="106">
         <v>45576</v>
@@ -8765,16 +8797,16 @@
         <v>0.57638888888888884</v>
       </c>
       <c r="G3" s="107" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="H3" s="106">
         <v>45231</v>
       </c>
       <c r="I3" s="108" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="104">
         <v>9</v>
       </c>
@@ -8785,7 +8817,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="105" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E4" s="106">
         <v>45574</v>
@@ -8794,7 +8826,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="G4" s="107" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="H4" s="106">
         <v>45325</v>
@@ -8803,7 +8835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="104">
         <v>5</v>
       </c>
@@ -8814,7 +8846,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="105" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E5" s="106">
         <v>45573</v>
@@ -8823,7 +8855,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G5" s="105" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="H5" s="106">
         <v>45084</v>
@@ -8832,7 +8864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="109">
         <v>7</v>
       </c>
@@ -8843,7 +8875,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="110" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E6" s="111">
         <v>45566</v>
@@ -8852,13 +8884,13 @@
         <v>0.5229166666666667</v>
       </c>
       <c r="G6" s="110" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="H6" s="111">
         <v>45420</v>
       </c>
       <c r="I6" s="113" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -8905,12 +8937,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1">
       <c r="A1" s="117" t="s">
         <v>31</v>
       </c>
@@ -8945,7 +8977,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1">
       <c r="A2" s="117" t="s">
         <v>41</v>
       </c>
@@ -8991,7 +9023,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1">
       <c r="A3" s="117" t="s">
         <v>43</v>
       </c>
@@ -9037,7 +9069,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1">
       <c r="A4" s="117" t="s">
         <v>45</v>
       </c>
@@ -9083,7 +9115,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1">
       <c r="A5" s="117" t="s">
         <v>47</v>
       </c>
@@ -9129,7 +9161,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1">
       <c r="A6" s="117" t="s">
         <v>49</v>
       </c>
@@ -9175,7 +9207,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1">
       <c r="A7" s="117" t="s">
         <v>52</v>
       </c>
@@ -9209,7 +9241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1">
       <c r="A8" s="117" t="s">
         <v>54</v>
       </c>
@@ -9243,7 +9275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1">
       <c r="A9" s="117" t="s">
         <v>56</v>
       </c>
@@ -9274,7 +9306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1">
       <c r="A10" s="117" t="s">
         <v>58</v>
       </c>
@@ -9290,7 +9322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1">
       <c r="A11" s="117" t="s">
         <v>59</v>
       </c>
@@ -9309,7 +9341,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1">
       <c r="A12" s="117" t="s">
         <v>61</v>
       </c>
@@ -9340,7 +9372,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1">
       <c r="A13" s="117" t="s">
         <v>62</v>
       </c>
@@ -9371,7 +9403,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1">
       <c r="A14" s="117" t="s">
         <v>67</v>
       </c>
@@ -9387,7 +9419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1">
       <c r="A15" s="117" t="s">
         <v>68</v>
       </c>
@@ -9403,7 +9435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1">
       <c r="A16" s="117" t="s">
         <v>69</v>
       </c>
@@ -9419,7 +9451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1">
       <c r="A17" s="117" t="s">
         <v>70</v>
       </c>
@@ -9435,7 +9467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1">
       <c r="A18" s="117" t="s">
         <v>71</v>
       </c>
@@ -9451,7 +9483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1">
       <c r="A19" s="117" t="s">
         <v>72</v>
       </c>
@@ -9467,7 +9499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1">
       <c r="A20" s="117" t="s">
         <v>73</v>
       </c>
@@ -9483,7 +9515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1">
       <c r="A21" s="117" t="s">
         <v>74</v>
       </c>
@@ -9499,7 +9531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1">
       <c r="A22" s="117" t="s">
         <v>76</v>
       </c>
@@ -9515,7 +9547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1">
       <c r="A23" s="117" t="s">
         <v>77</v>
       </c>
@@ -9531,7 +9563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1">
       <c r="A24" s="117" t="s">
         <v>78</v>
       </c>
@@ -9548,7 +9580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1">
       <c r="A25" s="117" t="s">
         <v>79</v>
       </c>
@@ -9564,7 +9596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1">
       <c r="A26" s="117" t="s">
         <v>81</v>
       </c>
@@ -9580,7 +9612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>82</v>
       </c>
@@ -9596,7 +9628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>83</v>
       </c>
@@ -9613,7 +9645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>84</v>
       </c>
@@ -9629,7 +9661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>85</v>
       </c>
@@ -9645,7 +9677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>86</v>
       </c>
@@ -9661,7 +9693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>87</v>
       </c>
@@ -9677,7 +9709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>88</v>
       </c>
@@ -9693,7 +9725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>89</v>
       </c>
@@ -9709,7 +9741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>90</v>
       </c>
@@ -9725,7 +9757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1">
       <c r="A36" s="117" t="s">
         <v>91</v>
       </c>
@@ -9741,7 +9773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1">
       <c r="A37" s="117" t="s">
         <v>92</v>
       </c>
@@ -9757,7 +9789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1">
       <c r="A38" s="117" t="s">
         <v>93</v>
       </c>
@@ -9774,7 +9806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1">
       <c r="A39" s="117" t="s">
         <v>94</v>
       </c>
@@ -9790,7 +9822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1">
       <c r="A40" s="117" t="s">
         <v>95</v>
       </c>
@@ -9806,7 +9838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1">
       <c r="A41" s="117" t="s">
         <v>96</v>
       </c>
@@ -9822,7 +9854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1">
       <c r="A42" s="117" t="s">
         <v>97</v>
       </c>
@@ -9838,7 +9870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1">
       <c r="A43" s="117" t="s">
         <v>98</v>
       </c>
@@ -9854,7 +9886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1">
       <c r="A44" s="117" t="s">
         <v>99</v>
       </c>
@@ -9870,7 +9902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1">
       <c r="A45" s="117" t="s">
         <v>100</v>
       </c>
@@ -9886,7 +9918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1">
       <c r="A46" s="117" t="s">
         <v>101</v>
       </c>
@@ -9902,7 +9934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1">
       <c r="A47" s="117" t="s">
         <v>102</v>
       </c>
@@ -9918,7 +9950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1">
       <c r="A48" s="117" t="s">
         <v>103</v>
       </c>
@@ -9934,7 +9966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1">
       <c r="A49" s="117" t="s">
         <v>104</v>
       </c>
@@ -9950,7 +9982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1">
       <c r="A50" s="117" t="s">
         <v>105</v>
       </c>
@@ -9967,7 +9999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1">
       <c r="A51" s="117" t="s">
         <v>106</v>
       </c>
@@ -9984,7 +10016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1">
       <c r="A52" s="117" t="s">
         <v>107</v>
       </c>
@@ -10000,7 +10032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1">
       <c r="A53" s="117" t="s">
         <v>108</v>
       </c>
@@ -10016,7 +10048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1">
       <c r="A54" s="117" t="s">
         <v>109</v>
       </c>
@@ -10032,7 +10064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1">
       <c r="A55" s="117" t="s">
         <v>110</v>
       </c>
@@ -10048,7 +10080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1">
       <c r="A56" s="117" t="s">
         <v>111</v>
       </c>
@@ -10064,7 +10096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1">
       <c r="A57" s="117" t="s">
         <v>112</v>
       </c>
@@ -10080,7 +10112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="117" t="s">
         <v>113</v>
       </c>
@@ -10096,7 +10128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1">
       <c r="A59" s="117" t="s">
         <v>114</v>
       </c>
@@ -10112,7 +10144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1">
       <c r="A60" s="117" t="s">
         <v>115</v>
       </c>
@@ -10128,7 +10160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1">
       <c r="A61" s="117" t="s">
         <v>116</v>
       </c>
@@ -10144,7 +10176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1">
       <c r="A62" s="117" t="s">
         <v>117</v>
       </c>
@@ -10160,7 +10192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1">
       <c r="A63" s="117" t="s">
         <v>118</v>
       </c>
@@ -10176,7 +10208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1">
       <c r="A64" s="117" t="s">
         <v>119</v>
       </c>
@@ -10192,7 +10224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1">
       <c r="A65" s="117" t="s">
         <v>120</v>
       </c>
@@ -10208,7 +10240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1">
       <c r="A66" s="117" t="s">
         <v>121</v>
       </c>
@@ -10224,7 +10256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1">
       <c r="A67" s="117" t="s">
         <v>122</v>
       </c>
@@ -10240,7 +10272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1">
       <c r="A68" s="117" t="s">
         <v>123</v>
       </c>
@@ -10256,7 +10288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1">
       <c r="A69" s="117" t="s">
         <v>125</v>
       </c>
@@ -10272,7 +10304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1">
       <c r="A70" s="117" t="s">
         <v>127</v>
       </c>
@@ -10288,7 +10320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1">
       <c r="A71" s="117" t="s">
         <v>129</v>
       </c>
@@ -10304,7 +10336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1">
       <c r="A72" s="117" t="s">
         <v>130</v>
       </c>
@@ -10320,7 +10352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1">
       <c r="A73" s="117" t="s">
         <v>131</v>
       </c>
@@ -10336,7 +10368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1">
       <c r="A74" s="117" t="s">
         <v>132</v>
       </c>
@@ -10352,7 +10384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1">
       <c r="A75" s="117" t="s">
         <v>133</v>
       </c>
@@ -10368,7 +10400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1">
       <c r="A76" s="117" t="s">
         <v>134</v>
       </c>
@@ -10384,7 +10416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1">
       <c r="A77" s="117" t="s">
         <v>135</v>
       </c>
@@ -10400,7 +10432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1">
       <c r="A78" s="117" t="s">
         <v>136</v>
       </c>
@@ -10416,7 +10448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1">
       <c r="A79" s="117" t="s">
         <v>137</v>
       </c>
@@ -10432,7 +10464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1">
       <c r="A80" s="117" t="s">
         <v>138</v>
       </c>
@@ -10448,7 +10480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1">
       <c r="A81" s="117" t="s">
         <v>139</v>
       </c>
@@ -10464,7 +10496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1">
       <c r="A82" s="117" t="s">
         <v>141</v>
       </c>
@@ -10480,7 +10512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1">
       <c r="A83" s="117" t="s">
         <v>142</v>
       </c>
@@ -10496,7 +10528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1">
       <c r="A84" s="117" t="s">
         <v>143</v>
       </c>
@@ -10512,7 +10544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1">
       <c r="A85" s="117" t="s">
         <v>144</v>
       </c>
@@ -10528,7 +10560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1">
       <c r="A86" s="117" t="s">
         <v>146</v>
       </c>
@@ -10544,7 +10576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1">
       <c r="A87" s="117" t="s">
         <v>147</v>
       </c>
@@ -10560,7 +10592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1">
       <c r="A88" s="117" t="s">
         <v>148</v>
       </c>
@@ -10576,7 +10608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1">
       <c r="A89" s="117" t="s">
         <v>149</v>
       </c>
@@ -10592,7 +10624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1">
       <c r="A90" s="117" t="s">
         <v>150</v>
       </c>
@@ -10608,7 +10640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1">
       <c r="A91" s="117" t="s">
         <v>151</v>
       </c>
@@ -10624,7 +10656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1">
       <c r="A92" s="117" t="s">
         <v>152</v>
       </c>
@@ -10640,7 +10672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1">
       <c r="A93" s="117" t="s">
         <v>153</v>
       </c>
@@ -10656,7 +10688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1">
       <c r="A94" s="117" t="s">
         <v>154</v>
       </c>
@@ -10672,7 +10704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1">
       <c r="A95" s="117" t="s">
         <v>155</v>
       </c>
@@ -10688,7 +10720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1">
       <c r="A96" s="117" t="s">
         <v>156</v>
       </c>
@@ -10704,7 +10736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1">
       <c r="A97" s="117" t="s">
         <v>157</v>
       </c>
@@ -10720,7 +10752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1">
       <c r="A98" s="117" t="s">
         <v>158</v>
       </c>
@@ -10736,7 +10768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1">
       <c r="A99" s="117" t="s">
         <v>159</v>
       </c>
@@ -10752,20 +10784,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1">
       <c r="A100" s="117" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45716.378380439812</v>
+        <v>45721.473067708335</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1">
       <c r="A101" s="117" t="s">
         <v>161</v>
       </c>
@@ -10781,7 +10813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1">
       <c r="A102" s="117" t="s">
         <v>162</v>
       </c>
@@ -10797,7 +10829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1">
       <c r="A103" s="117" t="s">
         <v>163</v>
       </c>
@@ -10813,7 +10845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1">
       <c r="A104" s="117" t="s">
         <v>164</v>
       </c>
@@ -10829,7 +10861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1">
       <c r="A105" s="117" t="s">
         <v>165</v>
       </c>
@@ -10845,7 +10877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1">
       <c r="A106" s="117" t="s">
         <v>166</v>
       </c>
@@ -10861,7 +10893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1">
       <c r="A107" s="117" t="s">
         <v>167</v>
       </c>
@@ -10877,7 +10909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1">
       <c r="A108" s="117" t="s">
         <v>168</v>
       </c>
@@ -10893,7 +10925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1">
       <c r="A109" s="117" t="s">
         <v>169</v>
       </c>
@@ -10909,7 +10941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1">
       <c r="A110" s="117" t="s">
         <v>170</v>
       </c>
@@ -10925,7 +10957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1">
       <c r="A111" s="117" t="s">
         <v>171</v>
       </c>
@@ -10941,12 +10973,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1">
       <c r="A112" s="117"/>
       <c r="B112" s="117"/>
       <c r="D112" s="117"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1">
       <c r="A113" s="117" t="s">
         <v>172</v>
       </c>
@@ -10962,7 +10994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1">
       <c r="A114" s="117" t="s">
         <v>173</v>
       </c>
@@ -10978,7 +11010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1">
       <c r="A115" s="117" t="s">
         <v>175</v>
       </c>
@@ -10994,7 +11026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1">
       <c r="A116" s="117" t="s">
         <v>177</v>
       </c>
@@ -11010,7 +11042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1">
       <c r="A117" s="117" t="s">
         <v>178</v>
       </c>
@@ -11026,7 +11058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1">
       <c r="A118" s="117" t="s">
         <v>179</v>
       </c>
@@ -11042,7 +11074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1">
       <c r="A119" s="117" t="s">
         <v>180</v>
       </c>
@@ -11058,7 +11090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1">
       <c r="A120" s="117" t="s">
         <v>181</v>
       </c>
@@ -11074,7 +11106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1">
       <c r="A121" s="117" t="s">
         <v>182</v>
       </c>
@@ -11090,7 +11122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1">
       <c r="A122" s="117" t="s">
         <v>183</v>
       </c>
@@ -11106,7 +11138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1">
       <c r="A123" s="117" t="s">
         <v>184</v>
       </c>
@@ -11122,7 +11154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1">
       <c r="A124" s="117" t="s">
         <v>185</v>
       </c>
@@ -11138,7 +11170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1">
       <c r="A125" s="117" t="s">
         <v>186</v>
       </c>
@@ -11154,7 +11186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1">
       <c r="A126" s="117" t="s">
         <v>187</v>
       </c>
@@ -11170,7 +11202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1">
       <c r="A127" s="117" t="s">
         <v>188</v>
       </c>
@@ -11186,7 +11218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1">
       <c r="A128" s="117" t="s">
         <v>189</v>
       </c>
@@ -11202,7 +11234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1">
       <c r="A129" s="117" t="s">
         <v>190</v>
       </c>
@@ -11218,7 +11250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1">
       <c r="A130" s="117" t="s">
         <v>191</v>
       </c>
@@ -11234,7 +11266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1">
       <c r="A131" s="117" t="s">
         <v>192</v>
       </c>
@@ -11250,7 +11282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1">
       <c r="A132" s="117" t="s">
         <v>193</v>
       </c>
@@ -11266,7 +11298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1">
       <c r="A133" s="117" t="s">
         <v>194</v>
       </c>
@@ -11282,7 +11314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1">
       <c r="A134" s="117" t="s">
         <v>195</v>
       </c>
@@ -11298,7 +11330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1">
       <c r="A135" s="117" t="s">
         <v>196</v>
       </c>
@@ -11314,7 +11346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1">
       <c r="A136" s="117" t="s">
         <v>198</v>
       </c>
@@ -11330,7 +11362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1">
       <c r="A137" s="117" t="s">
         <v>199</v>
       </c>
@@ -11346,7 +11378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1">
       <c r="A138" s="117" t="s">
         <v>200</v>
       </c>
@@ -11362,7 +11394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1">
       <c r="A139" s="117" t="s">
         <v>201</v>
       </c>
@@ -11378,7 +11410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1">
       <c r="A140" s="117" t="s">
         <v>202</v>
       </c>
@@ -11394,7 +11426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1">
       <c r="A141" s="117" t="s">
         <v>203</v>
       </c>
@@ -11410,7 +11442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1">
       <c r="A142" s="117" t="s">
         <v>205</v>
       </c>
@@ -11426,7 +11458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1">
       <c r="A143" s="117" t="s">
         <v>206</v>
       </c>
@@ -11442,20 +11474,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1">
       <c r="A144" s="117" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45716</v>
+        <v>45721</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1">
       <c r="A145" s="117" t="s">
         <v>208</v>
       </c>
@@ -11471,7 +11503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1">
       <c r="A146" s="117" t="s">
         <v>210</v>
       </c>
@@ -11487,7 +11519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1">
       <c r="A147" s="117" t="s">
         <v>211</v>
       </c>
@@ -11503,7 +11535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1">
       <c r="A148" s="117" t="s">
         <v>213</v>
       </c>
@@ -11519,7 +11551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1">
       <c r="A149" s="117" t="s">
         <v>214</v>
       </c>
@@ -11535,7 +11567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1">
       <c r="A150" s="117" t="s">
         <v>215</v>
       </c>
@@ -11551,7 +11583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1">
       <c r="A151" s="117" t="s">
         <v>216</v>
       </c>
@@ -11567,7 +11599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1">
       <c r="A152" s="117" t="s">
         <v>217</v>
       </c>
@@ -11583,7 +11615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1">
       <c r="A153" s="117" t="s">
         <v>218</v>
       </c>
@@ -11599,7 +11631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1">
       <c r="A154" s="117" t="s">
         <v>219</v>
       </c>
@@ -11616,7 +11648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1">
       <c r="A155" s="117" t="s">
         <v>220</v>
       </c>
@@ -11632,7 +11664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1">
       <c r="A156" s="117" t="s">
         <v>221</v>
       </c>
@@ -11648,7 +11680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1">
       <c r="A157" s="117" t="s">
         <v>222</v>
       </c>
@@ -11664,7 +11696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1">
       <c r="A158" s="117" t="s">
         <v>223</v>
       </c>
@@ -11680,7 +11712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1">
       <c r="A159" s="117" t="s">
         <v>224</v>
       </c>
@@ -11696,7 +11728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1">
       <c r="A160" s="117" t="s">
         <v>225</v>
       </c>
@@ -11712,7 +11744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1">
       <c r="A161" s="117" t="s">
         <v>226</v>
       </c>
@@ -11728,7 +11760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1">
       <c r="A162" s="117" t="s">
         <v>227</v>
       </c>
@@ -11744,7 +11776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1">
       <c r="A163" s="117" t="s">
         <v>229</v>
       </c>
@@ -11762,10 +11794,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11780,7 +11812,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -11790,17 +11822,17 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="122" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="123"/>
+      <c r="E1" s="122"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -11808,19 +11840,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
@@ -11828,25 +11860,25 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="75" customHeight="1">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="17" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="18" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:8" outlineLevel="1"/>
+    <row r="11" spans="1:8" outlineLevel="1"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
+    <row r="16" spans="1:8" outlineLevel="1"/>
+    <row r="17" outlineLevel="1"/>
+    <row r="18" outlineLevel="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:E2"/>
@@ -11863,14 +11895,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -11892,7 +11924,7 @@
       </c>
       <c r="M1" s="36"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
@@ -11918,7 +11950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
@@ -11941,7 +11973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -11967,7 +11999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
@@ -11987,7 +12019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
@@ -12010,7 +12042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15.75">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -12030,7 +12062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="21">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -12053,7 +12085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -12070,7 +12102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
@@ -12078,7 +12110,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -12087,7 +12119,7 @@
       </c>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1">
       <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
@@ -12101,7 +12133,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
@@ -12112,7 +12144,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
@@ -12126,7 +12158,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
@@ -12137,7 +12169,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
       <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
@@ -12151,12 +12183,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -12168,7 +12200,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -12179,7 +12211,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -12193,12 +12225,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -12207,13 +12239,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -12222,20 +12254,20 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
+    <row r="30" spans="1:6">
       <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
@@ -12249,13 +12281,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -12272,7 +12304,7 @@
       <c r="I1" s="36"/>
       <c r="J1" s="36"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
@@ -12295,7 +12327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
@@ -12318,7 +12350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
@@ -12338,7 +12370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
@@ -12362,7 +12394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
@@ -12385,7 +12417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
@@ -12411,7 +12443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
@@ -12422,7 +12454,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
@@ -12431,7 +12463,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -12449,7 +12481,7 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
@@ -12472,13 +12504,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45716</v>
+        <v>45721</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -12497,7 +12529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
@@ -12520,7 +12552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
@@ -12546,7 +12578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
@@ -12566,7 +12598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
@@ -12589,7 +12621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
@@ -12612,7 +12644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
@@ -12635,7 +12667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
@@ -12658,7 +12690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
@@ -12681,7 +12713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
@@ -12707,7 +12739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
@@ -12733,7 +12765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
@@ -12759,7 +12791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
@@ -12776,7 +12808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
@@ -12802,7 +12834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
@@ -12822,7 +12854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
@@ -12848,7 +12880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
@@ -12868,7 +12900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="G29" s="34" t="s">
         <v>375</v>
       </c>
@@ -12888,7 +12920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="G30" s="34" t="s">
         <v>376</v>
       </c>
@@ -12908,7 +12940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1">
       <c r="G31" s="35" t="s">
         <v>377</v>
       </c>
@@ -12922,7 +12954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="G32" s="34" t="s">
         <v>378</v>
       </c>
@@ -12936,7 +12968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="7:10">
       <c r="G33" s="34" t="s">
         <v>379</v>
       </c>
@@ -12950,7 +12982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="7:10">
       <c r="G34" s="34" t="s">
         <v>380</v>
       </c>
@@ -12964,7 +12996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="7:10">
       <c r="G35" s="34" t="s">
         <v>381</v>
       </c>
@@ -12978,7 +13010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="7:10">
       <c r="G36" s="34" t="s">
         <v>382</v>
       </c>
@@ -12992,7 +13024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="7:10">
       <c r="G37" s="34" t="s">
         <v>383</v>
       </c>
@@ -13006,110 +13038,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="7:10">
       <c r="G39" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="22" priority="58">
+    <cfRule type="expression" dxfId="40" priority="58">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="21" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="20" priority="114"/>
+    <cfRule type="aboveAverage" dxfId="38" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="19" priority="73" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="37" priority="73" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="18" priority="71">
+    <cfRule type="containsBlanks" dxfId="36" priority="71">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="17" priority="70">
+    <cfRule type="containsErrors" dxfId="35" priority="70">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="16" priority="69" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="34" priority="69" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="15" priority="67" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="33" priority="67" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="14" priority="66">
+    <cfRule type="notContainsBlanks" dxfId="32" priority="66">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="13" priority="65">
+    <cfRule type="notContainsErrors" dxfId="31" priority="65">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="12" priority="64" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="30" priority="64" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="11" priority="63" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="29" priority="63" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="10" priority="115" rank="1"/>
+    <cfRule type="top10" dxfId="28" priority="115" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="9" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="45" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="8" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="26" priority="56" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -13143,10 +13175,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="0" priority="96"/>
+    <cfRule type="uniqueValues" dxfId="18" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="44">
@@ -13569,7 +13601,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -13581,12 +13613,12 @@
     <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -13612,7 +13644,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="C4" s="117" t="s">
         <v>42</v>
       </c>
@@ -13643,7 +13675,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="117" t="s">
         <v>44</v>
       </c>
@@ -13674,7 +13706,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="C6" s="117" t="s">
         <v>391</v>
       </c>
@@ -13707,7 +13739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>392</v>
       </c>
@@ -13718,22 +13750,22 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>435</v>
+        <v>393</v>
       </c>
       <c r="G8" t="s">
-        <v>436</v>
+        <v>394</v>
       </c>
       <c r="H8" t="s">
-        <v>437</v>
+        <v>395</v>
       </c>
       <c r="I8" t="s">
-        <v>438</v>
+        <v>396</v>
       </c>
       <c r="J8" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="C9">
         <v>3</v>
       </c>
@@ -13761,18 +13793,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C11" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D11" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="C12">
         <v>3</v>
       </c>
@@ -13780,9 +13812,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -13791,7 +13823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="C15">
         <v>3</v>
       </c>
@@ -13799,9 +13831,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -13810,7 +13842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4">
       <c r="C18">
         <v>3</v>
       </c>
@@ -13818,9 +13850,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -13829,7 +13861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4">
       <c r="C21">
         <v>3</v>
       </c>
@@ -13837,9 +13869,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -13848,7 +13880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4">
       <c r="C24">
         <v>3</v>
       </c>
@@ -13856,9 +13888,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4">
       <c r="B26" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -13867,7 +13899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4">
       <c r="C27">
         <v>3</v>
       </c>
@@ -13875,7 +13907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4">
       <c r="C28" t="s">
         <v>391</v>
       </c>
@@ -13884,36 +13916,36 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4">
       <c r="B30" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C30" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D30" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" hidden="1">
       <c r="C31" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D31" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
       <c r="C32" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D32" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -13936,7 +13968,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -13957,9 +13989,9 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15">
       <c r="A1" s="92" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -13967,7 +13999,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -13975,21 +14007,21 @@
       <c r="E2" s="117"/>
       <c r="F2" s="117"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="89" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="117"/>
       <c r="B4" s="117"/>
       <c r="C4" s="89" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D4">
         <v>12.1</v>
@@ -14016,10 +14048,10 @@
         <v>12052</v>
       </c>
       <c r="L4" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="117"/>
       <c r="B5" s="117"/>
       <c r="C5" s="90" t="s">
@@ -14032,7 +14064,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" s="117"/>
       <c r="B6" s="117"/>
       <c r="C6" s="91">
@@ -14045,7 +14077,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" s="117"/>
       <c r="B7" s="117"/>
       <c r="C7" s="90" t="s">
@@ -14058,7 +14090,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" s="117"/>
       <c r="B8" s="117"/>
       <c r="C8" s="91">
@@ -14071,7 +14103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" s="117"/>
       <c r="B9" s="117"/>
       <c r="C9" s="90" t="s">
@@ -14084,7 +14116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" s="117"/>
       <c r="B10" s="117"/>
       <c r="C10" s="91">
@@ -14097,7 +14129,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -14108,7 +14140,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -14119,7 +14151,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -14130,7 +14162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -14141,7 +14173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -14152,7 +14184,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -14163,7 +14195,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:12">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -14174,7 +14206,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -14185,7 +14217,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -14196,7 +14228,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -14207,9 +14239,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12">
       <c r="C21" s="90" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -14248,31 +14280,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B2" s="117"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -14284,25 +14316,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="51">
       <c r="A1" s="99" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B7" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -14310,7 +14342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -14318,7 +14350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -14326,7 +14358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4</v>
       </c>
@@ -14334,7 +14366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28715"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28723"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ABEBB5E-CC42-4D3F-B076-13470D76BC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4533F51F-F931-45DF-A942-2AE56A765B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
   </externalReferences>
   <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="3062" r:id="rId16"/>
+    <pivotCache cacheId="5712" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3117,6 +3117,22 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="6350" cap="rnd" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -3660,6 +3676,19 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -5068,6 +5097,19 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$27:$B$35</c:f>
@@ -5381,6 +5423,20 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -6193,6 +6249,19 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:strRef>
               <c:f>Sheet1!A27:A35</c:f>
@@ -7902,7 +7971,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="3062" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="5712" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -11070,7 +11139,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45736.475918171294</v>
+        <v>45741.742819212966</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -11760,7 +11829,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45736</v>
+        <v>45741</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -12790,7 +12859,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45736</v>
+        <v>45741</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA4A409-66E7-4CFC-A548-ECD1D6D1B504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CDD9BA5-D2AB-4895-AC80-1F8DA821EE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23295" yWindow="195" windowWidth="21600" windowHeight="11385" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23295" yWindow="195" windowWidth="21600" windowHeight="11385" firstSheet="13" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,9 @@
   <externalReferences>
     <externalReference r:id="rId15"/>
   </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
+    <pivotCache cacheId="1350" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1372,7 +1372,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2372,7 +2372,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2385,6 +2384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2392,6 +2392,157 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2798,157 +2949,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -3048,7 +3048,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3099,6 +3099,22 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="6350" cap="rnd" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -3370,7 +3386,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3403,7 +3419,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3474,7 +3490,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3507,7 +3523,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3551,7 +3567,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3579,7 +3595,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3642,6 +3658,11 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -3906,7 +3927,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -3968,7 +3989,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -3996,7 +4017,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4614,7 +4635,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4980,7 +5001,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5050,6 +5071,11 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:trendline>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$27:$B$35</c:f>
@@ -5192,7 +5218,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5251,7 +5277,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5279,7 +5305,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5363,6 +5389,12 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -5625,7 +5657,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -5687,7 +5719,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -5715,7 +5747,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -6027,7 +6059,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="88853993"/>
@@ -6089,7 +6121,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="17781237"/>
@@ -6117,7 +6149,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -6444,7 +6476,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="344680958"/>
@@ -6520,7 +6552,7 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="998664793"/>
@@ -6543,7 +6575,7 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -7572,7 +7604,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="1350" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -7722,7 +7754,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7734,22 +7766,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7859,9 +7891,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7899,7 +7931,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -8005,7 +8037,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8147,7 +8179,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -8159,7 +8191,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -8168,7 +8200,7 @@
     <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1">
       <c r="A1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -8177,7 +8209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.75">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -8190,25 +8222,25 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="119"/>
+      <c r="I2" s="123"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1">
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="120">
+      <c r="K3" s="119">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1">
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
@@ -8221,50 +8253,50 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="121"/>
+      <c r="K4" s="120"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1">
       <c r="C5" s="117">
         <v>42</v>
       </c>
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="121"/>
+      <c r="K5" s="120"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1">
       <c r="G6" s="117">
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="121"/>
+      <c r="K6" s="120"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1">
       <c r="C7" s="117">
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="121"/>
+      <c r="K7" s="120"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1">
       <c r="G8" s="117">
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="122"/>
+      <c r="K8" s="121"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1">
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -8274,7 +8306,7 @@
       </c>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1">
       <c r="C10" s="117">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -8283,13 +8315,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1">
       <c r="C11" s="117">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1">
       <c r="C12" s="117">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -8298,13 +8330,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1">
       <c r="G13" s="117">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -8313,32 +8345,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1">
       <c r="C15" s="117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1">
       <c r="C16" s="117" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1">
       <c r="C17" s="117" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1">
       <c r="C18" s="117" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1">
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1">
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
@@ -8352,7 +8384,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -8362,7 +8394,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
@@ -8376,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
       <c r="C24" s="16">
         <v>10</v>
       </c>
@@ -8387,7 +8419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
@@ -8398,7 +8430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="B26" s="117" t="s">
         <v>20</v>
       </c>
@@ -8412,7 +8444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>22</v>
       </c>
@@ -8429,7 +8461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>23</v>
       </c>
@@ -8446,7 +8478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>24</v>
       </c>
@@ -8463,7 +8495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>25</v>
       </c>
@@ -8480,7 +8512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>26</v>
       </c>
@@ -8497,7 +8529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>27</v>
       </c>
@@ -8514,7 +8546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>28</v>
       </c>
@@ -8531,7 +8563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>29</v>
       </c>
@@ -8542,7 +8574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>30</v>
       </c>
@@ -8559,7 +8591,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8604,7 +8636,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8613,7 +8645,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8622,7 +8654,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -8639,7 +8671,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8649,7 +8681,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
@@ -8658,7 +8690,7 @@
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="114" t="s">
         <v>417</v>
       </c>
@@ -8687,7 +8719,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="104">
         <v>4</v>
       </c>
@@ -8716,7 +8748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" s="104">
         <v>3</v>
       </c>
@@ -8745,7 +8777,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" s="104">
         <v>9</v>
       </c>
@@ -8774,7 +8806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="104">
         <v>5</v>
       </c>
@@ -8803,7 +8835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="109">
         <v>7</v>
       </c>
@@ -8876,12 +8908,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1">
       <c r="A1" s="117" t="s">
         <v>31</v>
       </c>
@@ -8916,7 +8948,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1">
       <c r="A2" s="117" t="s">
         <v>41</v>
       </c>
@@ -8962,7 +8994,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1">
       <c r="A3" s="117" t="s">
         <v>43</v>
       </c>
@@ -9008,7 +9040,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1">
       <c r="A4" s="117" t="s">
         <v>45</v>
       </c>
@@ -9054,7 +9086,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1">
       <c r="A5" s="117" t="s">
         <v>47</v>
       </c>
@@ -9100,7 +9132,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1">
       <c r="A6" s="117" t="s">
         <v>49</v>
       </c>
@@ -9146,7 +9178,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1">
       <c r="A7" s="117" t="s">
         <v>52</v>
       </c>
@@ -9180,7 +9212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1">
       <c r="A8" s="117" t="s">
         <v>54</v>
       </c>
@@ -9214,7 +9246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1">
       <c r="A9" s="117" t="s">
         <v>56</v>
       </c>
@@ -9245,7 +9277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1">
       <c r="A10" s="117" t="s">
         <v>58</v>
       </c>
@@ -9261,7 +9293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1">
       <c r="A11" s="117" t="s">
         <v>59</v>
       </c>
@@ -9280,7 +9312,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1">
       <c r="A12" s="117" t="s">
         <v>61</v>
       </c>
@@ -9311,7 +9343,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1">
       <c r="A13" s="117" t="s">
         <v>62</v>
       </c>
@@ -9342,7 +9374,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1">
       <c r="A14" s="117" t="s">
         <v>67</v>
       </c>
@@ -9358,7 +9390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1">
       <c r="A15" s="117" t="s">
         <v>68</v>
       </c>
@@ -9374,7 +9406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1">
       <c r="A16" s="117" t="s">
         <v>69</v>
       </c>
@@ -9390,7 +9422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1">
       <c r="A17" s="117" t="s">
         <v>70</v>
       </c>
@@ -9406,7 +9438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1">
       <c r="A18" s="117" t="s">
         <v>71</v>
       </c>
@@ -9422,7 +9454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1">
       <c r="A19" s="117" t="s">
         <v>72</v>
       </c>
@@ -9438,7 +9470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1">
       <c r="A20" s="117" t="s">
         <v>73</v>
       </c>
@@ -9454,7 +9486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1">
       <c r="A21" s="117" t="s">
         <v>74</v>
       </c>
@@ -9470,7 +9502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1">
       <c r="A22" s="117" t="s">
         <v>76</v>
       </c>
@@ -9486,7 +9518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1">
       <c r="A23" s="117" t="s">
         <v>77</v>
       </c>
@@ -9502,7 +9534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1">
       <c r="A24" s="117" t="s">
         <v>78</v>
       </c>
@@ -9519,7 +9551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1">
       <c r="A25" s="117" t="s">
         <v>79</v>
       </c>
@@ -9535,7 +9567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1">
       <c r="A26" s="117" t="s">
         <v>81</v>
       </c>
@@ -9551,7 +9583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>82</v>
       </c>
@@ -9567,7 +9599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>83</v>
       </c>
@@ -9584,7 +9616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>84</v>
       </c>
@@ -9600,7 +9632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>85</v>
       </c>
@@ -9616,7 +9648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>86</v>
       </c>
@@ -9632,7 +9664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>87</v>
       </c>
@@ -9648,7 +9680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>88</v>
       </c>
@@ -9664,7 +9696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>89</v>
       </c>
@@ -9680,7 +9712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>90</v>
       </c>
@@ -9696,7 +9728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1">
       <c r="A36" s="117" t="s">
         <v>91</v>
       </c>
@@ -9712,7 +9744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1">
       <c r="A37" s="117" t="s">
         <v>92</v>
       </c>
@@ -9728,7 +9760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1">
       <c r="A38" s="117" t="s">
         <v>93</v>
       </c>
@@ -9745,7 +9777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1">
       <c r="A39" s="117" t="s">
         <v>94</v>
       </c>
@@ -9761,7 +9793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1">
       <c r="A40" s="117" t="s">
         <v>95</v>
       </c>
@@ -9777,7 +9809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1">
       <c r="A41" s="117" t="s">
         <v>96</v>
       </c>
@@ -9793,7 +9825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1">
       <c r="A42" s="117" t="s">
         <v>97</v>
       </c>
@@ -9809,7 +9841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1">
       <c r="A43" s="117" t="s">
         <v>98</v>
       </c>
@@ -9825,7 +9857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1">
       <c r="A44" s="117" t="s">
         <v>99</v>
       </c>
@@ -9841,7 +9873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1">
       <c r="A45" s="117" t="s">
         <v>100</v>
       </c>
@@ -9857,7 +9889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1">
       <c r="A46" s="117" t="s">
         <v>101</v>
       </c>
@@ -9873,7 +9905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1">
       <c r="A47" s="117" t="s">
         <v>102</v>
       </c>
@@ -9889,7 +9921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1">
       <c r="A48" s="117" t="s">
         <v>103</v>
       </c>
@@ -9905,7 +9937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1">
       <c r="A49" s="117" t="s">
         <v>104</v>
       </c>
@@ -9921,7 +9953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1">
       <c r="A50" s="117" t="s">
         <v>105</v>
       </c>
@@ -9938,7 +9970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1">
       <c r="A51" s="117" t="s">
         <v>106</v>
       </c>
@@ -9955,7 +9987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1">
       <c r="A52" s="117" t="s">
         <v>107</v>
       </c>
@@ -9971,7 +10003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1">
       <c r="A53" s="117" t="s">
         <v>108</v>
       </c>
@@ -9987,7 +10019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1">
       <c r="A54" s="117" t="s">
         <v>109</v>
       </c>
@@ -10003,7 +10035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1">
       <c r="A55" s="117" t="s">
         <v>110</v>
       </c>
@@ -10019,7 +10051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1">
       <c r="A56" s="117" t="s">
         <v>111</v>
       </c>
@@ -10035,7 +10067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1">
       <c r="A57" s="117" t="s">
         <v>112</v>
       </c>
@@ -10051,7 +10083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="117" t="s">
         <v>113</v>
       </c>
@@ -10067,7 +10099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1">
       <c r="A59" s="117" t="s">
         <v>114</v>
       </c>
@@ -10083,7 +10115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1">
       <c r="A60" s="117" t="s">
         <v>115</v>
       </c>
@@ -10099,7 +10131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1">
       <c r="A61" s="117" t="s">
         <v>116</v>
       </c>
@@ -10115,7 +10147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1">
       <c r="A62" s="117" t="s">
         <v>117</v>
       </c>
@@ -10131,7 +10163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1">
       <c r="A63" s="117" t="s">
         <v>118</v>
       </c>
@@ -10147,7 +10179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1">
       <c r="A64" s="117" t="s">
         <v>119</v>
       </c>
@@ -10163,7 +10195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1">
       <c r="A65" s="117" t="s">
         <v>120</v>
       </c>
@@ -10179,7 +10211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1">
       <c r="A66" s="117" t="s">
         <v>121</v>
       </c>
@@ -10195,7 +10227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1">
       <c r="A67" s="117" t="s">
         <v>122</v>
       </c>
@@ -10211,7 +10243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1">
       <c r="A68" s="117" t="s">
         <v>123</v>
       </c>
@@ -10227,7 +10259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1">
       <c r="A69" s="117" t="s">
         <v>125</v>
       </c>
@@ -10243,7 +10275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1">
       <c r="A70" s="117" t="s">
         <v>127</v>
       </c>
@@ -10259,7 +10291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1">
       <c r="A71" s="117" t="s">
         <v>129</v>
       </c>
@@ -10275,7 +10307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1">
       <c r="A72" s="117" t="s">
         <v>130</v>
       </c>
@@ -10291,7 +10323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1">
       <c r="A73" s="117" t="s">
         <v>131</v>
       </c>
@@ -10307,7 +10339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1">
       <c r="A74" s="117" t="s">
         <v>132</v>
       </c>
@@ -10323,7 +10355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1">
       <c r="A75" s="117" t="s">
         <v>133</v>
       </c>
@@ -10339,7 +10371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1">
       <c r="A76" s="117" t="s">
         <v>134</v>
       </c>
@@ -10355,7 +10387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1">
       <c r="A77" s="117" t="s">
         <v>135</v>
       </c>
@@ -10371,7 +10403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1">
       <c r="A78" s="117" t="s">
         <v>136</v>
       </c>
@@ -10387,7 +10419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1">
       <c r="A79" s="117" t="s">
         <v>137</v>
       </c>
@@ -10403,7 +10435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1">
       <c r="A80" s="117" t="s">
         <v>138</v>
       </c>
@@ -10419,7 +10451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1">
       <c r="A81" s="117" t="s">
         <v>139</v>
       </c>
@@ -10435,7 +10467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1">
       <c r="A82" s="117" t="s">
         <v>141</v>
       </c>
@@ -10451,7 +10483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1">
       <c r="A83" s="117" t="s">
         <v>142</v>
       </c>
@@ -10467,7 +10499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1">
       <c r="A84" s="117" t="s">
         <v>143</v>
       </c>
@@ -10483,7 +10515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1">
       <c r="A85" s="117" t="s">
         <v>144</v>
       </c>
@@ -10499,7 +10531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1">
       <c r="A86" s="117" t="s">
         <v>146</v>
       </c>
@@ -10515,7 +10547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1">
       <c r="A87" s="117" t="s">
         <v>147</v>
       </c>
@@ -10531,7 +10563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1">
       <c r="A88" s="117" t="s">
         <v>148</v>
       </c>
@@ -10547,7 +10579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1">
       <c r="A89" s="117" t="s">
         <v>149</v>
       </c>
@@ -10563,7 +10595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1">
       <c r="A90" s="117" t="s">
         <v>150</v>
       </c>
@@ -10579,7 +10611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1">
       <c r="A91" s="117" t="s">
         <v>151</v>
       </c>
@@ -10595,7 +10627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1">
       <c r="A92" s="117" t="s">
         <v>152</v>
       </c>
@@ -10611,7 +10643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1">
       <c r="A93" s="117" t="s">
         <v>153</v>
       </c>
@@ -10627,7 +10659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1">
       <c r="A94" s="117" t="s">
         <v>154</v>
       </c>
@@ -10643,7 +10675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1">
       <c r="A95" s="117" t="s">
         <v>155</v>
       </c>
@@ -10659,7 +10691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1">
       <c r="A96" s="117" t="s">
         <v>156</v>
       </c>
@@ -10675,7 +10707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1">
       <c r="A97" s="117" t="s">
         <v>157</v>
       </c>
@@ -10691,7 +10723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1">
       <c r="A98" s="117" t="s">
         <v>158</v>
       </c>
@@ -10707,7 +10739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1">
       <c r="A99" s="117" t="s">
         <v>159</v>
       </c>
@@ -10723,20 +10755,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1">
       <c r="A100" s="117" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45594.46900636574</v>
+        <v>45631.469745023147</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1">
       <c r="A101" s="117" t="s">
         <v>161</v>
       </c>
@@ -10752,7 +10784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1">
       <c r="A102" s="117" t="s">
         <v>162</v>
       </c>
@@ -10768,7 +10800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1">
       <c r="A103" s="117" t="s">
         <v>163</v>
       </c>
@@ -10784,7 +10816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1">
       <c r="A104" s="117" t="s">
         <v>164</v>
       </c>
@@ -10800,7 +10832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1">
       <c r="A105" s="117" t="s">
         <v>165</v>
       </c>
@@ -10816,7 +10848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1">
       <c r="A106" s="117" t="s">
         <v>166</v>
       </c>
@@ -10832,7 +10864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1">
       <c r="A107" s="117" t="s">
         <v>167</v>
       </c>
@@ -10848,7 +10880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1">
       <c r="A108" s="117" t="s">
         <v>168</v>
       </c>
@@ -10864,7 +10896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1">
       <c r="A109" s="117" t="s">
         <v>169</v>
       </c>
@@ -10880,7 +10912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1">
       <c r="A110" s="117" t="s">
         <v>170</v>
       </c>
@@ -10896,7 +10928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1">
       <c r="A111" s="117" t="s">
         <v>171</v>
       </c>
@@ -10912,12 +10944,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1">
       <c r="A112" s="117"/>
       <c r="B112" s="117"/>
       <c r="D112" s="117"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1">
       <c r="A113" s="117" t="s">
         <v>172</v>
       </c>
@@ -10933,7 +10965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1">
       <c r="A114" s="117" t="s">
         <v>173</v>
       </c>
@@ -10949,7 +10981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1">
       <c r="A115" s="117" t="s">
         <v>175</v>
       </c>
@@ -10965,7 +10997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1">
       <c r="A116" s="117" t="s">
         <v>177</v>
       </c>
@@ -10981,7 +11013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1">
       <c r="A117" s="117" t="s">
         <v>178</v>
       </c>
@@ -10997,7 +11029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1">
       <c r="A118" s="117" t="s">
         <v>179</v>
       </c>
@@ -11013,7 +11045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1">
       <c r="A119" s="117" t="s">
         <v>180</v>
       </c>
@@ -11029,7 +11061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1">
       <c r="A120" s="117" t="s">
         <v>181</v>
       </c>
@@ -11045,7 +11077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1">
       <c r="A121" s="117" t="s">
         <v>182</v>
       </c>
@@ -11061,7 +11093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1">
       <c r="A122" s="117" t="s">
         <v>183</v>
       </c>
@@ -11077,7 +11109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1">
       <c r="A123" s="117" t="s">
         <v>184</v>
       </c>
@@ -11093,7 +11125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1">
       <c r="A124" s="117" t="s">
         <v>185</v>
       </c>
@@ -11109,7 +11141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1">
       <c r="A125" s="117" t="s">
         <v>186</v>
       </c>
@@ -11125,7 +11157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1">
       <c r="A126" s="117" t="s">
         <v>187</v>
       </c>
@@ -11141,7 +11173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1">
       <c r="A127" s="117" t="s">
         <v>188</v>
       </c>
@@ -11157,7 +11189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1">
       <c r="A128" s="117" t="s">
         <v>189</v>
       </c>
@@ -11173,7 +11205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1">
       <c r="A129" s="117" t="s">
         <v>190</v>
       </c>
@@ -11189,7 +11221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1">
       <c r="A130" s="117" t="s">
         <v>191</v>
       </c>
@@ -11205,7 +11237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1">
       <c r="A131" s="117" t="s">
         <v>192</v>
       </c>
@@ -11221,7 +11253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1">
       <c r="A132" s="117" t="s">
         <v>193</v>
       </c>
@@ -11237,7 +11269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1">
       <c r="A133" s="117" t="s">
         <v>194</v>
       </c>
@@ -11253,7 +11285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1">
       <c r="A134" s="117" t="s">
         <v>195</v>
       </c>
@@ -11269,7 +11301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1">
       <c r="A135" s="117" t="s">
         <v>196</v>
       </c>
@@ -11285,7 +11317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1">
       <c r="A136" s="117" t="s">
         <v>198</v>
       </c>
@@ -11301,7 +11333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1">
       <c r="A137" s="117" t="s">
         <v>199</v>
       </c>
@@ -11317,7 +11349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1">
       <c r="A138" s="117" t="s">
         <v>200</v>
       </c>
@@ -11333,7 +11365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1">
       <c r="A139" s="117" t="s">
         <v>201</v>
       </c>
@@ -11349,7 +11381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1">
       <c r="A140" s="117" t="s">
         <v>202</v>
       </c>
@@ -11365,7 +11397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1">
       <c r="A141" s="117" t="s">
         <v>203</v>
       </c>
@@ -11381,7 +11413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1">
       <c r="A142" s="117" t="s">
         <v>205</v>
       </c>
@@ -11397,7 +11429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1">
       <c r="A143" s="117" t="s">
         <v>206</v>
       </c>
@@ -11413,20 +11445,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1">
       <c r="A144" s="117" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45594</v>
+        <v>45631</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1">
       <c r="A145" s="117" t="s">
         <v>208</v>
       </c>
@@ -11442,7 +11474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1">
       <c r="A146" s="117" t="s">
         <v>210</v>
       </c>
@@ -11458,7 +11490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1">
       <c r="A147" s="117" t="s">
         <v>211</v>
       </c>
@@ -11474,7 +11506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1">
       <c r="A148" s="117" t="s">
         <v>213</v>
       </c>
@@ -11490,7 +11522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1">
       <c r="A149" s="117" t="s">
         <v>214</v>
       </c>
@@ -11506,7 +11538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1">
       <c r="A150" s="117" t="s">
         <v>215</v>
       </c>
@@ -11522,7 +11554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1">
       <c r="A151" s="117" t="s">
         <v>216</v>
       </c>
@@ -11538,7 +11570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1">
       <c r="A152" s="117" t="s">
         <v>217</v>
       </c>
@@ -11554,7 +11586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1">
       <c r="A153" s="117" t="s">
         <v>218</v>
       </c>
@@ -11570,7 +11602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1">
       <c r="A154" s="117" t="s">
         <v>219</v>
       </c>
@@ -11587,7 +11619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1">
       <c r="A155" s="117" t="s">
         <v>220</v>
       </c>
@@ -11603,7 +11635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1">
       <c r="A156" s="117" t="s">
         <v>221</v>
       </c>
@@ -11619,7 +11651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1">
       <c r="A157" s="117" t="s">
         <v>222</v>
       </c>
@@ -11635,7 +11667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1">
       <c r="A158" s="117" t="s">
         <v>223</v>
       </c>
@@ -11651,7 +11683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1">
       <c r="A159" s="117" t="s">
         <v>224</v>
       </c>
@@ -11667,7 +11699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1">
       <c r="A160" s="117" t="s">
         <v>225</v>
       </c>
@@ -11683,7 +11715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1">
       <c r="A161" s="117" t="s">
         <v>226</v>
       </c>
@@ -11699,7 +11731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1">
       <c r="A162" s="117" t="s">
         <v>227</v>
       </c>
@@ -11715,7 +11747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1">
       <c r="A163" s="117" t="s">
         <v>229</v>
       </c>
@@ -11733,10 +11765,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11751,7 +11783,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -11761,17 +11793,17 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="122" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="123"/>
+      <c r="E1" s="122"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -11779,19 +11811,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
@@ -11799,25 +11831,25 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="75" customHeight="1">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="17" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="18" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:8" outlineLevel="1"/>
+    <row r="11" spans="1:8" outlineLevel="1"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
+    <row r="16" spans="1:8" outlineLevel="1"/>
+    <row r="17" outlineLevel="1"/>
+    <row r="18" outlineLevel="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:E2"/>
@@ -11834,14 +11866,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -11863,7 +11895,7 @@
       </c>
       <c r="M1" s="36"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
@@ -11889,7 +11921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
@@ -11912,7 +11944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -11938,7 +11970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
@@ -11958,7 +11990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
@@ -11981,7 +12013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15.75">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -12001,7 +12033,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="21">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -12024,7 +12056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -12041,7 +12073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
@@ -12049,7 +12081,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -12058,7 +12090,7 @@
       </c>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1">
       <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
@@ -12072,7 +12104,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
@@ -12083,7 +12115,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
@@ -12097,7 +12129,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
@@ -12108,7 +12140,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
       <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
@@ -12122,12 +12154,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -12139,7 +12171,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -12150,7 +12182,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -12164,12 +12196,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -12178,13 +12210,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -12193,20 +12225,20 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
+    <row r="30" spans="1:6">
       <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
@@ -12220,13 +12252,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -12243,7 +12275,7 @@
       <c r="I1" s="36"/>
       <c r="J1" s="36"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
@@ -12266,7 +12298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
@@ -12289,7 +12321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
@@ -12309,7 +12341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
@@ -12333,7 +12365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
@@ -12356,7 +12388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
@@ -12382,7 +12414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
@@ -12393,7 +12425,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
@@ -12402,7 +12434,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -12420,7 +12452,7 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
@@ -12443,13 +12475,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45594</v>
+        <v>45631</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -12468,7 +12500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
@@ -12491,7 +12523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
@@ -12517,7 +12549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
@@ -12537,7 +12569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
@@ -12560,7 +12592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
@@ -12583,7 +12615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
@@ -12606,7 +12638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
@@ -12629,7 +12661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
@@ -12652,7 +12684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
@@ -12678,7 +12710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
@@ -12704,7 +12736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
@@ -12730,7 +12762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
@@ -12747,7 +12779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
@@ -12773,7 +12805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
@@ -12793,7 +12825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
@@ -12819,7 +12851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
@@ -12839,7 +12871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="G29" s="34" t="s">
         <v>375</v>
       </c>
@@ -12859,7 +12891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="G30" s="34" t="s">
         <v>376</v>
       </c>
@@ -12879,7 +12911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1">
       <c r="G31" s="35" t="s">
         <v>377</v>
       </c>
@@ -12893,7 +12925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="G32" s="34" t="s">
         <v>378</v>
       </c>
@@ -12907,7 +12939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="7:10">
       <c r="G33" s="34" t="s">
         <v>379</v>
       </c>
@@ -12921,7 +12953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="7:10">
       <c r="G34" s="34" t="s">
         <v>380</v>
       </c>
@@ -12935,7 +12967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="7:10">
       <c r="G35" s="34" t="s">
         <v>381</v>
       </c>
@@ -12949,7 +12981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="7:10">
       <c r="G36" s="34" t="s">
         <v>382</v>
       </c>
@@ -12963,7 +12995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="7:10">
       <c r="G37" s="34" t="s">
         <v>383</v>
       </c>
@@ -12977,110 +13009,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="7:10">
       <c r="G39" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="22" priority="58">
+    <cfRule type="expression" dxfId="40" priority="58">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="21" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="20" priority="114"/>
+    <cfRule type="aboveAverage" dxfId="38" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="19" priority="73" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="37" priority="73" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="18" priority="71">
+    <cfRule type="containsBlanks" dxfId="36" priority="71">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="17" priority="70">
+    <cfRule type="containsErrors" dxfId="35" priority="70">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="16" priority="69" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="34" priority="69" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="15" priority="67" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="33" priority="67" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="14" priority="66">
+    <cfRule type="notContainsBlanks" dxfId="32" priority="66">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="13" priority="65">
+    <cfRule type="notContainsErrors" dxfId="31" priority="65">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="12" priority="64" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="30" priority="64" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="11" priority="63" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="29" priority="63" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="10" priority="115" rank="1"/>
+    <cfRule type="top10" dxfId="28" priority="115" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="9" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="45" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="8" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="26" priority="56" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -13114,10 +13146,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="0" priority="96"/>
+    <cfRule type="uniqueValues" dxfId="18" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="44">
@@ -13540,7 +13572,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -13552,12 +13584,12 @@
     <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -13583,7 +13615,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="C4" s="117" t="s">
         <v>42</v>
       </c>
@@ -13614,7 +13646,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="117" t="s">
         <v>44</v>
       </c>
@@ -13645,7 +13677,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="C6" s="117" t="s">
         <v>391</v>
       </c>
@@ -13678,7 +13710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>392</v>
       </c>
@@ -13689,7 +13721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="C9">
         <v>3</v>
       </c>
@@ -13697,7 +13729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
         <v>393</v>
       </c>
@@ -13708,7 +13740,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="C12">
         <v>3</v>
       </c>
@@ -13716,7 +13748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
         <v>396</v>
       </c>
@@ -13727,7 +13759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="C15">
         <v>3</v>
       </c>
@@ -13735,7 +13767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4">
       <c r="B17" t="s">
         <v>397</v>
       </c>
@@ -13746,7 +13778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4">
       <c r="C18">
         <v>3</v>
       </c>
@@ -13754,7 +13786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
         <v>398</v>
       </c>
@@ -13765,7 +13797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4">
       <c r="C21">
         <v>3</v>
       </c>
@@ -13773,7 +13805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
         <v>399</v>
       </c>
@@ -13784,7 +13816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4">
       <c r="C24">
         <v>3</v>
       </c>
@@ -13792,7 +13824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4">
       <c r="B26" t="s">
         <v>400</v>
       </c>
@@ -13803,7 +13835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4">
       <c r="C27">
         <v>3</v>
       </c>
@@ -13811,7 +13843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4">
       <c r="C28" t="s">
         <v>391</v>
       </c>
@@ -13820,7 +13852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4">
       <c r="B30" t="s">
         <v>401</v>
       </c>
@@ -13831,7 +13863,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:4" hidden="1">
       <c r="C31" t="s">
         <v>404</v>
       </c>
@@ -13839,7 +13871,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:4">
       <c r="C32" t="s">
         <v>405</v>
       </c>
@@ -13847,7 +13879,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
         <v>406</v>
       </c>
@@ -13872,7 +13904,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -13893,7 +13925,7 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15">
       <c r="A1" s="92" t="s">
         <v>407</v>
       </c>
@@ -13903,7 +13935,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -13911,7 +13943,7 @@
       <c r="E2" s="117"/>
       <c r="F2" s="117"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="89" t="s">
@@ -13921,7 +13953,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4" s="117"/>
       <c r="B4" s="117"/>
       <c r="C4" s="89" t="s">
@@ -13955,7 +13987,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12">
       <c r="A5" s="117"/>
       <c r="B5" s="117"/>
       <c r="C5" s="90" t="s">
@@ -13968,7 +14000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" s="117"/>
       <c r="B6" s="117"/>
       <c r="C6" s="91">
@@ -13981,7 +14013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" s="117"/>
       <c r="B7" s="117"/>
       <c r="C7" s="90" t="s">
@@ -13994,7 +14026,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" s="117"/>
       <c r="B8" s="117"/>
       <c r="C8" s="91">
@@ -14007,7 +14039,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" s="117"/>
       <c r="B9" s="117"/>
       <c r="C9" s="90" t="s">
@@ -14020,7 +14052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" s="117"/>
       <c r="B10" s="117"/>
       <c r="C10" s="91">
@@ -14033,7 +14065,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -14044,7 +14076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -14055,7 +14087,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -14066,7 +14098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -14077,7 +14109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -14088,7 +14120,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -14099,7 +14131,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:12">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -14110,7 +14142,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -14121,7 +14153,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -14132,7 +14164,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -14143,7 +14175,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12">
       <c r="C21" s="90" t="s">
         <v>411</v>
       </c>
@@ -14184,29 +14216,29 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>413</v>
       </c>
       <c r="B2" s="117"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>415</v>
       </c>
@@ -14220,9 +14252,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="51">
       <c r="A1" s="99" t="s">
         <v>416</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28715"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28724"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ABEBB5E-CC42-4D3F-B076-13470D76BC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0F3413D-2983-43BC-B7D9-48EACAB90F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,14 @@
   <externalReferences>
     <externalReference r:id="rId15"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$27:$A$35</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$26</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$27:$B$35</definedName>
+  </definedNames>
   <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="3062" r:id="rId16"/>
+    <pivotCache cacheId="1259" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3608,6 +3613,793 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>doughnut chart with hole</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.30285577409492809"/>
+          <c:y val="1.397398743755821E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>first dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F77B4"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000014-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF7F0E"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="AEC7E8"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000018-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFBB78"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001A-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2CA02C"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001C-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="98DF8A"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001E-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="D62728"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000020-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF9896"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000022-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9467BD"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000024-D17F-47AA-A8EC-52019D60CBD0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000025-D17F-47AA-A8EC-52019D60CBD0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>first dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>second dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$27:$C$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="998664793"/>
+        <c:axId val="344680958"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="998664793"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="344680958"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="344680958"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998664793"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -6436,38 +7228,58 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>horizontal bar chart</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>first dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4472C4"/>
+              <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
@@ -6549,41 +7361,32 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="7030A0"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000000-2AE2-4EDC-856C-ECBD6B1ECD21}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>second dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ED7D31"/>
+              <a:srgbClr val="C65911"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="C65911"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
@@ -6665,16 +7468,17 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="C65911"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000001-2AE2-4EDC-856C-ECBD6B1ECD21}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6686,17 +7490,26 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="998664793"/>
-        <c:axId val="344680958"/>
+        <c:gapWidth val="70"/>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="998664793"/>
+        <c:axId val="17781237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6711,14 +7524,14 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:txPr>
@@ -6726,7 +7539,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6736,7 +7549,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="344680958"/>
+        <c:crossAx val="88853993"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6744,32 +7557,21 @@
         <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="344680958"/>
+        <c:axId val="88853993"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln cmpd="sng">
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6784,25 +7586,22 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6812,10 +7611,15 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="998664793"/>
+        <c:crossAx val="17781237"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -6825,9 +7629,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0">
+            <a:defRPr sz="1000" b="0" i="0">
               <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
@@ -6840,12 +7644,163 @@
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Chart Title</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1400" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>Chart Title</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="waterfall" uniqueId="{5051EC33-743B-4C68-89C0-7179D8BFE55F}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v>first dataset</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels pos="outEnd">
+            <cx:txPr>
+              <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr" rtl="0">
+                  <a:defRPr sz="1200" b="0" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </cx:txPr>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:subtotals/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0.5"/>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1200" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1200" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0">
+      <cx:txPr>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1200" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </cx:txPr>
+    </cx:legend>
+  </cx:chart>
+</cx:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6888,7 +7843,555 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="395">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="2">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7324,6 +8827,89 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB44F912-9067-8FA7-675B-52C07F194DE5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
       <xdr:row>4</xdr:row>
@@ -7643,10 +9229,92 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B187E09F-172F-47EE-A6CD-3039B7DE0CE4}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5D2716A1-A175-44F9-BBD0-26D27F88F15C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>781050</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89D5E293-E7D5-4DCE-B066-872C6428DD51}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B187E09F-172F-47EE-A6CD-3039B7DE0CE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -7694,7 +9362,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -7902,7 +9570,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="3062" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="1259" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8939,6 +10607,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -11070,7 +12739,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45736.475918171294</v>
+        <v>45748.695485300923</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -11760,7 +13429,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45736</v>
+        <v>45748</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -12790,7 +14459,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45736</v>
+        <v>45748</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28507"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{157AC437-DB84-431C-BDD0-6A0421B0B149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A0F40E7-3C8A-4E57-BEF5-0AD89070EFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23295" yWindow="195" windowWidth="21600" windowHeight="11385" firstSheet="13" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23295" yWindow="195" windowWidth="21600" windowHeight="11385" firstSheet="8" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
   </externalReferences>
   <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="3563" r:id="rId16"/>
+    <pivotCache cacheId="4689" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2375,6 +2375,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2387,7 +2388,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -3593,6 +3593,422 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>first dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>second dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$27:$C$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="998664793"/>
+        <c:axId val="344680958"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="998664793"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="344680958"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="344680958"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998664793"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -6150,38 +6566,58 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>horizontal bar chart</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>first dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4472C4"/>
+              <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
@@ -6263,41 +6699,32 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="7030A0"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000000-F453-4C27-9300-76287E40C06A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>second dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ED7D31"/>
+              <a:srgbClr val="C65911"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="C65911"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
@@ -6379,16 +6806,17 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="C65911"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000001-F453-4C27-9300-76287E40C06A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6400,17 +6828,26 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="998664793"/>
-        <c:axId val="344680958"/>
+        <c:gapWidth val="70"/>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="998664793"/>
+        <c:axId val="17781237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6425,14 +6862,14 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:txPr>
@@ -6440,7 +6877,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6450,7 +6887,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="344680958"/>
+        <c:crossAx val="88853993"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6458,32 +6895,21 @@
         <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="344680958"/>
+        <c:axId val="88853993"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln cmpd="sng">
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6498,25 +6924,22 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6526,22 +6949,27 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="998664793"/>
+        <c:crossAx val="17781237"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:txPr>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0">
+            <a:defRPr sz="1000" b="0" i="0">
               <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
@@ -6554,6 +6982,380 @@
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>single dataset doughnut chart</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2400"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>first dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F77B4"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF7F0E"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="AEC7E8"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFBB78"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2CA02C"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="98DF8A"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="D62728"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF9896"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9467BD"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-0405-4A2D-A579-D08CD080C2D2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000012-0405-4A2D-A579-D08CD080C2D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -7316,6 +8118,88 @@
     </xdr:graphicFrame>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5814E5DD-0992-44E8-87F0-31C94A544112}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E2B20B98-FA84-44C9-8DBB-5852658E9967}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>895350</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD226922-C98E-43FE-A6FF-0C6686AB1592}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5814E5DD-0992-44E8-87F0-31C94A544112}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7575,7 +8459,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="3563" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="4689" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8193,7 +9077,7 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="123"/>
+      <c r="I2" s="119"/>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1">
@@ -8203,10 +9087,10 @@
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="119">
+      <c r="K3" s="120">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
@@ -8224,10 +9108,10 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1">
@@ -8237,10 +9121,10 @@
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1">
@@ -8248,7 +9132,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="120"/>
+      <c r="K6" s="121"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1">
@@ -8256,7 +9140,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="120"/>
+      <c r="K7" s="121"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1">
@@ -8264,7 +9148,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="121"/>
+      <c r="K8" s="122"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1">
@@ -10732,7 +11616,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45663.51402037037</v>
+        <v>45667.778077893519</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -11422,7 +12306,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -11771,10 +12655,10 @@
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="122" t="s">
+      <c r="D1" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="122"/>
+      <c r="E1" s="123"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -11787,8 +12671,8 @@
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
@@ -12452,7 +13336,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28723"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28919"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4533F51F-F931-45DF-A942-2AE56A765B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{680A992B-769D-4DF5-8BBD-9B4319917BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
   </externalReferences>
   <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5712" r:id="rId16"/>
+    <pivotCache cacheId="11034" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3624,6 +3624,785 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>doughnut chart with hole</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>first dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F77B4"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000014-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF7F0E"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="AEC7E8"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000018-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFBB78"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001A-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2CA02C"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001C-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="98DF8A"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001E-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="D62728"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000020-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF9896"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000022-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9467BD"/>
+              </a:solidFill>
+              <a:ln w="14288" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000024-4968-47CD-A428-E1CFDB94D5E6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000025-4968-47CD-A428-E1CFDB94D5E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>first dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>second dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$27:$C$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="998664793"/>
+        <c:axId val="344680958"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="998664793"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="344680958"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="344680958"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998664793"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -6505,41 +7284,74 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>horizontal bar chart</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>first dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4472C4"/>
+              <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -6618,41 +7430,32 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="7030A0"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000001-4F1A-4275-B2BE-C9AFCD205303}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>second dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ED7D31"/>
+              <a:srgbClr val="C65911"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="C65911"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
@@ -6734,16 +7537,17 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="C65911"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000002-4F1A-4275-B2BE-C9AFCD205303}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6755,17 +7559,26 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="998664793"/>
-        <c:axId val="344680958"/>
+        <c:gapWidth val="70"/>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="998664793"/>
+        <c:axId val="17781237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6780,14 +7593,14 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:txPr>
@@ -6795,7 +7608,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6805,7 +7618,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="344680958"/>
+        <c:crossAx val="88853993"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6813,32 +7626,21 @@
         <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="344680958"/>
+        <c:axId val="88853993"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln cmpd="sng">
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6853,25 +7655,22 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6881,10 +7680,15 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="998664793"/>
+        <c:crossAx val="17781237"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -6894,9 +7698,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0">
+            <a:defRPr sz="1000" b="0" i="0">
               <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
@@ -6909,6 +7713,16 @@
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -7712,6 +8526,88 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8A2F032-405F-4BA7-AB00-B42F129443DB}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5D2716A1-A175-44F9-BBD0-26D27F88F15C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C61D9073-4096-46BA-BD71-5483ACC71F2A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B8A2F032-405F-4BA7-AB00-B42F129443DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7971,7 +8867,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="5712" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="11034" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -11139,7 +12035,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45741.742819212966</v>
+        <v>45799.563060763889</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -11829,7 +12725,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45741</v>
+        <v>45799</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -12859,7 +13755,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45741</v>
+        <v>45799</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rar/rar-workspace/os2/tests/__xlsx__/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A476F739-B139-4713-A5CB-3C0E11EABA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DD048F-3D20-334B-864B-CDAF5F5A5BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="680" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,15 @@
     <sheet name="jestImages" sheetId="15" r:id="rId12"/>
     <sheet name="jestOneCellAnchor" sheetId="16" r:id="rId13"/>
     <sheet name="jestDataValidations" sheetId="17" r:id="rId14"/>
+    <sheet name="jestLocked" sheetId="18" r:id="rId15"/>
+    <sheet name="jestPartiallyLocked" sheetId="19" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId17"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId16"/>
+    <pivotCache cacheId="5" r:id="rId18"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2372,7 +2374,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="47">
     <dxf>
       <font>
         <b val="0"/>
@@ -2584,194 +2586,6 @@
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
@@ -2783,207 +2597,6 @@
           <bgColor theme="9"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3344,8 +2957,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="2" xr9:uid="{33B8EB55-D8D8-4B00-B5CF-C84A8AC9E775}">
-      <tableStyleElement type="wholeTable" dxfId="70"/>
-      <tableStyleElement type="firstRowStripe" dxfId="69"/>
+      <tableStyleElement type="wholeTable" dxfId="46"/>
+      <tableStyleElement type="firstRowStripe" dxfId="45"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3373,7 +2986,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3990,7 +3603,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4353,7 +3966,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -4769,7 +4382,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5214,7 +4827,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5832,7 +5445,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6198,7 +5811,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -6510,7 +6123,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6941,7 +6554,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7343,7 +6956,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7646,7 +7259,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9230,7 +8843,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -9380,7 +8993,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="68" dataDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9392,22 +9005,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="66" totalsRowDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="59">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="57">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="55">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="52" totalsRowDxfId="51">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9828,13 +9441,13 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" customWidth="1"/>
+    <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.19921875" customWidth="1"/>
+    <col min="6" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9846,7 +9459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -10228,7 +9841,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10273,7 +9886,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10282,7 +9895,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10291,10 +9904,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.140625" customWidth="1"/>
-    <col min="2" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="65.19921875" customWidth="1"/>
+    <col min="2" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10308,7 +9921,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10318,13 +9931,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="3" max="4" width="14.19921875" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" customWidth="1"/>
+    <col min="7" max="7" width="14.19921875" customWidth="1"/>
+    <col min="8" max="8" width="20.19921875" customWidth="1"/>
+    <col min="9" max="9" width="17.19921875" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10562,15 +10175,35 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{827A154B-649F-9248-B45E-D1F5000EB396}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E9A493-0805-C541-B367-D56900C82F13}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0630FA18-71FC-4ACD-8379-39A3603D1DD6}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12421,7 +12054,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45989.427180092593</v>
+        <v>46028.934024074071</v>
       </c>
       <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -13111,7 +12744,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45989</v>
+        <v>46028</v>
       </c>
       <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -13425,10 +13058,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13443,14 +13076,14 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" outlineLevel="1"/>
-    <col min="11" max="11" width="9.140625" outlineLevel="1" collapsed="1"/>
+    <col min="6" max="6" width="14.19921875" customWidth="1"/>
+    <col min="10" max="10" width="9.19921875" outlineLevel="1"/>
+    <col min="11" max="11" width="9.19921875" outlineLevel="1" collapsed="1"/>
     <col min="12" max="14" width="0" hidden="1" outlineLevel="2"/>
-    <col min="15" max="18" width="9.140625" outlineLevel="1"/>
+    <col min="15" max="18" width="9.19921875" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -13513,21 +13146,21 @@
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.38411710219623751</v>
+        <v>0.69450535790710388</v>
       </c>
       <c r="B30">
         <f ca="1"/>
-        <v>9.794149803384844E-2</v>
+        <v>0.36697595067154309</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <f ca="1"/>
-        <v>0.66351595791263507</v>
+        <v>5.6962617314857855E-2</v>
       </c>
       <c r="B31">
         <f ca="1"/>
-        <v>5.0911295821026714E-2</v>
+        <v>4.4896354655804327E-2</v>
       </c>
     </row>
   </sheetData>
@@ -13546,14 +13179,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.796875" customWidth="1"/>
+    <col min="5" max="5" width="18.19921875" customWidth="1"/>
+    <col min="13" max="13" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -13624,7 +13257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -13693,7 +13326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -13713,7 +13346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -13736,7 +13369,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -13761,7 +13394,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -13834,12 +13467,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -13851,7 +13484,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -13862,7 +13495,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="61" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -13876,12 +13509,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -13890,13 +13523,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -13905,19 +13538,19 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="87" t="s">
         <v>314</v>
@@ -13932,13 +13565,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.19921875" customWidth="1"/>
+    <col min="7" max="7" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -14114,7 +13747,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -14161,7 +13794,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45989</v>
+        <v>46028</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -14600,7 +14233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G31" s="35" t="s">
         <v>377</v>
       </c>
@@ -14704,104 +14337,104 @@
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="47" priority="59">
+    <cfRule type="expression" dxfId="23" priority="59">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="46" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="45" priority="115"/>
+    <cfRule type="aboveAverage" dxfId="21" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="44" priority="74" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="20" priority="74" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="43" priority="72">
+    <cfRule type="containsBlanks" dxfId="19" priority="72">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="42" priority="71">
+    <cfRule type="containsErrors" dxfId="18" priority="71">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="41" priority="70" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="17" priority="70" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="40" priority="68" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="16" priority="68" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="39" priority="67">
+    <cfRule type="notContainsBlanks" dxfId="15" priority="67">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="38" priority="66">
+    <cfRule type="notContainsErrors" dxfId="14" priority="66">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="37" priority="65" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="13" priority="65" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="36" priority="64" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="12" priority="64" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="24" priority="116" percent="1" bottom="1" rank="50"/>
+    <cfRule type="top10" dxfId="11" priority="116" percent="1" bottom="1" rank="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="35" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="34" priority="57" operator="notEqual">
+    <cfRule type="cellIs" dxfId="9" priority="57" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="31" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -14835,16 +14468,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:C29">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
       <formula>$B$23</formula>
       <formula>2+2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="26" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="25" priority="97"/>
+    <cfRule type="uniqueValues" dxfId="0" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="45">
@@ -15267,16 +14900,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.19921875" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" customWidth="1"/>
+    <col min="5" max="5" width="26.3984375" customWidth="1"/>
+    <col min="6" max="6" width="27.59765625" customWidth="1"/>
+    <col min="7" max="7" width="23.59765625" customWidth="1"/>
+    <col min="8" max="8" width="16.19921875" customWidth="1"/>
+    <col min="9" max="9" width="18.796875" customWidth="1"/>
+    <col min="10" max="10" width="17.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -15284,7 +14917,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -15634,28 +15267,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="92" t="s">
         <v>412</v>
       </c>
@@ -15946,10 +15579,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.140625" customWidth="1"/>
-    <col min="2" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="65.19921875" customWidth="1"/>
+    <col min="2" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -15982,9 +15615,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>421</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rar/rar-workspace/o-spreadsheet/tests/__xlsx__/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F832354-F3E9-4BC5-A260-88E8A391D52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426B52DC-0E6D-434B-97A7-7C1D77E909FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,15 @@
     <sheet name="jestImages" sheetId="15" r:id="rId12"/>
     <sheet name="jestOneCellAnchor" sheetId="16" r:id="rId13"/>
     <sheet name="jestDataValidations" sheetId="17" r:id="rId14"/>
+    <sheet name="jestLocked" sheetId="18" r:id="rId15"/>
+    <sheet name="jestPartiallyLocked" sheetId="19" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId17"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
+    <pivotCache cacheId="0" r:id="rId18"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -77,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="443">
   <si>
     <t>CF =42</t>
   </si>
@@ -1404,6 +1406,9 @@
   </si>
   <si>
     <t>Decimal with formula</t>
+  </si>
+  <si>
+    <t>jestPar</t>
   </si>
 </sst>
 </file>
@@ -1563,6 +1568,7 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1581,6 +1587,7 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="29">
@@ -2151,7 +2158,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2335,6 +2342,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2351,21 +2371,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2980,7 +2985,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3597,7 +3602,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3960,7 +3965,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -4376,7 +4381,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4821,7 +4826,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5439,7 +5444,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5805,7 +5810,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -6117,7 +6122,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6548,7 +6553,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6950,7 +6955,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7253,7 +7258,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9435,13 +9440,13 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" customWidth="1"/>
+    <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.19921875" customWidth="1"/>
+    <col min="6" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9453,7 +9458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -9463,10 +9468,10 @@
       <c r="G2" s="104">
         <v>5</v>
       </c>
-      <c r="H2" s="105" t="s">
+      <c r="H2" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="111"/>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9476,10 +9481,10 @@
       <c r="G3" s="104">
         <v>8</v>
       </c>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="107">
+      <c r="K3" s="112">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
@@ -9497,10 +9502,10 @@
       <c r="G4" s="104">
         <v>9</v>
       </c>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="108"/>
+      <c r="K4" s="113"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9510,10 +9515,10 @@
       <c r="G5" s="104">
         <v>15</v>
       </c>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="108"/>
+      <c r="K5" s="113"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9521,7 +9526,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="108"/>
+      <c r="K6" s="113"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9529,7 +9534,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="108"/>
+      <c r="K7" s="113"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9537,7 +9542,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="109"/>
+      <c r="K8" s="114"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9880,7 +9885,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9889,7 +9894,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9898,10 +9903,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.140625" customWidth="1"/>
-    <col min="2" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="65.19921875" customWidth="1"/>
+    <col min="2" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9915,7 +9920,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9925,74 +9930,74 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="3" max="4" width="14.19921875" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" customWidth="1"/>
+    <col min="7" max="7" width="14.19921875" customWidth="1"/>
+    <col min="8" max="8" width="20.19921875" customWidth="1"/>
+    <col min="9" max="9" width="17.19921875" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="106" t="s">
         <v>423</v>
       </c>
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="107" t="s">
         <v>424</v>
       </c>
-      <c r="C1" s="113" t="s">
+      <c r="C1" s="107" t="s">
         <v>425</v>
       </c>
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="107" t="s">
         <v>426</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="E1" s="107" t="s">
         <v>427</v>
       </c>
-      <c r="F1" s="113" t="s">
+      <c r="F1" s="107" t="s">
         <v>428</v>
       </c>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="107" t="s">
         <v>429</v>
       </c>
-      <c r="H1" s="113" t="s">
+      <c r="H1" s="107" t="s">
         <v>430</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="108" t="s">
         <v>431</v>
       </c>
-      <c r="J1" s="111" t="s">
+      <c r="J1" s="105" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="115">
+      <c r="A2">
         <v>4</v>
       </c>
-      <c r="B2" s="115">
+      <c r="B2">
         <v>99.5</v>
       </c>
-      <c r="C2" s="115">
-        <v>1</v>
-      </c>
-      <c r="D2" s="115" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>432</v>
       </c>
-      <c r="E2" s="116">
+      <c r="E2" s="39">
         <v>45575</v>
       </c>
-      <c r="F2" s="117">
+      <c r="F2" s="109">
         <v>0.64583333333333337</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="G2" s="109" t="s">
         <v>433</v>
       </c>
-      <c r="H2" s="116">
+      <c r="H2" s="39">
         <v>45292</v>
       </c>
-      <c r="I2" s="115">
+      <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
@@ -10000,31 +10005,31 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="115">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="115">
+      <c r="B3">
         <v>40</v>
       </c>
-      <c r="C3" s="115">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" t="s">
         <v>434</v>
       </c>
-      <c r="E3" s="116">
+      <c r="E3" s="39">
         <v>45576</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="109">
         <v>0.57638888888888884</v>
       </c>
-      <c r="G3" s="117" t="s">
+      <c r="G3" s="109" t="s">
         <v>435</v>
       </c>
-      <c r="H3" s="116">
+      <c r="H3" s="39">
         <v>45231</v>
       </c>
-      <c r="I3" s="115" t="s">
+      <c r="I3" t="s">
         <v>433</v>
       </c>
       <c r="J3">
@@ -10032,31 +10037,31 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="115">
+      <c r="A4">
         <v>9</v>
       </c>
-      <c r="B4" s="115">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="115">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="D4" t="s">
         <v>436</v>
       </c>
-      <c r="E4" s="116">
+      <c r="E4" s="39">
         <v>45574</v>
       </c>
-      <c r="F4" s="117">
+      <c r="F4" s="109">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G4" s="117" t="s">
+      <c r="G4" s="109" t="s">
         <v>437</v>
       </c>
-      <c r="H4" s="116">
+      <c r="H4" s="39">
         <v>45325</v>
       </c>
-      <c r="I4" s="115">
+      <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
@@ -10064,31 +10069,31 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="115">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="115">
+      <c r="B5">
         <v>120</v>
       </c>
-      <c r="C5" s="115">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="115" t="s">
+      <c r="D5" t="s">
         <v>434</v>
       </c>
-      <c r="E5" s="116">
+      <c r="E5" s="39">
         <v>45573</v>
       </c>
-      <c r="F5" s="117">
+      <c r="F5" s="109">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G5" s="115" t="s">
+      <c r="G5" t="s">
         <v>438</v>
       </c>
-      <c r="H5" s="116">
+      <c r="H5" s="39">
         <v>45084</v>
       </c>
-      <c r="I5" s="115">
+      <c r="I5">
         <v>3</v>
       </c>
       <c r="J5">
@@ -10096,31 +10101,31 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="115">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B6" s="115">
+      <c r="B6">
         <v>12</v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="115" t="s">
+      <c r="D6" t="s">
         <v>436</v>
       </c>
-      <c r="E6" s="116">
+      <c r="E6" s="39">
         <v>45566</v>
       </c>
-      <c r="F6" s="117">
+      <c r="F6" s="109">
         <v>0.5229166666666667</v>
       </c>
-      <c r="G6" s="115" t="s">
+      <c r="G6" t="s">
         <v>439</v>
       </c>
-      <c r="H6" s="116">
+      <c r="H6" s="39">
         <v>45420</v>
       </c>
-      <c r="I6" s="115" t="s">
+      <c r="I6" t="s">
         <v>438</v>
       </c>
       <c r="J6">
@@ -10169,15 +10174,41 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F1EE53-8DB1-8E42-8F85-8DA1198B2F8E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9764D1-3430-D84E-97FD-5994DCB5A95F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
+        <v>442</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0630FA18-71FC-4ACD-8379-39A3603D1DD6}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12028,7 +12059,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45938.493500231481</v>
+        <v>45958.349332986108</v>
       </c>
       <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -12718,7 +12749,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>45958</v>
       </c>
       <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -13050,14 +13081,14 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" outlineLevel="1"/>
-    <col min="11" max="11" width="9.140625" outlineLevel="1" collapsed="1"/>
+    <col min="6" max="6" width="14.19921875" customWidth="1"/>
+    <col min="10" max="10" width="9.19921875" outlineLevel="1"/>
+    <col min="11" max="11" width="9.19921875" outlineLevel="1" collapsed="1"/>
     <col min="12" max="14" width="0" hidden="1" outlineLevel="2"/>
-    <col min="15" max="18" width="9.140625" outlineLevel="1"/>
+    <col min="15" max="18" width="9.19921875" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -13067,10 +13098,10 @@
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="115" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="110"/>
+      <c r="E1" s="115"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -13083,8 +13114,8 @@
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
@@ -13120,21 +13151,21 @@
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.7272925709748963</v>
+        <v>0.19306066892136098</v>
       </c>
       <c r="B30">
         <f ca="1"/>
-        <v>0.95782684877879687</v>
+        <v>0.63094881256040525</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <f ca="1"/>
-        <v>0.31704384406036645</v>
+        <v>0.6492933023183558</v>
       </c>
       <c r="B31">
         <f ca="1"/>
-        <v>8.7112099778747121E-2</v>
+        <v>0.95172352038340891</v>
       </c>
     </row>
   </sheetData>
@@ -13153,14 +13184,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.796875" customWidth="1"/>
+    <col min="5" max="5" width="18.19921875" customWidth="1"/>
+    <col min="13" max="13" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -13231,7 +13262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -13300,7 +13331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -13320,7 +13351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -13343,7 +13374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -13368,7 +13399,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -13441,12 +13472,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -13458,7 +13489,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -13469,7 +13500,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="61" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -13483,12 +13514,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -13497,13 +13528,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -13512,19 +13543,19 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="87" t="s">
         <v>314</v>
@@ -13539,13 +13570,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.19921875" customWidth="1"/>
+    <col min="7" max="7" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -13721,7 +13752,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -13768,7 +13799,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>45958</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -14207,7 +14238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G31" s="35" t="s">
         <v>377</v>
       </c>
@@ -14874,16 +14905,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.19921875" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" customWidth="1"/>
+    <col min="5" max="5" width="26.3984375" customWidth="1"/>
+    <col min="6" max="6" width="27.59765625" customWidth="1"/>
+    <col min="7" max="7" width="23.59765625" customWidth="1"/>
+    <col min="8" max="8" width="16.19921875" customWidth="1"/>
+    <col min="9" max="9" width="18.796875" customWidth="1"/>
+    <col min="10" max="10" width="17.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -14891,7 +14922,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -15241,28 +15272,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="92" t="s">
         <v>412</v>
       </c>
@@ -15553,10 +15584,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.140625" customWidth="1"/>
-    <col min="2" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="65.19921875" customWidth="1"/>
+    <col min="2" max="26" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -15589,9 +15620,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>421</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F832354-F3E9-4BC5-A260-88E8A391D52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A476F739-B139-4713-A5CB-3C0E11EABA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
+    <pivotCache cacheId="1" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1563,6 +1563,7 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1581,6 +1582,7 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="29">
@@ -2151,7 +2153,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2335,6 +2337,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2351,28 +2366,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="71">
     <dxf>
       <font>
         <b val="0"/>
@@ -2553,6 +2553,399 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2951,8 +3344,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="2" xr9:uid="{33B8EB55-D8D8-4B00-B5CF-C84A8AC9E775}">
-      <tableStyleElement type="wholeTable" dxfId="46"/>
-      <tableStyleElement type="firstRowStripe" dxfId="45"/>
+      <tableStyleElement type="wholeTable" dxfId="70"/>
+      <tableStyleElement type="firstRowStripe" dxfId="69"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -8837,7 +9230,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8987,7 +9380,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="68" dataDxfId="67">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8999,22 +9392,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="59">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="57">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="55">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="52" totalsRowDxfId="51">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9463,10 +9856,10 @@
       <c r="G2" s="104">
         <v>5</v>
       </c>
-      <c r="H2" s="105" t="s">
+      <c r="H2" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="111"/>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9476,10 +9869,10 @@
       <c r="G3" s="104">
         <v>8</v>
       </c>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="107">
+      <c r="K3" s="112">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
@@ -9497,10 +9890,10 @@
       <c r="G4" s="104">
         <v>9</v>
       </c>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="108"/>
+      <c r="K4" s="113"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9510,10 +9903,10 @@
       <c r="G5" s="104">
         <v>15</v>
       </c>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="108"/>
+      <c r="K5" s="113"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9521,7 +9914,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="108"/>
+      <c r="K6" s="113"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9529,7 +9922,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="108"/>
+      <c r="K7" s="113"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9537,7 +9930,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="109"/>
+      <c r="K8" s="114"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9835,7 +10228,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9936,63 +10329,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="106" t="s">
         <v>423</v>
       </c>
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="107" t="s">
         <v>424</v>
       </c>
-      <c r="C1" s="113" t="s">
+      <c r="C1" s="107" t="s">
         <v>425</v>
       </c>
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="107" t="s">
         <v>426</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="E1" s="107" t="s">
         <v>427</v>
       </c>
-      <c r="F1" s="113" t="s">
+      <c r="F1" s="107" t="s">
         <v>428</v>
       </c>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="107" t="s">
         <v>429</v>
       </c>
-      <c r="H1" s="113" t="s">
+      <c r="H1" s="107" t="s">
         <v>430</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="108" t="s">
         <v>431</v>
       </c>
-      <c r="J1" s="111" t="s">
+      <c r="J1" s="105" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="115">
+      <c r="A2">
         <v>4</v>
       </c>
-      <c r="B2" s="115">
+      <c r="B2">
         <v>99.5</v>
       </c>
-      <c r="C2" s="115">
-        <v>1</v>
-      </c>
-      <c r="D2" s="115" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>432</v>
       </c>
-      <c r="E2" s="116">
+      <c r="E2" s="39">
         <v>45575</v>
       </c>
-      <c r="F2" s="117">
+      <c r="F2" s="109">
         <v>0.64583333333333337</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="G2" s="109" t="s">
         <v>433</v>
       </c>
-      <c r="H2" s="116">
+      <c r="H2" s="39">
         <v>45292</v>
       </c>
-      <c r="I2" s="115">
+      <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
@@ -10000,31 +10393,31 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="115">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="115">
+      <c r="B3">
         <v>40</v>
       </c>
-      <c r="C3" s="115">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" t="s">
         <v>434</v>
       </c>
-      <c r="E3" s="116">
+      <c r="E3" s="39">
         <v>45576</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="109">
         <v>0.57638888888888884</v>
       </c>
-      <c r="G3" s="117" t="s">
+      <c r="G3" s="109" t="s">
         <v>435</v>
       </c>
-      <c r="H3" s="116">
+      <c r="H3" s="39">
         <v>45231</v>
       </c>
-      <c r="I3" s="115" t="s">
+      <c r="I3" t="s">
         <v>433</v>
       </c>
       <c r="J3">
@@ -10032,31 +10425,31 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="115">
+      <c r="A4">
         <v>9</v>
       </c>
-      <c r="B4" s="115">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="115">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="D4" t="s">
         <v>436</v>
       </c>
-      <c r="E4" s="116">
+      <c r="E4" s="39">
         <v>45574</v>
       </c>
-      <c r="F4" s="117">
+      <c r="F4" s="109">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G4" s="117" t="s">
+      <c r="G4" s="109" t="s">
         <v>437</v>
       </c>
-      <c r="H4" s="116">
+      <c r="H4" s="39">
         <v>45325</v>
       </c>
-      <c r="I4" s="115">
+      <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
@@ -10064,31 +10457,31 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="115">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="115">
+      <c r="B5">
         <v>120</v>
       </c>
-      <c r="C5" s="115">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="115" t="s">
+      <c r="D5" t="s">
         <v>434</v>
       </c>
-      <c r="E5" s="116">
+      <c r="E5" s="39">
         <v>45573</v>
       </c>
-      <c r="F5" s="117">
+      <c r="F5" s="109">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G5" s="115" t="s">
+      <c r="G5" t="s">
         <v>438</v>
       </c>
-      <c r="H5" s="116">
+      <c r="H5" s="39">
         <v>45084</v>
       </c>
-      <c r="I5" s="115">
+      <c r="I5">
         <v>3</v>
       </c>
       <c r="J5">
@@ -10096,31 +10489,31 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="115">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B6" s="115">
+      <c r="B6">
         <v>12</v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="115" t="s">
+      <c r="D6" t="s">
         <v>436</v>
       </c>
-      <c r="E6" s="116">
+      <c r="E6" s="39">
         <v>45566</v>
       </c>
-      <c r="F6" s="117">
+      <c r="F6" s="109">
         <v>0.5229166666666667</v>
       </c>
-      <c r="G6" s="115" t="s">
+      <c r="G6" t="s">
         <v>439</v>
       </c>
-      <c r="H6" s="116">
+      <c r="H6" s="39">
         <v>45420</v>
       </c>
-      <c r="I6" s="115" t="s">
+      <c r="I6" t="s">
         <v>438</v>
       </c>
       <c r="J6">
@@ -12028,7 +12421,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45938.493500231481</v>
+        <v>45989.427180092593</v>
       </c>
       <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -12718,7 +13111,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>45989</v>
       </c>
       <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -13032,10 +13425,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13067,10 +13460,10 @@
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="115" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="110"/>
+      <c r="E1" s="115"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -13083,8 +13476,8 @@
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
@@ -13120,21 +13513,21 @@
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.7272925709748963</v>
+        <v>0.38411710219623751</v>
       </c>
       <c r="B30">
         <f ca="1"/>
-        <v>0.95782684877879687</v>
+        <v>9.794149803384844E-2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <f ca="1"/>
-        <v>0.31704384406036645</v>
+        <v>0.66351595791263507</v>
       </c>
       <c r="B31">
         <f ca="1"/>
-        <v>8.7112099778747121E-2</v>
+        <v>5.0911295821026714E-2</v>
       </c>
     </row>
   </sheetData>
@@ -13768,7 +14161,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>45989</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -14311,104 +14704,104 @@
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="23" priority="59">
+    <cfRule type="expression" dxfId="47" priority="59">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="47" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="21" priority="115"/>
+    <cfRule type="aboveAverage" dxfId="45" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="20" priority="74" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="44" priority="74" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="19" priority="72">
+    <cfRule type="containsBlanks" dxfId="43" priority="72">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="18" priority="71">
+    <cfRule type="containsErrors" dxfId="42" priority="71">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="17" priority="70" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="41" priority="70" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="16" priority="68" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="40" priority="68" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="67">
+    <cfRule type="notContainsBlanks" dxfId="39" priority="67">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="14" priority="66">
+    <cfRule type="notContainsErrors" dxfId="38" priority="66">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="13" priority="65" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="37" priority="65" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="12" priority="64" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="36" priority="64" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="11" priority="116" rank="1"/>
+    <cfRule type="top10" dxfId="24" priority="116" percent="1" bottom="1" rank="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="9" priority="57" operator="notEqual">
+    <cfRule type="cellIs" dxfId="34" priority="57" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="6" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -14442,16 +14835,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:C29">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="between">
       <formula>$B$23</formula>
       <formula>2+2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="0" priority="97"/>
+    <cfRule type="uniqueValues" dxfId="25" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="45">

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F832354-F3E9-4BC5-A260-88E8A391D52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2566513C-8E6E-494F-AFB8-1020D2EDD842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,9 @@
   <externalReferences>
     <externalReference r:id="rId15"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
+    <pivotCache cacheId="9922" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1204,6 +1204,9 @@
     <t>5Rating</t>
   </si>
   <si>
+    <t>CF with formulas</t>
+  </si>
+  <si>
     <t>5Quarters</t>
   </si>
   <si>
@@ -1376,6 +1379,9 @@
     <t>Custom Formula</t>
   </si>
   <si>
+    <t>Decimal with formula</t>
+  </si>
+  <si>
     <t>option1</t>
   </si>
   <si>
@@ -1398,12 +1404,6 @@
   </si>
   <si>
     <t>A1234556</t>
-  </si>
-  <si>
-    <t>CF with formulas</t>
-  </si>
-  <si>
-    <t>Decimal with formula</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1418,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2151,7 +2151,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2335,10 +2335,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2351,28 +2363,165 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="47">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2786,157 +2935,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -2980,7 +2978,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3597,7 +3595,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3960,7 +3958,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -4376,7 +4374,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4425,6 +4423,27 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:trendline>
             <c:spPr>
               <a:ln>
@@ -4821,7 +4840,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5439,7 +5458,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5805,7 +5824,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -6117,7 +6136,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6548,7 +6567,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6950,7 +6969,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7253,7 +7272,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7309,6 +7328,27 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:trendline>
             <c:spPr>
               <a:ln>
@@ -7429,6 +7469,27 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$27:$A$35</c:f>
@@ -8837,7 +8898,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="9922" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8987,7 +9048,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8999,22 +9060,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9135,9 +9196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9175,7 +9236,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9281,7 +9342,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9423,7 +9484,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9435,7 +9496,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -9444,7 +9505,7 @@
     <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1">
       <c r="A1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -9453,7 +9514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.75">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -9463,28 +9524,28 @@
       <c r="G2" s="104">
         <v>5</v>
       </c>
-      <c r="H2" s="105" t="s">
+      <c r="H2" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="115"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1">
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="104">
         <v>8</v>
       </c>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="107">
+      <c r="K3" s="111">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1">
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
@@ -9497,50 +9558,50 @@
       <c r="G4" s="104">
         <v>9</v>
       </c>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="108"/>
+      <c r="K4" s="112"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1">
       <c r="C5" s="104">
         <v>42</v>
       </c>
       <c r="G5" s="104">
         <v>15</v>
       </c>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="108"/>
+      <c r="K5" s="112"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1">
       <c r="G6" s="104">
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="108"/>
+      <c r="K6" s="112"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1">
       <c r="C7" s="104">
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="108"/>
+      <c r="K7" s="112"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1">
       <c r="G8" s="104">
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="109"/>
+      <c r="K8" s="113"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1">
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -9550,7 +9611,7 @@
       </c>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1">
       <c r="C10" s="104">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -9559,13 +9620,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1">
       <c r="C11" s="104">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1">
       <c r="C12" s="104">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -9574,13 +9635,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1">
       <c r="G13" s="104">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -9589,32 +9650,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1">
       <c r="C15" s="104" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1">
       <c r="C16" s="104" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1">
       <c r="C17" s="104" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1">
       <c r="C18" s="104" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1">
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1">
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
@@ -9628,7 +9689,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -9638,7 +9699,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
@@ -9652,7 +9713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
       <c r="C24" s="16">
         <v>10</v>
       </c>
@@ -9663,7 +9724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
@@ -9674,7 +9735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="B26" s="104" t="s">
         <v>20</v>
       </c>
@@ -9688,7 +9749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="104" t="s">
         <v>22</v>
       </c>
@@ -9705,7 +9766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="104" t="s">
         <v>23</v>
       </c>
@@ -9722,7 +9783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="104" t="s">
         <v>24</v>
       </c>
@@ -9739,7 +9800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="104" t="s">
         <v>25</v>
       </c>
@@ -9756,7 +9817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="104" t="s">
         <v>26</v>
       </c>
@@ -9773,7 +9834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="104" t="s">
         <v>27</v>
       </c>
@@ -9790,7 +9851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
       <c r="A33" s="104" t="s">
         <v>28</v>
       </c>
@@ -9807,7 +9868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1">
       <c r="A34" s="104" t="s">
         <v>29</v>
       </c>
@@ -9818,7 +9879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1">
       <c r="A35" s="104" t="s">
         <v>30</v>
       </c>
@@ -9835,7 +9896,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9880,7 +9941,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9889,7 +9950,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9898,7 +9959,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -9915,7 +9976,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9925,7 +9986,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
@@ -9935,193 +9996,193 @@
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="112" t="s">
-        <v>423</v>
-      </c>
-      <c r="B1" s="113" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="106" t="s">
         <v>424</v>
       </c>
-      <c r="C1" s="113" t="s">
+      <c r="B1" s="107" t="s">
         <v>425</v>
       </c>
-      <c r="D1" s="113" t="s">
+      <c r="C1" s="107" t="s">
         <v>426</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="D1" s="107" t="s">
         <v>427</v>
       </c>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="107" t="s">
         <v>428</v>
       </c>
-      <c r="G1" s="113" t="s">
+      <c r="F1" s="107" t="s">
         <v>429</v>
       </c>
-      <c r="H1" s="113" t="s">
+      <c r="G1" s="107" t="s">
         <v>430</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="H1" s="107" t="s">
         <v>431</v>
       </c>
-      <c r="J1" s="111" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="115">
+      <c r="I1" s="108" t="s">
+        <v>432</v>
+      </c>
+      <c r="J1" s="105" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
         <v>4</v>
       </c>
-      <c r="B2" s="115">
+      <c r="B2">
         <v>99.5</v>
       </c>
-      <c r="C2" s="115">
-        <v>1</v>
-      </c>
-      <c r="D2" s="115" t="s">
-        <v>432</v>
-      </c>
-      <c r="E2" s="116">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E2" s="39">
         <v>45575</v>
       </c>
-      <c r="F2" s="117">
+      <c r="F2" s="109">
         <v>0.64583333333333337</v>
       </c>
-      <c r="G2" s="117" t="s">
-        <v>433</v>
-      </c>
-      <c r="H2" s="116">
+      <c r="G2" s="109" t="s">
+        <v>435</v>
+      </c>
+      <c r="H2" s="39">
         <v>45292</v>
       </c>
-      <c r="I2" s="115">
+      <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="115">
+    <row r="3" spans="1:10">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="115">
+      <c r="B3">
         <v>40</v>
       </c>
-      <c r="C3" s="115">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="115" t="s">
-        <v>434</v>
-      </c>
-      <c r="E3" s="116">
+      <c r="D3" t="s">
+        <v>436</v>
+      </c>
+      <c r="E3" s="39">
         <v>45576</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="109">
         <v>0.57638888888888884</v>
       </c>
-      <c r="G3" s="117" t="s">
+      <c r="G3" s="109" t="s">
+        <v>437</v>
+      </c>
+      <c r="H3" s="39">
+        <v>45231</v>
+      </c>
+      <c r="I3" t="s">
         <v>435</v>
-      </c>
-      <c r="H3" s="116">
-        <v>45231</v>
-      </c>
-      <c r="I3" s="115" t="s">
-        <v>433</v>
       </c>
       <c r="J3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="115">
+    <row r="4" spans="1:10">
+      <c r="A4">
         <v>9</v>
       </c>
-      <c r="B4" s="115">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="115">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="115" t="s">
-        <v>436</v>
-      </c>
-      <c r="E4" s="116">
+      <c r="D4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="39">
         <v>45574</v>
       </c>
-      <c r="F4" s="117">
+      <c r="F4" s="109">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G4" s="117" t="s">
-        <v>437</v>
-      </c>
-      <c r="H4" s="116">
+      <c r="G4" s="109" t="s">
+        <v>439</v>
+      </c>
+      <c r="H4" s="39">
         <v>45325</v>
       </c>
-      <c r="I4" s="115">
+      <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="115">
+    <row r="5" spans="1:10">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="115">
+      <c r="B5">
         <v>120</v>
       </c>
-      <c r="C5" s="115">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="115" t="s">
-        <v>434</v>
-      </c>
-      <c r="E5" s="116">
+      <c r="D5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E5" s="39">
         <v>45573</v>
       </c>
-      <c r="F5" s="117">
+      <c r="F5" s="109">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G5" s="115" t="s">
-        <v>438</v>
-      </c>
-      <c r="H5" s="116">
+      <c r="G5" t="s">
+        <v>440</v>
+      </c>
+      <c r="H5" s="39">
         <v>45084</v>
       </c>
-      <c r="I5" s="115">
+      <c r="I5">
         <v>3</v>
       </c>
       <c r="J5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="115">
+    <row r="6" spans="1:10">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B6" s="115">
+      <c r="B6">
         <v>12</v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="115" t="s">
-        <v>436</v>
-      </c>
-      <c r="E6" s="116">
+      <c r="D6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E6" s="39">
         <v>45566</v>
       </c>
-      <c r="F6" s="117">
+      <c r="F6" s="109">
         <v>0.5229166666666667</v>
       </c>
-      <c r="G6" s="115" t="s">
-        <v>439</v>
-      </c>
-      <c r="H6" s="116">
+      <c r="G6" t="s">
+        <v>441</v>
+      </c>
+      <c r="H6" s="39">
         <v>45420</v>
       </c>
-      <c r="I6" s="115" t="s">
-        <v>438</v>
+      <c r="I6" t="s">
+        <v>440</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -10175,12 +10236,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1">
       <c r="A1" s="104" t="s">
         <v>31</v>
       </c>
@@ -10215,7 +10276,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1">
       <c r="A2" s="104" t="s">
         <v>41</v>
       </c>
@@ -10261,7 +10322,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1">
       <c r="A3" s="104" t="s">
         <v>43</v>
       </c>
@@ -10307,7 +10368,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1">
       <c r="A4" s="104" t="s">
         <v>45</v>
       </c>
@@ -10353,7 +10414,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1">
       <c r="A5" s="104" t="s">
         <v>47</v>
       </c>
@@ -10399,7 +10460,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1">
       <c r="A6" s="104" t="s">
         <v>49</v>
       </c>
@@ -10445,7 +10506,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1">
       <c r="A7" s="104" t="s">
         <v>52</v>
       </c>
@@ -10479,7 +10540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1">
       <c r="A8" s="104" t="s">
         <v>54</v>
       </c>
@@ -10513,7 +10574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1">
       <c r="A9" s="104" t="s">
         <v>56</v>
       </c>
@@ -10544,7 +10605,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1">
       <c r="A10" s="104" t="s">
         <v>58</v>
       </c>
@@ -10560,7 +10621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1">
       <c r="A11" s="104" t="s">
         <v>59</v>
       </c>
@@ -10579,7 +10640,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1">
       <c r="A12" s="104" t="s">
         <v>61</v>
       </c>
@@ -10610,7 +10671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1">
       <c r="A13" s="104" t="s">
         <v>62</v>
       </c>
@@ -10641,7 +10702,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1">
       <c r="A14" s="104" t="s">
         <v>67</v>
       </c>
@@ -10657,7 +10718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1">
       <c r="A15" s="104" t="s">
         <v>68</v>
       </c>
@@ -10673,7 +10734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1">
       <c r="A16" s="104" t="s">
         <v>69</v>
       </c>
@@ -10689,7 +10750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1">
       <c r="A17" s="104" t="s">
         <v>70</v>
       </c>
@@ -10705,7 +10766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1">
       <c r="A18" s="104" t="s">
         <v>71</v>
       </c>
@@ -10721,7 +10782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1">
       <c r="A19" s="104" t="s">
         <v>72</v>
       </c>
@@ -10737,7 +10798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1">
       <c r="A20" s="104" t="s">
         <v>73</v>
       </c>
@@ -10753,7 +10814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1">
       <c r="A21" s="104" t="s">
         <v>74</v>
       </c>
@@ -10769,7 +10830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1">
       <c r="A22" s="104" t="s">
         <v>76</v>
       </c>
@@ -10785,7 +10846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1">
       <c r="A23" s="104" t="s">
         <v>77</v>
       </c>
@@ -10801,7 +10862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1">
       <c r="A24" s="104" t="s">
         <v>78</v>
       </c>
@@ -10818,7 +10879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1">
       <c r="A25" s="104" t="s">
         <v>79</v>
       </c>
@@ -10834,7 +10895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1">
       <c r="A26" s="104" t="s">
         <v>81</v>
       </c>
@@ -10850,7 +10911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1">
       <c r="A27" s="104" t="s">
         <v>82</v>
       </c>
@@ -10866,7 +10927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1">
       <c r="A28" s="104" t="s">
         <v>83</v>
       </c>
@@ -10883,7 +10944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1">
       <c r="A29" s="104" t="s">
         <v>84</v>
       </c>
@@ -10899,7 +10960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1">
       <c r="A30" s="104" t="s">
         <v>85</v>
       </c>
@@ -10915,7 +10976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1">
       <c r="A31" s="104" t="s">
         <v>86</v>
       </c>
@@ -10931,7 +10992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1">
       <c r="A32" s="104" t="s">
         <v>87</v>
       </c>
@@ -10947,7 +11008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1">
       <c r="A33" s="104" t="s">
         <v>88</v>
       </c>
@@ -10963,7 +11024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1">
       <c r="A34" s="104" t="s">
         <v>89</v>
       </c>
@@ -10979,7 +11040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1">
       <c r="A35" s="104" t="s">
         <v>90</v>
       </c>
@@ -10995,7 +11056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1">
       <c r="A36" s="104" t="s">
         <v>91</v>
       </c>
@@ -11011,7 +11072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1">
       <c r="A37" s="104" t="s">
         <v>92</v>
       </c>
@@ -11027,7 +11088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1">
       <c r="A38" s="104" t="s">
         <v>93</v>
       </c>
@@ -11044,7 +11105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1">
       <c r="A39" s="104" t="s">
         <v>94</v>
       </c>
@@ -11060,7 +11121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1">
       <c r="A40" s="104" t="s">
         <v>95</v>
       </c>
@@ -11076,7 +11137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1">
       <c r="A41" s="104" t="s">
         <v>96</v>
       </c>
@@ -11092,7 +11153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1">
       <c r="A42" s="104" t="s">
         <v>97</v>
       </c>
@@ -11108,7 +11169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1">
       <c r="A43" s="104" t="s">
         <v>98</v>
       </c>
@@ -11124,7 +11185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1">
       <c r="A44" s="104" t="s">
         <v>99</v>
       </c>
@@ -11140,7 +11201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1">
       <c r="A45" s="104" t="s">
         <v>100</v>
       </c>
@@ -11156,7 +11217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1">
       <c r="A46" s="104" t="s">
         <v>101</v>
       </c>
@@ -11172,7 +11233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1">
       <c r="A47" s="104" t="s">
         <v>102</v>
       </c>
@@ -11188,7 +11249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1">
       <c r="A48" s="104" t="s">
         <v>103</v>
       </c>
@@ -11204,7 +11265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1">
       <c r="A49" s="104" t="s">
         <v>104</v>
       </c>
@@ -11220,7 +11281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1">
       <c r="A50" s="104" t="s">
         <v>105</v>
       </c>
@@ -11237,7 +11298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1">
       <c r="A51" s="104" t="s">
         <v>106</v>
       </c>
@@ -11254,7 +11315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1">
       <c r="A52" s="104" t="s">
         <v>107</v>
       </c>
@@ -11270,7 +11331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1">
       <c r="A53" s="104" t="s">
         <v>108</v>
       </c>
@@ -11286,7 +11347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1">
       <c r="A54" s="104" t="s">
         <v>109</v>
       </c>
@@ -11302,7 +11363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1">
       <c r="A55" s="104" t="s">
         <v>110</v>
       </c>
@@ -11318,7 +11379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1">
       <c r="A56" s="104" t="s">
         <v>111</v>
       </c>
@@ -11334,7 +11395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1">
       <c r="A57" s="104" t="s">
         <v>112</v>
       </c>
@@ -11350,7 +11411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="104" t="s">
         <v>113</v>
       </c>
@@ -11366,7 +11427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1">
       <c r="A59" s="104" t="s">
         <v>114</v>
       </c>
@@ -11382,7 +11443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1">
       <c r="A60" s="104" t="s">
         <v>115</v>
       </c>
@@ -11398,7 +11459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1">
       <c r="A61" s="104" t="s">
         <v>116</v>
       </c>
@@ -11414,7 +11475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1">
       <c r="A62" s="104" t="s">
         <v>117</v>
       </c>
@@ -11430,7 +11491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1">
       <c r="A63" s="104" t="s">
         <v>118</v>
       </c>
@@ -11446,7 +11507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1">
       <c r="A64" s="104" t="s">
         <v>119</v>
       </c>
@@ -11462,7 +11523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1">
       <c r="A65" s="104" t="s">
         <v>120</v>
       </c>
@@ -11478,7 +11539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1">
       <c r="A66" s="104" t="s">
         <v>121</v>
       </c>
@@ -11494,7 +11555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1">
       <c r="A67" s="104" t="s">
         <v>122</v>
       </c>
@@ -11510,7 +11571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1">
       <c r="A68" s="104" t="s">
         <v>123</v>
       </c>
@@ -11526,7 +11587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1">
       <c r="A69" s="104" t="s">
         <v>125</v>
       </c>
@@ -11542,7 +11603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1">
       <c r="A70" s="104" t="s">
         <v>127</v>
       </c>
@@ -11558,7 +11619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1">
       <c r="A71" s="104" t="s">
         <v>129</v>
       </c>
@@ -11574,7 +11635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1">
       <c r="A72" s="104" t="s">
         <v>130</v>
       </c>
@@ -11590,7 +11651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1">
       <c r="A73" s="104" t="s">
         <v>131</v>
       </c>
@@ -11606,7 +11667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1">
       <c r="A74" s="104" t="s">
         <v>132</v>
       </c>
@@ -11622,7 +11683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1">
       <c r="A75" s="104" t="s">
         <v>133</v>
       </c>
@@ -11638,7 +11699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1">
       <c r="A76" s="104" t="s">
         <v>134</v>
       </c>
@@ -11654,7 +11715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1">
       <c r="A77" s="104" t="s">
         <v>135</v>
       </c>
@@ -11670,7 +11731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1">
       <c r="A78" s="104" t="s">
         <v>136</v>
       </c>
@@ -11686,7 +11747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1">
       <c r="A79" s="104" t="s">
         <v>137</v>
       </c>
@@ -11702,7 +11763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1">
       <c r="A80" s="104" t="s">
         <v>138</v>
       </c>
@@ -11718,7 +11779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1">
       <c r="A81" s="104" t="s">
         <v>139</v>
       </c>
@@ -11734,7 +11795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1">
       <c r="A82" s="104" t="s">
         <v>141</v>
       </c>
@@ -11750,7 +11811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1">
       <c r="A83" s="104" t="s">
         <v>142</v>
       </c>
@@ -11766,7 +11827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1">
       <c r="A84" s="104" t="s">
         <v>143</v>
       </c>
@@ -11782,7 +11843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1">
       <c r="A85" s="104" t="s">
         <v>144</v>
       </c>
@@ -11798,7 +11859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1">
       <c r="A86" s="104" t="s">
         <v>146</v>
       </c>
@@ -11814,7 +11875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1">
       <c r="A87" s="104" t="s">
         <v>147</v>
       </c>
@@ -11830,7 +11891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1">
       <c r="A88" s="104" t="s">
         <v>148</v>
       </c>
@@ -11846,7 +11907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1">
       <c r="A89" s="104" t="s">
         <v>149</v>
       </c>
@@ -11862,7 +11923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1">
       <c r="A90" s="104" t="s">
         <v>150</v>
       </c>
@@ -11878,7 +11939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1">
       <c r="A91" s="104" t="s">
         <v>151</v>
       </c>
@@ -11894,7 +11955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1">
       <c r="A92" s="104" t="s">
         <v>152</v>
       </c>
@@ -11910,7 +11971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1">
       <c r="A93" s="104" t="s">
         <v>153</v>
       </c>
@@ -11926,7 +11987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1">
       <c r="A94" s="104" t="s">
         <v>154</v>
       </c>
@@ -11942,7 +12003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1">
       <c r="A95" s="104" t="s">
         <v>155</v>
       </c>
@@ -11958,7 +12019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1">
       <c r="A96" s="104" t="s">
         <v>156</v>
       </c>
@@ -11974,7 +12035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1">
       <c r="A97" s="104" t="s">
         <v>157</v>
       </c>
@@ -11990,7 +12051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1">
       <c r="A98" s="104" t="s">
         <v>158</v>
       </c>
@@ -12006,7 +12067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1">
       <c r="A99" s="104" t="s">
         <v>159</v>
       </c>
@@ -12022,20 +12083,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1">
       <c r="A100" s="104" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45938.493500231481</v>
+        <v>45995.606012037038</v>
       </c>
       <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1">
       <c r="A101" s="104" t="s">
         <v>161</v>
       </c>
@@ -12051,7 +12112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1">
       <c r="A102" s="104" t="s">
         <v>162</v>
       </c>
@@ -12067,7 +12128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1">
       <c r="A103" s="104" t="s">
         <v>163</v>
       </c>
@@ -12083,7 +12144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1">
       <c r="A104" s="104" t="s">
         <v>164</v>
       </c>
@@ -12099,7 +12160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1">
       <c r="A105" s="104" t="s">
         <v>165</v>
       </c>
@@ -12115,7 +12176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1">
       <c r="A106" s="104" t="s">
         <v>166</v>
       </c>
@@ -12131,7 +12192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1">
       <c r="A107" s="104" t="s">
         <v>167</v>
       </c>
@@ -12147,7 +12208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1">
       <c r="A108" s="104" t="s">
         <v>168</v>
       </c>
@@ -12163,7 +12224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1">
       <c r="A109" s="104" t="s">
         <v>169</v>
       </c>
@@ -12179,7 +12240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1">
       <c r="A110" s="104" t="s">
         <v>170</v>
       </c>
@@ -12195,7 +12256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1">
       <c r="A111" s="104" t="s">
         <v>171</v>
       </c>
@@ -12211,12 +12272,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1">
       <c r="A112" s="104"/>
       <c r="B112" s="104"/>
       <c r="D112" s="104"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1">
       <c r="A113" s="104" t="s">
         <v>172</v>
       </c>
@@ -12232,7 +12293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1">
       <c r="A114" s="104" t="s">
         <v>173</v>
       </c>
@@ -12248,7 +12309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1">
       <c r="A115" s="104" t="s">
         <v>175</v>
       </c>
@@ -12264,7 +12325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1">
       <c r="A116" s="104" t="s">
         <v>177</v>
       </c>
@@ -12280,7 +12341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1">
       <c r="A117" s="104" t="s">
         <v>178</v>
       </c>
@@ -12296,7 +12357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1">
       <c r="A118" s="104" t="s">
         <v>179</v>
       </c>
@@ -12312,7 +12373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1">
       <c r="A119" s="104" t="s">
         <v>180</v>
       </c>
@@ -12328,7 +12389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1">
       <c r="A120" s="104" t="s">
         <v>181</v>
       </c>
@@ -12344,7 +12405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1">
       <c r="A121" s="104" t="s">
         <v>182</v>
       </c>
@@ -12360,7 +12421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1">
       <c r="A122" s="104" t="s">
         <v>183</v>
       </c>
@@ -12376,7 +12437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1">
       <c r="A123" s="104" t="s">
         <v>184</v>
       </c>
@@ -12392,7 +12453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1">
       <c r="A124" s="104" t="s">
         <v>185</v>
       </c>
@@ -12408,7 +12469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1">
       <c r="A125" s="104" t="s">
         <v>186</v>
       </c>
@@ -12424,7 +12485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1">
       <c r="A126" s="104" t="s">
         <v>187</v>
       </c>
@@ -12440,7 +12501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1">
       <c r="A127" s="104" t="s">
         <v>188</v>
       </c>
@@ -12456,7 +12517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1">
       <c r="A128" s="104" t="s">
         <v>189</v>
       </c>
@@ -12472,7 +12533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1">
       <c r="A129" s="104" t="s">
         <v>190</v>
       </c>
@@ -12488,7 +12549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1">
       <c r="A130" s="104" t="s">
         <v>191</v>
       </c>
@@ -12504,7 +12565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1">
       <c r="A131" s="104" t="s">
         <v>192</v>
       </c>
@@ -12520,7 +12581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1">
       <c r="A132" s="104" t="s">
         <v>193</v>
       </c>
@@ -12536,7 +12597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1">
       <c r="A133" s="104" t="s">
         <v>194</v>
       </c>
@@ -12552,7 +12613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1">
       <c r="A134" s="104" t="s">
         <v>195</v>
       </c>
@@ -12568,7 +12629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1">
       <c r="A135" s="104" t="s">
         <v>196</v>
       </c>
@@ -12584,7 +12645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1">
       <c r="A136" s="104" t="s">
         <v>198</v>
       </c>
@@ -12600,7 +12661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1">
       <c r="A137" s="104" t="s">
         <v>199</v>
       </c>
@@ -12616,7 +12677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1">
       <c r="A138" s="104" t="s">
         <v>200</v>
       </c>
@@ -12632,7 +12693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1">
       <c r="A139" s="104" t="s">
         <v>201</v>
       </c>
@@ -12648,7 +12709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1">
       <c r="A140" s="104" t="s">
         <v>202</v>
       </c>
@@ -12664,7 +12725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1">
       <c r="A141" s="104" t="s">
         <v>203</v>
       </c>
@@ -12680,7 +12741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1">
       <c r="A142" s="104" t="s">
         <v>205</v>
       </c>
@@ -12696,7 +12757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1">
       <c r="A143" s="104" t="s">
         <v>206</v>
       </c>
@@ -12712,20 +12773,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1">
       <c r="A144" s="104" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>45995</v>
       </c>
       <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1">
       <c r="A145" s="104" t="s">
         <v>208</v>
       </c>
@@ -12741,7 +12802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1">
       <c r="A146" s="104" t="s">
         <v>210</v>
       </c>
@@ -12757,7 +12818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1">
       <c r="A147" s="104" t="s">
         <v>211</v>
       </c>
@@ -12773,7 +12834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1">
       <c r="A148" s="104" t="s">
         <v>213</v>
       </c>
@@ -12789,7 +12850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1">
       <c r="A149" s="104" t="s">
         <v>214</v>
       </c>
@@ -12805,7 +12866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1">
       <c r="A150" s="104" t="s">
         <v>215</v>
       </c>
@@ -12821,7 +12882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1">
       <c r="A151" s="104" t="s">
         <v>216</v>
       </c>
@@ -12837,7 +12898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1">
       <c r="A152" s="104" t="s">
         <v>217</v>
       </c>
@@ -12853,7 +12914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1">
       <c r="A153" s="104" t="s">
         <v>218</v>
       </c>
@@ -12869,7 +12930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1">
       <c r="A154" s="104" t="s">
         <v>219</v>
       </c>
@@ -12886,7 +12947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1">
       <c r="A155" s="104" t="s">
         <v>220</v>
       </c>
@@ -12902,7 +12963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1">
       <c r="A156" s="104" t="s">
         <v>221</v>
       </c>
@@ -12918,7 +12979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1">
       <c r="A157" s="104" t="s">
         <v>222</v>
       </c>
@@ -12934,7 +12995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1">
       <c r="A158" s="104" t="s">
         <v>223</v>
       </c>
@@ -12950,7 +13011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1">
       <c r="A159" s="104" t="s">
         <v>224</v>
       </c>
@@ -12966,7 +13027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1">
       <c r="A160" s="104" t="s">
         <v>225</v>
       </c>
@@ -12982,7 +13043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1">
       <c r="A161" s="104" t="s">
         <v>226</v>
       </c>
@@ -12998,7 +13059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1">
       <c r="A162" s="104" t="s">
         <v>227</v>
       </c>
@@ -13014,7 +13075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1">
       <c r="A163" s="104" t="s">
         <v>229</v>
       </c>
@@ -13032,10 +13093,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13050,7 +13111,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -13060,17 +13121,17 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="114" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="110"/>
+      <c r="E1" s="114"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -13078,19 +13139,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
@@ -13098,43 +13159,43 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="75" customHeight="1">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="1:2" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:2" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" outlineLevel="1"/>
+    <row r="11" spans="1:8" outlineLevel="1"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
+    <row r="16" spans="1:8" outlineLevel="1"/>
+    <row r="17" spans="1:2" outlineLevel="1"/>
+    <row r="18" spans="1:2" outlineLevel="1"/>
+    <row r="30" spans="1:2">
       <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.7272925709748963</v>
+        <v>0.71838237714175435</v>
       </c>
       <c r="B30">
         <f ca="1"/>
-        <v>0.95782684877879687</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.36236179614680708</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <f ca="1"/>
-        <v>0.31704384406036645</v>
+        <v>0.40388442517560574</v>
       </c>
       <c r="B31">
         <f ca="1"/>
-        <v>8.7112099778747121E-2</v>
+        <v>0.47343726914281192</v>
       </c>
     </row>
   </sheetData>
@@ -13153,14 +13214,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -13182,7 +13243,7 @@
       </c>
       <c r="M1" s="36"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
@@ -13208,7 +13269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
@@ -13231,7 +13292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -13257,7 +13318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
@@ -13277,7 +13338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
@@ -13300,7 +13361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15.75">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -13320,7 +13381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="21">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -13343,7 +13404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -13360,7 +13421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
@@ -13368,7 +13429,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -13377,7 +13438,7 @@
       </c>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1">
       <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
@@ -13391,7 +13452,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
@@ -13402,7 +13463,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
@@ -13416,7 +13477,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
@@ -13427,7 +13488,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
       <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
@@ -13441,12 +13502,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -13458,7 +13519,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -13469,7 +13530,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -13483,12 +13544,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -13497,13 +13558,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -13512,20 +13573,20 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
+    <row r="30" spans="1:6">
       <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
@@ -13539,13 +13600,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -13562,7 +13623,7 @@
       <c r="I1" s="36"/>
       <c r="J1" s="36"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
@@ -13585,7 +13646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
@@ -13608,7 +13669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
@@ -13628,7 +13689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
@@ -13652,7 +13713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
@@ -13675,7 +13736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
@@ -13701,7 +13762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
@@ -13712,7 +13773,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
@@ -13721,7 +13782,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -13739,7 +13800,7 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
@@ -13762,13 +13823,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>45995</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -13787,7 +13848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
@@ -13810,7 +13871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
@@ -13836,7 +13897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
@@ -13856,7 +13917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
@@ -13879,7 +13940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
@@ -13902,7 +13963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
@@ -13925,7 +13986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
@@ -13948,7 +14009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
@@ -13971,7 +14032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
@@ -13997,7 +14058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
@@ -14023,7 +14084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
@@ -14049,7 +14110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
@@ -14066,7 +14127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
@@ -14092,7 +14153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
@@ -14112,7 +14173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
@@ -14138,7 +14199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
@@ -14158,9 +14219,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" s="38" t="s">
-        <v>440</v>
+        <v>375</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -14169,7 +14230,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -14187,9 +14248,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="G30" s="34" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -14207,9 +14268,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1">
       <c r="G31" s="35" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H31" s="36">
         <v>5</v>
@@ -14221,9 +14282,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="G32" s="34" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -14235,9 +14296,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="7:10">
       <c r="G33" s="34" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -14249,9 +14310,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="7:10">
       <c r="G34" s="34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -14263,9 +14324,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="7:10">
       <c r="G35" s="34" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -14277,9 +14338,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="7:10">
       <c r="G36" s="34" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -14291,9 +14352,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="7:10">
       <c r="G37" s="34" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -14305,110 +14366,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="7:10">
       <c r="G39" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="23" priority="59">
+    <cfRule type="expression" dxfId="41" priority="59">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="47" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="21" priority="115"/>
+    <cfRule type="aboveAverage" dxfId="39" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="20" priority="74" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="38" priority="74" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="19" priority="72">
+    <cfRule type="containsBlanks" dxfId="37" priority="72">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="18" priority="71">
+    <cfRule type="containsErrors" dxfId="36" priority="71">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="17" priority="70" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="35" priority="70" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="16" priority="68" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="34" priority="68" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="67">
+    <cfRule type="notContainsBlanks" dxfId="33" priority="67">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="14" priority="66">
+    <cfRule type="notContainsErrors" dxfId="32" priority="66">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="13" priority="65" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="31" priority="65" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="12" priority="64" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="30" priority="64" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="11" priority="116" rank="1"/>
+    <cfRule type="top10" dxfId="29" priority="116" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="9" priority="57" operator="notEqual">
+    <cfRule type="cellIs" dxfId="27" priority="57" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -14442,16 +14503,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:C29">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="between">
       <formula>$B$23</formula>
       <formula>2+2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="0" priority="97"/>
+    <cfRule type="uniqueValues" dxfId="18" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="45">
@@ -14874,7 +14935,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -14886,12 +14947,12 @@
     <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -14899,25 +14960,25 @@
         <v>36</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="104" t="s">
         <v>42</v>
       </c>
@@ -14948,7 +15009,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="104" t="s">
         <v>44</v>
       </c>
@@ -14979,9 +15040,9 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="C6" s="104" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D6" s="104">
         <f>SUBTOTAL(109,Table3[Age])</f>
@@ -15012,9 +15073,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -15023,22 +15084,22 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J8" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="C9">
         <v>3</v>
       </c>
@@ -15066,18 +15127,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="C12">
         <v>3</v>
       </c>
@@ -15085,9 +15146,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -15096,7 +15157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="C15">
         <v>3</v>
       </c>
@@ -15104,9 +15165,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -15115,7 +15176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4">
       <c r="C18">
         <v>3</v>
       </c>
@@ -15123,9 +15184,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -15134,7 +15195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4">
       <c r="C21">
         <v>3</v>
       </c>
@@ -15142,9 +15203,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -15153,7 +15214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4">
       <c r="C24">
         <v>3</v>
       </c>
@@ -15161,9 +15222,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4">
       <c r="B26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -15172,7 +15233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4">
       <c r="C27">
         <v>3</v>
       </c>
@@ -15180,45 +15241,45 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4">
       <c r="C28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D28">
         <f>SUBTOTAL(109,Table4910[Column2])</f>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4">
       <c r="B30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D30" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" hidden="1">
       <c r="C31" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D31" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
       <c r="C32" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D32" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -15241,7 +15302,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -15262,9 +15323,9 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15">
       <c r="A1" s="92" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -15272,7 +15333,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="104"/>
       <c r="B2" s="104"/>
       <c r="C2" s="104"/>
@@ -15280,21 +15341,21 @@
       <c r="E2" s="104"/>
       <c r="F2" s="104"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3" s="104"/>
       <c r="B3" s="104"/>
       <c r="C3" s="89" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="104"/>
       <c r="B4" s="104"/>
       <c r="C4" s="89" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D4">
         <v>12.1</v>
@@ -15321,10 +15382,10 @@
         <v>12052</v>
       </c>
       <c r="L4" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="104"/>
       <c r="B5" s="104"/>
       <c r="C5" s="90" t="s">
@@ -15337,7 +15398,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" s="104"/>
       <c r="B6" s="104"/>
       <c r="C6" s="91">
@@ -15350,7 +15411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" s="104"/>
       <c r="B7" s="104"/>
       <c r="C7" s="90" t="s">
@@ -15363,7 +15424,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" s="104"/>
       <c r="B8" s="104"/>
       <c r="C8" s="91">
@@ -15376,7 +15437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" s="104"/>
       <c r="B9" s="104"/>
       <c r="C9" s="90" t="s">
@@ -15389,7 +15450,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" s="104"/>
       <c r="B10" s="104"/>
       <c r="C10" s="91">
@@ -15402,7 +15463,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -15413,7 +15474,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -15424,7 +15485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -15435,7 +15496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -15446,7 +15507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -15457,7 +15518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -15468,7 +15529,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:12">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -15479,7 +15540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -15490,7 +15551,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -15501,7 +15562,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -15512,9 +15573,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12">
       <c r="C21" s="90" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -15553,31 +15614,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B2" s="104"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -15589,25 +15650,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="51">
       <c r="A1" s="99" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -15615,7 +15676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -15623,7 +15684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -15631,7 +15692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4</v>
       </c>
@@ -15639,7 +15700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rar/rar-workspace/o-spreadsheet/tests/__xlsx__/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C7959D-379F-564A-B7D4-13925F876C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346363BF-6AD4-4354-A44F-43A8F3AE431A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23400" yWindow="2720" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1860" windowWidth="29040" windowHeight="18240" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,11 @@
   <externalReferences>
     <externalReference r:id="rId17"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="My_Named_Range">jestMiscTest!$A$8:$B$10</definedName>
+    <definedName name="Table_Col_Named_Range">Table10[Col1]</definedName>
+    <definedName name="Table_Named_Range">Table10[]</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId18"/>
@@ -2986,7 +2991,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3603,7 +3608,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3966,7 +3971,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -4382,7 +4387,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4848,7 +4853,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5466,7 +5471,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5832,7 +5837,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -6144,7 +6149,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6575,7 +6580,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6977,7 +6982,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7280,7 +7285,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8771,6 +8776,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Feuil1"/>
     </sheetNames>
@@ -9504,13 +9512,13 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.19921875" customWidth="1"/>
-    <col min="2" max="2" width="13.796875" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.19921875" customWidth="1"/>
-    <col min="6" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9522,7 +9530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -9949,7 +9957,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9958,7 +9966,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9967,10 +9975,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.19921875" customWidth="1"/>
-    <col min="2" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="65.140625" customWidth="1"/>
+    <col min="2" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9984,7 +9992,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9994,13 +10002,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="14.19921875" customWidth="1"/>
-    <col min="5" max="5" width="14.796875" customWidth="1"/>
-    <col min="7" max="7" width="14.19921875" customWidth="1"/>
-    <col min="8" max="8" width="20.19921875" customWidth="1"/>
-    <col min="9" max="9" width="17.19921875" customWidth="1"/>
+    <col min="3" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10241,7 +10249,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175FB5D6-D3ED-FD4F-886B-71BD0CB28755}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10251,7 +10259,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B936FE7B-5147-E945-A711-7FBABD0575D3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10264,9 +10272,9 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12117,7 +12125,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>46050.431470138887</v>
+        <v>46113.450567939813</v>
       </c>
       <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -12807,7 +12815,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>46050</v>
+        <v>46113</v>
       </c>
       <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -13139,14 +13147,14 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.19921875" customWidth="1"/>
-    <col min="10" max="10" width="9.19921875" outlineLevel="1"/>
-    <col min="11" max="11" width="9.19921875" outlineLevel="1" collapsed="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" outlineLevel="1"/>
+    <col min="11" max="11" width="9.140625" outlineLevel="1" collapsed="1"/>
     <col min="12" max="14" width="0" hidden="1" outlineLevel="2"/>
-    <col min="15" max="18" width="9.19921875" outlineLevel="1"/>
+    <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -13209,21 +13217,21 @@
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.77093979243831789</v>
+        <v>0.46080895274950051</v>
       </c>
       <c r="B30">
         <f ca="1"/>
-        <v>0.89996963625071968</v>
+        <v>0.12189382146451888</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <f ca="1"/>
-        <v>4.753041610255937E-2</v>
+        <v>0.83857971910007767</v>
       </c>
       <c r="B31">
         <f ca="1"/>
-        <v>0.61224139121963739</v>
+        <v>0.50857115329836389</v>
       </c>
     </row>
   </sheetData>
@@ -13242,14 +13250,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.796875" customWidth="1"/>
-    <col min="5" max="5" width="18.19921875" customWidth="1"/>
-    <col min="13" max="13" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -13320,7 +13328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -13389,7 +13397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -13409,7 +13417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -13432,7 +13440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -13457,7 +13465,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -13530,12 +13538,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -13547,7 +13555,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -13558,7 +13566,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="61" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -13572,12 +13580,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -13586,13 +13594,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -13601,19 +13609,19 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="87" t="s">
         <v>314</v>
@@ -13628,13 +13636,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.19921875" customWidth="1"/>
-    <col min="7" max="7" width="15.796875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -13810,7 +13818,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -13857,7 +13865,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>46050</v>
+        <v>46113</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -14296,7 +14304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G31" s="35" t="s">
         <v>378</v>
       </c>
@@ -14963,16 +14971,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.19921875" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" customWidth="1"/>
-    <col min="5" max="5" width="26.3984375" customWidth="1"/>
-    <col min="6" max="6" width="27.59765625" customWidth="1"/>
-    <col min="7" max="7" width="23.59765625" customWidth="1"/>
-    <col min="8" max="8" width="16.19921875" customWidth="1"/>
-    <col min="9" max="9" width="18.796875" customWidth="1"/>
-    <col min="10" max="10" width="17.19921875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -14980,7 +14988,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -15330,28 +15338,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="92" t="s">
         <v>413</v>
       </c>
@@ -15361,7 +15369,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
       <c r="B2" s="104"/>
       <c r="C2" s="104"/>
@@ -15369,7 +15377,7 @@
       <c r="E2" s="104"/>
       <c r="F2" s="104"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
       <c r="B3" s="104"/>
       <c r="C3" s="89" t="s">
@@ -15379,7 +15387,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="104"/>
       <c r="C4" s="89" t="s">
@@ -15413,7 +15421,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="104"/>
       <c r="C5" s="90" t="s">
@@ -15426,7 +15434,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A6" s="104"/>
       <c r="B6" s="104"/>
       <c r="C6" s="91">
@@ -15439,7 +15447,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A7" s="104"/>
       <c r="B7" s="104"/>
       <c r="C7" s="90" t="s">
@@ -15452,7 +15460,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A8" s="104"/>
       <c r="B8" s="104"/>
       <c r="C8" s="91">
@@ -15465,7 +15473,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A9" s="104"/>
       <c r="B9" s="104"/>
       <c r="C9" s="90" t="s">
@@ -15478,7 +15486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A10" s="104"/>
       <c r="B10" s="104"/>
       <c r="C10" s="91">
@@ -15491,7 +15499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -15502,7 +15510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -15513,7 +15521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -15524,7 +15532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -15535,7 +15543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -15546,7 +15554,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -15557,7 +15565,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -15568,7 +15576,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -15579,7 +15587,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -15590,7 +15598,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -15601,7 +15609,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C21" s="90" t="s">
         <v>417</v>
       </c>
@@ -15642,10 +15650,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.19921875" customWidth="1"/>
-    <col min="2" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="65.140625" customWidth="1"/>
+    <col min="2" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -15678,9 +15686,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>422</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dhrutik Patel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DA6F05-B302-48AE-B11C-1FB2528D58DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B86E9B1-DF37-4B7C-B14C-0625DAE1CA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,9 @@
   <externalReferences>
     <externalReference r:id="rId15"/>
   </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
+    <pivotCache cacheId="4560" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,6 +46,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1203,6 +1204,9 @@
     <t>5Rating</t>
   </si>
   <si>
+    <t>CF with formulas</t>
+  </si>
+  <si>
     <t>5Quarters</t>
   </si>
   <si>
@@ -1397,9 +1401,6 @@
   </si>
   <si>
     <t>A1234556</t>
-  </si>
-  <si>
-    <t>CF with formulas</t>
   </si>
 </sst>
 </file>
@@ -1414,7 +1415,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2414,7 +2415,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2427,13 +2427,165 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="47">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2847,157 +2999,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -3041,7 +3042,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3642,7 +3643,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4074,7 +4075,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4692,7 +4693,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5058,7 +5059,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5357,7 +5358,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5774,7 +5775,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6176,7 +6177,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6466,7 +6467,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -7798,6 +7799,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Feuil1"/>
     </sheetNames>
@@ -7933,7 +7937,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="4560" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8083,7 +8087,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8095,22 +8099,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8531,7 +8535,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -8540,7 +8544,7 @@
     <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1">
       <c r="A1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -8549,7 +8553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.75">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -8562,25 +8566,25 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="119"/>
+      <c r="I2" s="123"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1">
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="120">
+      <c r="K3" s="119">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1">
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
@@ -8593,50 +8597,50 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="121"/>
+      <c r="K4" s="120"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1">
       <c r="C5" s="117">
         <v>42</v>
       </c>
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="121"/>
+      <c r="K5" s="120"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1">
       <c r="G6" s="117">
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="121"/>
+      <c r="K6" s="120"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1">
       <c r="C7" s="117">
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="121"/>
+      <c r="K7" s="120"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1">
       <c r="G8" s="117">
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="122"/>
+      <c r="K8" s="121"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1">
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -8646,7 +8650,7 @@
       </c>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1">
       <c r="C10" s="117">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -8655,13 +8659,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1">
       <c r="C11" s="117">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1">
       <c r="C12" s="117">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -8670,13 +8674,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1">
       <c r="G13" s="117">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -8685,32 +8689,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1">
       <c r="C15" s="117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1">
       <c r="C16" s="117" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1">
       <c r="C17" s="117" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1">
       <c r="C18" s="117" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1">
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1">
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
@@ -8724,7 +8728,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -8734,7 +8738,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
@@ -8748,7 +8752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
       <c r="C24" s="16">
         <v>10</v>
       </c>
@@ -8759,7 +8763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
@@ -8770,7 +8774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="B26" s="117" t="s">
         <v>20</v>
       </c>
@@ -8784,7 +8788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>22</v>
       </c>
@@ -8801,7 +8805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>23</v>
       </c>
@@ -8818,7 +8822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>24</v>
       </c>
@@ -8835,7 +8839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>25</v>
       </c>
@@ -8852,7 +8856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>26</v>
       </c>
@@ -8869,7 +8873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>27</v>
       </c>
@@ -8886,7 +8890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>28</v>
       </c>
@@ -8903,7 +8907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>29</v>
       </c>
@@ -8914,7 +8918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>30</v>
       </c>
@@ -8931,7 +8935,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8976,7 +8980,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8985,7 +8989,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8994,7 +8998,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -9011,7 +9015,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9020,8 +9024,8 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
@@ -9030,36 +9034,36 @@
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="114" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B1" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C1" s="115" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D1" s="115" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1" s="115" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F1" s="115" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G1" s="115" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I1" s="116" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="104">
         <v>4</v>
       </c>
@@ -9070,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="105" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E2" s="106">
         <v>45575</v>
@@ -9079,7 +9083,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="G2" s="107" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2" s="106">
         <v>45292</v>
@@ -9087,8 +9091,11 @@
       <c r="I2" s="108">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="104">
         <v>3</v>
       </c>
@@ -9099,7 +9106,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="105" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E3" s="106">
         <v>45576</v>
@@ -9108,16 +9115,19 @@
         <v>0.57638888888888884</v>
       </c>
       <c r="G3" s="107" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H3" s="106">
         <v>45231</v>
       </c>
       <c r="I3" s="108" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="104">
         <v>9</v>
       </c>
@@ -9128,7 +9138,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="105" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E4" s="106">
         <v>45574</v>
@@ -9137,7 +9147,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="G4" s="107" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H4" s="106">
         <v>45325</v>
@@ -9145,8 +9155,11 @@
       <c r="I4" s="108">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="104">
         <v>5</v>
       </c>
@@ -9157,7 +9170,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="105" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E5" s="106">
         <v>45573</v>
@@ -9166,7 +9179,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G5" s="105" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H5" s="106">
         <v>45084</v>
@@ -9174,8 +9187,11 @@
       <c r="I5" s="108">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="109">
         <v>7</v>
       </c>
@@ -9186,7 +9202,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="110" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E6" s="111">
         <v>45566</v>
@@ -9195,17 +9211,20 @@
         <v>0.5229166666666667</v>
       </c>
       <c r="G6" s="110" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H6" s="111">
         <v>45420</v>
       </c>
       <c r="I6" s="113" t="s">
-        <v>438</v>
+        <v>439</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A6" xr:uid="{B9309757-E2F4-49A1-880B-2F47F04364D6}">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -9237,6 +9256,10 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{1E18A174-B5CF-4015-B7DC-F1491351E054}">
       <formula1>"option1,option2,option3"</formula1>
     </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J6" xr:uid="{EAFFF3C7-1A46-48EE-850D-DE4852C6359D}">
+      <formula1>$A$2</formula1>
+      <formula2>2+10</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9248,12 +9271,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1">
       <c r="A1" s="117" t="s">
         <v>31</v>
       </c>
@@ -9288,7 +9311,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1">
       <c r="A2" s="117" t="s">
         <v>41</v>
       </c>
@@ -9334,7 +9357,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1">
       <c r="A3" s="117" t="s">
         <v>43</v>
       </c>
@@ -9380,7 +9403,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1">
       <c r="A4" s="117" t="s">
         <v>45</v>
       </c>
@@ -9426,7 +9449,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1">
       <c r="A5" s="117" t="s">
         <v>47</v>
       </c>
@@ -9472,7 +9495,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1">
       <c r="A6" s="117" t="s">
         <v>49</v>
       </c>
@@ -9518,7 +9541,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1">
       <c r="A7" s="117" t="s">
         <v>52</v>
       </c>
@@ -9552,7 +9575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1">
       <c r="A8" s="117" t="s">
         <v>54</v>
       </c>
@@ -9586,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1">
       <c r="A9" s="117" t="s">
         <v>56</v>
       </c>
@@ -9617,7 +9640,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1">
       <c r="A10" s="117" t="s">
         <v>58</v>
       </c>
@@ -9633,7 +9656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1">
       <c r="A11" s="117" t="s">
         <v>59</v>
       </c>
@@ -9652,7 +9675,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1">
       <c r="A12" s="117" t="s">
         <v>61</v>
       </c>
@@ -9683,7 +9706,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1">
       <c r="A13" s="117" t="s">
         <v>62</v>
       </c>
@@ -9714,7 +9737,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1">
       <c r="A14" s="117" t="s">
         <v>67</v>
       </c>
@@ -9730,7 +9753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1">
       <c r="A15" s="117" t="s">
         <v>68</v>
       </c>
@@ -9746,7 +9769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1">
       <c r="A16" s="117" t="s">
         <v>69</v>
       </c>
@@ -9762,7 +9785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1">
       <c r="A17" s="117" t="s">
         <v>70</v>
       </c>
@@ -9778,7 +9801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1">
       <c r="A18" s="117" t="s">
         <v>71</v>
       </c>
@@ -9794,7 +9817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1">
       <c r="A19" s="117" t="s">
         <v>72</v>
       </c>
@@ -9810,7 +9833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1">
       <c r="A20" s="117" t="s">
         <v>73</v>
       </c>
@@ -9826,7 +9849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1">
       <c r="A21" s="117" t="s">
         <v>74</v>
       </c>
@@ -9842,7 +9865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1">
       <c r="A22" s="117" t="s">
         <v>76</v>
       </c>
@@ -9858,7 +9881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1">
       <c r="A23" s="117" t="s">
         <v>77</v>
       </c>
@@ -9874,7 +9897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1">
       <c r="A24" s="117" t="s">
         <v>78</v>
       </c>
@@ -9891,7 +9914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1">
       <c r="A25" s="117" t="s">
         <v>79</v>
       </c>
@@ -9907,7 +9930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1">
       <c r="A26" s="117" t="s">
         <v>81</v>
       </c>
@@ -9923,7 +9946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>82</v>
       </c>
@@ -9939,7 +9962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>83</v>
       </c>
@@ -9956,7 +9979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>84</v>
       </c>
@@ -9972,7 +9995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>85</v>
       </c>
@@ -9988,7 +10011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>86</v>
       </c>
@@ -10004,7 +10027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>87</v>
       </c>
@@ -10020,7 +10043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>88</v>
       </c>
@@ -10036,7 +10059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>89</v>
       </c>
@@ -10052,7 +10075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>90</v>
       </c>
@@ -10068,7 +10091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1">
       <c r="A36" s="117" t="s">
         <v>91</v>
       </c>
@@ -10084,7 +10107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1">
       <c r="A37" s="117" t="s">
         <v>92</v>
       </c>
@@ -10100,7 +10123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1">
       <c r="A38" s="117" t="s">
         <v>93</v>
       </c>
@@ -10117,7 +10140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1">
       <c r="A39" s="117" t="s">
         <v>94</v>
       </c>
@@ -10133,7 +10156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1">
       <c r="A40" s="117" t="s">
         <v>95</v>
       </c>
@@ -10149,7 +10172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1">
       <c r="A41" s="117" t="s">
         <v>96</v>
       </c>
@@ -10165,7 +10188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1">
       <c r="A42" s="117" t="s">
         <v>97</v>
       </c>
@@ -10181,7 +10204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1">
       <c r="A43" s="117" t="s">
         <v>98</v>
       </c>
@@ -10197,7 +10220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1">
       <c r="A44" s="117" t="s">
         <v>99</v>
       </c>
@@ -10213,7 +10236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1">
       <c r="A45" s="117" t="s">
         <v>100</v>
       </c>
@@ -10229,7 +10252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1">
       <c r="A46" s="117" t="s">
         <v>101</v>
       </c>
@@ -10245,7 +10268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1">
       <c r="A47" s="117" t="s">
         <v>102</v>
       </c>
@@ -10261,7 +10284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1">
       <c r="A48" s="117" t="s">
         <v>103</v>
       </c>
@@ -10277,7 +10300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1">
       <c r="A49" s="117" t="s">
         <v>104</v>
       </c>
@@ -10293,7 +10316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1">
       <c r="A50" s="117" t="s">
         <v>105</v>
       </c>
@@ -10310,7 +10333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1">
       <c r="A51" s="117" t="s">
         <v>106</v>
       </c>
@@ -10327,7 +10350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1">
       <c r="A52" s="117" t="s">
         <v>107</v>
       </c>
@@ -10343,7 +10366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1">
       <c r="A53" s="117" t="s">
         <v>108</v>
       </c>
@@ -10359,7 +10382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1">
       <c r="A54" s="117" t="s">
         <v>109</v>
       </c>
@@ -10375,7 +10398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1">
       <c r="A55" s="117" t="s">
         <v>110</v>
       </c>
@@ -10391,7 +10414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1">
       <c r="A56" s="117" t="s">
         <v>111</v>
       </c>
@@ -10407,7 +10430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1">
       <c r="A57" s="117" t="s">
         <v>112</v>
       </c>
@@ -10423,7 +10446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="117" t="s">
         <v>113</v>
       </c>
@@ -10439,7 +10462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1">
       <c r="A59" s="117" t="s">
         <v>114</v>
       </c>
@@ -10455,7 +10478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1">
       <c r="A60" s="117" t="s">
         <v>115</v>
       </c>
@@ -10471,7 +10494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1">
       <c r="A61" s="117" t="s">
         <v>116</v>
       </c>
@@ -10487,7 +10510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1">
       <c r="A62" s="117" t="s">
         <v>117</v>
       </c>
@@ -10503,7 +10526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1">
       <c r="A63" s="117" t="s">
         <v>118</v>
       </c>
@@ -10519,7 +10542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1">
       <c r="A64" s="117" t="s">
         <v>119</v>
       </c>
@@ -10535,7 +10558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1">
       <c r="A65" s="117" t="s">
         <v>120</v>
       </c>
@@ -10551,7 +10574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1">
       <c r="A66" s="117" t="s">
         <v>121</v>
       </c>
@@ -10567,7 +10590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1">
       <c r="A67" s="117" t="s">
         <v>122</v>
       </c>
@@ -10583,7 +10606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1">
       <c r="A68" s="117" t="s">
         <v>123</v>
       </c>
@@ -10599,7 +10622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1">
       <c r="A69" s="117" t="s">
         <v>125</v>
       </c>
@@ -10615,7 +10638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1">
       <c r="A70" s="117" t="s">
         <v>127</v>
       </c>
@@ -10631,7 +10654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1">
       <c r="A71" s="117" t="s">
         <v>129</v>
       </c>
@@ -10647,7 +10670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1">
       <c r="A72" s="117" t="s">
         <v>130</v>
       </c>
@@ -10663,7 +10686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1">
       <c r="A73" s="117" t="s">
         <v>131</v>
       </c>
@@ -10679,7 +10702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1">
       <c r="A74" s="117" t="s">
         <v>132</v>
       </c>
@@ -10695,7 +10718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1">
       <c r="A75" s="117" t="s">
         <v>133</v>
       </c>
@@ -10711,7 +10734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1">
       <c r="A76" s="117" t="s">
         <v>134</v>
       </c>
@@ -10727,7 +10750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1">
       <c r="A77" s="117" t="s">
         <v>135</v>
       </c>
@@ -10743,7 +10766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1">
       <c r="A78" s="117" t="s">
         <v>136</v>
       </c>
@@ -10759,7 +10782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1">
       <c r="A79" s="117" t="s">
         <v>137</v>
       </c>
@@ -10775,7 +10798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1">
       <c r="A80" s="117" t="s">
         <v>138</v>
       </c>
@@ -10791,7 +10814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1">
       <c r="A81" s="117" t="s">
         <v>139</v>
       </c>
@@ -10807,7 +10830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1">
       <c r="A82" s="117" t="s">
         <v>141</v>
       </c>
@@ -10823,7 +10846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1">
       <c r="A83" s="117" t="s">
         <v>142</v>
       </c>
@@ -10839,7 +10862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1">
       <c r="A84" s="117" t="s">
         <v>143</v>
       </c>
@@ -10855,7 +10878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1">
       <c r="A85" s="117" t="s">
         <v>144</v>
       </c>
@@ -10871,7 +10894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1">
       <c r="A86" s="117" t="s">
         <v>146</v>
       </c>
@@ -10887,7 +10910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1">
       <c r="A87" s="117" t="s">
         <v>147</v>
       </c>
@@ -10903,7 +10926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1">
       <c r="A88" s="117" t="s">
         <v>148</v>
       </c>
@@ -10919,7 +10942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1">
       <c r="A89" s="117" t="s">
         <v>149</v>
       </c>
@@ -10935,7 +10958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1">
       <c r="A90" s="117" t="s">
         <v>150</v>
       </c>
@@ -10951,7 +10974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1">
       <c r="A91" s="117" t="s">
         <v>151</v>
       </c>
@@ -10967,7 +10990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1">
       <c r="A92" s="117" t="s">
         <v>152</v>
       </c>
@@ -10983,7 +11006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1">
       <c r="A93" s="117" t="s">
         <v>153</v>
       </c>
@@ -10999,7 +11022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1">
       <c r="A94" s="117" t="s">
         <v>154</v>
       </c>
@@ -11015,7 +11038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1">
       <c r="A95" s="117" t="s">
         <v>155</v>
       </c>
@@ -11031,7 +11054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1">
       <c r="A96" s="117" t="s">
         <v>156</v>
       </c>
@@ -11047,7 +11070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1">
       <c r="A97" s="117" t="s">
         <v>157</v>
       </c>
@@ -11063,7 +11086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1">
       <c r="A98" s="117" t="s">
         <v>158</v>
       </c>
@@ -11079,7 +11102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1">
       <c r="A99" s="117" t="s">
         <v>159</v>
       </c>
@@ -11095,20 +11118,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1">
       <c r="A100" s="117" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45905.868253935187</v>
+        <v>46076.541597106479</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1">
       <c r="A101" s="117" t="s">
         <v>161</v>
       </c>
@@ -11124,7 +11147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1">
       <c r="A102" s="117" t="s">
         <v>162</v>
       </c>
@@ -11140,7 +11163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1">
       <c r="A103" s="117" t="s">
         <v>163</v>
       </c>
@@ -11156,7 +11179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1">
       <c r="A104" s="117" t="s">
         <v>164</v>
       </c>
@@ -11172,7 +11195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1">
       <c r="A105" s="117" t="s">
         <v>165</v>
       </c>
@@ -11188,7 +11211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1">
       <c r="A106" s="117" t="s">
         <v>166</v>
       </c>
@@ -11204,7 +11227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1">
       <c r="A107" s="117" t="s">
         <v>167</v>
       </c>
@@ -11220,7 +11243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1">
       <c r="A108" s="117" t="s">
         <v>168</v>
       </c>
@@ -11236,7 +11259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1">
       <c r="A109" s="117" t="s">
         <v>169</v>
       </c>
@@ -11252,7 +11275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1">
       <c r="A110" s="117" t="s">
         <v>170</v>
       </c>
@@ -11268,7 +11291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1">
       <c r="A111" s="117" t="s">
         <v>171</v>
       </c>
@@ -11284,12 +11307,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1">
       <c r="A112" s="117"/>
       <c r="B112" s="117"/>
       <c r="D112" s="117"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1">
       <c r="A113" s="117" t="s">
         <v>172</v>
       </c>
@@ -11305,7 +11328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1">
       <c r="A114" s="117" t="s">
         <v>173</v>
       </c>
@@ -11321,7 +11344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1">
       <c r="A115" s="117" t="s">
         <v>175</v>
       </c>
@@ -11337,7 +11360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1">
       <c r="A116" s="117" t="s">
         <v>177</v>
       </c>
@@ -11353,7 +11376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1">
       <c r="A117" s="117" t="s">
         <v>178</v>
       </c>
@@ -11369,7 +11392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1">
       <c r="A118" s="117" t="s">
         <v>179</v>
       </c>
@@ -11385,7 +11408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1">
       <c r="A119" s="117" t="s">
         <v>180</v>
       </c>
@@ -11401,7 +11424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1">
       <c r="A120" s="117" t="s">
         <v>181</v>
       </c>
@@ -11417,7 +11440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1">
       <c r="A121" s="117" t="s">
         <v>182</v>
       </c>
@@ -11433,7 +11456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1">
       <c r="A122" s="117" t="s">
         <v>183</v>
       </c>
@@ -11449,7 +11472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1">
       <c r="A123" s="117" t="s">
         <v>184</v>
       </c>
@@ -11465,7 +11488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1">
       <c r="A124" s="117" t="s">
         <v>185</v>
       </c>
@@ -11481,7 +11504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1">
       <c r="A125" s="117" t="s">
         <v>186</v>
       </c>
@@ -11497,7 +11520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1">
       <c r="A126" s="117" t="s">
         <v>187</v>
       </c>
@@ -11513,7 +11536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1">
       <c r="A127" s="117" t="s">
         <v>188</v>
       </c>
@@ -11529,7 +11552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1">
       <c r="A128" s="117" t="s">
         <v>189</v>
       </c>
@@ -11545,7 +11568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1">
       <c r="A129" s="117" t="s">
         <v>190</v>
       </c>
@@ -11561,7 +11584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1">
       <c r="A130" s="117" t="s">
         <v>191</v>
       </c>
@@ -11577,7 +11600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1">
       <c r="A131" s="117" t="s">
         <v>192</v>
       </c>
@@ -11593,7 +11616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1">
       <c r="A132" s="117" t="s">
         <v>193</v>
       </c>
@@ -11609,7 +11632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1">
       <c r="A133" s="117" t="s">
         <v>194</v>
       </c>
@@ -11625,7 +11648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1">
       <c r="A134" s="117" t="s">
         <v>195</v>
       </c>
@@ -11641,7 +11664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1">
       <c r="A135" s="117" t="s">
         <v>196</v>
       </c>
@@ -11657,7 +11680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1">
       <c r="A136" s="117" t="s">
         <v>198</v>
       </c>
@@ -11673,7 +11696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1">
       <c r="A137" s="117" t="s">
         <v>199</v>
       </c>
@@ -11689,7 +11712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1">
       <c r="A138" s="117" t="s">
         <v>200</v>
       </c>
@@ -11705,7 +11728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1">
       <c r="A139" s="117" t="s">
         <v>201</v>
       </c>
@@ -11721,7 +11744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1">
       <c r="A140" s="117" t="s">
         <v>202</v>
       </c>
@@ -11737,7 +11760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1">
       <c r="A141" s="117" t="s">
         <v>203</v>
       </c>
@@ -11753,7 +11776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1">
       <c r="A142" s="117" t="s">
         <v>205</v>
       </c>
@@ -11769,7 +11792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1">
       <c r="A143" s="117" t="s">
         <v>206</v>
       </c>
@@ -11785,20 +11808,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1">
       <c r="A144" s="117" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45905</v>
+        <v>46076</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1">
       <c r="A145" s="117" t="s">
         <v>208</v>
       </c>
@@ -11814,7 +11837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1">
       <c r="A146" s="117" t="s">
         <v>210</v>
       </c>
@@ -11830,7 +11853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1">
       <c r="A147" s="117" t="s">
         <v>211</v>
       </c>
@@ -11846,7 +11869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1">
       <c r="A148" s="117" t="s">
         <v>213</v>
       </c>
@@ -11862,7 +11885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1">
       <c r="A149" s="117" t="s">
         <v>214</v>
       </c>
@@ -11878,7 +11901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1">
       <c r="A150" s="117" t="s">
         <v>215</v>
       </c>
@@ -11894,7 +11917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1">
       <c r="A151" s="117" t="s">
         <v>216</v>
       </c>
@@ -11910,7 +11933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1">
       <c r="A152" s="117" t="s">
         <v>217</v>
       </c>
@@ -11926,7 +11949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1">
       <c r="A153" s="117" t="s">
         <v>218</v>
       </c>
@@ -11942,7 +11965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1">
       <c r="A154" s="117" t="s">
         <v>219</v>
       </c>
@@ -11959,7 +11982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1">
       <c r="A155" s="117" t="s">
         <v>220</v>
       </c>
@@ -11975,7 +11998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1">
       <c r="A156" s="117" t="s">
         <v>221</v>
       </c>
@@ -11991,7 +12014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1">
       <c r="A157" s="117" t="s">
         <v>222</v>
       </c>
@@ -12007,7 +12030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1">
       <c r="A158" s="117" t="s">
         <v>223</v>
       </c>
@@ -12023,7 +12046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1">
       <c r="A159" s="117" t="s">
         <v>224</v>
       </c>
@@ -12039,7 +12062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1">
       <c r="A160" s="117" t="s">
         <v>225</v>
       </c>
@@ -12055,7 +12078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1">
       <c r="A161" s="117" t="s">
         <v>226</v>
       </c>
@@ -12071,7 +12094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1">
       <c r="A162" s="117" t="s">
         <v>227</v>
       </c>
@@ -12087,7 +12110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1">
       <c r="A163" s="117" t="s">
         <v>229</v>
       </c>
@@ -12105,10 +12128,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12123,7 +12146,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -12133,17 +12156,17 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="122" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="123"/>
+      <c r="E1" s="122"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -12151,19 +12174,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
@@ -12171,26 +12194,26 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="75" customHeight="1">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" outlineLevel="1"/>
+    <row r="11" spans="1:8" outlineLevel="1"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
+    <row r="16" spans="1:8" outlineLevel="1"/>
+    <row r="17" spans="1:1" outlineLevel="1"/>
+    <row r="18" spans="1:1" outlineLevel="1"/>
+    <row r="30" spans="1:1">
       <c r="A30" t="e" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">RANDARRAY(2, 2)</f>
         <v>#NAME?</v>
@@ -12212,14 +12235,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -12241,7 +12264,7 @@
       </c>
       <c r="M1" s="36"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
@@ -12267,7 +12290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
@@ -12290,7 +12313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -12316,7 +12339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
@@ -12336,7 +12359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
@@ -12359,7 +12382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15.75">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -12379,7 +12402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="21">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -12402,7 +12425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -12419,7 +12442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
@@ -12427,7 +12450,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -12436,7 +12459,7 @@
       </c>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1">
       <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
@@ -12450,7 +12473,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
@@ -12461,7 +12484,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
@@ -12475,7 +12498,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
@@ -12486,7 +12509,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
       <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
@@ -12500,12 +12523,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -12517,7 +12540,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -12528,7 +12551,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -12542,12 +12565,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -12556,13 +12579,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -12571,20 +12594,20 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
+    <row r="30" spans="1:6">
       <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
@@ -12598,13 +12621,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -12621,7 +12644,7 @@
       <c r="I1" s="36"/>
       <c r="J1" s="36"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
@@ -12644,7 +12667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
@@ -12667,7 +12690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
@@ -12687,7 +12710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
@@ -12711,7 +12734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
@@ -12734,7 +12757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
@@ -12760,7 +12783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
@@ -12771,7 +12794,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
@@ -12780,7 +12803,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -12798,7 +12821,7 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
@@ -12821,13 +12844,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45905</v>
+        <v>46076</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -12846,7 +12869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
@@ -12869,7 +12892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
@@ -12895,7 +12918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
@@ -12915,7 +12938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
@@ -12938,7 +12961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
@@ -12961,7 +12984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
@@ -12984,7 +13007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
@@ -13007,7 +13030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
@@ -13030,7 +13053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
@@ -13056,7 +13079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
@@ -13082,7 +13105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
@@ -13108,7 +13131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
@@ -13125,7 +13148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
@@ -13151,7 +13174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
@@ -13171,7 +13194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
@@ -13197,7 +13220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
@@ -13217,9 +13240,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" s="38" t="s">
-        <v>440</v>
+        <v>375</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -13228,7 +13251,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -13246,9 +13269,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="G30" s="34" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -13266,9 +13289,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1">
       <c r="G31" s="35" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H31" s="36">
         <v>5</v>
@@ -13280,9 +13303,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="G32" s="34" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -13294,9 +13317,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="7:10">
       <c r="G33" s="34" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -13308,9 +13331,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="7:10">
       <c r="G34" s="34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -13322,9 +13345,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="7:10">
       <c r="G35" s="34" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -13336,9 +13359,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="7:10">
       <c r="G36" s="34" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -13350,9 +13373,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="7:10">
       <c r="G37" s="34" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -13364,110 +13387,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="7:10">
       <c r="G39" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="23" priority="59">
+    <cfRule type="expression" dxfId="41" priority="59">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="47" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="21" priority="115"/>
+    <cfRule type="aboveAverage" dxfId="39" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="20" priority="74" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="38" priority="74" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="19" priority="72">
+    <cfRule type="containsBlanks" dxfId="37" priority="72">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="18" priority="71">
+    <cfRule type="containsErrors" dxfId="36" priority="71">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="17" priority="70" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="35" priority="70" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="16" priority="68" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="34" priority="68" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="67">
+    <cfRule type="notContainsBlanks" dxfId="33" priority="67">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="14" priority="66">
+    <cfRule type="notContainsErrors" dxfId="32" priority="66">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="13" priority="65" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="31" priority="65" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="12" priority="64" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="30" priority="64" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="11" priority="116" rank="1"/>
+    <cfRule type="top10" dxfId="29" priority="116" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="9" priority="57" operator="notEqual">
+    <cfRule type="cellIs" dxfId="27" priority="57" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -13501,16 +13524,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:C29">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="between">
       <formula>$B$23</formula>
       <formula>2+2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="0" priority="97"/>
+    <cfRule type="uniqueValues" dxfId="18" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="45">
@@ -13933,7 +13956,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -13945,12 +13968,12 @@
     <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -13958,25 +13981,25 @@
         <v>36</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="117" t="s">
         <v>42</v>
       </c>
@@ -14007,7 +14030,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="117" t="s">
         <v>44</v>
       </c>
@@ -14038,9 +14061,9 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="C6" s="117" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D6" s="117">
         <f>SUBTOTAL(109,Table3[Age])</f>
@@ -14071,9 +14094,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -14082,22 +14105,22 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J8" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="C9">
         <v>3</v>
       </c>
@@ -14125,18 +14148,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="C12">
         <v>3</v>
       </c>
@@ -14144,9 +14167,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -14155,7 +14178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="C15">
         <v>3</v>
       </c>
@@ -14163,9 +14186,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -14174,7 +14197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4">
       <c r="C18">
         <v>3</v>
       </c>
@@ -14182,9 +14205,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -14193,7 +14216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4">
       <c r="C21">
         <v>3</v>
       </c>
@@ -14201,9 +14224,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -14212,7 +14235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4">
       <c r="C24">
         <v>3</v>
       </c>
@@ -14220,9 +14243,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4">
       <c r="B26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -14231,7 +14254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4">
       <c r="C27">
         <v>3</v>
       </c>
@@ -14239,45 +14262,45 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4">
       <c r="C28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D28">
         <f>SUBTOTAL(109,Table4910[Column2])</f>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4">
       <c r="B30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D30" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" hidden="1">
       <c r="C31" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D31" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
       <c r="C32" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D32" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -14300,7 +14323,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -14321,9 +14344,9 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15">
       <c r="A1" s="92" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -14331,7 +14354,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -14339,21 +14362,21 @@
       <c r="E2" s="117"/>
       <c r="F2" s="117"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="89" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="117"/>
       <c r="B4" s="117"/>
       <c r="C4" s="89" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D4">
         <v>12.1</v>
@@ -14380,10 +14403,10 @@
         <v>12052</v>
       </c>
       <c r="L4" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="117"/>
       <c r="B5" s="117"/>
       <c r="C5" s="90" t="s">
@@ -14396,7 +14419,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" s="117"/>
       <c r="B6" s="117"/>
       <c r="C6" s="91">
@@ -14409,7 +14432,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" s="117"/>
       <c r="B7" s="117"/>
       <c r="C7" s="90" t="s">
@@ -14422,7 +14445,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" s="117"/>
       <c r="B8" s="117"/>
       <c r="C8" s="91">
@@ -14435,7 +14458,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" s="117"/>
       <c r="B9" s="117"/>
       <c r="C9" s="90" t="s">
@@ -14448,7 +14471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" s="117"/>
       <c r="B10" s="117"/>
       <c r="C10" s="91">
@@ -14461,7 +14484,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -14472,7 +14495,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -14483,7 +14506,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -14494,7 +14517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -14505,7 +14528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -14516,7 +14539,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -14527,7 +14550,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:12">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -14538,7 +14561,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -14549,7 +14572,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -14560,7 +14583,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -14571,9 +14594,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12">
       <c r="C21" s="90" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -14612,31 +14635,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B2" s="117"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -14648,25 +14671,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="51">
       <c r="A1" s="99" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -14674,7 +14697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -14682,7 +14705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -14690,7 +14713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4</v>
       </c>
@@ -14698,7 +14721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dhrutik Patel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DA6F05-B302-48AE-B11C-1FB2528D58DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{880E0E36-3FD6-4555-B701-A081A5B535D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,9 @@
   <externalReferences>
     <externalReference r:id="rId15"/>
   </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
+    <pivotCache cacheId="5782" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,6 +46,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="442">
   <si>
     <t>CF =42</t>
   </si>
@@ -1201,6 +1202,9 @@
   </si>
   <si>
     <t>5Rating</t>
+  </si>
+  <si>
+    <t>CF with formulas</t>
   </si>
   <si>
     <t>5Quarters</t>
@@ -1375,6 +1379,9 @@
     <t>Custom Formula</t>
   </si>
   <si>
+    <t>Decimal with formula</t>
+  </si>
+  <si>
     <t>option1</t>
   </si>
   <si>
@@ -1397,9 +1404,6 @@
   </si>
   <si>
     <t>A1234556</t>
-  </si>
-  <si>
-    <t>CF with formulas</t>
   </si>
 </sst>
 </file>
@@ -1414,7 +1418,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2208,7 +2212,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2414,7 +2418,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2427,13 +2430,169 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="47">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2847,157 +3006,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -3041,7 +3049,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3642,7 +3650,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4074,7 +4082,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4692,7 +4700,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5058,7 +5066,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5357,7 +5365,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5774,7 +5782,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6176,7 +6184,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6466,7 +6474,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -7933,7 +7941,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="5782" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8083,7 +8091,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8095,22 +8103,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8531,7 +8539,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -8540,7 +8548,7 @@
     <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1">
       <c r="A1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -8549,7 +8557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.75">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -8562,25 +8570,25 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="119"/>
+      <c r="I2" s="125"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1">
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="120">
+      <c r="K3" s="119">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1">
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
@@ -8593,50 +8601,50 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="121"/>
+      <c r="K4" s="120"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1">
       <c r="C5" s="117">
         <v>42</v>
       </c>
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="121"/>
+      <c r="K5" s="120"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1">
       <c r="G6" s="117">
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="121"/>
+      <c r="K6" s="120"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1">
       <c r="C7" s="117">
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="121"/>
+      <c r="K7" s="120"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1">
       <c r="G8" s="117">
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="122"/>
+      <c r="K8" s="121"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1">
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -8646,7 +8654,7 @@
       </c>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1">
       <c r="C10" s="117">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -8655,13 +8663,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1">
       <c r="C11" s="117">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1">
       <c r="C12" s="117">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -8670,13 +8678,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1">
       <c r="G13" s="117">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -8685,32 +8693,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1">
       <c r="C15" s="117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1">
       <c r="C16" s="117" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1">
       <c r="C17" s="117" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1">
       <c r="C18" s="117" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1">
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1">
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
@@ -8724,7 +8732,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -8734,7 +8742,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
@@ -8748,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
       <c r="C24" s="16">
         <v>10</v>
       </c>
@@ -8759,7 +8767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
@@ -8770,7 +8778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="B26" s="117" t="s">
         <v>20</v>
       </c>
@@ -8784,7 +8792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>22</v>
       </c>
@@ -8801,7 +8809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>23</v>
       </c>
@@ -8818,7 +8826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>24</v>
       </c>
@@ -8835,7 +8843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>25</v>
       </c>
@@ -8852,7 +8860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>26</v>
       </c>
@@ -8869,7 +8877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>27</v>
       </c>
@@ -8886,7 +8894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>28</v>
       </c>
@@ -8903,7 +8911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>29</v>
       </c>
@@ -8914,7 +8922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>30</v>
       </c>
@@ -8931,7 +8939,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8976,7 +8984,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8985,7 +8993,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8994,7 +9002,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -9011,7 +9019,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9020,46 +9028,49 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" customWidth="1"/>
     <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="9" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="114" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B1" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C1" s="115" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D1" s="115" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1" s="115" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F1" s="115" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G1" s="115" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I1" s="116" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>432</v>
+      </c>
+      <c r="J1" s="123" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="104">
         <v>4</v>
       </c>
@@ -9070,7 +9081,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="105" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E2" s="106">
         <v>45575</v>
@@ -9079,7 +9090,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="G2" s="107" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H2" s="106">
         <v>45292</v>
@@ -9087,8 +9098,11 @@
       <c r="I2" s="108">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="124">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="104">
         <v>3</v>
       </c>
@@ -9099,7 +9113,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="105" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E3" s="106">
         <v>45576</v>
@@ -9108,16 +9122,19 @@
         <v>0.57638888888888884</v>
       </c>
       <c r="G3" s="107" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H3" s="106">
         <v>45231</v>
       </c>
       <c r="I3" s="108" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+      <c r="J3" s="124">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="104">
         <v>9</v>
       </c>
@@ -9128,7 +9145,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="105" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E4" s="106">
         <v>45574</v>
@@ -9137,7 +9154,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="G4" s="107" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H4" s="106">
         <v>45325</v>
@@ -9145,8 +9162,11 @@
       <c r="I4" s="108">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="124">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="104">
         <v>5</v>
       </c>
@@ -9157,7 +9177,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="105" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E5" s="106">
         <v>45573</v>
@@ -9166,7 +9186,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G5" s="105" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H5" s="106">
         <v>45084</v>
@@ -9174,8 +9194,11 @@
       <c r="I5" s="108">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" s="124">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="109">
         <v>7</v>
       </c>
@@ -9186,7 +9209,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="110" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E6" s="111">
         <v>45566</v>
@@ -9195,17 +9218,20 @@
         <v>0.5229166666666667</v>
       </c>
       <c r="G6" s="110" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H6" s="111">
         <v>45420</v>
       </c>
       <c r="I6" s="113" t="s">
-        <v>438</v>
+        <v>440</v>
+      </c>
+      <c r="J6" s="124">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A6" xr:uid="{B9309757-E2F4-49A1-880B-2F47F04364D6}">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -9237,6 +9263,10 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{1E18A174-B5CF-4015-B7DC-F1491351E054}">
       <formula1>"option1,option2,option3"</formula1>
     </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J6" xr:uid="{E43B85E8-D498-4841-B610-8D8CED09FAA7}">
+      <formula1>$A$2</formula1>
+      <formula2>2+10</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9248,12 +9278,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1">
       <c r="A1" s="117" t="s">
         <v>31</v>
       </c>
@@ -9288,7 +9318,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1">
       <c r="A2" s="117" t="s">
         <v>41</v>
       </c>
@@ -9334,7 +9364,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1">
       <c r="A3" s="117" t="s">
         <v>43</v>
       </c>
@@ -9380,7 +9410,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1">
       <c r="A4" s="117" t="s">
         <v>45</v>
       </c>
@@ -9426,7 +9456,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1">
       <c r="A5" s="117" t="s">
         <v>47</v>
       </c>
@@ -9472,7 +9502,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1">
       <c r="A6" s="117" t="s">
         <v>49</v>
       </c>
@@ -9518,7 +9548,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1">
       <c r="A7" s="117" t="s">
         <v>52</v>
       </c>
@@ -9552,7 +9582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1">
       <c r="A8" s="117" t="s">
         <v>54</v>
       </c>
@@ -9586,7 +9616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1">
       <c r="A9" s="117" t="s">
         <v>56</v>
       </c>
@@ -9617,7 +9647,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1">
       <c r="A10" s="117" t="s">
         <v>58</v>
       </c>
@@ -9633,7 +9663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1">
       <c r="A11" s="117" t="s">
         <v>59</v>
       </c>
@@ -9652,7 +9682,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1">
       <c r="A12" s="117" t="s">
         <v>61</v>
       </c>
@@ -9683,7 +9713,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1">
       <c r="A13" s="117" t="s">
         <v>62</v>
       </c>
@@ -9714,7 +9744,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1">
       <c r="A14" s="117" t="s">
         <v>67</v>
       </c>
@@ -9730,7 +9760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1">
       <c r="A15" s="117" t="s">
         <v>68</v>
       </c>
@@ -9746,7 +9776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1">
       <c r="A16" s="117" t="s">
         <v>69</v>
       </c>
@@ -9762,7 +9792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1">
       <c r="A17" s="117" t="s">
         <v>70</v>
       </c>
@@ -9778,7 +9808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1">
       <c r="A18" s="117" t="s">
         <v>71</v>
       </c>
@@ -9794,7 +9824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1">
       <c r="A19" s="117" t="s">
         <v>72</v>
       </c>
@@ -9810,7 +9840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1">
       <c r="A20" s="117" t="s">
         <v>73</v>
       </c>
@@ -9826,7 +9856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1">
       <c r="A21" s="117" t="s">
         <v>74</v>
       </c>
@@ -9842,7 +9872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1">
       <c r="A22" s="117" t="s">
         <v>76</v>
       </c>
@@ -9858,7 +9888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1">
       <c r="A23" s="117" t="s">
         <v>77</v>
       </c>
@@ -9874,7 +9904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1">
       <c r="A24" s="117" t="s">
         <v>78</v>
       </c>
@@ -9891,7 +9921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1">
       <c r="A25" s="117" t="s">
         <v>79</v>
       </c>
@@ -9907,7 +9937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1">
       <c r="A26" s="117" t="s">
         <v>81</v>
       </c>
@@ -9923,7 +9953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1">
       <c r="A27" s="117" t="s">
         <v>82</v>
       </c>
@@ -9939,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1">
       <c r="A28" s="117" t="s">
         <v>83</v>
       </c>
@@ -9956,7 +9986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1">
       <c r="A29" s="117" t="s">
         <v>84</v>
       </c>
@@ -9972,7 +10002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1">
       <c r="A30" s="117" t="s">
         <v>85</v>
       </c>
@@ -9988,7 +10018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1">
       <c r="A31" s="117" t="s">
         <v>86</v>
       </c>
@@ -10004,7 +10034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1">
       <c r="A32" s="117" t="s">
         <v>87</v>
       </c>
@@ -10020,7 +10050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1">
       <c r="A33" s="117" t="s">
         <v>88</v>
       </c>
@@ -10036,7 +10066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1">
       <c r="A34" s="117" t="s">
         <v>89</v>
       </c>
@@ -10052,7 +10082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1">
       <c r="A35" s="117" t="s">
         <v>90</v>
       </c>
@@ -10068,7 +10098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1">
       <c r="A36" s="117" t="s">
         <v>91</v>
       </c>
@@ -10084,7 +10114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1">
       <c r="A37" s="117" t="s">
         <v>92</v>
       </c>
@@ -10100,7 +10130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1">
       <c r="A38" s="117" t="s">
         <v>93</v>
       </c>
@@ -10117,7 +10147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1">
       <c r="A39" s="117" t="s">
         <v>94</v>
       </c>
@@ -10133,7 +10163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1">
       <c r="A40" s="117" t="s">
         <v>95</v>
       </c>
@@ -10149,7 +10179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1">
       <c r="A41" s="117" t="s">
         <v>96</v>
       </c>
@@ -10165,7 +10195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1">
       <c r="A42" s="117" t="s">
         <v>97</v>
       </c>
@@ -10181,7 +10211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1">
       <c r="A43" s="117" t="s">
         <v>98</v>
       </c>
@@ -10197,7 +10227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1">
       <c r="A44" s="117" t="s">
         <v>99</v>
       </c>
@@ -10213,7 +10243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1">
       <c r="A45" s="117" t="s">
         <v>100</v>
       </c>
@@ -10229,7 +10259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1">
       <c r="A46" s="117" t="s">
         <v>101</v>
       </c>
@@ -10245,7 +10275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1">
       <c r="A47" s="117" t="s">
         <v>102</v>
       </c>
@@ -10261,7 +10291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1">
       <c r="A48" s="117" t="s">
         <v>103</v>
       </c>
@@ -10277,7 +10307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1">
       <c r="A49" s="117" t="s">
         <v>104</v>
       </c>
@@ -10293,7 +10323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1">
       <c r="A50" s="117" t="s">
         <v>105</v>
       </c>
@@ -10310,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1">
       <c r="A51" s="117" t="s">
         <v>106</v>
       </c>
@@ -10327,7 +10357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1">
       <c r="A52" s="117" t="s">
         <v>107</v>
       </c>
@@ -10343,7 +10373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1">
       <c r="A53" s="117" t="s">
         <v>108</v>
       </c>
@@ -10359,7 +10389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1">
       <c r="A54" s="117" t="s">
         <v>109</v>
       </c>
@@ -10375,7 +10405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1">
       <c r="A55" s="117" t="s">
         <v>110</v>
       </c>
@@ -10391,7 +10421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1">
       <c r="A56" s="117" t="s">
         <v>111</v>
       </c>
@@ -10407,7 +10437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1">
       <c r="A57" s="117" t="s">
         <v>112</v>
       </c>
@@ -10423,7 +10453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="117" t="s">
         <v>113</v>
       </c>
@@ -10439,7 +10469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1">
       <c r="A59" s="117" t="s">
         <v>114</v>
       </c>
@@ -10455,7 +10485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1">
       <c r="A60" s="117" t="s">
         <v>115</v>
       </c>
@@ -10471,7 +10501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1">
       <c r="A61" s="117" t="s">
         <v>116</v>
       </c>
@@ -10487,7 +10517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1">
       <c r="A62" s="117" t="s">
         <v>117</v>
       </c>
@@ -10503,7 +10533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1">
       <c r="A63" s="117" t="s">
         <v>118</v>
       </c>
@@ -10519,7 +10549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1">
       <c r="A64" s="117" t="s">
         <v>119</v>
       </c>
@@ -10535,7 +10565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1">
       <c r="A65" s="117" t="s">
         <v>120</v>
       </c>
@@ -10551,7 +10581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1">
       <c r="A66" s="117" t="s">
         <v>121</v>
       </c>
@@ -10567,7 +10597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1">
       <c r="A67" s="117" t="s">
         <v>122</v>
       </c>
@@ -10583,7 +10613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1">
       <c r="A68" s="117" t="s">
         <v>123</v>
       </c>
@@ -10599,7 +10629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1">
       <c r="A69" s="117" t="s">
         <v>125</v>
       </c>
@@ -10615,7 +10645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1">
       <c r="A70" s="117" t="s">
         <v>127</v>
       </c>
@@ -10631,7 +10661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1">
       <c r="A71" s="117" t="s">
         <v>129</v>
       </c>
@@ -10647,7 +10677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1">
       <c r="A72" s="117" t="s">
         <v>130</v>
       </c>
@@ -10663,7 +10693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1">
       <c r="A73" s="117" t="s">
         <v>131</v>
       </c>
@@ -10679,7 +10709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1">
       <c r="A74" s="117" t="s">
         <v>132</v>
       </c>
@@ -10695,7 +10725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1">
       <c r="A75" s="117" t="s">
         <v>133</v>
       </c>
@@ -10711,7 +10741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1">
       <c r="A76" s="117" t="s">
         <v>134</v>
       </c>
@@ -10727,7 +10757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1">
       <c r="A77" s="117" t="s">
         <v>135</v>
       </c>
@@ -10743,7 +10773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1">
       <c r="A78" s="117" t="s">
         <v>136</v>
       </c>
@@ -10759,7 +10789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1">
       <c r="A79" s="117" t="s">
         <v>137</v>
       </c>
@@ -10775,7 +10805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1">
       <c r="A80" s="117" t="s">
         <v>138</v>
       </c>
@@ -10791,7 +10821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1">
       <c r="A81" s="117" t="s">
         <v>139</v>
       </c>
@@ -10807,7 +10837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1">
       <c r="A82" s="117" t="s">
         <v>141</v>
       </c>
@@ -10823,7 +10853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1">
       <c r="A83" s="117" t="s">
         <v>142</v>
       </c>
@@ -10839,7 +10869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1">
       <c r="A84" s="117" t="s">
         <v>143</v>
       </c>
@@ -10855,7 +10885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1">
       <c r="A85" s="117" t="s">
         <v>144</v>
       </c>
@@ -10871,7 +10901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1">
       <c r="A86" s="117" t="s">
         <v>146</v>
       </c>
@@ -10887,7 +10917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1">
       <c r="A87" s="117" t="s">
         <v>147</v>
       </c>
@@ -10903,7 +10933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1">
       <c r="A88" s="117" t="s">
         <v>148</v>
       </c>
@@ -10919,7 +10949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1">
       <c r="A89" s="117" t="s">
         <v>149</v>
       </c>
@@ -10935,7 +10965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1">
       <c r="A90" s="117" t="s">
         <v>150</v>
       </c>
@@ -10951,7 +10981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1">
       <c r="A91" s="117" t="s">
         <v>151</v>
       </c>
@@ -10967,7 +10997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1">
       <c r="A92" s="117" t="s">
         <v>152</v>
       </c>
@@ -10983,7 +11013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1">
       <c r="A93" s="117" t="s">
         <v>153</v>
       </c>
@@ -10999,7 +11029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1">
       <c r="A94" s="117" t="s">
         <v>154</v>
       </c>
@@ -11015,7 +11045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1">
       <c r="A95" s="117" t="s">
         <v>155</v>
       </c>
@@ -11031,7 +11061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1">
       <c r="A96" s="117" t="s">
         <v>156</v>
       </c>
@@ -11047,7 +11077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1">
       <c r="A97" s="117" t="s">
         <v>157</v>
       </c>
@@ -11063,7 +11093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1">
       <c r="A98" s="117" t="s">
         <v>158</v>
       </c>
@@ -11079,7 +11109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1">
       <c r="A99" s="117" t="s">
         <v>159</v>
       </c>
@@ -11095,20 +11125,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1">
       <c r="A100" s="117" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45905.868253935187</v>
+        <v>46044.440208912034</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1">
       <c r="A101" s="117" t="s">
         <v>161</v>
       </c>
@@ -11124,7 +11154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1">
       <c r="A102" s="117" t="s">
         <v>162</v>
       </c>
@@ -11140,7 +11170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1">
       <c r="A103" s="117" t="s">
         <v>163</v>
       </c>
@@ -11156,7 +11186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1">
       <c r="A104" s="117" t="s">
         <v>164</v>
       </c>
@@ -11172,7 +11202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1">
       <c r="A105" s="117" t="s">
         <v>165</v>
       </c>
@@ -11188,7 +11218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1">
       <c r="A106" s="117" t="s">
         <v>166</v>
       </c>
@@ -11204,7 +11234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1">
       <c r="A107" s="117" t="s">
         <v>167</v>
       </c>
@@ -11220,7 +11250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1">
       <c r="A108" s="117" t="s">
         <v>168</v>
       </c>
@@ -11236,7 +11266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1">
       <c r="A109" s="117" t="s">
         <v>169</v>
       </c>
@@ -11252,7 +11282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1">
       <c r="A110" s="117" t="s">
         <v>170</v>
       </c>
@@ -11268,7 +11298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1">
       <c r="A111" s="117" t="s">
         <v>171</v>
       </c>
@@ -11284,12 +11314,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1">
       <c r="A112" s="117"/>
       <c r="B112" s="117"/>
       <c r="D112" s="117"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1">
       <c r="A113" s="117" t="s">
         <v>172</v>
       </c>
@@ -11305,7 +11335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1">
       <c r="A114" s="117" t="s">
         <v>173</v>
       </c>
@@ -11321,7 +11351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1">
       <c r="A115" s="117" t="s">
         <v>175</v>
       </c>
@@ -11337,7 +11367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1">
       <c r="A116" s="117" t="s">
         <v>177</v>
       </c>
@@ -11353,7 +11383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1">
       <c r="A117" s="117" t="s">
         <v>178</v>
       </c>
@@ -11369,7 +11399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1">
       <c r="A118" s="117" t="s">
         <v>179</v>
       </c>
@@ -11385,7 +11415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1">
       <c r="A119" s="117" t="s">
         <v>180</v>
       </c>
@@ -11401,7 +11431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1">
       <c r="A120" s="117" t="s">
         <v>181</v>
       </c>
@@ -11417,7 +11447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1">
       <c r="A121" s="117" t="s">
         <v>182</v>
       </c>
@@ -11433,7 +11463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1">
       <c r="A122" s="117" t="s">
         <v>183</v>
       </c>
@@ -11449,7 +11479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1">
       <c r="A123" s="117" t="s">
         <v>184</v>
       </c>
@@ -11465,7 +11495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1">
       <c r="A124" s="117" t="s">
         <v>185</v>
       </c>
@@ -11481,7 +11511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1">
       <c r="A125" s="117" t="s">
         <v>186</v>
       </c>
@@ -11497,7 +11527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1">
       <c r="A126" s="117" t="s">
         <v>187</v>
       </c>
@@ -11513,7 +11543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1">
       <c r="A127" s="117" t="s">
         <v>188</v>
       </c>
@@ -11529,7 +11559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1">
       <c r="A128" s="117" t="s">
         <v>189</v>
       </c>
@@ -11545,7 +11575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1">
       <c r="A129" s="117" t="s">
         <v>190</v>
       </c>
@@ -11561,7 +11591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1">
       <c r="A130" s="117" t="s">
         <v>191</v>
       </c>
@@ -11577,7 +11607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1">
       <c r="A131" s="117" t="s">
         <v>192</v>
       </c>
@@ -11593,7 +11623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1">
       <c r="A132" s="117" t="s">
         <v>193</v>
       </c>
@@ -11609,7 +11639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1">
       <c r="A133" s="117" t="s">
         <v>194</v>
       </c>
@@ -11625,7 +11655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1">
       <c r="A134" s="117" t="s">
         <v>195</v>
       </c>
@@ -11641,7 +11671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1">
       <c r="A135" s="117" t="s">
         <v>196</v>
       </c>
@@ -11657,7 +11687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1">
       <c r="A136" s="117" t="s">
         <v>198</v>
       </c>
@@ -11673,7 +11703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1">
       <c r="A137" s="117" t="s">
         <v>199</v>
       </c>
@@ -11689,7 +11719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1">
       <c r="A138" s="117" t="s">
         <v>200</v>
       </c>
@@ -11705,7 +11735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1">
       <c r="A139" s="117" t="s">
         <v>201</v>
       </c>
@@ -11721,7 +11751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1">
       <c r="A140" s="117" t="s">
         <v>202</v>
       </c>
@@ -11737,7 +11767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1">
       <c r="A141" s="117" t="s">
         <v>203</v>
       </c>
@@ -11753,7 +11783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1">
       <c r="A142" s="117" t="s">
         <v>205</v>
       </c>
@@ -11769,7 +11799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1">
       <c r="A143" s="117" t="s">
         <v>206</v>
       </c>
@@ -11785,20 +11815,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1">
       <c r="A144" s="117" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45905</v>
+        <v>46044</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1">
       <c r="A145" s="117" t="s">
         <v>208</v>
       </c>
@@ -11814,7 +11844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1">
       <c r="A146" s="117" t="s">
         <v>210</v>
       </c>
@@ -11830,7 +11860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1">
       <c r="A147" s="117" t="s">
         <v>211</v>
       </c>
@@ -11846,7 +11876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1">
       <c r="A148" s="117" t="s">
         <v>213</v>
       </c>
@@ -11862,7 +11892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1">
       <c r="A149" s="117" t="s">
         <v>214</v>
       </c>
@@ -11878,7 +11908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1">
       <c r="A150" s="117" t="s">
         <v>215</v>
       </c>
@@ -11894,7 +11924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1">
       <c r="A151" s="117" t="s">
         <v>216</v>
       </c>
@@ -11910,7 +11940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1">
       <c r="A152" s="117" t="s">
         <v>217</v>
       </c>
@@ -11926,7 +11956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1">
       <c r="A153" s="117" t="s">
         <v>218</v>
       </c>
@@ -11942,7 +11972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1">
       <c r="A154" s="117" t="s">
         <v>219</v>
       </c>
@@ -11959,7 +11989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1">
       <c r="A155" s="117" t="s">
         <v>220</v>
       </c>
@@ -11975,7 +12005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1">
       <c r="A156" s="117" t="s">
         <v>221</v>
       </c>
@@ -11991,7 +12021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1">
       <c r="A157" s="117" t="s">
         <v>222</v>
       </c>
@@ -12007,7 +12037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1">
       <c r="A158" s="117" t="s">
         <v>223</v>
       </c>
@@ -12023,7 +12053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1">
       <c r="A159" s="117" t="s">
         <v>224</v>
       </c>
@@ -12039,7 +12069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1">
       <c r="A160" s="117" t="s">
         <v>225</v>
       </c>
@@ -12055,7 +12085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1">
       <c r="A161" s="117" t="s">
         <v>226</v>
       </c>
@@ -12071,7 +12101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1">
       <c r="A162" s="117" t="s">
         <v>227</v>
       </c>
@@ -12087,7 +12117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1">
       <c r="A163" s="117" t="s">
         <v>229</v>
       </c>
@@ -12105,10 +12135,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12123,7 +12153,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -12133,17 +12163,17 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="122" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="123"/>
+      <c r="E1" s="122"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -12151,19 +12181,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
@@ -12171,28 +12201,28 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="75" customHeight="1">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" outlineLevel="1"/>
+    <row r="11" spans="1:8" outlineLevel="1"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
+    <row r="16" spans="1:8" outlineLevel="1"/>
+    <row r="17" spans="1:1" outlineLevel="1"/>
+    <row r="18" spans="1:1" outlineLevel="1"/>
+    <row r="30" spans="1:1">
       <c r="A30" t="e" cm="1">
-        <f t="array" aca="1" ref="A30" ca="1">RANDARRAY(2, 2)</f>
+        <f t="array" aca="1" ref="A30" ca="1">_xludf.RANDARRAY(2, 2)</f>
         <v>#NAME?</v>
       </c>
     </row>
@@ -12212,14 +12242,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -12241,7 +12271,7 @@
       </c>
       <c r="M1" s="36"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
@@ -12267,7 +12297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
@@ -12290,7 +12320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -12316,7 +12346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
@@ -12336,7 +12366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
@@ -12359,7 +12389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15.75">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -12379,7 +12409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="21">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -12402,7 +12432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -12419,7 +12449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
@@ -12427,7 +12457,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -12436,7 +12466,7 @@
       </c>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1">
       <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
@@ -12450,7 +12480,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
@@ -12461,7 +12491,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
@@ -12475,7 +12505,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
@@ -12486,7 +12516,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
       <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
@@ -12500,12 +12530,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -12517,7 +12547,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -12528,7 +12558,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -12542,12 +12572,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -12556,13 +12586,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -12571,20 +12601,20 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
+    <row r="30" spans="1:6">
       <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
@@ -12598,13 +12628,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -12621,7 +12651,7 @@
       <c r="I1" s="36"/>
       <c r="J1" s="36"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
@@ -12644,7 +12674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
@@ -12667,7 +12697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
@@ -12687,7 +12717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
@@ -12711,7 +12741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
@@ -12734,7 +12764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
@@ -12760,7 +12790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
@@ -12771,7 +12801,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
@@ -12780,7 +12810,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -12798,7 +12828,7 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
@@ -12821,13 +12851,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45905</v>
+        <v>46044</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -12846,7 +12876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
@@ -12869,7 +12899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
@@ -12895,7 +12925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
@@ -12915,7 +12945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
@@ -12938,7 +12968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
@@ -12961,7 +12991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
@@ -12984,7 +13014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
@@ -13007,7 +13037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
@@ -13030,7 +13060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
@@ -13056,7 +13086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
@@ -13082,7 +13112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
@@ -13108,7 +13138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
@@ -13125,7 +13155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
@@ -13151,7 +13181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
@@ -13171,7 +13201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
@@ -13197,7 +13227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
@@ -13217,9 +13247,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" s="38" t="s">
-        <v>440</v>
+        <v>375</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -13228,7 +13258,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -13246,9 +13276,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="G30" s="34" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -13266,9 +13296,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1">
       <c r="G31" s="35" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H31" s="36">
         <v>5</v>
@@ -13280,9 +13310,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="G32" s="34" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -13294,9 +13324,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="7:10">
       <c r="G33" s="34" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -13308,9 +13338,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="7:10">
       <c r="G34" s="34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -13322,9 +13352,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="7:10">
       <c r="G35" s="34" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -13336,9 +13366,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="7:10">
       <c r="G36" s="34" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -13350,9 +13380,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="7:10">
       <c r="G37" s="34" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -13364,110 +13394,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="7:10">
       <c r="G39" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="23" priority="59">
+    <cfRule type="expression" dxfId="41" priority="59">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="47" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="21" priority="115"/>
+    <cfRule type="aboveAverage" dxfId="39" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="20" priority="74" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="38" priority="74" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="19" priority="72">
+    <cfRule type="containsBlanks" dxfId="37" priority="72">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="18" priority="71">
+    <cfRule type="containsErrors" dxfId="36" priority="71">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="17" priority="70" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="35" priority="70" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="16" priority="68" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="34" priority="68" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="67">
+    <cfRule type="notContainsBlanks" dxfId="33" priority="67">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="14" priority="66">
+    <cfRule type="notContainsErrors" dxfId="32" priority="66">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="13" priority="65" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="31" priority="65" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="12" priority="64" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="30" priority="64" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="11" priority="116" rank="1"/>
+    <cfRule type="top10" dxfId="29" priority="116" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="9" priority="57" operator="notEqual">
+    <cfRule type="cellIs" dxfId="27" priority="57" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -13501,16 +13531,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:C29">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="between">
       <formula>$B$23</formula>
       <formula>2+2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="0" priority="97"/>
+    <cfRule type="uniqueValues" dxfId="18" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="45">
@@ -13933,7 +13963,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -13945,12 +13975,12 @@
     <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -13958,25 +13988,25 @@
         <v>36</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="117" t="s">
         <v>42</v>
       </c>
@@ -14007,7 +14037,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="117" t="s">
         <v>44</v>
       </c>
@@ -14038,9 +14068,9 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="C6" s="117" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D6" s="117">
         <f>SUBTOTAL(109,Table3[Age])</f>
@@ -14071,9 +14101,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -14082,22 +14112,22 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J8" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="C9">
         <v>3</v>
       </c>
@@ -14125,18 +14155,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="C12">
         <v>3</v>
       </c>
@@ -14144,9 +14174,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -14155,7 +14185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="C15">
         <v>3</v>
       </c>
@@ -14163,9 +14193,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -14174,7 +14204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4">
       <c r="C18">
         <v>3</v>
       </c>
@@ -14182,9 +14212,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -14193,7 +14223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4">
       <c r="C21">
         <v>3</v>
       </c>
@@ -14201,9 +14231,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -14212,7 +14242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4">
       <c r="C24">
         <v>3</v>
       </c>
@@ -14220,9 +14250,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4">
       <c r="B26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -14231,7 +14261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4">
       <c r="C27">
         <v>3</v>
       </c>
@@ -14239,45 +14269,45 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4">
       <c r="C28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D28">
         <f>SUBTOTAL(109,Table4910[Column2])</f>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4">
       <c r="B30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D30" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" hidden="1">
       <c r="C31" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D31" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
       <c r="C32" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D32" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -14300,7 +14330,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -14321,9 +14351,9 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15">
       <c r="A1" s="92" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -14331,7 +14361,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -14339,21 +14369,21 @@
       <c r="E2" s="117"/>
       <c r="F2" s="117"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="89" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="117"/>
       <c r="B4" s="117"/>
       <c r="C4" s="89" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D4">
         <v>12.1</v>
@@ -14380,10 +14410,10 @@
         <v>12052</v>
       </c>
       <c r="L4" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="117"/>
       <c r="B5" s="117"/>
       <c r="C5" s="90" t="s">
@@ -14396,7 +14426,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" s="117"/>
       <c r="B6" s="117"/>
       <c r="C6" s="91">
@@ -14409,7 +14439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" s="117"/>
       <c r="B7" s="117"/>
       <c r="C7" s="90" t="s">
@@ -14422,7 +14452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" s="117"/>
       <c r="B8" s="117"/>
       <c r="C8" s="91">
@@ -14435,7 +14465,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" s="117"/>
       <c r="B9" s="117"/>
       <c r="C9" s="90" t="s">
@@ -14448,7 +14478,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" s="117"/>
       <c r="B10" s="117"/>
       <c r="C10" s="91">
@@ -14461,7 +14491,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -14472,7 +14502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -14483,7 +14513,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -14494,7 +14524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -14505,7 +14535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -14516,7 +14546,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -14527,7 +14557,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:12">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -14538,7 +14568,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -14549,7 +14579,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -14560,7 +14590,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -14571,9 +14601,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12">
       <c r="C21" s="90" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -14612,31 +14642,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B2" s="117"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -14648,25 +14678,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="51">
       <c r="A1" s="99" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -14674,7 +14704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -14682,7 +14712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -14690,7 +14720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4</v>
       </c>
@@ -14698,7 +14728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346363BF-6AD4-4354-A44F-43A8F3AE431A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C25BF4FD-CBA3-4F6C-88EB-5301832C5180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1860" windowWidth="29040" windowHeight="18240" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1860" windowWidth="29040" windowHeight="18240" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,9 @@
     <definedName name="Table_Col_Named_Range">Table10[Col1]</definedName>
     <definedName name="Table_Named_Range">Table10[]</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId18"/>
+    <pivotCache cacheId="926" r:id="rId18"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1425,7 +1425,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2160,7 +2160,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2341,9 +2341,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2361,6 +2358,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2373,6 +2373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2380,6 +2381,157 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="47">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2797,157 +2949,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -4904,7 +4905,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1F77B4"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="14288" cmpd="sng">
                 <a:solidFill>
@@ -4923,7 +4924,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF7F0E"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:ln w="14288" cmpd="sng">
                 <a:solidFill>
@@ -5166,7 +5167,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1F77B4"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="14288" cmpd="sng">
                 <a:solidFill>
@@ -5185,7 +5186,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF7F0E"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:ln w="14288" cmpd="sng">
                 <a:solidFill>
@@ -5533,7 +5534,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1F77B4"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="14288" cmpd="sng">
                 <a:solidFill>
@@ -5552,7 +5553,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF7F0E"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:ln w="14288" cmpd="sng">
                 <a:solidFill>
@@ -8914,7 +8915,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="926" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -9064,7 +9065,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9076,22 +9077,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9212,9 +9213,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9252,7 +9253,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9358,7 +9359,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9500,7 +9501,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9512,7 +9513,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -9521,181 +9522,341 @@
     <col min="6" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1">
       <c r="A1" s="21"/>
+      <c r="B1" s="110"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="104" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+    </row>
+    <row r="2" spans="1:12" ht="27.75">
+      <c r="A2" s="110"/>
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
       <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="104">
+      <c r="G2" s="109">
         <v>5</v>
       </c>
-      <c r="H2" s="110" t="s">
+      <c r="H2" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="111"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="110"/>
       <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L2" s="110"/>
+    </row>
+    <row r="3" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A3" s="110"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="104">
+      <c r="G3" s="109">
         <v>8</v>
       </c>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
       <c r="J3" s="5"/>
       <c r="K3" s="112">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A4" s="110"/>
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="104">
+      <c r="C4" s="109">
         <v>12.4</v>
       </c>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
       <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="104">
+      <c r="G4" s="109">
         <v>9</v>
       </c>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
       <c r="J4" s="5"/>
       <c r="K4" s="113"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="104">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="109">
         <v>42</v>
       </c>
-      <c r="G5" s="104">
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="109">
         <v>15</v>
       </c>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
       <c r="J5" s="5"/>
       <c r="K5" s="113"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G6" s="104">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A6" s="110"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="109">
         <v>22</v>
       </c>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
       <c r="J6" s="5"/>
       <c r="K6" s="113"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="104">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="109">
         <v>3</v>
       </c>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
       <c r="J7" s="5"/>
       <c r="K7" s="113"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G8" s="104">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A8" s="110"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="109">
         <v>30</v>
       </c>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
       <c r="J8" s="5"/>
       <c r="K8" s="114"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A9" s="110"/>
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="104">
+      <c r="C9" s="109">
         <f>SUM(C4:C5)</f>
         <v>54.4</v>
       </c>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="110"/>
       <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="104">
+      <c r="L9" s="110"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A10" s="110"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="109">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
       </c>
-      <c r="D10" s="104" t="s">
+      <c r="D10" s="109" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="104">
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A11" s="110"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="109">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C12" s="104">
+      <c r="D11" s="110"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="110"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="110"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A12" s="110"/>
+      <c r="B12" s="110"/>
+      <c r="C12" s="109">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
       </c>
-      <c r="D12" s="104" t="s">
+      <c r="D12" s="109" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G13" s="104">
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="110"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A13" s="110"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="109">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="110"/>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A14" s="110"/>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="104" t="str">
+      <c r="C14" s="109" t="str">
         <f ca="1">C14</f>
         <v>#CYCLE</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="104" t="s">
+      <c r="D14" s="110"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="110"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A15" s="110"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="109" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="104" t="str">
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A16" s="110"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="109" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="104" t="s">
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+    </row>
+    <row r="17" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A17" s="110"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="104" t="s">
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A18" s="110"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="109" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
       <c r="E19" s="3"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+    </row>
+    <row r="20" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A20" s="110"/>
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="D20" s="110"/>
       <c r="E20" s="10" t="s">
         <v>16</v>
       </c>
@@ -9704,8 +9865,9 @@
         <v>17</v>
       </c>
       <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I20" s="110"/>
+    </row>
+    <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -9713,198 +9875,266 @@
         <f>jestCharts!B2</f>
         <v>0</v>
       </c>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
       <c r="G21" s="10"/>
-    </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+    </row>
+    <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
+      <c r="B23" s="110"/>
       <c r="C23" s="15">
         <v>0.43</v>
       </c>
-      <c r="H23" s="104">
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="109">
         <v>0</v>
       </c>
-      <c r="I23" s="104">
+      <c r="I23" s="109">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A24" s="110"/>
+      <c r="B24" s="110"/>
       <c r="C24" s="16">
         <v>10</v>
       </c>
-      <c r="H24" s="104">
-        <v>1</v>
-      </c>
-      <c r="I24" s="104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="109">
+        <v>1</v>
+      </c>
+      <c r="I24" s="109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A25" s="110"/>
+      <c r="B25" s="110"/>
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
-      <c r="H25" s="104">
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="109">
         <v>2</v>
       </c>
-      <c r="I25" s="104">
+      <c r="I25" s="109">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="104" t="s">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A26" s="110"/>
+      <c r="B26" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="104" t="s">
+      <c r="C26" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="104">
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="109">
         <v>3</v>
       </c>
-      <c r="I26" s="104">
+      <c r="I26" s="109">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="104" t="s">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A27" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="104">
+      <c r="B27" s="109">
         <v>12</v>
       </c>
-      <c r="C27" s="104">
+      <c r="C27" s="109">
         <v>24</v>
       </c>
-      <c r="H27" s="104">
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="109">
         <v>4</v>
       </c>
-      <c r="I27" s="104">
+      <c r="I27" s="109">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="104" t="s">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A28" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="104">
+      <c r="B28" s="109">
         <v>48</v>
       </c>
-      <c r="C28" s="104">
+      <c r="C28" s="109">
         <v>12</v>
       </c>
-      <c r="H28" s="104">
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="109">
         <v>5</v>
       </c>
-      <c r="I28" s="104">
+      <c r="I28" s="109">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="104" t="s">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A29" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="104">
+      <c r="B29" s="109">
         <v>45</v>
       </c>
-      <c r="C29" s="104">
+      <c r="C29" s="109">
         <v>27</v>
       </c>
-      <c r="H29" s="104">
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="109">
         <v>6</v>
       </c>
-      <c r="I29" s="104">
+      <c r="I29" s="109">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="104" t="s">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A30" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="104">
-        <v>1</v>
-      </c>
-      <c r="C30" s="104">
+      <c r="B30" s="109">
+        <v>1</v>
+      </c>
+      <c r="C30" s="109">
         <v>9</v>
       </c>
-      <c r="H30" s="104">
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="109">
         <v>7</v>
       </c>
-      <c r="I30" s="104">
+      <c r="I30" s="109">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="104" t="s">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A31" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="104">
+      <c r="B31" s="109">
         <v>25</v>
       </c>
-      <c r="C31" s="104">
+      <c r="C31" s="109">
         <v>45</v>
       </c>
-      <c r="H31" s="104">
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="109">
         <v>8</v>
       </c>
-      <c r="I31" s="104">
+      <c r="I31" s="109">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="104" t="s">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A32" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="104">
+      <c r="B32" s="109">
         <v>31</v>
       </c>
-      <c r="C32" s="104">
+      <c r="C32" s="109">
         <v>17</v>
       </c>
-      <c r="H32" s="104">
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="109">
         <v>9</v>
       </c>
-      <c r="I32" s="104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="104" t="s">
+      <c r="I32" s="109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A33" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="104">
+      <c r="B33" s="109">
         <v>20</v>
       </c>
-      <c r="C33" s="104">
+      <c r="C33" s="109">
         <v>43</v>
       </c>
-      <c r="H33" s="104">
+      <c r="D33" s="110"/>
+      <c r="E33" s="110"/>
+      <c r="F33" s="110"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="109">
         <v>10</v>
       </c>
-      <c r="I33" s="104">
+      <c r="I33" s="109">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="104" t="s">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A34" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="104">
+      <c r="B34" s="109">
         <v>19</v>
       </c>
-      <c r="C34" s="104">
+      <c r="C34" s="109">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="104" t="s">
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="110"/>
+      <c r="G34" s="110"/>
+      <c r="H34" s="110"/>
+      <c r="I34" s="110"/>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A35" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="104">
+      <c r="B35" s="109">
         <v>16</v>
       </c>
-      <c r="C35" s="104">
+      <c r="C35" s="109">
         <v>16</v>
       </c>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="110"/>
+      <c r="I35" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9912,7 +10142,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9957,7 +10187,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9966,7 +10196,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9975,7 +10205,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.85546875" customWidth="1"/>
@@ -9992,7 +10222,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10002,7 +10232,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="4" width="14.140625" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" customWidth="1"/>
@@ -10012,195 +10242,195 @@
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="105" t="s">
         <v>424</v>
       </c>
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="106" t="s">
         <v>425</v>
       </c>
-      <c r="C1" s="107" t="s">
+      <c r="C1" s="106" t="s">
         <v>426</v>
       </c>
-      <c r="D1" s="107" t="s">
+      <c r="D1" s="106" t="s">
         <v>427</v>
       </c>
-      <c r="E1" s="107" t="s">
+      <c r="E1" s="106" t="s">
         <v>428</v>
       </c>
-      <c r="F1" s="107" t="s">
+      <c r="F1" s="106" t="s">
         <v>429</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="G1" s="106" t="s">
         <v>430</v>
       </c>
-      <c r="H1" s="107" t="s">
+      <c r="H1" s="106" t="s">
         <v>431</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="107" t="s">
         <v>432</v>
       </c>
-      <c r="J1" s="105" t="s">
+      <c r="J1" s="104" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:10">
+      <c r="A2" s="110">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="110">
         <v>99.5</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="110">
+        <v>1</v>
+      </c>
+      <c r="D2" s="110" t="s">
         <v>434</v>
       </c>
       <c r="E2" s="39">
         <v>45575</v>
       </c>
-      <c r="F2" s="109">
+      <c r="F2" s="108">
         <v>0.64583333333333337</v>
       </c>
-      <c r="G2" s="109" t="s">
+      <c r="G2" s="108" t="s">
         <v>435</v>
       </c>
       <c r="H2" s="39">
         <v>45292</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="110">
         <v>4</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="110">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3" spans="1:10">
+      <c r="A3" s="110">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="110">
         <v>40</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="110">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="110" t="s">
         <v>436</v>
       </c>
       <c r="E3" s="39">
         <v>45576</v>
       </c>
-      <c r="F3" s="109">
+      <c r="F3" s="108">
         <v>0.57638888888888884</v>
       </c>
-      <c r="G3" s="109" t="s">
+      <c r="G3" s="108" t="s">
         <v>437</v>
       </c>
       <c r="H3" s="39">
         <v>45231</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="110" t="s">
         <v>435</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="110">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4" spans="1:10">
+      <c r="A4" s="110">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="110">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="110">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="110" t="s">
         <v>438</v>
       </c>
       <c r="E4" s="39">
         <v>45574</v>
       </c>
-      <c r="F4" s="109">
+      <c r="F4" s="108">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G4" s="109" t="s">
+      <c r="G4" s="108" t="s">
         <v>439</v>
       </c>
       <c r="H4" s="39">
         <v>45325</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="110">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="110">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5" spans="1:10">
+      <c r="A5" s="110">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="110">
         <v>120</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="110">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="110" t="s">
         <v>436</v>
       </c>
       <c r="E5" s="39">
         <v>45573</v>
       </c>
-      <c r="F5" s="109">
+      <c r="F5" s="108">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="110" t="s">
         <v>440</v>
       </c>
       <c r="H5" s="39">
         <v>45084</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="110">
         <v>3</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="110">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="1:10">
+      <c r="A6" s="110">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="110">
         <v>12</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="110">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="110" t="s">
         <v>438</v>
       </c>
       <c r="E6" s="39">
         <v>45566</v>
       </c>
-      <c r="F6" s="109">
+      <c r="F6" s="108">
         <v>0.5229166666666667</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="110" t="s">
         <v>441</v>
       </c>
       <c r="H6" s="39">
         <v>45420</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="110" t="s">
         <v>440</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="110">
         <v>15</v>
       </c>
     </row>
@@ -10249,7 +10479,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175FB5D6-D3ED-FD4F-886B-71BD0CB28755}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10259,7 +10489,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B936FE7B-5147-E945-A711-7FBABD0575D3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10272,24 +10502,26 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A1" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="104" t="s">
+      <c r="D1" s="109" t="s">
         <v>34</v>
       </c>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
       <c r="G1" s="17" t="s">
         <v>35</v>
       </c>
@@ -10305,392 +10537,476 @@
       <c r="K1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="104">
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="109">
         <v>0.1</v>
       </c>
+      <c r="O1" s="110"/>
       <c r="P1" s="17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="104" t="s">
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A2" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="104">
+      <c r="B2" s="109">
         <f>ABS(-5.5)</f>
         <v>5.5</v>
       </c>
-      <c r="C2" s="104">
+      <c r="C2" s="109">
         <v>5.5</v>
       </c>
-      <c r="D2" s="104">
+      <c r="D2" s="109">
         <f t="shared" ref="D2:D33" si="0">IF(B2=C2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="G2" s="104" t="s">
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="109" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="104">
+      <c r="H2" s="109">
         <v>26</v>
       </c>
-      <c r="I2" s="104">
+      <c r="I2" s="109">
         <v>1204.7</v>
       </c>
-      <c r="J2" s="104">
+      <c r="J2" s="109">
         <v>25618</v>
       </c>
-      <c r="K2" s="104">
+      <c r="K2" s="109">
         <v>5</v>
       </c>
-      <c r="N2" s="104">
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="109">
         <v>0.2</v>
       </c>
-      <c r="P2">
+      <c r="O2" s="110"/>
+      <c r="P2" s="110">
         <f>SUM(H2, I$2)</f>
         <v>1230.7</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="110">
         <f>SUM(H2, $I2)</f>
         <v>1230.7</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="110">
         <f>SUM(H2, $I$2)</f>
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="104" t="s">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A3" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="104">
+      <c r="B3" s="109">
         <f>ACOS(1)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="104">
+      <c r="C3" s="109">
         <v>0</v>
       </c>
-      <c r="D3" s="104">
+      <c r="D3" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="104">
+      <c r="H3" s="109">
         <v>13</v>
       </c>
-      <c r="I3" s="104">
+      <c r="I3" s="109">
         <v>500.9</v>
       </c>
-      <c r="J3" s="104">
+      <c r="J3" s="109">
         <v>23000</v>
       </c>
-      <c r="K3" s="104">
+      <c r="K3" s="109">
         <v>7</v>
       </c>
-      <c r="N3" s="104">
+      <c r="L3" s="110"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="109">
         <v>0.4</v>
       </c>
-      <c r="P3">
+      <c r="O3" s="110"/>
+      <c r="P3" s="110">
         <f t="shared" ref="P3:P6" si="1">SUM(H3, I$2)</f>
         <v>1217.7</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="110">
         <f t="shared" ref="Q3:Q6" si="2">SUM(H3, $I3)</f>
         <v>513.9</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="110">
         <f t="shared" ref="R3:R6" si="3">SUM(H3, $I$2)</f>
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="104" t="s">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A4" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="104">
+      <c r="B4" s="109">
         <f>ROUND(ACOSH(2),5)</f>
         <v>1.3169599999999999</v>
       </c>
-      <c r="C4" s="104">
+      <c r="C4" s="109">
         <v>1.3169599999999999</v>
       </c>
-      <c r="D4" s="104">
+      <c r="D4" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G4" s="104" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="104">
+      <c r="H4" s="109">
         <v>26</v>
       </c>
-      <c r="I4" s="104">
+      <c r="I4" s="109">
         <v>252.4</v>
       </c>
-      <c r="J4" s="104">
+      <c r="J4" s="109">
         <v>110120.5</v>
       </c>
-      <c r="K4" s="104">
+      <c r="K4" s="109">
         <v>3</v>
       </c>
-      <c r="N4" s="104">
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="109">
         <v>0.5</v>
       </c>
-      <c r="P4">
+      <c r="O4" s="110"/>
+      <c r="P4" s="110">
         <f t="shared" si="1"/>
         <v>1230.7</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="110">
         <f t="shared" si="2"/>
         <v>278.39999999999998</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="110">
         <f t="shared" si="3"/>
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="104" t="s">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A5" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="104">
+      <c r="B5" s="109">
         <f>ROUND(_xlfn.ACOT(1),5)</f>
         <v>0.78539999999999999</v>
       </c>
-      <c r="C5" s="104">
+      <c r="C5" s="109">
         <v>0.78539999999999999</v>
       </c>
-      <c r="D5" s="104">
+      <c r="D5" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G5" s="104" t="s">
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="104">
+      <c r="H5" s="109">
         <v>42</v>
       </c>
-      <c r="I5" s="104">
+      <c r="I5" s="109">
         <v>4701.3</v>
       </c>
-      <c r="J5" s="104">
+      <c r="J5" s="109">
         <v>50024</v>
       </c>
-      <c r="K5" s="104">
+      <c r="K5" s="109">
         <v>4</v>
       </c>
-      <c r="N5" s="104">
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="109">
         <v>0.6</v>
       </c>
-      <c r="P5">
+      <c r="O5" s="110"/>
+      <c r="P5" s="110">
         <f t="shared" si="1"/>
         <v>1246.7</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="110">
         <f t="shared" si="2"/>
         <v>4743.3</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="110">
         <f t="shared" si="3"/>
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="104" t="s">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A6" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="104">
+      <c r="B6" s="109">
         <f>ROUND(_xlfn.ACOTH(2),5)</f>
         <v>0.54930999999999996</v>
       </c>
-      <c r="C6" s="104">
+      <c r="C6" s="109">
         <v>0.54930999999999996</v>
       </c>
-      <c r="D6" s="104">
+      <c r="D6" s="109">
         <f>IF(B6=C6,1,0)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="104" t="s">
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="104">
+      <c r="H6" s="109">
         <v>9</v>
       </c>
-      <c r="I6" s="104">
+      <c r="I6" s="109">
         <v>12.1</v>
       </c>
-      <c r="J6" s="104">
+      <c r="J6" s="109">
         <v>2</v>
       </c>
-      <c r="K6" s="104">
+      <c r="K6" s="109">
         <v>1000</v>
       </c>
-      <c r="N6" s="104" t="s">
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="P6">
+      <c r="O6" s="110"/>
+      <c r="P6" s="110">
         <f t="shared" si="1"/>
         <v>1213.7</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="110">
         <f t="shared" si="2"/>
         <v>21.1</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="110">
         <f t="shared" si="3"/>
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="104" t="s">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A7" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="104" t="b">
+      <c r="B7" s="109" t="b">
         <f>AND(TRUE,TRUE)</f>
         <v>1</v>
       </c>
-      <c r="C7" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="104">
+      <c r="C7" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G7" s="104" t="s">
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="104">
+      <c r="H7" s="109">
         <v>27</v>
       </c>
-      <c r="I7" s="104">
+      <c r="I7" s="109">
         <v>4000</v>
       </c>
-      <c r="J7" s="104">
+      <c r="J7" s="109">
         <v>189576</v>
       </c>
-      <c r="K7" s="104">
+      <c r="K7" s="109">
         <v>2</v>
       </c>
-      <c r="N7" s="104" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="104" t="s">
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+    </row>
+    <row r="8" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A8" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="104">
+      <c r="B8" s="109">
         <f>ROUND(ASIN(0.5),5)</f>
         <v>0.52359999999999995</v>
       </c>
-      <c r="C8" s="104">
+      <c r="C8" s="109">
         <v>0.52359999999999995</v>
       </c>
-      <c r="D8" s="104">
+      <c r="D8" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G8" s="104" t="s">
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="104">
+      <c r="H8" s="109">
         <v>30</v>
       </c>
-      <c r="I8" s="104">
+      <c r="I8" s="109">
         <v>12052</v>
       </c>
-      <c r="J8" s="104">
+      <c r="J8" s="109">
         <v>256018</v>
       </c>
-      <c r="K8" s="104">
-        <v>1</v>
-      </c>
-      <c r="N8" s="104" t="b">
+      <c r="K8" s="109">
+        <v>1</v>
+      </c>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="109" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="104" t="s">
+      <c r="O8" s="110"/>
+      <c r="P8" s="110"/>
+      <c r="Q8" s="110"/>
+      <c r="R8" s="110"/>
+    </row>
+    <row r="9" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A9" s="109" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="104">
+      <c r="B9" s="109">
         <f>ROUND(ASINH(2),5)</f>
         <v>1.44364</v>
       </c>
-      <c r="C9" s="104">
+      <c r="C9" s="109">
         <v>1.44364</v>
       </c>
-      <c r="D9" s="104">
+      <c r="D9" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G9" s="104" t="s">
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="104">
+      <c r="H9" s="109">
         <v>37</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="109">
         <v>4890.1000000000004</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="109">
         <v>5000</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="109">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="104" t="s">
+      <c r="L9" s="110"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="110"/>
+      <c r="Q9" s="110"/>
+      <c r="R9" s="110"/>
+    </row>
+    <row r="10" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A10" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="104">
+      <c r="B10" s="109">
         <f>ROUND(ATAN(1),5)</f>
         <v>0.78539999999999999</v>
       </c>
-      <c r="C10" s="104">
+      <c r="C10" s="109">
         <v>0.78539999999999999</v>
       </c>
-      <c r="D10" s="104">
+      <c r="D10" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="104" t="s">
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="110"/>
+      <c r="Q10" s="110"/>
+      <c r="R10" s="110"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A11" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="104">
+      <c r="B11" s="109">
         <f>ROUND(ATAN2(-1,0),5)</f>
         <v>3.1415899999999999</v>
       </c>
-      <c r="C11" s="104">
+      <c r="C11" s="109">
         <v>3.1415899999999999</v>
       </c>
-      <c r="D11" s="104">
+      <c r="D11" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G11" s="104" t="s">
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="109" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="104" t="s">
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="110"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="110"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="110"/>
+      <c r="P11" s="110"/>
+      <c r="Q11" s="110"/>
+      <c r="R11" s="110"/>
+    </row>
+    <row r="12" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A12" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="104">
+      <c r="B12" s="109">
         <f>ROUND(ATANH(0.7),5)</f>
         <v>0.86729999999999996</v>
       </c>
-      <c r="C12" s="104">
+      <c r="C12" s="109">
         <v>0.86729999999999996</v>
       </c>
-      <c r="D12" s="104">
+      <c r="D12" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
       <c r="G12" s="17" t="s">
         <v>35</v>
       </c>
@@ -10706,459 +11022,517 @@
       <c r="K12" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="104" t="s">
+      <c r="L12" s="110"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="110"/>
+      <c r="P12" s="110"/>
+      <c r="Q12" s="110"/>
+      <c r="R12" s="110"/>
+    </row>
+    <row r="13" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A13" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="104">
+      <c r="B13" s="109">
         <f>ROUND(AVEDEV(I2:I9),5)</f>
         <v>2959.1624999999999</v>
       </c>
-      <c r="C13" s="104">
+      <c r="C13" s="109">
         <v>2959.1624999999999</v>
       </c>
-      <c r="D13" s="104">
+      <c r="D13" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="104" t="s">
+      <c r="H13" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="104" t="s">
+      <c r="I13" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="104" t="s">
+      <c r="J13" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="104" t="s">
+      <c r="K13" s="109" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="104" t="s">
+      <c r="L13" s="110"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="110"/>
+      <c r="P13" s="110"/>
+      <c r="Q13" s="110"/>
+      <c r="R13" s="110"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A14" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="104">
+      <c r="B14" s="109">
         <f>ROUND(AVERAGE(H2:H9),5)</f>
         <v>26.25</v>
       </c>
-      <c r="C14" s="104">
+      <c r="C14" s="109">
         <v>26.25</v>
       </c>
-      <c r="D14" s="104">
+      <c r="D14" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="104" t="s">
+      <c r="E14" s="110"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="110"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="110"/>
+      <c r="P14" s="110"/>
+      <c r="Q14" s="110"/>
+      <c r="R14" s="110"/>
+    </row>
+    <row r="15" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A15" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="104">
+      <c r="B15" s="109">
         <f>AVERAGEA(G2:H9)</f>
         <v>13.125</v>
       </c>
-      <c r="C15" s="104">
+      <c r="C15" s="109">
         <v>13.125</v>
       </c>
-      <c r="D15" s="104">
+      <c r="D15" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="104" t="s">
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="110"/>
+      <c r="R15" s="110"/>
+    </row>
+    <row r="16" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A16" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="104">
+      <c r="B16" s="109">
         <f>ROUND(AVERAGEIF(J2:J9,"&gt;150000"),5)</f>
         <v>222797</v>
       </c>
-      <c r="C16" s="104">
+      <c r="C16" s="109">
         <v>222797</v>
       </c>
-      <c r="D16" s="104">
+      <c r="D16" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="104" t="s">
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="110"/>
+      <c r="R16" s="110"/>
+    </row>
+    <row r="17" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A17" s="109" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="104">
+      <c r="B17" s="109">
         <f>ROUND(AVERAGEIFS(I2:I9,H2:H9,"&gt;=30",K2:K9,"&lt;10"),5)</f>
         <v>8376.65</v>
       </c>
-      <c r="C17" s="104">
+      <c r="C17" s="109">
         <v>8376.65</v>
       </c>
-      <c r="D17" s="104">
+      <c r="D17" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="104" t="s">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A18" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="104">
+      <c r="B18" s="109">
         <f>CEILING(20.4,1)</f>
         <v>21</v>
       </c>
-      <c r="C18" s="104">
+      <c r="C18" s="109">
         <v>21</v>
       </c>
-      <c r="D18" s="104">
+      <c r="D18" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="104" t="s">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A19" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="104">
+      <c r="B19" s="109">
         <f>_xlfn.CEILING.MATH(-5.5,1,0)</f>
         <v>-5</v>
       </c>
-      <c r="C19" s="104">
+      <c r="C19" s="109">
         <v>-5</v>
       </c>
-      <c r="D19" s="104">
+      <c r="D19" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="104" t="s">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A20" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="104">
+      <c r="B20" s="109">
         <f>_xlfn.CEILING.PRECISE(230,100)</f>
         <v>300</v>
       </c>
-      <c r="C20" s="104">
+      <c r="C20" s="109">
         <v>300</v>
       </c>
-      <c r="D20" s="104">
+      <c r="D20" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="104" t="s">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A21" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="104" t="str">
+      <c r="B21" s="109" t="str">
         <f>CHAR(74)</f>
         <v>J</v>
       </c>
-      <c r="C21" s="104" t="s">
+      <c r="C21" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="104">
+      <c r="D21" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="104" t="s">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A22" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="104">
+      <c r="B22" s="109">
         <f>COLUMN(C4)</f>
         <v>3</v>
       </c>
-      <c r="C22" s="104">
+      <c r="C22" s="109">
         <v>3</v>
       </c>
-      <c r="D22" s="104">
+      <c r="D22" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="104" t="s">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A23" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="104">
+      <c r="B23" s="109">
         <f>COLUMNS(A5:D12)</f>
         <v>4</v>
       </c>
-      <c r="C23" s="104">
+      <c r="C23" s="109">
         <v>4</v>
       </c>
-      <c r="D23" s="104">
+      <c r="D23" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="104" t="s">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A24" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="104" t="str">
+      <c r="B24" s="109" t="str">
         <f>_xlfn.CONCAT(1,23)</f>
         <v>123</v>
       </c>
-      <c r="C24" s="104" t="str">
+      <c r="C24" s="109" t="str">
         <f>"123"</f>
         <v>123</v>
       </c>
-      <c r="D24" s="104">
+      <c r="D24" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="104" t="s">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A25" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="104" t="str">
+      <c r="B25" s="109" t="str">
         <f>CONCATENATE("BUT, ","MICHEL")</f>
         <v>BUT, MICHEL</v>
       </c>
-      <c r="C25" s="104" t="s">
+      <c r="C25" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="104">
+      <c r="D25" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="104" t="s">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A26" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="104">
+      <c r="B26" s="109">
         <f>ROUND(COS(PI()/3),2)</f>
         <v>0.5</v>
       </c>
-      <c r="C26" s="104">
+      <c r="C26" s="109">
         <v>0.5</v>
       </c>
-      <c r="D26" s="104">
+      <c r="D26" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="104" t="s">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A27" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="104">
+      <c r="B27" s="109">
         <f>ROUND(COSH(2),5)</f>
         <v>3.7622</v>
       </c>
-      <c r="C27" s="104">
+      <c r="C27" s="109">
         <v>3.7622</v>
       </c>
-      <c r="D27" s="104">
+      <c r="D27" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="104" t="s">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A28" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="104">
+      <c r="B28" s="109">
         <f>ROUND(_xlfn.COT(PI()/6),5)</f>
         <v>1.7320500000000001</v>
       </c>
-      <c r="C28" s="104">
+      <c r="C28" s="109">
         <f>ROUND(SQRT(3),5)</f>
         <v>1.7320500000000001</v>
       </c>
-      <c r="D28" s="104">
+      <c r="D28" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="104" t="s">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A29" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="104">
+      <c r="B29" s="109">
         <f>ROUND(_xlfn.COTH(0.5),5)</f>
         <v>2.1639499999999998</v>
       </c>
-      <c r="C29" s="104">
+      <c r="C29" s="109">
         <v>2.1639499999999998</v>
       </c>
-      <c r="D29" s="104">
+      <c r="D29" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="104" t="s">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A30" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="104">
+      <c r="B30" s="109">
         <f>COUNT(1,"a","5","2021-03-14")</f>
         <v>3</v>
       </c>
-      <c r="C30" s="104">
+      <c r="C30" s="109">
         <v>2</v>
       </c>
-      <c r="D30" s="104">
+      <c r="D30" s="109">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="104" t="s">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A31" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="104">
+      <c r="B31" s="109">
         <f>COUNTA(1,"a","5","2021-03-14")</f>
         <v>4</v>
       </c>
-      <c r="C31" s="104">
+      <c r="C31" s="109">
         <v>4</v>
       </c>
-      <c r="D31" s="104">
+      <c r="D31" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="104" t="s">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A32" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="104">
+      <c r="B32" s="109">
         <f>COUNTBLANK(F1:G1)</f>
         <v>1</v>
       </c>
-      <c r="C32" s="104">
-        <v>1</v>
-      </c>
-      <c r="D32" s="104">
+      <c r="C32" s="109">
+        <v>1</v>
+      </c>
+      <c r="D32" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="104" t="s">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A33" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="104">
+      <c r="B33" s="109">
         <f>COUNTIF(H2:H9,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="C33" s="104">
+      <c r="C33" s="109">
         <v>2</v>
       </c>
-      <c r="D33" s="104">
+      <c r="D33" s="109">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="104" t="s">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A34" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="104">
+      <c r="B34" s="109">
         <f>COUNTIFS(H2:H9,"&gt;25",K2:K9,"&lt;4")</f>
         <v>3</v>
       </c>
-      <c r="C34" s="104">
+      <c r="C34" s="109">
         <v>3</v>
       </c>
-      <c r="D34" s="104">
+      <c r="D34" s="109">
         <f t="shared" ref="D34:D65" si="4">IF(B34=C34,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="104" t="s">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A35" s="109" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="104">
+      <c r="B35" s="109">
         <f>ROUND(COVAR(H2:H9,K2:K9),5)</f>
         <v>-2119.25</v>
       </c>
-      <c r="C35" s="104">
+      <c r="C35" s="109">
         <v>-2119.25</v>
       </c>
-      <c r="D35" s="104">
+      <c r="D35" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="104" t="s">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A36" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="104">
+      <c r="B36" s="109">
         <f>ROUND(_xlfn.COVARIANCE.P(K2:K9,H2:H9),5)</f>
         <v>-2119.25</v>
       </c>
-      <c r="C36" s="104">
+      <c r="C36" s="109">
         <v>-2119.25</v>
       </c>
-      <c r="D36" s="104">
+      <c r="D36" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="104" t="s">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A37" s="109" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="104">
+      <c r="B37" s="109">
         <f>ROUND(_xlfn.COVARIANCE.P(I2:I9,J2:J9),5)</f>
         <v>237217364.71641001</v>
       </c>
-      <c r="C37" s="104">
+      <c r="C37" s="109">
         <v>237217364.71641001</v>
       </c>
-      <c r="D37" s="104">
+      <c r="D37" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="104" t="s">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A38" s="109" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="104">
+      <c r="B38" s="109">
         <f>ROUND(_xlfn.CSC(PI()/4),5)</f>
         <v>1.41421</v>
       </c>
-      <c r="C38" s="104">
+      <c r="C38" s="109">
         <f>ROUND(SQRT(2),5)</f>
         <v>1.41421</v>
       </c>
-      <c r="D38" s="104">
+      <c r="D38" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="104" t="s">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A39" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="104">
+      <c r="B39" s="109">
         <f>ROUND(_xlfn.CSCH(PI()/3),5)</f>
         <v>0.80040999999999995</v>
       </c>
-      <c r="C39" s="104">
+      <c r="C39" s="109">
         <v>0.80040999999999995</v>
       </c>
-      <c r="D39" s="104">
+      <c r="D39" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="104" t="s">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A40" s="109" t="s">
         <v>95</v>
       </c>
       <c r="B40" s="18">
@@ -11168,287 +11542,287 @@
       <c r="C40" s="18">
         <v>43976</v>
       </c>
-      <c r="D40" s="104">
+      <c r="D40" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="104" t="s">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A41" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="104">
+      <c r="B41" s="109">
         <f>DATEVALUE("1969-08-15")</f>
         <v>25430</v>
       </c>
-      <c r="C41" s="104">
+      <c r="C41" s="109">
         <v>25430</v>
       </c>
-      <c r="D41" s="104">
+      <c r="D41" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="104" t="s">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A42" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="104">
+      <c r="B42" s="109">
         <f>ROUND(DAVERAGE(G1:K9,"Tot. Score",J12:J13),5)</f>
         <v>151434.625</v>
       </c>
-      <c r="C42" s="104">
+      <c r="C42" s="109">
         <v>151434.625</v>
       </c>
-      <c r="D42" s="104">
+      <c r="D42" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="104" t="s">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A43" s="109" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="104">
+      <c r="B43" s="109">
         <f>DAY("2020-03-17")</f>
         <v>17</v>
       </c>
-      <c r="C43" s="104">
+      <c r="C43" s="109">
         <v>17</v>
       </c>
-      <c r="D43" s="104">
+      <c r="D43" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="104" t="s">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A44" s="109" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="104">
+      <c r="B44" s="109">
         <f>_xlfn.DAYS("2022-03-17","2021-03-17")</f>
         <v>365</v>
       </c>
-      <c r="C44" s="104">
+      <c r="C44" s="109">
         <v>365</v>
       </c>
-      <c r="D44" s="104">
+      <c r="D44" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="104" t="s">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A45" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="104">
+      <c r="B45" s="109">
         <f>DCOUNT(G1:K9,"Name",H12:H13)</f>
         <v>0</v>
       </c>
-      <c r="C45" s="104">
+      <c r="C45" s="109">
         <v>0</v>
       </c>
-      <c r="D45" s="104">
+      <c r="D45" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="104" t="s">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A46" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="104">
+      <c r="B46" s="109">
         <f>DCOUNTA(G1:K9,"Name",H12:H13)</f>
         <v>3</v>
       </c>
-      <c r="C46" s="104">
+      <c r="C46" s="109">
         <v>3</v>
       </c>
-      <c r="D46" s="104">
+      <c r="D46" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="104" t="s">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A47" s="109" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="104">
+      <c r="B47" s="109">
         <f>_xlfn.DECIMAL(20,16)</f>
         <v>32</v>
       </c>
-      <c r="C47" s="104">
+      <c r="C47" s="109">
         <v>32</v>
       </c>
-      <c r="D47" s="104">
+      <c r="D47" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="104" t="s">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A48" s="109" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="104">
+      <c r="B48" s="109">
         <f>DEGREES(PI()/4)</f>
         <v>45</v>
       </c>
-      <c r="C48" s="104">
+      <c r="C48" s="109">
         <v>45</v>
       </c>
-      <c r="D48" s="104">
+      <c r="D48" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="104" t="s">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A49" s="109" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="104">
+      <c r="B49" s="109">
         <f>DGET(G1:K9,"Hours Played",G12:G13)</f>
         <v>252.4</v>
       </c>
-      <c r="C49" s="104">
+      <c r="C49" s="109">
         <v>252.4</v>
       </c>
-      <c r="D49" s="104">
+      <c r="D49" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="104" t="s">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A50" s="109" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="104">
+      <c r="B50" s="109">
         <f>DMAX(G1:K9,"Tot. Score",I12:I13)</f>
         <v>189576</v>
       </c>
-      <c r="C50" s="104">
+      <c r="C50" s="109">
         <f>J7</f>
         <v>189576</v>
       </c>
-      <c r="D50" s="104">
+      <c r="D50" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="104" t="s">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A51" s="109" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="104">
+      <c r="B51" s="109">
         <f>DMIN(G1:K9,"Tot. Score",H12:H13)</f>
         <v>5000</v>
       </c>
-      <c r="C51" s="104">
+      <c r="C51" s="109">
         <f>J9</f>
         <v>5000</v>
       </c>
-      <c r="D51" s="104">
+      <c r="D51" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="104" t="s">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A52" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="104">
+      <c r="B52" s="109">
         <f>DPRODUCT(G1:K9,"Age",K12:K13)</f>
         <v>333</v>
       </c>
-      <c r="C52" s="104">
+      <c r="C52" s="109">
         <v>333</v>
       </c>
-      <c r="D52" s="104">
+      <c r="D52" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="104" t="s">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A53" s="109" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="104">
+      <c r="B53" s="109">
         <f>ROUND(DSTDEV(G1:K9,"Age",H12:H13),5)</f>
         <v>6.0277099999999999</v>
       </c>
-      <c r="C53" s="104">
+      <c r="C53" s="109">
         <v>6.0277099999999999</v>
       </c>
-      <c r="D53" s="104">
+      <c r="D53" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="104" t="s">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A54" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="B54" s="104">
+      <c r="B54" s="109">
         <f>ROUND(DSTDEVP(G1:K9,"Age",H12:H13),5)</f>
         <v>4.9216100000000003</v>
       </c>
-      <c r="C54" s="104">
+      <c r="C54" s="109">
         <v>4.9216100000000003</v>
       </c>
-      <c r="D54" s="104">
+      <c r="D54" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="104" t="s">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A55" s="109" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="104">
+      <c r="B55" s="109">
         <f>DSUM(G1:K9,"Age",I12:I13)</f>
         <v>101</v>
       </c>
-      <c r="C55" s="104">
+      <c r="C55" s="109">
         <v>101</v>
       </c>
-      <c r="D55" s="104">
+      <c r="D55" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="104" t="s">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A56" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="B56" s="104">
+      <c r="B56" s="109">
         <f>ROUND(DVAR(G1:K9,"Hours Played",H12:H13),5)</f>
         <v>17560207.923330002</v>
       </c>
-      <c r="C56" s="104">
+      <c r="C56" s="109">
         <v>17560207.923330002</v>
       </c>
-      <c r="D56" s="104">
+      <c r="D56" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="104" t="s">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A57" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="104">
+      <c r="B57" s="109">
         <f>ROUND(DVARP(G1:K9,"Hours Played",H12:H13),5)</f>
         <v>11706805.28222</v>
       </c>
-      <c r="C57" s="104">
+      <c r="C57" s="109">
         <v>11706805.28222</v>
       </c>
-      <c r="D57" s="104">
+      <c r="D57" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="104" t="s">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A58" s="109" t="s">
         <v>113</v>
       </c>
       <c r="B58" s="18">
@@ -11458,13 +11832,13 @@
       <c r="C58" s="18">
         <v>25345</v>
       </c>
-      <c r="D58" s="104">
+      <c r="D58" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="104" t="s">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A59" s="109" t="s">
         <v>114</v>
       </c>
       <c r="B59" s="18">
@@ -11474,1311 +11848,1313 @@
       <c r="C59" s="18">
         <v>44074</v>
       </c>
-      <c r="D59" s="104">
+      <c r="D59" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="104" t="s">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A60" s="109" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="104" t="b">
+      <c r="B60" s="109" t="b">
         <f>EXACT("AbsSdf%","AbsSdf%")</f>
         <v>1</v>
       </c>
-      <c r="C60" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D60" s="104">
+      <c r="C60" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="104" t="s">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A61" s="109" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="104">
+      <c r="B61" s="109">
         <f>ROUND(EXP(4),5)</f>
         <v>54.598149999999997</v>
       </c>
-      <c r="C61" s="104">
+      <c r="C61" s="109">
         <v>54.598149999999997</v>
       </c>
-      <c r="D61" s="104">
+      <c r="D61" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="104" t="s">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A62" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="104">
+      <c r="B62" s="109">
         <f>FIND("A","qbdahbaazo A")</f>
         <v>12</v>
       </c>
-      <c r="C62" s="104">
+      <c r="C62" s="109">
         <v>12</v>
       </c>
-      <c r="D62" s="104">
+      <c r="D62" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="104" t="s">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A63" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="B63" s="104">
+      <c r="B63" s="109">
         <f>FLOOR(5.5,2)</f>
         <v>4</v>
       </c>
-      <c r="C63" s="104">
+      <c r="C63" s="109">
         <v>4</v>
       </c>
-      <c r="D63" s="104">
+      <c r="D63" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="104" t="s">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A64" s="109" t="s">
         <v>119</v>
       </c>
-      <c r="B64" s="104">
+      <c r="B64" s="109">
         <f>_xlfn.FLOOR.MATH(-5.55,2,1)</f>
         <v>-4</v>
       </c>
-      <c r="C64" s="104">
+      <c r="C64" s="109">
         <v>-4</v>
       </c>
-      <c r="D64" s="104">
+      <c r="D64" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="104" t="s">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A65" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="B65" s="104">
+      <c r="B65" s="109">
         <f>_xlfn.FLOOR.PRECISE(199,100)</f>
         <v>100</v>
       </c>
-      <c r="C65" s="104">
+      <c r="C65" s="109">
         <v>100</v>
       </c>
-      <c r="D65" s="104">
+      <c r="D65" s="109">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="104" t="s">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A66" s="109" t="s">
         <v>121</v>
       </c>
-      <c r="B66" s="104">
+      <c r="B66" s="109">
         <f>HLOOKUP("Tot. Score",H1:K9,4,FALSE)</f>
         <v>110120.5</v>
       </c>
-      <c r="C66" s="104">
+      <c r="C66" s="109">
         <v>110120.5</v>
       </c>
-      <c r="D66" s="104">
+      <c r="D66" s="109">
         <f t="shared" ref="D66:D97" si="5">IF(B66=C66,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="104" t="s">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A67" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="B67" s="104">
+      <c r="B67" s="109">
         <f>HOUR("02:14:56")</f>
         <v>2</v>
       </c>
-      <c r="C67" s="104">
+      <c r="C67" s="109">
         <v>2</v>
       </c>
-      <c r="D67" s="104">
+      <c r="D67" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="104" t="s">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A68" s="109" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="104" t="str">
+      <c r="B68" s="109" t="str">
         <f>IF(TRUE,"TABOURET","JAMBON")</f>
         <v>TABOURET</v>
       </c>
-      <c r="C68" s="104" t="s">
+      <c r="C68" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="D68" s="104">
+      <c r="D68" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="104" t="s">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A69" s="109" t="s">
         <v>125</v>
       </c>
-      <c r="B69" s="104" t="str">
+      <c r="B69" s="109" t="str">
         <f>IFERROR(0/0,"no diving by zero.")</f>
         <v>no diving by zero.</v>
       </c>
-      <c r="C69" s="104" t="s">
+      <c r="C69" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="104">
+      <c r="D69" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="104" t="s">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A70" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="B70" s="104" t="str">
+      <c r="B70" s="109" t="str">
         <f>_xlfn.IFS($H2&gt;$H3,"first player is older",$H3&gt;$H2,"second player is older")</f>
         <v>first player is older</v>
       </c>
-      <c r="C70" s="104" t="s">
+      <c r="C70" s="109" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="104">
+      <c r="D70" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="104" t="s">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A71" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="104" t="b">
+      <c r="B71" s="109" t="b">
         <f>ISERROR(0/0)</f>
         <v>1</v>
       </c>
-      <c r="C71" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D71" s="104">
+      <c r="C71" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="104" t="s">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A72" s="109" t="s">
         <v>130</v>
       </c>
-      <c r="B72" s="104" t="b">
+      <c r="B72" s="109" t="b">
         <f>ISEVEN(3)</f>
         <v>0</v>
       </c>
-      <c r="C72" s="104" t="b">
+      <c r="C72" s="109" t="b">
         <v>0</v>
       </c>
-      <c r="D72" s="104">
+      <c r="D72" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="104" t="s">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A73" s="109" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="104" t="b">
+      <c r="B73" s="109" t="b">
         <f>ISLOGICAL("TRUE")</f>
         <v>0</v>
       </c>
-      <c r="C73" s="104" t="b">
+      <c r="C73" s="109" t="b">
         <v>0</v>
       </c>
-      <c r="D73" s="104">
+      <c r="D73" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="104" t="s">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A74" s="109" t="s">
         <v>132</v>
       </c>
-      <c r="B74" s="104" t="b">
+      <c r="B74" s="109" t="b">
         <f>ISNONTEXT(TRUE)</f>
         <v>1</v>
       </c>
-      <c r="C74" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D74" s="104">
+      <c r="C74" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="104" t="s">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A75" s="109" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="104" t="b">
+      <c r="B75" s="109" t="b">
         <f>ISNUMBER(1231.5)</f>
         <v>1</v>
       </c>
-      <c r="C75" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" s="104">
+      <c r="C75" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="104" t="s">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A76" s="109" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="104">
+      <c r="B76" s="109">
         <f>ISO.CEILING(-7.89)</f>
         <v>-7</v>
       </c>
-      <c r="C76" s="104">
+      <c r="C76" s="109">
         <v>-7</v>
       </c>
-      <c r="D76" s="104">
+      <c r="D76" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="104" t="s">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A77" s="109" t="s">
         <v>135</v>
       </c>
-      <c r="B77" s="104" t="b">
+      <c r="B77" s="109" t="b">
         <f>ISODD(4)</f>
         <v>0</v>
       </c>
-      <c r="C77" s="104" t="b">
+      <c r="C77" s="109" t="b">
         <v>0</v>
       </c>
-      <c r="D77" s="104">
+      <c r="D77" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="104" t="s">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A78" s="109" t="s">
         <v>136</v>
       </c>
-      <c r="B78" s="104">
+      <c r="B78" s="109">
         <f>_xlfn.ISOWEEKNUM("2016-01-03")</f>
         <v>53</v>
       </c>
-      <c r="C78" s="104">
+      <c r="C78" s="109">
         <v>53</v>
       </c>
-      <c r="D78" s="104">
+      <c r="D78" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="104" t="s">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A79" s="109" t="s">
         <v>137</v>
       </c>
-      <c r="B79" s="104" t="b">
+      <c r="B79" s="109" t="b">
         <f>ISTEXT("123")</f>
         <v>1</v>
       </c>
-      <c r="C79" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="104">
+      <c r="C79" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="104" t="s">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A80" s="109" t="s">
         <v>138</v>
       </c>
-      <c r="B80" s="104">
+      <c r="B80" s="109">
         <f>LARGE(H2:H9,3)</f>
         <v>30</v>
       </c>
-      <c r="C80" s="104">
+      <c r="C80" s="109">
         <v>30</v>
       </c>
-      <c r="D80" s="104">
+      <c r="D80" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="104" t="s">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A81" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="B81" s="104" t="str">
+      <c r="B81" s="109" t="str">
         <f>LEFT("Mich",4)</f>
         <v>Mich</v>
       </c>
-      <c r="C81" s="104" t="s">
+      <c r="C81" s="109" t="s">
         <v>140</v>
       </c>
-      <c r="D81" s="104">
+      <c r="D81" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="104" t="s">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A82" s="109" t="s">
         <v>141</v>
       </c>
-      <c r="B82" s="104">
+      <c r="B82" s="109">
         <f>LEN("anticonstitutionnellement")</f>
         <v>25</v>
       </c>
-      <c r="C82" s="104">
+      <c r="C82" s="109">
         <v>25</v>
       </c>
-      <c r="D82" s="104">
+      <c r="D82" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="104" t="s">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A83" s="109" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="104">
+      <c r="B83" s="109">
         <f>ROUND(LN(2),5)</f>
         <v>0.69315000000000004</v>
       </c>
-      <c r="C83" s="104">
+      <c r="C83" s="109">
         <v>0.69315000000000004</v>
       </c>
-      <c r="D83" s="104">
+      <c r="D83" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="104" t="s">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A84" s="109" t="s">
         <v>143</v>
       </c>
-      <c r="B84" s="104">
+      <c r="B84" s="109">
         <f>LOOKUP(23000,H3:J3,H5:J5)</f>
         <v>50024</v>
       </c>
-      <c r="C84" s="104">
+      <c r="C84" s="109">
         <v>50024</v>
       </c>
-      <c r="D84" s="104">
+      <c r="D84" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="104" t="s">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A85" s="109" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="104" t="str">
+      <c r="B85" s="109" t="str">
         <f>LOWER("オAドB")</f>
         <v>オaドb</v>
       </c>
-      <c r="C85" s="104" t="s">
+      <c r="C85" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D85" s="104">
+      <c r="D85" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="104" t="s">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A86" s="109" t="s">
         <v>146</v>
       </c>
-      <c r="B86" s="104">
+      <c r="B86" s="109">
         <f>MATCH(42,H2:H9,0)</f>
         <v>4</v>
       </c>
-      <c r="C86" s="104">
+      <c r="C86" s="109">
         <v>4</v>
       </c>
-      <c r="D86" s="104">
+      <c r="D86" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="104" t="s">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A87" s="109" t="s">
         <v>147</v>
       </c>
-      <c r="B87" s="104">
+      <c r="B87" s="109">
         <f>MAX(N1:N8)</f>
         <v>0.6</v>
       </c>
-      <c r="C87" s="104">
+      <c r="C87" s="109">
         <v>0.6</v>
       </c>
-      <c r="D87" s="104">
+      <c r="D87" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="104" t="s">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A88" s="109" t="s">
         <v>148</v>
       </c>
-      <c r="B88" s="104">
+      <c r="B88" s="109">
         <f>MAXA(N1:N8)</f>
         <v>1</v>
       </c>
-      <c r="C88" s="104">
-        <v>1</v>
-      </c>
-      <c r="D88" s="104">
+      <c r="C88" s="109">
+        <v>1</v>
+      </c>
+      <c r="D88" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="104" t="s">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A89" s="109" t="s">
         <v>149</v>
       </c>
-      <c r="B89" s="104">
+      <c r="B89" s="109">
         <f>_xlfn.MAXIFS(H2:H9,K2:K9,"&lt;20",K2:K9,"&lt;&gt;4")</f>
         <v>30</v>
       </c>
-      <c r="C89" s="104">
+      <c r="C89" s="109">
         <v>30</v>
       </c>
-      <c r="D89" s="104">
+      <c r="D89" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="104" t="s">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A90" s="109" t="s">
         <v>150</v>
       </c>
-      <c r="B90" s="104">
+      <c r="B90" s="109">
         <f>MEDIAN(-1,6,7,234,163845)</f>
         <v>7</v>
       </c>
-      <c r="C90" s="104">
+      <c r="C90" s="109">
         <v>7</v>
       </c>
-      <c r="D90" s="104">
+      <c r="D90" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="104" t="s">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A91" s="109" t="s">
         <v>151</v>
       </c>
-      <c r="B91" s="104">
+      <c r="B91" s="109">
         <f>MIN(N1:N8)</f>
         <v>0.1</v>
       </c>
-      <c r="C91" s="104">
+      <c r="C91" s="109">
         <v>0.1</v>
       </c>
-      <c r="D91" s="104">
+      <c r="D91" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="104" t="s">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A92" s="109" t="s">
         <v>152</v>
       </c>
-      <c r="B92" s="104">
+      <c r="B92" s="109">
         <f>MINA(N1:N8)</f>
         <v>0</v>
       </c>
-      <c r="C92" s="104">
+      <c r="C92" s="109">
         <v>0</v>
       </c>
-      <c r="D92" s="104">
+      <c r="D92" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="104" t="s">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A93" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="B93" s="104">
+      <c r="B93" s="109">
         <f>_xlfn.MINIFS(J2:J9,H2:H9,"&gt;20")</f>
         <v>5000</v>
       </c>
-      <c r="C93" s="104">
+      <c r="C93" s="109">
         <v>5000</v>
       </c>
-      <c r="D93" s="104">
+      <c r="D93" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="104" t="s">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A94" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="B94" s="104">
+      <c r="B94" s="109">
         <f>MINUTE(0.126)</f>
         <v>1</v>
       </c>
-      <c r="C94" s="104">
-        <v>1</v>
-      </c>
-      <c r="D94" s="104">
+      <c r="C94" s="109">
+        <v>1</v>
+      </c>
+      <c r="D94" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="104" t="s">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A95" s="109" t="s">
         <v>155</v>
       </c>
-      <c r="B95" s="104">
+      <c r="B95" s="109">
         <f>MOD(42,12)</f>
         <v>6</v>
       </c>
-      <c r="C95" s="104">
+      <c r="C95" s="109">
         <v>6</v>
       </c>
-      <c r="D95" s="104">
+      <c r="D95" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="104" t="s">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A96" s="109" t="s">
         <v>156</v>
       </c>
-      <c r="B96" s="104">
+      <c r="B96" s="109">
         <f>MONTH("1954-05-02")</f>
         <v>5</v>
       </c>
-      <c r="C96" s="104">
+      <c r="C96" s="109">
         <v>5</v>
       </c>
-      <c r="D96" s="104">
+      <c r="D96" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="104" t="s">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A97" s="109" t="s">
         <v>157</v>
       </c>
-      <c r="B97" s="104">
+      <c r="B97" s="109">
         <f>NETWORKDAYS("2013-01-01","2013-02-01")</f>
         <v>24</v>
       </c>
-      <c r="C97" s="104">
+      <c r="C97" s="109">
         <v>24</v>
       </c>
-      <c r="D97" s="104">
+      <c r="D97" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="104" t="s">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A98" s="109" t="s">
         <v>158</v>
       </c>
-      <c r="B98" s="104">
+      <c r="B98" s="109">
         <f>NETWORKDAYS.INTL("2013-01-01","2013-02-01","0000111")</f>
         <v>19</v>
       </c>
-      <c r="C98" s="104">
+      <c r="C98" s="109">
         <v>19</v>
       </c>
-      <c r="D98" s="104">
+      <c r="D98" s="109">
         <f t="shared" ref="D98:D99" si="6">IF(B98=C98,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="104" t="s">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A99" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="B99" s="104" t="b">
+      <c r="B99" s="109" t="b">
         <f>NOT(FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C99" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D99" s="104">
+      <c r="C99" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" s="109">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="104" t="s">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A100" s="109" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>46113.450567939813</v>
-      </c>
-      <c r="D100" s="104">
+        <v>46163.643839930555</v>
+      </c>
+      <c r="C100" s="110"/>
+      <c r="D100" s="109">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="104" t="s">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A101" s="109" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="104">
+      <c r="B101" s="109">
         <f>ODD(4)</f>
         <v>5</v>
       </c>
-      <c r="C101" s="104">
+      <c r="C101" s="109">
         <v>5</v>
       </c>
-      <c r="D101" s="104">
+      <c r="D101" s="109">
         <f t="shared" ref="D101:D111" si="7">IF(B101=C101,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="104" t="s">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A102" s="109" t="s">
         <v>162</v>
       </c>
-      <c r="B102" s="104" t="b">
+      <c r="B102" s="109" t="b">
         <f>OR("true",FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C102" s="104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D102" s="104">
+      <c r="C102" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="104" t="s">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A103" s="109" t="s">
         <v>163</v>
       </c>
-      <c r="B103" s="104">
+      <c r="B103" s="109">
         <f>PERCENTILE(N1:N5,1)</f>
         <v>0.6</v>
       </c>
-      <c r="C103" s="104">
+      <c r="C103" s="109">
         <v>0.6</v>
       </c>
-      <c r="D103" s="104">
+      <c r="D103" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="104" t="s">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A104" s="109" t="s">
         <v>164</v>
       </c>
-      <c r="B104" s="104">
+      <c r="B104" s="109">
         <f>_xlfn.PERCENTILE.EXC(N1:N5,0.5)</f>
         <v>0.4</v>
       </c>
-      <c r="C104" s="104">
+      <c r="C104" s="109">
         <v>0.4</v>
       </c>
-      <c r="D104" s="104">
+      <c r="D104" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="104" t="s">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A105" s="109" t="s">
         <v>165</v>
       </c>
-      <c r="B105" s="104">
+      <c r="B105" s="109">
         <f>_xlfn.PERCENTILE.INC(N1:N5,0)</f>
         <v>0.1</v>
       </c>
-      <c r="C105" s="104">
+      <c r="C105" s="109">
         <v>0.1</v>
       </c>
-      <c r="D105" s="104">
+      <c r="D105" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="104" t="s">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A106" s="109" t="s">
         <v>166</v>
       </c>
-      <c r="B106" s="104">
+      <c r="B106" s="109">
         <f>ROUND(PI(),5)</f>
         <v>3.1415899999999999</v>
       </c>
-      <c r="C106" s="104">
+      <c r="C106" s="109">
         <v>3.1415899999999999</v>
       </c>
-      <c r="D106" s="104">
+      <c r="D106" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="104" t="s">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A107" s="109" t="s">
         <v>167</v>
       </c>
-      <c r="B107" s="104">
+      <c r="B107" s="109">
         <f>POWER(42,2)</f>
         <v>1764</v>
       </c>
-      <c r="C107" s="104">
+      <c r="C107" s="109">
         <v>1764</v>
       </c>
-      <c r="D107" s="104">
+      <c r="D107" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="104" t="s">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A108" s="109" t="s">
         <v>168</v>
       </c>
-      <c r="B108" s="104">
+      <c r="B108" s="109">
         <f>PRODUCT(1,2,3)</f>
         <v>6</v>
       </c>
-      <c r="C108" s="104">
+      <c r="C108" s="109">
         <v>6</v>
       </c>
-      <c r="D108" s="104">
+      <c r="D108" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="104" t="s">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A109" s="109" t="s">
         <v>169</v>
       </c>
-      <c r="B109" s="104">
+      <c r="B109" s="109">
         <f>QUARTILE(N1:N5,0)</f>
         <v>0.1</v>
       </c>
-      <c r="C109" s="104">
+      <c r="C109" s="109">
         <v>0.1</v>
       </c>
-      <c r="D109" s="104">
+      <c r="D109" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="104" t="s">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A110" s="109" t="s">
         <v>170</v>
       </c>
-      <c r="B110" s="104">
+      <c r="B110" s="109">
         <f>ROUND(_xlfn.QUARTILE.EXC(N1:N5,1),5)</f>
         <v>0.15</v>
       </c>
-      <c r="C110" s="104">
+      <c r="C110" s="109">
         <v>0.15</v>
       </c>
-      <c r="D110" s="104">
+      <c r="D110" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="104" t="s">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A111" s="109" t="s">
         <v>171</v>
       </c>
-      <c r="B111" s="104">
+      <c r="B111" s="109">
         <f>_xlfn.QUARTILE.INC(N1:N5,4)</f>
         <v>0.6</v>
       </c>
-      <c r="C111" s="104">
+      <c r="C111" s="109">
         <v>0.6</v>
       </c>
-      <c r="D111" s="104">
+      <c r="D111" s="109">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="104"/>
-      <c r="B112" s="104"/>
-      <c r="D112" s="104"/>
-    </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="104" t="s">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A112" s="109"/>
+      <c r="B112" s="109"/>
+      <c r="C112" s="110"/>
+      <c r="D112" s="109"/>
+    </row>
+    <row r="113" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A113" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="B113" s="104">
+      <c r="B113" s="109">
         <f ca="1">RANDBETWEEN(1.1,2)</f>
         <v>2</v>
       </c>
-      <c r="C113" s="104">
+      <c r="C113" s="109">
         <v>2</v>
       </c>
-      <c r="D113" s="104">
+      <c r="D113" s="109">
         <f t="shared" ref="D113:D143" ca="1" si="8">IF(B113=C113,1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="104" t="s">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A114" s="109" t="s">
         <v>173</v>
       </c>
-      <c r="B114" s="104" t="str">
+      <c r="B114" s="109" t="str">
         <f>REPLACE("ABZ",2,1,"Y")</f>
         <v>AYZ</v>
       </c>
-      <c r="C114" s="104" t="s">
+      <c r="C114" s="109" t="s">
         <v>174</v>
       </c>
-      <c r="D114" s="104">
+      <c r="D114" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="104" t="s">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A115" s="109" t="s">
         <v>175</v>
       </c>
-      <c r="B115" s="104" t="str">
+      <c r="B115" s="109" t="str">
         <f>RIGHT("kikou",2)</f>
         <v>ou</v>
       </c>
-      <c r="C115" s="104" t="s">
+      <c r="C115" s="109" t="s">
         <v>176</v>
       </c>
-      <c r="D115" s="104">
+      <c r="D115" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="104" t="s">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A116" s="109" t="s">
         <v>177</v>
       </c>
-      <c r="B116" s="104">
+      <c r="B116" s="109">
         <f>ROUND(49.9,0)</f>
         <v>50</v>
       </c>
-      <c r="C116" s="104">
+      <c r="C116" s="109">
         <v>50</v>
       </c>
-      <c r="D116" s="104">
+      <c r="D116" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="104" t="s">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A117" s="109" t="s">
         <v>178</v>
       </c>
-      <c r="B117" s="104">
+      <c r="B117" s="109">
         <f>ROUNDDOWN(42,-1)</f>
         <v>40</v>
       </c>
-      <c r="C117" s="104">
+      <c r="C117" s="109">
         <v>40</v>
       </c>
-      <c r="D117" s="104">
+      <c r="D117" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="104" t="s">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A118" s="109" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="104">
+      <c r="B118" s="109">
         <f>ROUNDUP(-1.6,0)</f>
         <v>-2</v>
       </c>
-      <c r="C118" s="104">
+      <c r="C118" s="109">
         <v>-2</v>
       </c>
-      <c r="D118" s="104">
+      <c r="D118" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="104" t="s">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A119" s="109" t="s">
         <v>180</v>
       </c>
-      <c r="B119" s="104">
+      <c r="B119" s="109">
         <f>ROW(A234)</f>
         <v>234</v>
       </c>
-      <c r="C119" s="104">
+      <c r="C119" s="109">
         <v>234</v>
       </c>
-      <c r="D119" s="104">
+      <c r="D119" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="104" t="s">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A120" s="109" t="s">
         <v>181</v>
       </c>
-      <c r="B120" s="104">
+      <c r="B120" s="109">
         <f>ROWS(B3:C40)</f>
         <v>38</v>
       </c>
-      <c r="C120" s="104">
+      <c r="C120" s="109">
         <v>38</v>
       </c>
-      <c r="D120" s="104">
+      <c r="D120" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="104" t="s">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A121" s="109" t="s">
         <v>182</v>
       </c>
-      <c r="B121" s="104">
+      <c r="B121" s="109">
         <f>SEARCH("C","ABCD")</f>
         <v>3</v>
       </c>
-      <c r="C121" s="104">
+      <c r="C121" s="109">
         <v>3</v>
       </c>
-      <c r="D121" s="104">
+      <c r="D121" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="104" t="s">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A122" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="B122" s="104">
+      <c r="B122" s="109">
         <f>ROUND(_xlfn.SEC(PI()/3),5)</f>
         <v>2</v>
       </c>
-      <c r="C122" s="104">
+      <c r="C122" s="109">
         <v>2</v>
       </c>
-      <c r="D122" s="104">
+      <c r="D122" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="104" t="s">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A123" s="109" t="s">
         <v>184</v>
       </c>
-      <c r="B123" s="104">
+      <c r="B123" s="109">
         <f>ROUND(_xlfn.SECH(1),5)</f>
         <v>0.64805000000000001</v>
       </c>
-      <c r="C123" s="104">
+      <c r="C123" s="109">
         <v>0.64805000000000001</v>
       </c>
-      <c r="D123" s="104">
+      <c r="D123" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="104" t="s">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A124" s="109" t="s">
         <v>185</v>
       </c>
-      <c r="B124" s="104">
+      <c r="B124" s="109">
         <f>SECOND("00:21:42")</f>
         <v>42</v>
       </c>
-      <c r="C124" s="104">
+      <c r="C124" s="109">
         <v>42</v>
       </c>
-      <c r="D124" s="104">
+      <c r="D124" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="104" t="s">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A125" s="109" t="s">
         <v>186</v>
       </c>
-      <c r="B125" s="104">
+      <c r="B125" s="109">
         <f>ROUND(SIN(PI()/6),5)</f>
         <v>0.5</v>
       </c>
-      <c r="C125" s="104">
+      <c r="C125" s="109">
         <v>0.5</v>
       </c>
-      <c r="D125" s="104">
+      <c r="D125" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="104" t="s">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A126" s="109" t="s">
         <v>187</v>
       </c>
-      <c r="B126" s="104">
+      <c r="B126" s="109">
         <f>ROUND(SINH(1),5)</f>
         <v>1.1752</v>
       </c>
-      <c r="C126" s="104">
+      <c r="C126" s="109">
         <v>1.1752</v>
       </c>
-      <c r="D126" s="104">
+      <c r="D126" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="104" t="s">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A127" s="109" t="s">
         <v>188</v>
       </c>
-      <c r="B127" s="104">
+      <c r="B127" s="109">
         <f>SMALL(H2:H9,3)</f>
         <v>26</v>
       </c>
-      <c r="C127" s="104">
+      <c r="C127" s="109">
         <v>26</v>
       </c>
-      <c r="D127" s="104">
+      <c r="D127" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="104" t="s">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A128" s="109" t="s">
         <v>189</v>
       </c>
-      <c r="B128" s="104">
+      <c r="B128" s="109">
         <f>SQRT(4)</f>
         <v>2</v>
       </c>
-      <c r="C128" s="104">
+      <c r="C128" s="109">
         <v>2</v>
       </c>
-      <c r="D128" s="104">
+      <c r="D128" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="104" t="s">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A129" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="B129" s="104">
+      <c r="B129" s="109">
         <f>STDEV(-2,0,2)</f>
         <v>2</v>
       </c>
-      <c r="C129" s="104">
+      <c r="C129" s="109">
         <v>2</v>
       </c>
-      <c r="D129" s="104">
+      <c r="D129" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="104" t="s">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A130" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="B130" s="104">
+      <c r="B130" s="109">
         <f>_xlfn.STDEV.P(2,4)</f>
         <v>1</v>
       </c>
-      <c r="C130" s="104">
-        <v>1</v>
-      </c>
-      <c r="D130" s="104">
+      <c r="C130" s="109">
+        <v>1</v>
+      </c>
+      <c r="D130" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="104" t="s">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A131" s="109" t="s">
         <v>192</v>
       </c>
-      <c r="B131" s="104">
+      <c r="B131" s="109">
         <f>_xlfn.STDEV.S(2,4,6)</f>
         <v>2</v>
       </c>
-      <c r="C131" s="104">
+      <c r="C131" s="109">
         <v>2</v>
       </c>
-      <c r="D131" s="104">
+      <c r="D131" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="104" t="s">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A132" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="B132" s="104">
+      <c r="B132" s="109">
         <f>STDEVA(TRUE,3,5)</f>
         <v>2</v>
       </c>
-      <c r="C132" s="104">
+      <c r="C132" s="109">
         <v>2</v>
       </c>
-      <c r="D132" s="104">
+      <c r="D132" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="104" t="s">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A133" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="B133" s="104">
+      <c r="B133" s="109">
         <f>ROUND(STDEVP(2,5,8),2)</f>
         <v>2.4500000000000002</v>
       </c>
-      <c r="C133" s="104">
+      <c r="C133" s="109">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D133" s="104">
+      <c r="D133" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="104" t="s">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A134" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="B134" s="104">
+      <c r="B134" s="109">
         <f>ROUND(STDEVPA(TRUE,4,7),2)</f>
         <v>2.4500000000000002</v>
       </c>
-      <c r="C134" s="104">
+      <c r="C134" s="109">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D134" s="104">
+      <c r="D134" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="104" t="s">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A135" s="109" t="s">
         <v>196</v>
       </c>
-      <c r="B135" s="104" t="str">
+      <c r="B135" s="109" t="str">
         <f>SUBSTITUTE("SAP is best","SAP","Odoo")</f>
         <v>Odoo is best</v>
       </c>
-      <c r="C135" s="104" t="s">
+      <c r="C135" s="109" t="s">
         <v>197</v>
       </c>
-      <c r="D135" s="104">
+      <c r="D135" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="104" t="s">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A136" s="109" t="s">
         <v>198</v>
       </c>
-      <c r="B136" s="104">
+      <c r="B136" s="109">
         <f>SUM(1,2,3,4,5)</f>
         <v>15</v>
       </c>
-      <c r="C136" s="104">
+      <c r="C136" s="109">
         <v>15</v>
       </c>
-      <c r="D136" s="104">
+      <c r="D136" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="104" t="s">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A137" s="109" t="s">
         <v>199</v>
       </c>
-      <c r="B137" s="104">
+      <c r="B137" s="109">
         <f>SUMIF(K2:K9,"&lt;100")</f>
         <v>52</v>
       </c>
-      <c r="C137" s="104">
+      <c r="C137" s="109">
         <v>52</v>
       </c>
-      <c r="D137" s="104">
+      <c r="D137" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="104" t="s">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A138" s="109" t="s">
         <v>200</v>
       </c>
-      <c r="B138" s="104">
+      <c r="B138" s="109">
         <f>SUMIFS(H2:H9,K2:K9,"&lt;100")</f>
         <v>201</v>
       </c>
-      <c r="C138" s="104">
+      <c r="C138" s="109">
         <v>201</v>
       </c>
-      <c r="D138" s="104">
+      <c r="D138" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="104" t="s">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A139" s="109" t="s">
         <v>201</v>
       </c>
-      <c r="B139" s="104">
+      <c r="B139" s="109">
         <f>ROUND(TAN(PI()/4),5)</f>
         <v>1</v>
       </c>
-      <c r="C139" s="104">
-        <v>1</v>
-      </c>
-      <c r="D139" s="104">
+      <c r="C139" s="109">
+        <v>1</v>
+      </c>
+      <c r="D139" s="109">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="104" t="s">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1">
+      <c r="A140" s="109" t="s">
         <v>202</v>
       </c>
-      <c r="B140" s="104">
+      <c r="B140" s="109">
         <f>ROUND(TANH(1),5)</f>
         <v>0.76158999999999999</v>
       </c>
-      <c r="C140" s="104">
+      <c r="C140" s="109">
         <v>0.76158999999999999</v>
       </c>
-      <c r="D140" s="104">
+      <c r="D140" s="109">
         <f t="shared" s